--- a/辐射报警仪协议命令和寄存器表10.xlsx
+++ b/辐射报警仪协议命令和寄存器表10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="具体命令" sheetId="1" r:id="rId1"/>

--- a/辐射报警仪协议命令和寄存器表10.xlsx
+++ b/辐射报警仪协议命令和寄存器表10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="1"/>
+    <workbookView windowWidth="27915" windowHeight="12345" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="具体命令" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="298">
   <si>
     <t>数据</t>
   </si>
@@ -742,6 +742,9 @@
   </si>
   <si>
     <t>pm2.5*10</t>
+  </si>
+  <si>
+    <t>ug/m3</t>
   </si>
   <si>
     <t>alarm_bit1</t>
@@ -9825,6 +9828,9 @@
       <c r="E7" t="s">
         <v>216</v>
       </c>
+      <c r="F7" t="s">
+        <v>217</v>
+      </c>
       <c r="G7" t="s">
         <v>201</v>
       </c>
@@ -9841,13 +9847,13 @@
         <v>197</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G8" t="s">
         <v>201</v>
@@ -9865,10 +9871,10 @@
         <v>197</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>70</v>
@@ -9923,16 +9929,16 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G14" t="s">
         <v>201</v>
@@ -9952,10 +9958,10 @@
         <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G15" t="s">
         <v>201</v>
@@ -9963,7 +9969,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" ht="51" customHeight="1" spans="1:7">
@@ -9977,16 +9983,16 @@
         <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1" spans="1:7">
@@ -10001,16 +10007,16 @@
         <v>197</v>
       </c>
       <c r="D22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" t="s">
         <v>232</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G22" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -10025,16 +10031,16 @@
         <v>197</v>
       </c>
       <c r="D23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F23" t="s">
         <v>205</v>
       </c>
       <c r="G23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -10049,16 +10055,16 @@
         <v>197</v>
       </c>
       <c r="D24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F24" t="s">
         <v>205</v>
       </c>
       <c r="G24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -10073,16 +10079,16 @@
         <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -10097,16 +10103,16 @@
         <v>197</v>
       </c>
       <c r="D26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F26" t="s">
         <v>241</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F26" t="s">
-        <v>240</v>
-      </c>
       <c r="G26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -10121,16 +10127,16 @@
         <v>197</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F27" t="s">
         <v>211</v>
       </c>
       <c r="G27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -10145,16 +10151,16 @@
         <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F28" t="s">
         <v>211</v>
       </c>
       <c r="G28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -10169,16 +10175,16 @@
         <v>197</v>
       </c>
       <c r="D29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F29" t="s">
         <v>211</v>
       </c>
       <c r="G29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -10193,13 +10199,13 @@
         <v>197</v>
       </c>
       <c r="D30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -10214,10 +10220,10 @@
         <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F31" t="s">
         <v>211</v>
@@ -10235,10 +10241,10 @@
         <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -10289,10 +10295,10 @@
         <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>139</v>
@@ -10319,19 +10325,19 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" ht="43" customHeight="1" spans="1:7">
@@ -10343,19 +10349,19 @@
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D40" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G40" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -10367,10 +10373,10 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E41" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>151</v>
@@ -10388,19 +10394,19 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E42" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" ht="27" spans="1:7">
@@ -10412,19 +10418,19 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -10435,16 +10441,16 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -10456,13 +10462,13 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -10473,19 +10479,19 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" ht="264.75" customHeight="1" spans="1:8">
@@ -10496,22 +10502,22 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:8">
@@ -10519,7 +10525,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:8">
@@ -10539,13 +10545,13 @@
         <v>179</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -10559,16 +10565,16 @@
         <v>197</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E56" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H56" s="1"/>
     </row>
@@ -10581,19 +10587,19 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G57" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H57" s="1"/>
     </row>
@@ -10603,22 +10609,22 @@
         <v>208</v>
       </c>
       <c r="B58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G58" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H58" s="1"/>
     </row>
@@ -10649,7 +10655,7 @@
   <sheetData>
     <row r="1" spans="2:17">
       <c r="B1" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>

--- a/辐射报警仪协议命令和寄存器表10.xlsx
+++ b/辐射报警仪协议命令和寄存器表10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27915" windowHeight="12345" activeTab="1"/>
+    <workbookView windowWidth="20355" windowHeight="9525" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="具体命令" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="325">
   <si>
     <t>数据</t>
   </si>
@@ -964,6 +964,87 @@
   </si>
   <si>
     <t>这里和转接板控制有些重合，从机不一定有蓝牙音箱这些</t>
+  </si>
+  <si>
+    <t>uchar[16]</t>
+  </si>
+  <si>
+    <t>product_type</t>
+  </si>
+  <si>
+    <t>16个字节的型号 “FSY-I”不足16位补零</t>
+  </si>
+  <si>
+    <t>uchar[4]</t>
+  </si>
+  <si>
+    <t>product_ip</t>
+  </si>
+  <si>
+    <t>ip地址</t>
+  </si>
+  <si>
+    <t>ip[0]ip[1]ip[2]ip[3]</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>16个字节的产品名称 “”不足16位补零</t>
+  </si>
+  <si>
+    <t>GEIGER_SENS</t>
+  </si>
+  <si>
+    <t>灵敏度</t>
+  </si>
+  <si>
+    <t>int33</t>
+  </si>
+  <si>
+    <t>EWMA threshold_cps</t>
+  </si>
+  <si>
+    <t>int34</t>
+  </si>
+  <si>
+    <t>EWMA threshold_delta</t>
+  </si>
+  <si>
+    <t>int35</t>
+  </si>
+  <si>
+    <t>EWMA alpha_low</t>
+  </si>
+  <si>
+    <t>int36</t>
+  </si>
+  <si>
+    <t>EWMA alpha_high</t>
+  </si>
+  <si>
+    <t>int37</t>
+  </si>
+  <si>
+    <t>EWMA boost_duration</t>
+  </si>
+  <si>
+    <t>int38</t>
+  </si>
+  <si>
+    <t>EWMA_limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhcp 1 使能 </t>
+  </si>
+  <si>
+    <t>语言 0中文 1英文</t>
+  </si>
+  <si>
+    <t>硬件版本</t>
   </si>
   <si>
     <t>程序更新</t>
@@ -1981,7 +2062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1999,6 +2080,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2752,243 +2836,243 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
       <c r="Y4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="3:26">
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="9" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="9"/>
+      <c r="Z5" s="10"/>
     </row>
     <row r="6" spans="3:26">
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13" t="s">
+      <c r="G6" s="13"/>
+      <c r="H6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="15" t="s">
+      <c r="I6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11" t="s">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11" t="s">
+      <c r="S6" s="12"/>
+      <c r="T6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11" t="s">
+      <c r="U6" s="12"/>
+      <c r="V6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="W6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="X6" s="11" t="s">
+      <c r="X6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
     </row>
     <row r="7" spans="3:26">
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="18" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="19" t="s">
+      <c r="I7" s="21"/>
+      <c r="J7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="19" t="s">
+      <c r="K7" s="21"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="18" t="s">
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="18" t="s">
+      <c r="S7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="T7" s="18" t="s">
+      <c r="T7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="U7" s="18" t="s">
+      <c r="U7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="18" t="s">
+      <c r="V7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="18" t="s">
+      <c r="W7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
     </row>
     <row r="8" spans="3:26">
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
     </row>
     <row r="9" spans="3:26">
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
     </row>
     <row r="10" spans="3:26">
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
     </row>
     <row r="12" spans="3:26">
       <c r="E12" s="3"/>
@@ -3113,7 +3197,7 @@
       <c r="H18" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="32" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="1"/>
@@ -3347,18 +3431,18 @@
       <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="32" t="s">
         <v>66</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="32" t="s">
+      <c r="L24" s="33" t="s">
         <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
@@ -3393,13 +3477,13 @@
       <c r="H25" t="s">
         <v>47</v>
       </c>
-      <c r="I25" s="33" t="s">
+      <c r="I25" s="34" t="s">
         <v>69</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
       </c>
-      <c r="M25" s="34" t="s">
+      <c r="M25" s="35" t="s">
         <v>70</v>
       </c>
       <c r="P25" s="1"/>
@@ -3424,13 +3508,13 @@
       <c r="H26" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="33" t="s">
+      <c r="I26" s="34" t="s">
         <v>72</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="35" t="s">
+      <c r="M26" s="36" t="s">
         <v>17</v>
       </c>
       <c r="P26" s="1"/>
@@ -3455,13 +3539,13 @@
       <c r="H27" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="33" t="s">
+      <c r="I27" s="34" t="s">
         <v>73</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="35" t="s">
+      <c r="M27" s="36" t="s">
         <v>17</v>
       </c>
       <c r="P27" s="1"/>
@@ -3486,13 +3570,13 @@
       <c r="H28" t="s">
         <v>47</v>
       </c>
-      <c r="I28" s="33" t="s">
+      <c r="I28" s="34" t="s">
         <v>74</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>17</v>
       </c>
       <c r="N28" s="1"/>
@@ -3530,7 +3614,7 @@
       <c r="L29" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="35" t="s">
         <v>77</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -3576,13 +3660,13 @@
       <c r="F32" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="33" t="s">
         <v>46</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="I32" s="37" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="1"/>
@@ -3604,59 +3688,59 @@
       </c>
     </row>
     <row r="36" spans="3:17">
-      <c r="E36" s="37"/>
-      <c r="F36" s="38" t="s">
+      <c r="E36" s="38"/>
+      <c r="F36" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="39" t="s">
+      <c r="H36" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39" t="s">
+      <c r="I36" s="40"/>
+      <c r="J36" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K36" s="39"/>
-      <c r="L36" s="38" t="s">
+      <c r="K36" s="40"/>
+      <c r="L36" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="38" t="s">
+      <c r="M36" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N36" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="38"/>
-      <c r="Q36" s="38"/>
+      <c r="N36" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
     </row>
     <row r="37" spans="3:17">
-      <c r="F37" s="40"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41" t="s">
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="41" t="s">
+      <c r="I37" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="41" t="s">
+      <c r="J37" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="41" t="s">
+      <c r="K37" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41" t="s">
+      <c r="L37" s="42"/>
+      <c r="M37" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="42"/>
-      <c r="Q37" s="42"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="1" t="s">
@@ -3665,46 +3749,46 @@
       <c r="D38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="44" t="s">
+      <c r="F38" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G38" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="I38" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J38" s="44" t="s">
+      <c r="I38" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K38" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L38" s="44" t="s">
+      <c r="K38" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M38" s="44" t="s">
+      <c r="M38" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" s="42"/>
-      <c r="Q38" s="42"/>
+      <c r="N38" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
     </row>
     <row r="39" spans="3:17">
       <c r="C39" s="1"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F39" t="s">
@@ -3735,7 +3819,7 @@
     <row r="40" spans="3:17">
       <c r="C40" s="1"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F40" t="s">
@@ -3766,187 +3850,187 @@
     <row r="41" spans="3:17">
       <c r="C41" s="1"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="38" t="s">
+      <c r="E41" s="47"/>
+      <c r="F41" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G41" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="39" t="s">
+      <c r="H41" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39" t="s">
+      <c r="I41" s="40"/>
+      <c r="J41" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K41" s="39"/>
-      <c r="L41" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N41" s="38"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="38"/>
-      <c r="Q41" s="38"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="1"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="46" t="s">
+      <c r="E42" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="H42" s="44" t="s">
+      <c r="H42" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="I42" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42" s="44" t="s">
+      <c r="I42" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K42" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M42" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N42" s="45"/>
+      <c r="K42" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L42" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="46"/>
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="1"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="47" t="s">
+      <c r="E43" s="47"/>
+      <c r="F43" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="47" t="s">
+      <c r="G43" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="47" t="s">
+      <c r="H43" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J43" s="47" t="s">
+      <c r="J43" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K43" s="48" t="s">
+      <c r="K43" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L43" s="48"/>
-      <c r="M43" s="47"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="48"/>
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="1"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="46" t="s">
+      <c r="E44" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="G44" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H44" s="44" t="s">
+      <c r="H44" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I44" s="44" t="s">
+      <c r="I44" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="J44" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K44" s="49" t="s">
+      <c r="J44" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O44" s="42" t="s">
+      <c r="L44" s="51"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="1"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="46" t="s">
+      <c r="E45" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="I45" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" s="45" t="s">
+      <c r="I45" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K45" s="45" t="s">
+      <c r="K45" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L45" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M45" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N45" s="45"/>
+      <c r="L45" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="46"/>
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="1"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="3:17">
-      <c r="F47" s="38" t="s">
+      <c r="F47" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="38" t="s">
+      <c r="G47" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="39" t="s">
+      <c r="H47" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39" t="s">
+      <c r="I47" s="40"/>
+      <c r="J47" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K47" s="39"/>
-      <c r="L47" s="38" t="s">
+      <c r="K47" s="40"/>
+      <c r="L47" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M47" s="38" t="s">
+      <c r="M47" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N47" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" s="38"/>
-      <c r="Q47" s="38"/>
+      <c r="N47" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" s="39"/>
+      <c r="Q47" s="39"/>
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="1" t="s">
@@ -3955,46 +4039,46 @@
       <c r="D48" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="43" t="s">
+      <c r="E48" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F48" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" s="44" t="s">
+      <c r="F48" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H48" s="44" t="s">
+      <c r="H48" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="I48" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" s="44" t="s">
+      <c r="I48" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K48" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L48" s="44" t="s">
+      <c r="K48" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L48" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M48" s="44" t="s">
+      <c r="M48" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="N48" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
+      <c r="N48" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="45"/>
+      <c r="Q48" s="45"/>
     </row>
     <row r="49" spans="3:17">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F49" t="s">
@@ -4025,7 +4109,7 @@
     <row r="50" spans="3:17">
       <c r="C50" s="1"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F50" t="s">
@@ -4056,184 +4140,184 @@
     <row r="51" spans="3:17">
       <c r="C51" s="1"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="38" t="s">
+      <c r="E51" s="47"/>
+      <c r="F51" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="38" t="s">
+      <c r="G51" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H51" s="39" t="s">
+      <c r="H51" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39" t="s">
+      <c r="I51" s="40"/>
+      <c r="J51" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K51" s="39"/>
-      <c r="L51" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M51" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" s="38"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M51" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="39"/>
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="1"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="46" t="s">
+      <c r="E52" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="45" t="s">
+      <c r="G52" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="44" t="s">
+      <c r="H52" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="I52" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J52" s="44" t="s">
+      <c r="I52" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K52" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L52" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M52" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" s="45"/>
+      <c r="K52" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L52" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="46"/>
     </row>
     <row r="53" spans="3:17">
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="47" t="s">
+      <c r="E53" s="47"/>
+      <c r="F53" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H53" s="47" t="s">
+      <c r="H53" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I53" s="47" t="s">
+      <c r="I53" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J53" s="47" t="s">
+      <c r="J53" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K53" s="48" t="s">
+      <c r="K53" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L53" s="48"/>
-      <c r="M53" s="47"/>
+      <c r="L53" s="49"/>
+      <c r="M53" s="48"/>
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="1"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="46" t="s">
+      <c r="E54" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="44" t="s">
+      <c r="G54" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H54" s="44" t="s">
+      <c r="H54" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I54" s="44" t="s">
+      <c r="I54" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="J54" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K54" s="49" t="s">
+      <c r="J54" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="L54" s="50"/>
-      <c r="M54" s="51"/>
-      <c r="N54" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" s="42" t="s">
+      <c r="L54" s="51"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="1"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="46" t="s">
+      <c r="E55" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H55" s="44" t="s">
+      <c r="H55" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="I55" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J55" s="45" t="s">
+      <c r="I55" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K55" s="45" t="s">
+      <c r="K55" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L55" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M55" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N55" s="45"/>
+      <c r="L55" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="46"/>
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="1"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="3:17">
-      <c r="F57" s="38" t="s">
+      <c r="F57" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G57" s="38" t="s">
+      <c r="G57" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="H57" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39" t="s">
+      <c r="I57" s="40"/>
+      <c r="J57" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K57" s="39"/>
-      <c r="L57" s="38" t="s">
+      <c r="K57" s="40"/>
+      <c r="L57" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M57" s="38" t="s">
+      <c r="M57" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N57" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O57" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
+      <c r="N57" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" s="39"/>
+      <c r="Q57" s="39"/>
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="1" t="s">
@@ -4242,44 +4326,44 @@
       <c r="D58" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E58" s="43" t="s">
+      <c r="E58" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F58" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="44" t="s">
+      <c r="F58" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="44" t="s">
+      <c r="H58" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I58" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J58" s="44" t="s">
+      <c r="I58" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K58" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="44" t="s">
+      <c r="K58" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L58" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M58" s="44" t="s">
+      <c r="M58" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="N58" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O58" s="42" t="s">
+      <c r="N58" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O58" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="1"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F59" t="s">
@@ -4310,7 +4394,7 @@
     <row r="60" spans="3:17">
       <c r="C60" s="1"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F60" t="s">
@@ -4341,184 +4425,184 @@
     <row r="61" spans="3:17">
       <c r="C61" s="1"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="38" t="s">
+      <c r="E61" s="47"/>
+      <c r="F61" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="38" t="s">
+      <c r="G61" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H61" s="39" t="s">
+      <c r="H61" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39" t="s">
+      <c r="I61" s="40"/>
+      <c r="J61" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K61" s="39"/>
-      <c r="L61" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M61" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="38"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M61" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="39"/>
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="1"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="46" t="s">
+      <c r="E62" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
       </c>
-      <c r="G62" s="45" t="s">
+      <c r="G62" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="44" t="s">
+      <c r="H62" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I62" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J62" s="44" t="s">
+      <c r="I62" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K62" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L62" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M62" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="45"/>
+      <c r="K62" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L62" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M62" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="46"/>
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="1"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="47" t="s">
+      <c r="E63" s="47"/>
+      <c r="F63" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G63" s="47" t="s">
+      <c r="G63" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="47" t="s">
+      <c r="H63" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="47" t="s">
+      <c r="I63" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J63" s="47" t="s">
+      <c r="J63" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K63" s="48" t="s">
+      <c r="K63" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L63" s="48"/>
-      <c r="M63" s="47"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="48"/>
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="1"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="46" t="s">
+      <c r="E64" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
       </c>
-      <c r="G64" s="44" t="s">
+      <c r="G64" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H64" s="44" t="s">
+      <c r="H64" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I64" s="44" t="s">
+      <c r="I64" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="J64" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" s="49" t="s">
+      <c r="J64" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="L64" s="50"/>
-      <c r="M64" s="51"/>
-      <c r="N64" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="42" t="s">
+      <c r="L64" s="51"/>
+      <c r="M64" s="52"/>
+      <c r="N64" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O64" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="65" spans="3:17">
       <c r="C65" s="1"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="46" t="s">
+      <c r="E65" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F65" t="s">
         <v>39</v>
       </c>
-      <c r="G65" s="45" t="s">
+      <c r="G65" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H65" s="44" t="s">
+      <c r="H65" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I65" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65" s="45" t="s">
+      <c r="I65" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K65" s="45" t="s">
+      <c r="K65" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L65" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M65" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N65" s="45"/>
+      <c r="L65" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M65" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="46"/>
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="1"/>
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="3:17">
-      <c r="F67" s="38" t="s">
+      <c r="F67" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G67" s="38" t="s">
+      <c r="G67" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H67" s="39" t="s">
+      <c r="H67" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39" t="s">
+      <c r="I67" s="40"/>
+      <c r="J67" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K67" s="39"/>
-      <c r="L67" s="38" t="s">
+      <c r="K67" s="40"/>
+      <c r="L67" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M67" s="38" t="s">
+      <c r="M67" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N67" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O67" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P67" s="38"/>
-      <c r="Q67" s="38"/>
+      <c r="N67" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O67" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="1" t="s">
@@ -4527,44 +4611,44 @@
       <c r="D68" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="43" t="s">
+      <c r="E68" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F68" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="44" t="s">
+      <c r="F68" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H68" s="44" t="s">
+      <c r="H68" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J68" s="44" t="s">
+      <c r="I68" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K68" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L68" s="44" t="s">
+      <c r="K68" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L68" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M68" s="44" t="s">
+      <c r="M68" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="N68" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O68" s="42" t="s">
+      <c r="N68" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="1"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="45" t="s">
+      <c r="E69" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F69" t="s">
@@ -4595,7 +4679,7 @@
     <row r="70" spans="3:17">
       <c r="C70" s="1"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="45" t="s">
+      <c r="E70" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F70" t="s">
@@ -4626,184 +4710,184 @@
     <row r="71" spans="3:17">
       <c r="C71" s="1"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="38" t="s">
+      <c r="E71" s="47"/>
+      <c r="F71" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G71" s="38" t="s">
+      <c r="G71" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H71" s="39" t="s">
+      <c r="H71" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39" t="s">
+      <c r="I71" s="40"/>
+      <c r="J71" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K71" s="39"/>
-      <c r="L71" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M71" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N71" s="38"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M71" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="39"/>
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="1"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="46" t="s">
+      <c r="E72" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F72" t="s">
         <v>39</v>
       </c>
-      <c r="G72" s="45" t="s">
+      <c r="G72" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="44" t="s">
+      <c r="H72" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I72" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J72" s="44" t="s">
+      <c r="I72" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K72" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L72" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M72" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N72" s="45"/>
+      <c r="K72" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="46"/>
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="47" t="s">
+      <c r="E73" s="47"/>
+      <c r="F73" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G73" s="47" t="s">
+      <c r="G73" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H73" s="47" t="s">
+      <c r="H73" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I73" s="47" t="s">
+      <c r="I73" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J73" s="47" t="s">
+      <c r="J73" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K73" s="48" t="s">
+      <c r="K73" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L73" s="48"/>
-      <c r="M73" s="47"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="48"/>
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="1"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="46" t="s">
+      <c r="E74" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="44" t="s">
+      <c r="G74" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H74" s="44" t="s">
+      <c r="H74" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I74" s="44" t="s">
+      <c r="I74" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="J74" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K74" s="49" t="s">
+      <c r="J74" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="L74" s="50"/>
-      <c r="M74" s="51"/>
-      <c r="N74" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O74" s="42" t="s">
+      <c r="L74" s="51"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O74" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="1"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="46" t="s">
+      <c r="E75" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F75" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="45" t="s">
+      <c r="G75" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H75" s="44" t="s">
+      <c r="H75" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I75" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J75" s="45" t="s">
+      <c r="I75" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J75" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K75" s="45" t="s">
+      <c r="K75" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L75" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M75" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N75" s="45"/>
+      <c r="L75" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M75" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75" s="46"/>
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="1"/>
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="3:17">
-      <c r="F77" s="38" t="s">
+      <c r="F77" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="38" t="s">
+      <c r="G77" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H77" s="39" t="s">
+      <c r="H77" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39" t="s">
+      <c r="I77" s="40"/>
+      <c r="J77" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K77" s="39"/>
-      <c r="L77" s="38" t="s">
+      <c r="K77" s="40"/>
+      <c r="L77" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M77" s="38" t="s">
+      <c r="M77" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N77" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O77" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P77" s="38"/>
-      <c r="Q77" s="38"/>
+      <c r="N77" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P77" s="39"/>
+      <c r="Q77" s="39"/>
     </row>
     <row r="78" spans="3:17">
       <c r="C78" s="1" t="s">
@@ -4812,44 +4896,44 @@
       <c r="D78" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="43" t="s">
+      <c r="E78" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="44" t="s">
+      <c r="F78" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H78" s="44" t="s">
+      <c r="H78" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I78" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="44" t="s">
+      <c r="I78" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K78" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L78" s="44" t="s">
+      <c r="K78" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L78" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M78" s="52" t="s">
+      <c r="M78" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="N78" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O78" s="42" t="s">
+      <c r="N78" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="1"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="45" t="s">
+      <c r="E79" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F79" t="s">
@@ -4880,7 +4964,7 @@
     <row r="80" spans="3:17">
       <c r="C80" s="1"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="45" t="s">
+      <c r="E80" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F80" t="s">
@@ -4911,184 +4995,184 @@
     <row r="81" spans="3:17">
       <c r="C81" s="1"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="46"/>
-      <c r="F81" s="38" t="s">
+      <c r="E81" s="47"/>
+      <c r="F81" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G81" s="38" t="s">
+      <c r="G81" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H81" s="39" t="s">
+      <c r="H81" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39" t="s">
+      <c r="I81" s="40"/>
+      <c r="J81" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K81" s="39"/>
-      <c r="L81" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M81" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N81" s="38"/>
+      <c r="K81" s="40"/>
+      <c r="L81" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M81" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81" s="39"/>
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="1"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="46" t="s">
+      <c r="E82" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F82" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="45" t="s">
+      <c r="G82" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="44" t="s">
+      <c r="H82" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I82" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J82" s="44" t="s">
+      <c r="I82" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K82" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L82" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M82" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N82" s="45"/>
+      <c r="K82" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L82" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M82" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N82" s="46"/>
     </row>
     <row r="83" spans="3:17">
       <c r="C83" s="1"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="47" t="s">
+      <c r="E83" s="47"/>
+      <c r="F83" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G83" s="47" t="s">
+      <c r="G83" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H83" s="47" t="s">
+      <c r="H83" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I83" s="47" t="s">
+      <c r="I83" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J83" s="47" t="s">
+      <c r="J83" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K83" s="48" t="s">
+      <c r="K83" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L83" s="48"/>
-      <c r="M83" s="47"/>
+      <c r="L83" s="49"/>
+      <c r="M83" s="48"/>
     </row>
     <row r="84" spans="3:17">
       <c r="C84" s="1"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="46" t="s">
+      <c r="E84" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F84" t="s">
         <v>39</v>
       </c>
-      <c r="G84" s="44" t="s">
+      <c r="G84" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H84" s="44" t="s">
+      <c r="H84" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I84" s="44" t="s">
+      <c r="I84" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="49" t="s">
+      <c r="J84" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="L84" s="50"/>
-      <c r="M84" s="51"/>
-      <c r="N84" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O84" s="42" t="s">
+      <c r="L84" s="51"/>
+      <c r="M84" s="52"/>
+      <c r="N84" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O84" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="1"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="46" t="s">
+      <c r="E85" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>39</v>
       </c>
-      <c r="G85" s="45" t="s">
+      <c r="G85" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H85" s="44" t="s">
+      <c r="H85" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I85" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" s="45" t="s">
+      <c r="I85" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K85" s="45" t="s">
+      <c r="K85" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L85" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M85" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N85" s="45"/>
+      <c r="L85" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M85" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="46"/>
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
     </row>
     <row r="87" spans="3:17">
-      <c r="F87" s="38" t="s">
+      <c r="F87" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H87" s="39" t="s">
+      <c r="H87" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I87" s="39"/>
-      <c r="J87" s="39" t="s">
+      <c r="I87" s="40"/>
+      <c r="J87" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K87" s="39"/>
-      <c r="L87" s="38" t="s">
+      <c r="K87" s="40"/>
+      <c r="L87" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M87" s="38" t="s">
+      <c r="M87" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N87" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O87" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P87" s="38"/>
-      <c r="Q87" s="38"/>
+      <c r="N87" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O87" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P87" s="39"/>
+      <c r="Q87" s="39"/>
     </row>
     <row r="88" spans="3:17">
       <c r="C88" s="1" t="s">
@@ -5097,44 +5181,44 @@
       <c r="D88" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E88" s="43" t="s">
+      <c r="E88" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F88" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G88" s="44" t="s">
+      <c r="F88" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G88" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="44" t="s">
+      <c r="H88" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="I88" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J88" s="44" t="s">
+      <c r="I88" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K88" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L88" s="44" t="s">
+      <c r="K88" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L88" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M88" s="52" t="s">
+      <c r="M88" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="N88" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O88" s="42" t="s">
+      <c r="N88" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="89" spans="3:17">
       <c r="C89" s="1"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="45" t="s">
+      <c r="E89" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F89" t="s">
@@ -5165,7 +5249,7 @@
     <row r="90" spans="3:17">
       <c r="C90" s="1"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="45" t="s">
+      <c r="E90" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F90" t="s">
@@ -5196,158 +5280,158 @@
     <row r="91" spans="3:17">
       <c r="C91" s="1"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="46" t="s">
+      <c r="E91" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F91" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="45" t="s">
+      <c r="G91" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="44" t="s">
+      <c r="H91" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="I91" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J91" s="44" t="s">
+      <c r="I91" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J91" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K91" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L91" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M91" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N91" s="45"/>
+      <c r="K91" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L91" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M91" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N91" s="46"/>
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="46"/>
-      <c r="F92" s="47" t="s">
+      <c r="E92" s="47"/>
+      <c r="F92" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="47" t="s">
+      <c r="G92" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H92" s="47" t="s">
+      <c r="H92" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I92" s="47" t="s">
+      <c r="I92" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J92" s="47" t="s">
+      <c r="J92" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K92" s="48" t="s">
+      <c r="K92" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L92" s="48"/>
-      <c r="M92" s="47"/>
+      <c r="L92" s="49"/>
+      <c r="M92" s="48"/>
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="1"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="46" t="s">
+      <c r="E93" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F93" t="s">
         <v>39</v>
       </c>
-      <c r="G93" s="44" t="s">
+      <c r="G93" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H93" s="44" t="s">
+      <c r="H93" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I93" s="44" t="s">
+      <c r="I93" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="J93" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" s="49" t="s">
+      <c r="J93" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K93" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="L93" s="50"/>
-      <c r="M93" s="51"/>
-      <c r="N93" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O93" s="42" t="s">
+      <c r="L93" s="51"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O93" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="1"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="46" t="s">
+      <c r="E94" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F94" t="s">
         <v>39</v>
       </c>
-      <c r="G94" s="45" t="s">
+      <c r="G94" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H94" s="44" t="s">
+      <c r="H94" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="I94" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J94" s="45" t="s">
+      <c r="I94" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K94" s="45" t="s">
+      <c r="K94" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L94" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M94" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N94" s="45"/>
+      <c r="L94" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M94" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94" s="46"/>
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="1"/>
       <c r="D95" s="2"/>
     </row>
     <row r="96" spans="3:17">
-      <c r="F96" s="38" t="s">
+      <c r="F96" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G96" s="38" t="s">
+      <c r="G96" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H96" s="39" t="s">
+      <c r="H96" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I96" s="39"/>
-      <c r="J96" s="39" t="s">
+      <c r="I96" s="40"/>
+      <c r="J96" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K96" s="39"/>
-      <c r="L96" s="38" t="s">
+      <c r="K96" s="40"/>
+      <c r="L96" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M96" s="38" t="s">
+      <c r="M96" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N96" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O96" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P96" s="38"/>
-      <c r="Q96" s="38"/>
+      <c r="N96" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O96" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" s="39"/>
+      <c r="Q96" s="39"/>
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="1" t="s">
@@ -5356,44 +5440,44 @@
       <c r="D97" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E97" s="43" t="s">
+      <c r="E97" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F97" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="44" t="s">
+      <c r="F97" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H97" s="44" t="s">
+      <c r="H97" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="I97" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J97" s="44" t="s">
+      <c r="I97" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K97" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L97" s="44" t="s">
+      <c r="K97" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L97" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M97" s="44" t="s">
+      <c r="M97" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="N97" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O97" s="42" t="s">
+      <c r="N97" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O97" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="98" spans="3:17">
       <c r="C98" s="1"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="45" t="s">
+      <c r="E98" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F98" t="s">
@@ -5424,7 +5508,7 @@
     <row r="99" spans="3:17">
       <c r="C99" s="1"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="45" t="s">
+      <c r="E99" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F99" t="s">
@@ -5455,158 +5539,158 @@
     <row r="100" spans="3:17">
       <c r="C100" s="1"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="46" t="s">
+      <c r="E100" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F100" t="s">
         <v>39</v>
       </c>
-      <c r="G100" s="45" t="s">
+      <c r="G100" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="44" t="s">
+      <c r="H100" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="I100" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J100" s="44" t="s">
+      <c r="I100" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J100" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K100" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L100" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M100" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N100" s="45"/>
+      <c r="K100" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L100" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N100" s="46"/>
     </row>
     <row r="101" spans="3:17">
       <c r="C101" s="1"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="47" t="s">
+      <c r="E101" s="47"/>
+      <c r="F101" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="47" t="s">
+      <c r="G101" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H101" s="47" t="s">
+      <c r="H101" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I101" s="47" t="s">
+      <c r="I101" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J101" s="47" t="s">
+      <c r="J101" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K101" s="48" t="s">
+      <c r="K101" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L101" s="48"/>
-      <c r="M101" s="47"/>
+      <c r="L101" s="49"/>
+      <c r="M101" s="48"/>
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="1"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="46" t="s">
+      <c r="E102" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F102" t="s">
         <v>39</v>
       </c>
-      <c r="G102" s="44" t="s">
+      <c r="G102" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H102" s="44" t="s">
+      <c r="H102" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I102" s="44" t="s">
+      <c r="I102" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="J102" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="49" t="s">
+      <c r="J102" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="L102" s="50"/>
-      <c r="M102" s="51"/>
-      <c r="N102" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O102" s="42" t="s">
+      <c r="L102" s="51"/>
+      <c r="M102" s="52"/>
+      <c r="N102" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O102" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="1"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="46" t="s">
+      <c r="E103" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F103" t="s">
         <v>39</v>
       </c>
-      <c r="G103" s="45" t="s">
+      <c r="G103" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H103" s="44" t="s">
+      <c r="H103" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="I103" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="45" t="s">
+      <c r="I103" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K103" s="45" t="s">
+      <c r="K103" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L103" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M103" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N103" s="45"/>
+      <c r="L103" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M103" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N103" s="46"/>
     </row>
     <row r="104" spans="3:17">
       <c r="C104" s="1"/>
       <c r="D104" s="2"/>
     </row>
     <row r="105" spans="3:17">
-      <c r="F105" s="38" t="s">
+      <c r="F105" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="38" t="s">
+      <c r="G105" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="39" t="s">
+      <c r="H105" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I105" s="39"/>
-      <c r="J105" s="39" t="s">
+      <c r="I105" s="40"/>
+      <c r="J105" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K105" s="39"/>
-      <c r="L105" s="38" t="s">
+      <c r="K105" s="40"/>
+      <c r="L105" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M105" s="38" t="s">
+      <c r="M105" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N105" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O105" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P105" s="38"/>
-      <c r="Q105" s="38"/>
+      <c r="N105" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O105" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P105" s="39"/>
+      <c r="Q105" s="39"/>
     </row>
     <row r="106" spans="3:17">
       <c r="C106" s="1" t="s">
@@ -5615,44 +5699,44 @@
       <c r="D106" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E106" s="43" t="s">
+      <c r="E106" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F106" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G106" s="44" t="s">
+      <c r="F106" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G106" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H106" s="44" t="s">
+      <c r="H106" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="I106" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J106" s="44" t="s">
+      <c r="I106" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J106" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K106" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="44" t="s">
+      <c r="K106" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M106" s="44" t="s">
+      <c r="M106" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="N106" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O106" s="42" t="s">
+      <c r="N106" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O106" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="1"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="45" t="s">
+      <c r="E107" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F107" t="s">
@@ -5683,7 +5767,7 @@
     <row r="108" spans="3:17">
       <c r="C108" s="1"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="45" t="s">
+      <c r="E108" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F108" t="s">
@@ -5714,158 +5798,158 @@
     <row r="109" spans="3:17">
       <c r="C109" s="1"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="46" t="s">
+      <c r="E109" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F109" t="s">
         <v>39</v>
       </c>
-      <c r="G109" s="45" t="s">
+      <c r="G109" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H109" s="44" t="s">
+      <c r="H109" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="I109" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="44" t="s">
+      <c r="I109" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K109" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L109" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M109" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N109" s="45"/>
+      <c r="K109" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L109" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M109" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N109" s="46"/>
     </row>
     <row r="110" spans="3:17">
       <c r="C110" s="1"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="46"/>
-      <c r="F110" s="47" t="s">
+      <c r="E110" s="47"/>
+      <c r="F110" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="47" t="s">
+      <c r="G110" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H110" s="47" t="s">
+      <c r="H110" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I110" s="47" t="s">
+      <c r="I110" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J110" s="47" t="s">
+      <c r="J110" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K110" s="48" t="s">
+      <c r="K110" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L110" s="48"/>
-      <c r="M110" s="47"/>
+      <c r="L110" s="49"/>
+      <c r="M110" s="48"/>
     </row>
     <row r="111" spans="3:17">
       <c r="C111" s="1"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="46" t="s">
+      <c r="E111" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F111" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="44" t="s">
+      <c r="G111" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H111" s="44" t="s">
+      <c r="H111" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I111" s="44" t="s">
+      <c r="I111" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="J111" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" s="49" t="s">
+      <c r="J111" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="L111" s="50"/>
-      <c r="M111" s="51"/>
-      <c r="N111" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O111" s="42" t="s">
+      <c r="L111" s="51"/>
+      <c r="M111" s="52"/>
+      <c r="N111" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O111" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="112" spans="3:17">
       <c r="C112" s="1"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="46" t="s">
+      <c r="E112" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F112" t="s">
         <v>39</v>
       </c>
-      <c r="G112" s="45" t="s">
+      <c r="G112" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H112" s="44" t="s">
+      <c r="H112" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="I112" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J112" s="45" t="s">
+      <c r="I112" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J112" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K112" s="45" t="s">
+      <c r="K112" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L112" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M112" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N112" s="45"/>
+      <c r="L112" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M112" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N112" s="46"/>
     </row>
     <row r="113" spans="3:17">
       <c r="C113" s="1"/>
       <c r="D113" s="2"/>
     </row>
     <row r="114" spans="3:17">
-      <c r="F114" s="38" t="s">
+      <c r="F114" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G114" s="38" t="s">
+      <c r="G114" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H114" s="39" t="s">
+      <c r="H114" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I114" s="39"/>
-      <c r="J114" s="39" t="s">
+      <c r="I114" s="40"/>
+      <c r="J114" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="39"/>
-      <c r="L114" s="38" t="s">
+      <c r="K114" s="40"/>
+      <c r="L114" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M114" s="38" t="s">
+      <c r="M114" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N114" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O114" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P114" s="38"/>
-      <c r="Q114" s="38"/>
+      <c r="N114" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O114" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P114" s="39"/>
+      <c r="Q114" s="39"/>
     </row>
     <row r="115" spans="3:17">
       <c r="C115" s="1" t="s">
@@ -5874,44 +5958,44 @@
       <c r="D115" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E115" s="43" t="s">
+      <c r="E115" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F115" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G115" s="44" t="s">
+      <c r="F115" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G115" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H115" s="44" t="s">
+      <c r="H115" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="I115" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J115" s="44" t="s">
+      <c r="I115" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J115" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K115" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L115" s="44" t="s">
+      <c r="K115" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L115" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M115" s="52" t="s">
+      <c r="M115" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="N115" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O115" s="42" t="s">
+      <c r="N115" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O115" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="116" spans="3:17">
       <c r="C116" s="1"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="45" t="s">
+      <c r="E116" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F116" t="s">
@@ -5942,7 +6026,7 @@
     <row r="117" spans="3:17">
       <c r="C117" s="1"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="45" t="s">
+      <c r="E117" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F117" t="s">
@@ -5973,158 +6057,158 @@
     <row r="118" spans="3:17">
       <c r="C118" s="1"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="46" t="s">
+      <c r="E118" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F118" t="s">
         <v>39</v>
       </c>
-      <c r="G118" s="45" t="s">
+      <c r="G118" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H118" s="44" t="s">
+      <c r="H118" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="I118" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J118" s="44" t="s">
+      <c r="I118" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J118" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K118" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L118" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M118" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N118" s="45"/>
+      <c r="K118" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L118" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M118" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N118" s="46"/>
     </row>
     <row r="119" spans="3:17">
       <c r="C119" s="1"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="46"/>
-      <c r="F119" s="47" t="s">
+      <c r="E119" s="47"/>
+      <c r="F119" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="47" t="s">
+      <c r="G119" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H119" s="47" t="s">
+      <c r="H119" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I119" s="47" t="s">
+      <c r="I119" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J119" s="47" t="s">
+      <c r="J119" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K119" s="48" t="s">
+      <c r="K119" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L119" s="48"/>
-      <c r="M119" s="47"/>
+      <c r="L119" s="49"/>
+      <c r="M119" s="48"/>
     </row>
     <row r="120" spans="3:17">
       <c r="C120" s="1"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="46" t="s">
+      <c r="E120" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F120" t="s">
         <v>39</v>
       </c>
-      <c r="G120" s="44" t="s">
+      <c r="G120" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H120" s="44" t="s">
+      <c r="H120" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I120" s="44" t="s">
+      <c r="I120" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="J120" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" s="49" t="s">
+      <c r="J120" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="L120" s="50"/>
-      <c r="M120" s="51"/>
-      <c r="N120" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O120" s="42" t="s">
+      <c r="L120" s="51"/>
+      <c r="M120" s="52"/>
+      <c r="N120" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O120" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="121" spans="3:17">
       <c r="C121" s="1"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="46" t="s">
+      <c r="E121" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F121" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="45" t="s">
+      <c r="G121" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H121" s="44" t="s">
+      <c r="H121" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="I121" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="45" t="s">
+      <c r="I121" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K121" s="45" t="s">
+      <c r="K121" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L121" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M121" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N121" s="45"/>
+      <c r="L121" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M121" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N121" s="46"/>
     </row>
     <row r="122" spans="3:17">
       <c r="C122" s="1"/>
       <c r="D122" s="2"/>
     </row>
     <row r="123" spans="3:17">
-      <c r="F123" s="38" t="s">
+      <c r="F123" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G123" s="38" t="s">
+      <c r="G123" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H123" s="39" t="s">
+      <c r="H123" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I123" s="39"/>
-      <c r="J123" s="39" t="s">
+      <c r="I123" s="40"/>
+      <c r="J123" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K123" s="39"/>
-      <c r="L123" s="38" t="s">
+      <c r="K123" s="40"/>
+      <c r="L123" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M123" s="38" t="s">
+      <c r="M123" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N123" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O123" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P123" s="38"/>
-      <c r="Q123" s="38"/>
+      <c r="N123" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O123" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P123" s="39"/>
+      <c r="Q123" s="39"/>
     </row>
     <row r="124" spans="3:17">
       <c r="C124" s="1" t="s">
@@ -6133,44 +6217,44 @@
       <c r="D124" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E124" s="43" t="s">
+      <c r="E124" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F124" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G124" s="44" t="s">
+      <c r="F124" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G124" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H124" s="44" t="s">
+      <c r="H124" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="I124" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J124" s="44" t="s">
+      <c r="I124" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K124" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L124" s="44" t="s">
+      <c r="K124" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L124" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M124" s="52" t="s">
+      <c r="M124" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="N124" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O124" s="42" t="s">
+      <c r="N124" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O124" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="125" spans="3:17">
       <c r="C125" s="1"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="45" t="s">
+      <c r="E125" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F125" t="s">
@@ -6201,7 +6285,7 @@
     <row r="126" spans="3:17">
       <c r="C126" s="1"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="45" t="s">
+      <c r="E126" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F126" t="s">
@@ -6232,158 +6316,158 @@
     <row r="127" spans="3:17">
       <c r="C127" s="1"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="46" t="s">
+      <c r="E127" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F127" t="s">
         <v>39</v>
       </c>
-      <c r="G127" s="45" t="s">
+      <c r="G127" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H127" s="44" t="s">
+      <c r="H127" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="I127" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J127" s="44" t="s">
+      <c r="I127" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J127" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K127" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L127" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M127" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N127" s="45"/>
+      <c r="K127" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L127" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M127" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N127" s="46"/>
     </row>
     <row r="128" spans="3:17">
       <c r="C128" s="1"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="46"/>
-      <c r="F128" s="47" t="s">
+      <c r="E128" s="47"/>
+      <c r="F128" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="47" t="s">
+      <c r="G128" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H128" s="47" t="s">
+      <c r="H128" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I128" s="47" t="s">
+      <c r="I128" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J128" s="47" t="s">
+      <c r="J128" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K128" s="48" t="s">
+      <c r="K128" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L128" s="48"/>
-      <c r="M128" s="47"/>
+      <c r="L128" s="49"/>
+      <c r="M128" s="48"/>
     </row>
     <row r="129" spans="3:17">
       <c r="C129" s="1"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="46" t="s">
+      <c r="E129" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F129" t="s">
         <v>39</v>
       </c>
-      <c r="G129" s="44" t="s">
+      <c r="G129" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H129" s="44" t="s">
+      <c r="H129" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I129" s="44" t="s">
+      <c r="I129" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="J129" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="53" t="s">
+      <c r="J129" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K129" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="L129" s="50"/>
-      <c r="M129" s="51"/>
-      <c r="N129" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O129" s="42" t="s">
+      <c r="L129" s="51"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O129" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="130" spans="3:17">
       <c r="C130" s="1"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="46" t="s">
+      <c r="E130" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F130" t="s">
         <v>39</v>
       </c>
-      <c r="G130" s="45" t="s">
+      <c r="G130" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H130" s="44" t="s">
+      <c r="H130" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="I130" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J130" s="45" t="s">
+      <c r="I130" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J130" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K130" s="45" t="s">
+      <c r="K130" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L130" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M130" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N130" s="45"/>
+      <c r="L130" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M130" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N130" s="46"/>
     </row>
     <row r="131" spans="3:17">
       <c r="C131" s="1"/>
       <c r="D131" s="2"/>
     </row>
     <row r="132" spans="3:17">
-      <c r="F132" s="38" t="s">
+      <c r="F132" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="38" t="s">
+      <c r="G132" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H132" s="39" t="s">
+      <c r="H132" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I132" s="39"/>
-      <c r="J132" s="39" t="s">
+      <c r="I132" s="40"/>
+      <c r="J132" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K132" s="39"/>
-      <c r="L132" s="38" t="s">
+      <c r="K132" s="40"/>
+      <c r="L132" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M132" s="38" t="s">
+      <c r="M132" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N132" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O132" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P132" s="38"/>
-      <c r="Q132" s="38"/>
+      <c r="N132" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O132" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P132" s="39"/>
+      <c r="Q132" s="39"/>
     </row>
     <row r="133" spans="3:17">
       <c r="C133" s="1" t="s">
@@ -6392,44 +6476,44 @@
       <c r="D133" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E133" s="43" t="s">
+      <c r="E133" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F133" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G133" s="44" t="s">
+      <c r="F133" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G133" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H133" s="44" t="s">
+      <c r="H133" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="I133" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="44" t="s">
+      <c r="I133" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K133" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L133" s="44" t="s">
+      <c r="K133" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L133" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M133" s="44" t="s">
+      <c r="M133" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="N133" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O133" s="42" t="s">
+      <c r="N133" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O133" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="134" spans="3:17">
       <c r="C134" s="1"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="45" t="s">
+      <c r="E134" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F134" t="s">
@@ -6460,7 +6544,7 @@
     <row r="135" spans="3:17">
       <c r="C135" s="1"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="45" t="s">
+      <c r="E135" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F135" t="s">
@@ -6491,158 +6575,158 @@
     <row r="136" spans="3:17">
       <c r="C136" s="1"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="46" t="s">
+      <c r="E136" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F136" t="s">
         <v>39</v>
       </c>
-      <c r="G136" s="45" t="s">
+      <c r="G136" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H136" s="44" t="s">
+      <c r="H136" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="I136" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J136" s="44" t="s">
+      <c r="I136" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K136" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L136" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M136" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N136" s="45"/>
+      <c r="K136" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L136" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M136" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N136" s="46"/>
     </row>
     <row r="137" spans="3:17">
       <c r="C137" s="1"/>
       <c r="D137" s="2"/>
-      <c r="E137" s="46"/>
-      <c r="F137" s="47" t="s">
+      <c r="E137" s="47"/>
+      <c r="F137" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G137" s="47" t="s">
+      <c r="G137" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H137" s="47" t="s">
+      <c r="H137" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I137" s="47" t="s">
+      <c r="I137" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J137" s="47" t="s">
+      <c r="J137" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K137" s="48" t="s">
+      <c r="K137" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L137" s="48"/>
-      <c r="M137" s="47"/>
+      <c r="L137" s="49"/>
+      <c r="M137" s="48"/>
     </row>
     <row r="138" spans="3:17">
       <c r="C138" s="1"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="46" t="s">
+      <c r="E138" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F138" t="s">
         <v>39</v>
       </c>
-      <c r="G138" s="44" t="s">
+      <c r="G138" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H138" s="44" t="s">
+      <c r="H138" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I138" s="44" t="s">
+      <c r="I138" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="J138" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K138" s="49" t="s">
+      <c r="J138" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K138" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="L138" s="50"/>
-      <c r="M138" s="51"/>
-      <c r="N138" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O138" s="42" t="s">
+      <c r="L138" s="51"/>
+      <c r="M138" s="52"/>
+      <c r="N138" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O138" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="139" spans="3:17">
       <c r="C139" s="1"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="46" t="s">
+      <c r="E139" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F139" t="s">
         <v>39</v>
       </c>
-      <c r="G139" s="45" t="s">
+      <c r="G139" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H139" s="44" t="s">
+      <c r="H139" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="I139" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" s="45" t="s">
+      <c r="I139" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J139" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K139" s="45" t="s">
+      <c r="K139" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L139" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M139" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N139" s="45"/>
+      <c r="L139" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M139" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N139" s="46"/>
     </row>
     <row r="140" spans="3:17">
       <c r="C140" s="1"/>
       <c r="D140" s="2"/>
     </row>
     <row r="141" spans="3:17">
-      <c r="F141" s="38" t="s">
+      <c r="F141" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G141" s="38" t="s">
+      <c r="G141" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H141" s="39" t="s">
+      <c r="H141" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I141" s="39"/>
-      <c r="J141" s="39" t="s">
+      <c r="I141" s="40"/>
+      <c r="J141" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K141" s="39"/>
-      <c r="L141" s="38" t="s">
+      <c r="K141" s="40"/>
+      <c r="L141" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M141" s="38" t="s">
+      <c r="M141" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N141" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O141" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P141" s="38"/>
-      <c r="Q141" s="38"/>
+      <c r="N141" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O141" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P141" s="39"/>
+      <c r="Q141" s="39"/>
     </row>
     <row r="142" spans="3:17">
       <c r="C142" s="1" t="s">
@@ -6651,44 +6735,44 @@
       <c r="D142" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E142" s="43" t="s">
+      <c r="E142" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F142" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G142" s="44" t="s">
+      <c r="F142" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H142" s="44" t="s">
+      <c r="H142" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I142" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="44" t="s">
+      <c r="I142" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J142" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K142" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L142" s="44" t="s">
+      <c r="K142" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L142" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M142" s="44" t="s">
+      <c r="M142" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="N142" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O142" s="42" t="s">
+      <c r="N142" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O142" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="143" spans="3:17">
       <c r="C143" s="1"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="45" t="s">
+      <c r="E143" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F143" t="s">
@@ -6719,7 +6803,7 @@
     <row r="144" spans="3:17">
       <c r="C144" s="1"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="45" t="s">
+      <c r="E144" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F144" t="s">
@@ -6750,158 +6834,158 @@
     <row r="145" spans="3:17">
       <c r="C145" s="1"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="46" t="s">
+      <c r="E145" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F145" t="s">
         <v>39</v>
       </c>
-      <c r="G145" s="45" t="s">
+      <c r="G145" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H145" s="44" t="s">
+      <c r="H145" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I145" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="44" t="s">
+      <c r="I145" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K145" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L145" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M145" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N145" s="45"/>
+      <c r="K145" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M145" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N145" s="46"/>
     </row>
     <row r="146" spans="3:17">
       <c r="C146" s="1"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="46"/>
-      <c r="F146" s="47" t="s">
+      <c r="E146" s="47"/>
+      <c r="F146" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G146" s="47" t="s">
+      <c r="G146" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H146" s="47" t="s">
+      <c r="H146" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I146" s="47" t="s">
+      <c r="I146" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J146" s="47" t="s">
+      <c r="J146" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K146" s="48" t="s">
+      <c r="K146" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L146" s="48"/>
-      <c r="M146" s="47"/>
+      <c r="L146" s="49"/>
+      <c r="M146" s="48"/>
     </row>
     <row r="147" spans="3:17">
       <c r="C147" s="1"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="46" t="s">
+      <c r="E147" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F147" t="s">
         <v>39</v>
       </c>
-      <c r="G147" s="44" t="s">
+      <c r="G147" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H147" s="44" t="s">
+      <c r="H147" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I147" s="44" t="s">
+      <c r="I147" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="J147" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="49" t="s">
+      <c r="J147" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="L147" s="50"/>
-      <c r="M147" s="51"/>
-      <c r="N147" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O147" s="42" t="s">
+      <c r="L147" s="51"/>
+      <c r="M147" s="52"/>
+      <c r="N147" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O147" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="148" spans="3:17">
       <c r="C148" s="1"/>
       <c r="D148" s="2"/>
-      <c r="E148" s="46" t="s">
+      <c r="E148" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F148" t="s">
         <v>39</v>
       </c>
-      <c r="G148" s="45" t="s">
+      <c r="G148" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H148" s="44" t="s">
+      <c r="H148" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I148" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="45" t="s">
+      <c r="I148" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K148" s="45" t="s">
+      <c r="K148" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L148" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M148" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N148" s="45"/>
+      <c r="L148" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M148" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N148" s="46"/>
     </row>
     <row r="149" spans="3:17">
       <c r="C149" s="1"/>
       <c r="D149" s="2"/>
     </row>
     <row r="150" spans="3:17">
-      <c r="F150" s="38" t="s">
+      <c r="F150" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G150" s="38" t="s">
+      <c r="G150" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H150" s="39" t="s">
+      <c r="H150" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I150" s="39"/>
-      <c r="J150" s="39" t="s">
+      <c r="I150" s="40"/>
+      <c r="J150" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K150" s="39"/>
-      <c r="L150" s="38" t="s">
+      <c r="K150" s="40"/>
+      <c r="L150" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M150" s="38" t="s">
+      <c r="M150" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N150" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O150" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P150" s="38"/>
-      <c r="Q150" s="38"/>
+      <c r="N150" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O150" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P150" s="39"/>
+      <c r="Q150" s="39"/>
     </row>
     <row r="151" ht="81" spans="3:17">
       <c r="C151" s="1" t="s">
@@ -6910,44 +6994,44 @@
       <c r="D151" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E151" s="43" t="s">
+      <c r="E151" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F151" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G151" s="44" t="s">
+      <c r="F151" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G151" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H151" s="44" t="s">
+      <c r="H151" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I151" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J151" s="44" t="s">
+      <c r="I151" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J151" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K151" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L151" s="44" t="s">
+      <c r="K151" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L151" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M151" s="54" t="s">
+      <c r="M151" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="N151" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O151" s="42" t="s">
+      <c r="N151" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O151" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="152" spans="3:17">
       <c r="C152" s="1"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="45" t="s">
+      <c r="E152" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F152" t="s">
@@ -6978,7 +7062,7 @@
     <row r="153" spans="3:17">
       <c r="C153" s="1"/>
       <c r="D153" s="2"/>
-      <c r="E153" s="45" t="s">
+      <c r="E153" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F153" t="s">
@@ -7009,160 +7093,160 @@
     <row r="154" spans="3:17">
       <c r="C154" s="1"/>
       <c r="D154" s="2"/>
-      <c r="E154" s="46" t="s">
+      <c r="E154" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F154" t="s">
         <v>39</v>
       </c>
-      <c r="G154" s="45" t="s">
+      <c r="G154" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H154" s="44" t="s">
+      <c r="H154" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I154" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J154" s="44" t="s">
+      <c r="I154" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K154" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L154" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M154" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N154" s="45"/>
+      <c r="K154" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L154" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M154" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N154" s="46"/>
     </row>
     <row r="155" spans="3:17">
       <c r="C155" s="1"/>
       <c r="D155" s="2"/>
-      <c r="E155" s="46"/>
-      <c r="F155" s="47" t="s">
+      <c r="E155" s="47"/>
+      <c r="F155" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G155" s="47" t="s">
+      <c r="G155" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H155" s="47" t="s">
+      <c r="H155" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I155" s="47" t="s">
+      <c r="I155" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J155" s="47" t="s">
+      <c r="J155" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K155" s="48" t="s">
+      <c r="K155" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L155" s="48"/>
-      <c r="M155" s="47"/>
-      <c r="N155" s="44"/>
-      <c r="O155" s="42"/>
+      <c r="L155" s="49"/>
+      <c r="M155" s="48"/>
+      <c r="N155" s="45"/>
+      <c r="O155" s="43"/>
     </row>
     <row r="156" spans="3:17">
       <c r="C156" s="1"/>
       <c r="D156" s="2"/>
-      <c r="E156" s="46" t="s">
+      <c r="E156" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F156" t="s">
         <v>39</v>
       </c>
-      <c r="G156" s="44" t="s">
+      <c r="G156" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H156" s="44" t="s">
+      <c r="H156" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I156" s="44" t="s">
+      <c r="I156" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="J156" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K156" s="49" t="s">
+      <c r="J156" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="L156" s="50"/>
-      <c r="M156" s="51"/>
-      <c r="N156" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O156" s="42" t="s">
+      <c r="L156" s="51"/>
+      <c r="M156" s="52"/>
+      <c r="N156" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O156" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="157" spans="3:17">
       <c r="C157" s="1"/>
       <c r="D157" s="2"/>
-      <c r="E157" s="46" t="s">
+      <c r="E157" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F157" t="s">
         <v>39</v>
       </c>
-      <c r="G157" s="45" t="s">
+      <c r="G157" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H157" s="44" t="s">
+      <c r="H157" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I157" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J157" s="45" t="s">
+      <c r="I157" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K157" s="45" t="s">
+      <c r="K157" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L157" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M157" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N157" s="45"/>
+      <c r="L157" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M157" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N157" s="46"/>
     </row>
     <row r="158" spans="3:17">
       <c r="C158" s="1"/>
       <c r="D158" s="2"/>
     </row>
     <row r="159" spans="3:17">
-      <c r="F159" s="38" t="s">
+      <c r="F159" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="38" t="s">
+      <c r="G159" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H159" s="39" t="s">
+      <c r="H159" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I159" s="39"/>
-      <c r="J159" s="39" t="s">
+      <c r="I159" s="40"/>
+      <c r="J159" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K159" s="39"/>
-      <c r="L159" s="38" t="s">
+      <c r="K159" s="40"/>
+      <c r="L159" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M159" s="38" t="s">
+      <c r="M159" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N159" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O159" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P159" s="38"/>
-      <c r="Q159" s="38"/>
+      <c r="N159" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O159" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P159" s="39"/>
+      <c r="Q159" s="39"/>
     </row>
     <row r="160" spans="3:17">
       <c r="C160" s="1" t="s">
@@ -7171,44 +7255,44 @@
       <c r="D160" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E160" s="43" t="s">
+      <c r="E160" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F160" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G160" s="44" t="s">
+      <c r="F160" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G160" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H160" s="44" t="s">
+      <c r="H160" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I160" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="44" t="s">
+      <c r="I160" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K160" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L160" s="44" t="s">
+      <c r="K160" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L160" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="M160" s="44" t="s">
+      <c r="M160" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="N160" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O160" s="42" t="s">
+      <c r="N160" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O160" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="161" spans="3:17">
       <c r="C161" s="1"/>
       <c r="D161" s="2"/>
-      <c r="E161" s="45" t="s">
+      <c r="E161" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F161" t="s">
@@ -7239,7 +7323,7 @@
     <row r="162" spans="3:17">
       <c r="C162" s="1"/>
       <c r="D162" s="2"/>
-      <c r="E162" s="45" t="s">
+      <c r="E162" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F162" t="s">
@@ -7270,160 +7354,160 @@
     <row r="163" spans="3:17">
       <c r="C163" s="1"/>
       <c r="D163" s="2"/>
-      <c r="E163" s="46" t="s">
+      <c r="E163" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F163" t="s">
         <v>39</v>
       </c>
-      <c r="G163" s="45" t="s">
+      <c r="G163" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H163" s="44" t="s">
+      <c r="H163" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I163" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J163" s="44" t="s">
+      <c r="I163" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K163" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L163" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M163" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N163" s="45"/>
+      <c r="K163" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L163" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M163" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N163" s="46"/>
     </row>
     <row r="164" spans="3:17">
       <c r="C164" s="1"/>
       <c r="D164" s="2"/>
-      <c r="E164" s="46"/>
-      <c r="F164" s="47" t="s">
+      <c r="E164" s="47"/>
+      <c r="F164" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G164" s="47" t="s">
+      <c r="G164" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H164" s="47" t="s">
+      <c r="H164" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I164" s="47" t="s">
+      <c r="I164" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J164" s="47" t="s">
+      <c r="J164" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K164" s="48" t="s">
+      <c r="K164" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L164" s="48"/>
-      <c r="M164" s="47"/>
-      <c r="N164" s="44"/>
-      <c r="O164" s="42"/>
+      <c r="L164" s="49"/>
+      <c r="M164" s="48"/>
+      <c r="N164" s="45"/>
+      <c r="O164" s="43"/>
     </row>
     <row r="165" spans="3:17">
       <c r="C165" s="1"/>
       <c r="D165" s="2"/>
-      <c r="E165" s="46" t="s">
+      <c r="E165" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F165" t="s">
         <v>39</v>
       </c>
-      <c r="G165" s="44" t="s">
+      <c r="G165" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H165" s="44" t="s">
+      <c r="H165" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="I165" s="44" t="s">
+      <c r="I165" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="J165" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K165" s="49" t="s">
+      <c r="J165" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K165" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="L165" s="50"/>
-      <c r="M165" s="51"/>
-      <c r="N165" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O165" s="42" t="s">
+      <c r="L165" s="51"/>
+      <c r="M165" s="52"/>
+      <c r="N165" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O165" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="166" spans="3:17">
       <c r="C166" s="1"/>
       <c r="D166" s="2"/>
-      <c r="E166" s="46" t="s">
+      <c r="E166" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F166" t="s">
         <v>39</v>
       </c>
-      <c r="G166" s="45" t="s">
+      <c r="G166" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H166" s="44" t="s">
+      <c r="H166" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I166" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J166" s="45" t="s">
+      <c r="I166" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K166" s="45" t="s">
+      <c r="K166" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L166" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M166" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N166" s="45"/>
+      <c r="L166" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M166" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N166" s="46"/>
     </row>
     <row r="167" spans="3:17">
       <c r="C167" s="1"/>
       <c r="D167" s="2"/>
     </row>
     <row r="168" spans="3:17">
-      <c r="F168" s="38" t="s">
+      <c r="F168" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G168" s="38" t="s">
+      <c r="G168" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H168" s="39" t="s">
+      <c r="H168" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I168" s="39"/>
-      <c r="J168" s="39" t="s">
+      <c r="I168" s="40"/>
+      <c r="J168" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K168" s="39"/>
-      <c r="L168" s="38" t="s">
+      <c r="K168" s="40"/>
+      <c r="L168" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M168" s="38" t="s">
+      <c r="M168" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N168" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O168" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P168" s="38"/>
-      <c r="Q168" s="38"/>
+      <c r="N168" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O168" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P168" s="39"/>
+      <c r="Q168" s="39"/>
     </row>
     <row r="169" ht="81" spans="3:17">
       <c r="C169" s="1" t="s">
@@ -7432,44 +7516,44 @@
       <c r="D169" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E169" s="43" t="s">
+      <c r="E169" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F169" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G169" s="44" t="s">
+      <c r="F169" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G169" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H169" s="44" t="s">
+      <c r="H169" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="I169" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J169" s="44" t="s">
+      <c r="I169" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="K169" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L169" s="44" t="s">
+      <c r="K169" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L169" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="M169" s="54" t="s">
+      <c r="M169" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="N169" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O169" s="42" t="s">
+      <c r="N169" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O169" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="170" spans="3:17">
       <c r="C170" s="1"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="45" t="s">
+      <c r="E170" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F170" t="s">
@@ -7500,7 +7584,7 @@
     <row r="171" spans="3:17">
       <c r="C171" s="1"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="45" t="s">
+      <c r="E171" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F171" t="s">
@@ -7531,126 +7615,126 @@
     <row r="172" spans="3:17">
       <c r="C172" s="1"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="46" t="s">
+      <c r="E172" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F172" t="s">
         <v>39</v>
       </c>
-      <c r="G172" s="45" t="s">
+      <c r="G172" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H172" s="44" t="s">
+      <c r="H172" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="I172" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J172" s="44" t="s">
+      <c r="I172" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="K172" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L172" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M172" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N172" s="45"/>
+      <c r="K172" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L172" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M172" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N172" s="46"/>
     </row>
     <row r="173" spans="3:17">
       <c r="C173" s="1"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="46"/>
-      <c r="F173" s="47" t="s">
+      <c r="E173" s="47"/>
+      <c r="F173" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G173" s="47" t="s">
+      <c r="G173" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H173" s="47" t="s">
+      <c r="H173" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I173" s="47" t="s">
+      <c r="I173" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J173" s="47" t="s">
+      <c r="J173" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K173" s="48" t="s">
+      <c r="K173" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L173" s="48"/>
-      <c r="M173" s="47"/>
-      <c r="N173" s="44"/>
-      <c r="O173" s="42"/>
+      <c r="L173" s="49"/>
+      <c r="M173" s="48"/>
+      <c r="N173" s="45"/>
+      <c r="O173" s="43"/>
     </row>
     <row r="174" ht="70" customHeight="1" spans="3:17">
       <c r="C174" s="1"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="46" t="s">
+      <c r="E174" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F174" t="s">
         <v>39</v>
       </c>
-      <c r="G174" s="44" t="s">
+      <c r="G174" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H174" s="44" t="s">
+      <c r="H174" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="I174" s="44" t="s">
+      <c r="I174" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="J174" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K174" s="55" t="s">
+      <c r="J174" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K174" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="L174" s="50"/>
-      <c r="M174" s="51"/>
-      <c r="N174" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O174" s="42" t="s">
+      <c r="L174" s="51"/>
+      <c r="M174" s="52"/>
+      <c r="N174" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O174" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="175" spans="3:17">
       <c r="C175" s="1"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="46" t="s">
+      <c r="E175" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F175" t="s">
         <v>39</v>
       </c>
-      <c r="G175" s="45" t="s">
+      <c r="G175" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H175" s="44" t="s">
+      <c r="H175" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="I175" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J175" s="45" t="s">
+      <c r="I175" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K175" s="45" t="s">
+      <c r="K175" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L175" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M175" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N175" s="45"/>
+      <c r="L175" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M175" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N175" s="46"/>
     </row>
     <row r="176" spans="3:17">
       <c r="C176" s="1"/>
@@ -7663,185 +7747,185 @@
       <c r="D178" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E178" s="43"/>
-      <c r="F178" s="44"/>
-      <c r="G178" s="44"/>
-      <c r="H178" s="44"/>
-      <c r="I178" s="44"/>
-      <c r="J178" s="44"/>
-      <c r="K178" s="44"/>
-      <c r="L178" s="44"/>
-      <c r="M178" s="44"/>
-      <c r="N178" s="44"/>
-      <c r="O178" s="42"/>
+      <c r="E178" s="44"/>
+      <c r="F178" s="45"/>
+      <c r="G178" s="45"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="45"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="45"/>
+      <c r="L178" s="45"/>
+      <c r="M178" s="45"/>
+      <c r="N178" s="45"/>
+      <c r="O178" s="43"/>
     </row>
     <row r="179" spans="3:17">
       <c r="C179" s="1"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="45"/>
+      <c r="E179" s="46"/>
     </row>
     <row r="180" spans="3:17">
       <c r="C180" s="1"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="45"/>
+      <c r="E180" s="46"/>
     </row>
     <row r="181" spans="3:17">
       <c r="C181" s="1"/>
       <c r="D181" s="2"/>
-      <c r="E181" s="46" t="s">
+      <c r="E181" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F181" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="45" t="s">
+      <c r="G181" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H181" s="44" t="s">
+      <c r="H181" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="I181" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J181" s="44" t="s">
+      <c r="I181" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J181" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="K181" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L181" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M181" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N181" s="45"/>
+      <c r="K181" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L181" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M181" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N181" s="46"/>
     </row>
     <row r="182" ht="21" customHeight="1" spans="3:17">
       <c r="C182" s="1"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="46"/>
-      <c r="F182" s="47" t="s">
+      <c r="E182" s="47"/>
+      <c r="F182" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G182" s="47" t="s">
+      <c r="G182" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H182" s="47" t="s">
+      <c r="H182" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I182" s="47" t="s">
+      <c r="I182" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J182" s="47" t="s">
+      <c r="J182" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K182" s="48" t="s">
+      <c r="K182" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L182" s="48"/>
-      <c r="M182" s="47"/>
-      <c r="N182" s="44"/>
-      <c r="O182" s="42"/>
+      <c r="L182" s="49"/>
+      <c r="M182" s="48"/>
+      <c r="N182" s="45"/>
+      <c r="O182" s="43"/>
     </row>
     <row r="183" ht="45" customHeight="1" spans="3:17">
       <c r="C183" s="1"/>
       <c r="D183" s="2"/>
-      <c r="E183" s="46" t="s">
+      <c r="E183" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F183" t="s">
         <v>39</v>
       </c>
-      <c r="G183" s="44" t="s">
+      <c r="G183" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H183" s="44" t="s">
+      <c r="H183" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="I183" s="44" t="s">
+      <c r="I183" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="J183" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K183" s="55" t="s">
+      <c r="J183" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K183" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="L183" s="50"/>
-      <c r="M183" s="51"/>
-      <c r="N183" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O183" s="42" t="s">
+      <c r="L183" s="51"/>
+      <c r="M183" s="52"/>
+      <c r="N183" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O183" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="184" spans="3:17">
       <c r="C184" s="1"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="46" t="s">
+      <c r="E184" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F184" t="s">
         <v>39</v>
       </c>
-      <c r="G184" s="45" t="s">
+      <c r="G184" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H184" s="44" t="s">
+      <c r="H184" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="I184" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J184" s="45" t="s">
+      <c r="I184" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J184" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K184" s="45" t="s">
+      <c r="K184" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L184" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M184" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N184" s="45"/>
+      <c r="L184" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M184" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N184" s="46"/>
     </row>
     <row r="185" spans="3:17">
       <c r="C185" s="1"/>
       <c r="D185" s="2"/>
     </row>
     <row r="186" spans="3:17">
-      <c r="F186" s="38" t="s">
+      <c r="F186" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G186" s="38" t="s">
+      <c r="G186" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H186" s="39" t="s">
+      <c r="H186" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I186" s="39"/>
-      <c r="J186" s="39" t="s">
+      <c r="I186" s="40"/>
+      <c r="J186" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K186" s="39"/>
-      <c r="L186" s="38" t="s">
+      <c r="K186" s="40"/>
+      <c r="L186" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M186" s="38" t="s">
+      <c r="M186" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N186" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O186" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P186" s="38"/>
-      <c r="Q186" s="38"/>
+      <c r="N186" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O186" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P186" s="39"/>
+      <c r="Q186" s="39"/>
     </row>
     <row r="187" spans="3:17">
       <c r="C187" s="1" t="s">
@@ -7850,44 +7934,44 @@
       <c r="D187" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E187" s="43" t="s">
+      <c r="E187" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F187" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G187" s="44" t="s">
+      <c r="F187" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G187" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H187" s="44" t="s">
+      <c r="H187" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="I187" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J187" s="44" t="s">
+      <c r="I187" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J187" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="K187" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L187" s="44" t="s">
+      <c r="K187" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L187" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="M187" s="44" t="s">
+      <c r="M187" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="N187" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O187" s="42" t="s">
+      <c r="N187" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O187" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="188" spans="3:17">
       <c r="C188" s="1"/>
       <c r="D188" s="2"/>
-      <c r="E188" s="45" t="s">
+      <c r="E188" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F188" t="s">
@@ -7918,7 +8002,7 @@
     <row r="189" spans="3:17">
       <c r="C189" s="1"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="45" t="s">
+      <c r="E189" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F189" t="s">
@@ -7949,56 +8033,56 @@
     <row r="190" spans="3:17">
       <c r="C190" s="1"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="46"/>
-      <c r="F190" s="56" t="s">
+      <c r="E190" s="47"/>
+      <c r="F190" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="G190" s="56" t="s">
+      <c r="G190" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="H190" s="56" t="s">
+      <c r="H190" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="I190" s="57" t="s">
+      <c r="I190" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="J190" s="57"/>
-      <c r="K190" s="57" t="s">
+      <c r="J190" s="58"/>
+      <c r="K190" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="L190" s="57"/>
-      <c r="M190" s="57"/>
-      <c r="N190" s="57"/>
-      <c r="O190" s="57"/>
+      <c r="L190" s="58"/>
+      <c r="M190" s="58"/>
+      <c r="N190" s="58"/>
+      <c r="O190" s="58"/>
     </row>
     <row r="191" spans="3:17">
       <c r="C191" s="1"/>
       <c r="D191" s="2"/>
-      <c r="E191" s="46" t="s">
+      <c r="E191" s="47" t="s">
         <v>156</v>
       </c>
       <c r="F191" t="s">
         <v>39</v>
       </c>
-      <c r="G191" s="58" t="s">
+      <c r="G191" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="H191" s="59" t="s">
+      <c r="H191" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="I191" s="59" t="s">
+      <c r="I191" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="J191" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="K191" s="60" t="s">
+      <c r="J191" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="K191" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="L191" s="61"/>
-      <c r="M191" s="61"/>
-      <c r="N191" s="61"/>
-      <c r="O191" s="61"/>
+      <c r="L191" s="62"/>
+      <c r="M191" s="62"/>
+      <c r="N191" s="62"/>
+      <c r="O191" s="62"/>
       <c r="P191" t="s">
         <v>31</v>
       </c>
@@ -8009,179 +8093,179 @@
     <row r="192" spans="3:17">
       <c r="C192" s="1"/>
       <c r="D192" s="2"/>
-      <c r="E192" s="46"/>
-      <c r="G192" s="62"/>
-      <c r="H192" s="63"/>
-      <c r="I192" s="63"/>
-      <c r="J192" s="63"/>
-      <c r="K192" s="63"/>
-      <c r="L192" s="62"/>
-      <c r="M192" s="62"/>
-      <c r="N192" s="62"/>
+      <c r="E192" s="47"/>
+      <c r="G192" s="63"/>
+      <c r="H192" s="64"/>
+      <c r="I192" s="64"/>
+      <c r="J192" s="64"/>
+      <c r="K192" s="64"/>
+      <c r="L192" s="63"/>
+      <c r="M192" s="63"/>
+      <c r="N192" s="63"/>
     </row>
     <row r="193" spans="3:17">
       <c r="C193" s="1"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="46"/>
-      <c r="G193" s="44"/>
-      <c r="H193" s="44"/>
-      <c r="I193" s="44"/>
-      <c r="J193" s="44"/>
-      <c r="K193" s="44"/>
-      <c r="L193" s="44"/>
-      <c r="M193" s="44"/>
-      <c r="N193" s="44"/>
-      <c r="O193" s="42"/>
+      <c r="E193" s="47"/>
+      <c r="G193" s="45"/>
+      <c r="H193" s="45"/>
+      <c r="I193" s="45"/>
+      <c r="J193" s="45"/>
+      <c r="K193" s="45"/>
+      <c r="L193" s="45"/>
+      <c r="M193" s="45"/>
+      <c r="N193" s="45"/>
+      <c r="O193" s="43"/>
     </row>
     <row r="194" spans="3:17">
       <c r="C194" s="1"/>
       <c r="D194" s="2"/>
-      <c r="E194" s="46"/>
-      <c r="G194" s="45"/>
-      <c r="H194" s="44"/>
-      <c r="I194" s="44"/>
-      <c r="J194" s="45"/>
-      <c r="K194" s="45"/>
-      <c r="L194" s="45"/>
-      <c r="M194" s="45"/>
-      <c r="N194" s="45"/>
+      <c r="E194" s="47"/>
+      <c r="G194" s="46"/>
+      <c r="H194" s="45"/>
+      <c r="I194" s="45"/>
+      <c r="J194" s="46"/>
+      <c r="K194" s="46"/>
+      <c r="L194" s="46"/>
+      <c r="M194" s="46"/>
+      <c r="N194" s="46"/>
     </row>
     <row r="195" spans="3:17">
       <c r="D195" s="3"/>
-      <c r="E195" s="45"/>
-      <c r="F195" s="38"/>
-      <c r="G195" s="38"/>
-      <c r="H195" s="39"/>
-      <c r="I195" s="39"/>
-      <c r="J195" s="39"/>
-      <c r="K195" s="39"/>
-      <c r="L195" s="38"/>
-      <c r="M195" s="38"/>
-      <c r="N195" s="38"/>
-      <c r="O195" s="38"/>
-      <c r="P195" s="38"/>
-      <c r="Q195" s="38"/>
+      <c r="E195" s="46"/>
+      <c r="F195" s="39"/>
+      <c r="G195" s="39"/>
+      <c r="H195" s="40"/>
+      <c r="I195" s="40"/>
+      <c r="J195" s="40"/>
+      <c r="K195" s="40"/>
+      <c r="L195" s="39"/>
+      <c r="M195" s="39"/>
+      <c r="N195" s="39"/>
+      <c r="O195" s="39"/>
+      <c r="P195" s="39"/>
+      <c r="Q195" s="39"/>
     </row>
     <row r="196" spans="3:17">
       <c r="C196" s="1"/>
       <c r="D196" s="2"/>
-      <c r="E196" s="43"/>
-      <c r="F196" s="44"/>
-      <c r="G196" s="44"/>
-      <c r="H196" s="44"/>
-      <c r="I196" s="44"/>
-      <c r="J196" s="44"/>
-      <c r="K196" s="44"/>
-      <c r="L196" s="44"/>
-      <c r="M196" s="44"/>
-      <c r="N196" s="44"/>
-      <c r="O196" s="42"/>
+      <c r="E196" s="44"/>
+      <c r="F196" s="45"/>
+      <c r="G196" s="45"/>
+      <c r="H196" s="45"/>
+      <c r="I196" s="45"/>
+      <c r="J196" s="45"/>
+      <c r="K196" s="45"/>
+      <c r="L196" s="45"/>
+      <c r="M196" s="45"/>
+      <c r="N196" s="45"/>
+      <c r="O196" s="43"/>
     </row>
     <row r="197" spans="3:17">
       <c r="C197" s="1"/>
       <c r="D197" s="2"/>
-      <c r="E197" s="45"/>
+      <c r="E197" s="46"/>
     </row>
     <row r="198" spans="3:17">
       <c r="C198" s="1"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="64"/>
+      <c r="E198" s="65"/>
     </row>
     <row r="199" spans="3:17">
       <c r="C199" s="1"/>
       <c r="D199" s="2"/>
-      <c r="H199" s="59"/>
-      <c r="I199" s="59"/>
-      <c r="J199" s="59"/>
-      <c r="K199" s="65"/>
-      <c r="L199" s="66"/>
-      <c r="M199" s="66"/>
-      <c r="N199" s="66"/>
-      <c r="O199" s="66"/>
+      <c r="H199" s="60"/>
+      <c r="I199" s="60"/>
+      <c r="J199" s="60"/>
+      <c r="K199" s="66"/>
+      <c r="L199" s="67"/>
+      <c r="M199" s="67"/>
+      <c r="N199" s="67"/>
+      <c r="O199" s="67"/>
     </row>
     <row r="200" spans="3:17">
       <c r="C200" s="1"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="67"/>
-      <c r="G200" s="62"/>
-      <c r="H200" s="63"/>
-      <c r="I200" s="63"/>
-      <c r="J200" s="63"/>
-      <c r="K200" s="63"/>
-      <c r="L200" s="62"/>
-      <c r="M200" s="62"/>
-      <c r="N200" s="62"/>
+      <c r="E200" s="68"/>
+      <c r="G200" s="63"/>
+      <c r="H200" s="64"/>
+      <c r="I200" s="64"/>
+      <c r="J200" s="64"/>
+      <c r="K200" s="64"/>
+      <c r="L200" s="63"/>
+      <c r="M200" s="63"/>
+      <c r="N200" s="63"/>
     </row>
     <row r="201" spans="3:17">
       <c r="C201" s="1"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="46"/>
-      <c r="G201" s="44"/>
-      <c r="H201" s="44"/>
-      <c r="I201" s="44"/>
-      <c r="J201" s="44"/>
-      <c r="K201" s="44"/>
-      <c r="L201" s="44"/>
-      <c r="M201" s="44"/>
-      <c r="N201" s="44"/>
-      <c r="O201" s="42"/>
+      <c r="E201" s="47"/>
+      <c r="G201" s="45"/>
+      <c r="H201" s="45"/>
+      <c r="I201" s="45"/>
+      <c r="J201" s="45"/>
+      <c r="K201" s="45"/>
+      <c r="L201" s="45"/>
+      <c r="M201" s="45"/>
+      <c r="N201" s="45"/>
+      <c r="O201" s="43"/>
     </row>
     <row r="202" spans="3:17">
       <c r="C202" s="1"/>
       <c r="D202" s="2"/>
-      <c r="E202" s="46"/>
-      <c r="G202" s="45"/>
-      <c r="H202" s="44"/>
-      <c r="I202" s="44"/>
-      <c r="J202" s="45"/>
-      <c r="K202" s="45"/>
-      <c r="L202" s="45"/>
-      <c r="M202" s="45"/>
-      <c r="N202" s="45"/>
+      <c r="E202" s="47"/>
+      <c r="G202" s="46"/>
+      <c r="H202" s="45"/>
+      <c r="I202" s="45"/>
+      <c r="J202" s="46"/>
+      <c r="K202" s="46"/>
+      <c r="L202" s="46"/>
+      <c r="M202" s="46"/>
+      <c r="N202" s="46"/>
     </row>
     <row r="203" spans="3:17">
-      <c r="F203" s="68" t="s">
+      <c r="F203" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="G203" s="68" t="s">
+      <c r="G203" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="H203" s="69" t="s">
+      <c r="H203" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="I203" s="69"/>
-      <c r="J203" s="69" t="s">
+      <c r="I203" s="70"/>
+      <c r="J203" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="K203" s="69"/>
-      <c r="L203" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="M203" s="68" t="s">
+      <c r="K203" s="70"/>
+      <c r="L203" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="M203" s="69" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="204" spans="3:17">
-      <c r="F204" s="58"/>
-      <c r="G204" s="58" t="s">
+      <c r="F204" s="59"/>
+      <c r="G204" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="H204" s="59" t="s">
+      <c r="H204" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="I204" s="59" t="s">
+      <c r="I204" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="J204" s="59" t="s">
+      <c r="J204" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="K204" s="59" t="s">
+      <c r="K204" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="L204" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="M204" s="58" t="s">
+      <c r="L204" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="M204" s="59" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8192,7 +8276,7 @@
       <c r="D205" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E205" s="43" t="s">
+      <c r="E205" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F205" t="s">
@@ -8223,7 +8307,7 @@
     <row r="206" spans="3:17">
       <c r="C206" s="1"/>
       <c r="D206" s="2"/>
-      <c r="E206" s="45" t="s">
+      <c r="E206" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F206" t="s">
@@ -8254,7 +8338,7 @@
     <row r="207" spans="3:17">
       <c r="C207" s="1"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="64" t="s">
+      <c r="E207" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F207" t="s">
@@ -8289,17 +8373,17 @@
     <row r="209" spans="3:17">
       <c r="C209" s="1"/>
       <c r="D209" s="2"/>
-      <c r="E209" s="67"/>
+      <c r="E209" s="68"/>
     </row>
     <row r="210" spans="3:17">
       <c r="C210" s="1"/>
       <c r="D210" s="2"/>
-      <c r="E210" s="46"/>
+      <c r="E210" s="47"/>
     </row>
     <row r="211" spans="3:17">
       <c r="C211" s="1"/>
       <c r="D211" s="2"/>
-      <c r="E211" s="46"/>
+      <c r="E211" s="47"/>
     </row>
     <row r="213" spans="3:17">
       <c r="C213" s="1" t="s">
@@ -8308,7 +8392,7 @@
       <c r="D213" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E213" s="43" t="s">
+      <c r="E213" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F213" t="s">
@@ -8317,7 +8401,7 @@
       <c r="G213" t="s">
         <v>157</v>
       </c>
-      <c r="H213" s="32" t="s">
+      <c r="H213" s="33" t="s">
         <v>163</v>
       </c>
       <c r="I213" t="s">
@@ -8339,7 +8423,7 @@
     <row r="214" spans="3:17">
       <c r="C214" s="1"/>
       <c r="D214" s="2"/>
-      <c r="E214" s="45" t="s">
+      <c r="E214" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F214" t="s">
@@ -8370,7 +8454,7 @@
     <row r="215" spans="3:17">
       <c r="C215" s="1"/>
       <c r="D215" s="2"/>
-      <c r="E215" s="64" t="s">
+      <c r="E215" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F215" t="s">
@@ -8401,7 +8485,7 @@
     <row r="216" spans="3:17">
       <c r="C216" s="1"/>
       <c r="D216" s="2"/>
-      <c r="E216" s="43" t="s">
+      <c r="E216" s="44" t="s">
         <v>166</v>
       </c>
       <c r="F216" t="s">
@@ -8432,7 +8516,7 @@
     <row r="217" spans="3:17">
       <c r="C217" s="1"/>
       <c r="D217" s="2"/>
-      <c r="E217" s="45" t="s">
+      <c r="E217" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F217" t="s">
@@ -8463,7 +8547,7 @@
     <row r="218" spans="3:17">
       <c r="C218" s="1"/>
       <c r="D218" s="2"/>
-      <c r="E218" s="64" t="s">
+      <c r="E218" s="65" t="s">
         <v>103</v>
       </c>
       <c r="F218" t="s">
@@ -8494,16 +8578,16 @@
     <row r="219" spans="3:17">
       <c r="C219" s="1"/>
       <c r="D219" s="2"/>
-      <c r="E219" s="46"/>
+      <c r="E219" s="47"/>
     </row>
     <row r="221" spans="3:17">
       <c r="C221" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D221" s="34" t="s">
+      <c r="D221" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="E221" s="43" t="s">
+      <c r="E221" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F221" t="s">
@@ -8530,15 +8614,15 @@
       <c r="M221" t="s">
         <v>32</v>
       </c>
-      <c r="N221" s="70"/>
-      <c r="O221" s="70"/>
-      <c r="P221" s="70"/>
-      <c r="Q221" s="70"/>
+      <c r="N221" s="71"/>
+      <c r="O221" s="71"/>
+      <c r="P221" s="71"/>
+      <c r="Q221" s="71"/>
     </row>
     <row r="222" spans="3:17">
       <c r="C222" s="1"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="45" t="s">
+      <c r="E222" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F222" t="s">
@@ -8565,13 +8649,13 @@
       <c r="M222" t="s">
         <v>32</v>
       </c>
-      <c r="N222" s="71"/>
-      <c r="O222" s="72"/>
+      <c r="N222" s="72"/>
+      <c r="O222" s="73"/>
     </row>
     <row r="223" spans="3:17">
       <c r="C223" s="1"/>
       <c r="D223" s="2"/>
-      <c r="E223" s="64" t="s">
+      <c r="E223" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F223" t="s">
@@ -8602,7 +8686,7 @@
     <row r="224" spans="3:17">
       <c r="C224" s="1"/>
       <c r="D224" s="2"/>
-      <c r="E224" s="43" t="s">
+      <c r="E224" s="44" t="s">
         <v>166</v>
       </c>
       <c r="F224" t="s">
@@ -8633,7 +8717,7 @@
     <row r="225" spans="3:15">
       <c r="C225" s="1"/>
       <c r="D225" s="2"/>
-      <c r="E225" s="45" t="s">
+      <c r="E225" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F225" t="s">
@@ -8660,12 +8744,12 @@
       <c r="M225" t="s">
         <v>32</v>
       </c>
-      <c r="N225" s="45"/>
+      <c r="N225" s="46"/>
     </row>
     <row r="226" spans="3:15">
       <c r="C226" s="1"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="64" t="s">
+      <c r="E226" s="65" t="s">
         <v>103</v>
       </c>
       <c r="F226" t="s">
@@ -8692,50 +8776,50 @@
       <c r="M226" t="s">
         <v>32</v>
       </c>
-      <c r="N226" s="44"/>
-      <c r="O226" s="42"/>
+      <c r="N226" s="45"/>
+      <c r="O226" s="43"/>
     </row>
     <row r="227" spans="3:15">
       <c r="C227" s="1"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="46"/>
-      <c r="G227" s="44"/>
-      <c r="H227" s="44"/>
-      <c r="I227" s="44"/>
-      <c r="J227" s="44"/>
-      <c r="K227" s="49"/>
-      <c r="L227" s="50"/>
-      <c r="M227" s="51"/>
-      <c r="N227" s="44"/>
-      <c r="O227" s="42"/>
+      <c r="E227" s="47"/>
+      <c r="G227" s="45"/>
+      <c r="H227" s="45"/>
+      <c r="I227" s="45"/>
+      <c r="J227" s="45"/>
+      <c r="K227" s="50"/>
+      <c r="L227" s="51"/>
+      <c r="M227" s="52"/>
+      <c r="N227" s="45"/>
+      <c r="O227" s="43"/>
     </row>
     <row r="228" spans="3:15">
-      <c r="E228" s="46"/>
-      <c r="G228" s="45"/>
-      <c r="H228" s="44"/>
-      <c r="I228" s="44"/>
-      <c r="J228" s="45"/>
-      <c r="K228" s="45"/>
-      <c r="L228" s="45"/>
-      <c r="M228" s="45"/>
-      <c r="N228" s="45"/>
+      <c r="E228" s="47"/>
+      <c r="G228" s="46"/>
+      <c r="H228" s="45"/>
+      <c r="I228" s="45"/>
+      <c r="J228" s="46"/>
+      <c r="K228" s="46"/>
+      <c r="L228" s="46"/>
+      <c r="M228" s="46"/>
+      <c r="N228" s="46"/>
     </row>
     <row r="229" spans="3:15">
-      <c r="E229" s="46"/>
-      <c r="G229" s="45"/>
-      <c r="H229" s="71"/>
-      <c r="I229" s="71"/>
-      <c r="J229" s="45"/>
-      <c r="K229" s="45"/>
-      <c r="L229" s="45"/>
-      <c r="M229" s="45"/>
-      <c r="N229" s="45"/>
+      <c r="E229" s="47"/>
+      <c r="G229" s="46"/>
+      <c r="H229" s="72"/>
+      <c r="I229" s="72"/>
+      <c r="J229" s="46"/>
+      <c r="K229" s="46"/>
+      <c r="L229" s="46"/>
+      <c r="M229" s="46"/>
+      <c r="N229" s="46"/>
     </row>
     <row r="230" ht="44" customHeight="1" spans="3:15">
       <c r="D230" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E230" s="43" t="s">
+      <c r="E230" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F230" t="s">
@@ -8762,11 +8846,11 @@
       <c r="M230" t="s">
         <v>32</v>
       </c>
-      <c r="O230" s="72"/>
+      <c r="O230" s="73"/>
     </row>
     <row r="231" spans="3:15">
       <c r="D231" s="2"/>
-      <c r="E231" s="45" t="s">
+      <c r="E231" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F231" t="s">
@@ -8796,7 +8880,7 @@
     </row>
     <row r="232" spans="3:15">
       <c r="D232" s="2"/>
-      <c r="E232" s="64" t="s">
+      <c r="E232" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F232" t="s">
@@ -8826,7 +8910,7 @@
     </row>
     <row r="233" spans="3:15">
       <c r="D233" s="2"/>
-      <c r="E233" s="43" t="s">
+      <c r="E233" s="44" t="s">
         <v>166</v>
       </c>
       <c r="F233" t="s">
@@ -8856,7 +8940,7 @@
     </row>
     <row r="234" spans="3:15">
       <c r="D234" s="2"/>
-      <c r="E234" s="45" t="s">
+      <c r="E234" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F234" t="s">
@@ -8883,11 +8967,11 @@
       <c r="M234" t="s">
         <v>32</v>
       </c>
-      <c r="O234" s="42"/>
+      <c r="O234" s="43"/>
     </row>
     <row r="235" spans="3:15">
       <c r="D235" s="2"/>
-      <c r="E235" s="64" t="s">
+      <c r="E235" s="65" t="s">
         <v>103</v>
       </c>
       <c r="F235" t="s">
@@ -8914,42 +8998,42 @@
       <c r="M235" t="s">
         <v>32</v>
       </c>
-      <c r="N235" s="45"/>
+      <c r="N235" s="46"/>
     </row>
     <row r="236" spans="3:15">
       <c r="D236" s="2"/>
     </row>
     <row r="242" spans="3:17">
       <c r="D242" s="3"/>
-      <c r="E242" s="45"/>
-      <c r="F242" s="38" t="s">
+      <c r="E242" s="46"/>
+      <c r="F242" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G242" s="38" t="s">
+      <c r="G242" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H242" s="39" t="s">
+      <c r="H242" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I242" s="39"/>
-      <c r="J242" s="39" t="s">
+      <c r="I242" s="40"/>
+      <c r="J242" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K242" s="39"/>
-      <c r="L242" s="38" t="s">
+      <c r="K242" s="40"/>
+      <c r="L242" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M242" s="38" t="s">
+      <c r="M242" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N242" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O242" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P242" s="38"/>
-      <c r="Q242" s="38"/>
+      <c r="N242" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O242" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P242" s="39"/>
+      <c r="Q242" s="39"/>
     </row>
     <row r="243" spans="3:17">
       <c r="C243" s="1" t="s">
@@ -8958,44 +9042,44 @@
       <c r="D243" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E243" s="43" t="s">
+      <c r="E243" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="F243" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G243" s="44" t="s">
+      <c r="F243" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G243" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H243" s="44" t="s">
+      <c r="H243" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="I243" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J243" s="44" t="s">
+      <c r="I243" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J243" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K243" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L243" s="44" t="s">
+      <c r="K243" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L243" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M243" s="44" t="s">
+      <c r="M243" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="N243" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O243" s="42" t="s">
+      <c r="N243" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O243" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="244" spans="3:17">
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
-      <c r="E244" s="45" t="s">
+      <c r="E244" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F244" t="s">
@@ -9026,7 +9110,7 @@
     <row r="245" spans="3:17">
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="64" t="s">
+      <c r="E245" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F245" t="s">
@@ -9057,56 +9141,56 @@
     <row r="246" spans="3:17">
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
-      <c r="H246" s="59"/>
-      <c r="I246" s="59"/>
-      <c r="J246" s="59"/>
-      <c r="K246" s="65"/>
-      <c r="L246" s="66"/>
-      <c r="M246" s="66"/>
-      <c r="N246" s="66"/>
-      <c r="O246" s="66"/>
+      <c r="H246" s="60"/>
+      <c r="I246" s="60"/>
+      <c r="J246" s="60"/>
+      <c r="K246" s="66"/>
+      <c r="L246" s="67"/>
+      <c r="M246" s="67"/>
+      <c r="N246" s="67"/>
+      <c r="O246" s="67"/>
     </row>
     <row r="247" spans="3:17">
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
-      <c r="E247" s="43" t="s">
+      <c r="E247" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="F247" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G247" s="44" t="s">
+      <c r="F247" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G247" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H247" s="44" t="s">
+      <c r="H247" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="I247" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J247" s="44" t="s">
+      <c r="I247" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J247" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="K247" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L247" s="44" t="s">
+      <c r="K247" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L247" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="M247" s="44" t="s">
+      <c r="M247" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="N247" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O247" s="42" t="s">
+      <c r="N247" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O247" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="248" spans="3:17">
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
-      <c r="E248" s="45" t="s">
+      <c r="E248" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F248" t="s">
@@ -9137,7 +9221,7 @@
     <row r="249" spans="3:17">
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="64" t="s">
+      <c r="E249" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F249" t="s">
@@ -9166,42 +9250,42 @@
       </c>
     </row>
     <row r="251" spans="3:17">
-      <c r="E251" s="43" t="s">
+      <c r="E251" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="F251" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G251" s="44" t="s">
+      <c r="F251" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G251" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H251" s="44" t="s">
+      <c r="H251" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="I251" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J251" s="44" t="s">
+      <c r="I251" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J251" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K251" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L251" s="44" t="s">
+      <c r="K251" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L251" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M251" s="44" t="s">
+      <c r="M251" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="N251" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O251" s="42" t="s">
+      <c r="N251" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O251" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="252" spans="3:17">
-      <c r="E252" s="45" t="s">
+      <c r="E252" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F252" t="s">
@@ -9230,7 +9314,7 @@
       </c>
     </row>
     <row r="253" spans="3:17">
-      <c r="E253" s="64" t="s">
+      <c r="E253" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F253" t="s">
@@ -9265,175 +9349,175 @@
       <c r="D255" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E255" s="43"/>
-      <c r="F255" s="44"/>
-      <c r="G255" s="44"/>
-      <c r="H255" s="44"/>
-      <c r="I255" s="44"/>
-      <c r="J255" s="44"/>
-      <c r="K255" s="44"/>
-      <c r="L255" s="44"/>
-      <c r="M255" s="44"/>
-      <c r="N255" s="44"/>
-      <c r="O255" s="42"/>
+      <c r="E255" s="44"/>
+      <c r="F255" s="45"/>
+      <c r="G255" s="45"/>
+      <c r="H255" s="45"/>
+      <c r="I255" s="45"/>
+      <c r="J255" s="45"/>
+      <c r="K255" s="45"/>
+      <c r="L255" s="45"/>
+      <c r="M255" s="45"/>
+      <c r="N255" s="45"/>
+      <c r="O255" s="43"/>
     </row>
     <row r="256" spans="3:17">
       <c r="C256" s="1"/>
       <c r="D256" s="2"/>
-      <c r="E256" s="45"/>
+      <c r="E256" s="46"/>
     </row>
     <row r="257" spans="3:17">
       <c r="C257" s="1"/>
       <c r="D257" s="2"/>
-      <c r="E257" s="45"/>
-      <c r="F257" s="38" t="s">
+      <c r="E257" s="46"/>
+      <c r="F257" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G257" s="38" t="s">
+      <c r="G257" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H257" s="39" t="s">
+      <c r="H257" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I257" s="39"/>
-      <c r="J257" s="39" t="s">
+      <c r="I257" s="40"/>
+      <c r="J257" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K257" s="39"/>
-      <c r="L257" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M257" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N257" s="38"/>
-      <c r="O257" s="38"/>
-      <c r="P257" s="38"/>
-      <c r="Q257" s="38"/>
+      <c r="K257" s="40"/>
+      <c r="L257" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M257" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N257" s="39"/>
+      <c r="O257" s="39"/>
+      <c r="P257" s="39"/>
+      <c r="Q257" s="39"/>
     </row>
     <row r="258" spans="3:17">
       <c r="C258" s="1"/>
       <c r="D258" s="2"/>
-      <c r="E258" s="46" t="s">
+      <c r="E258" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F258" t="s">
         <v>39</v>
       </c>
-      <c r="G258" s="45" t="s">
+      <c r="G258" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H258" s="44" t="s">
+      <c r="H258" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="I258" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J258" s="44" t="s">
+      <c r="I258" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J258" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K258" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L258" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M258" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N258" s="45"/>
+      <c r="K258" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L258" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M258" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N258" s="46"/>
     </row>
     <row r="259" spans="3:17">
       <c r="C259" s="1"/>
       <c r="D259" s="2"/>
-      <c r="E259" s="46"/>
-      <c r="F259" s="47" t="s">
+      <c r="E259" s="47"/>
+      <c r="F259" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G259" s="47" t="s">
+      <c r="G259" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H259" s="47" t="s">
+      <c r="H259" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I259" s="47" t="s">
+      <c r="I259" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J259" s="47" t="s">
+      <c r="J259" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K259" s="48" t="s">
+      <c r="K259" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L259" s="48"/>
-      <c r="M259" s="47"/>
-      <c r="N259" s="44"/>
-      <c r="O259" s="42"/>
+      <c r="L259" s="49"/>
+      <c r="M259" s="48"/>
+      <c r="N259" s="45"/>
+      <c r="O259" s="43"/>
     </row>
     <row r="260" spans="3:17">
       <c r="C260" s="1"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="46" t="s">
+      <c r="E260" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F260" t="s">
         <v>39</v>
       </c>
-      <c r="G260" s="44" t="s">
+      <c r="G260" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H260" s="44" t="s">
+      <c r="H260" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I260" s="44" t="s">
+      <c r="I260" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="J260" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K260" s="55" t="s">
+      <c r="J260" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K260" s="56" t="s">
         <v>190</v>
       </c>
-      <c r="L260" s="50"/>
-      <c r="M260" s="51"/>
-      <c r="N260" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O260" s="42" t="s">
+      <c r="L260" s="51"/>
+      <c r="M260" s="52"/>
+      <c r="N260" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O260" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="261" spans="3:17">
       <c r="C261" s="1"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="46" t="s">
+      <c r="E261" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F261" t="s">
         <v>39</v>
       </c>
-      <c r="G261" s="45" t="s">
+      <c r="G261" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H261" s="44" t="s">
+      <c r="H261" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="I261" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J261" s="45" t="s">
+      <c r="I261" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J261" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K261" s="45" t="s">
+      <c r="K261" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L261" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M261" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N261" s="45"/>
+      <c r="L261" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M261" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N261" s="46"/>
     </row>
     <row r="262" spans="3:17">
       <c r="D262" s="2"/>
@@ -9659,7 +9743,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="27.625" customWidth="1"/>
@@ -10521,125 +10605,366 @@
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:8">
-      <c r="F52" s="3"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" t="s">
+      <c r="A52">
+        <v>130</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="55" ht="16" customHeight="1" spans="1:8">
+      <c r="D52" t="s">
+        <v>283</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:8">
+      <c r="A53">
+        <f>A52+B52</f>
+        <v>138</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D53" t="s">
+        <v>286</v>
+      </c>
+      <c r="E53" t="s">
+        <v>287</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:8">
+      <c r="F54" s="3"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="1:8">
       <c r="A55">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>179</v>
+        <v>282</v>
+      </c>
+      <c r="D55" t="s">
+        <v>289</v>
       </c>
       <c r="E55" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G55" t="s">
-        <v>284</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:8">
       <c r="A56">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>197</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>286</v>
+        <v>202</v>
+      </c>
+      <c r="D56" t="s">
+        <v>292</v>
       </c>
       <c r="E56" t="s">
-        <v>286</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G56" t="s">
-        <v>284</v>
-      </c>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" ht="105" customHeight="1" spans="1:8">
+        <v>293</v>
+      </c>
+      <c r="F56" s="3"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:8">
       <c r="A57">
         <f>A56+B56</f>
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D57" t="s">
-        <v>289</v>
-      </c>
-      <c r="E57" t="s">
-        <v>290</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G57" t="s">
-        <v>292</v>
-      </c>
-      <c r="H57" s="1"/>
-    </row>
-    <row r="58" spans="1:8">
+        <v>295</v>
+      </c>
+      <c r="F57" s="3"/>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="1:8">
       <c r="A58">
         <f>A57+B57</f>
+        <v>158</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>296</v>
+      </c>
+      <c r="D58" t="s">
+        <v>297</v>
+      </c>
+      <c r="F58" s="3"/>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="1:8">
+      <c r="A59">
+        <f>A58+B58</f>
+        <v>160</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>298</v>
+      </c>
+      <c r="D59" t="s">
+        <v>299</v>
+      </c>
+      <c r="F59" s="3"/>
+    </row>
+    <row r="60" ht="18" customHeight="1" spans="1:8">
+      <c r="A60">
+        <f>A59+B59</f>
+        <v>162</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" t="s">
+        <v>301</v>
+      </c>
+      <c r="F60" s="3"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:8">
+      <c r="A61">
+        <f>A60+B60</f>
+        <v>164</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>302</v>
+      </c>
+      <c r="D61" t="s">
+        <v>303</v>
+      </c>
+      <c r="F61" s="3"/>
+    </row>
+    <row r="62" ht="35" customHeight="1" spans="1:8">
+      <c r="A62">
+        <f>A61+B61</f>
+        <v>166</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>304</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F62" s="3"/>
+    </row>
+    <row r="63" ht="18" customHeight="1" spans="1:8">
+      <c r="F63" s="3"/>
+    </row>
+    <row r="64" ht="18" customHeight="1" spans="1:8">
+      <c r="F64" s="3"/>
+    </row>
+    <row r="65" ht="18" customHeight="1" spans="1:8">
+      <c r="A65">
+        <v>170</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>269</v>
+      </c>
+      <c r="E65" t="s">
+        <v>306</v>
+      </c>
+      <c r="F65" s="3"/>
+    </row>
+    <row r="66" ht="18" customHeight="1" spans="1:8">
+      <c r="F66" s="3"/>
+    </row>
+    <row r="67" ht="18" customHeight="1" spans="1:8">
+      <c r="A67">
+        <v>174</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>269</v>
+      </c>
+      <c r="E67" t="s">
+        <v>307</v>
+      </c>
+      <c r="F67" s="3"/>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:8">
+      <c r="F68" s="3"/>
+    </row>
+    <row r="69" ht="18" customHeight="1" spans="1:8">
+      <c r="A69">
+        <v>180</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>282</v>
+      </c>
+      <c r="E69" t="s">
+        <v>308</v>
+      </c>
+      <c r="F69" s="3"/>
+    </row>
+    <row r="70" ht="18" customHeight="1" spans="1:8">
+      <c r="F70" s="3"/>
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:8">
+      <c r="F71" s="3"/>
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:8">
+      <c r="F72" s="3"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1" spans="1:8">
+      <c r="A75">
+        <v>200</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>197</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E75" t="s">
+        <v>179</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G75" t="s">
+        <v>311</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>202</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="E76" t="s">
+        <v>313</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G76" t="s">
+        <v>311</v>
+      </c>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" ht="105" customHeight="1" spans="1:8">
+      <c r="A77">
+        <f>A76+B76</f>
+        <v>204</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>315</v>
+      </c>
+      <c r="D77" t="s">
+        <v>316</v>
+      </c>
+      <c r="E77" t="s">
+        <v>317</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G77" t="s">
+        <v>319</v>
+      </c>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <f>A77+B77</f>
         <v>208</v>
       </c>
-      <c r="B58" t="s">
-        <v>293</v>
-      </c>
-      <c r="C58" t="s">
-        <v>294</v>
-      </c>
-      <c r="D58" t="s">
-        <v>295</v>
-      </c>
-      <c r="E58" t="s">
-        <v>295</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G58" t="s">
-        <v>284</v>
-      </c>
-      <c r="H58" s="1"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="H61" s="1"/>
+      <c r="B78" t="s">
+        <v>320</v>
+      </c>
+      <c r="C78" t="s">
+        <v>321</v>
+      </c>
+      <c r="D78" t="s">
+        <v>322</v>
+      </c>
+      <c r="E78" t="s">
+        <v>322</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G78" t="s">
+        <v>311</v>
+      </c>
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="8:8">
+      <c r="H81" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H55:H61"/>
+    <mergeCell ref="H75:H81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10655,7 +10980,7 @@
   <sheetData>
     <row r="1" spans="2:17">
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>

--- a/辐射报警仪协议命令和寄存器表10.xlsx
+++ b/辐射报警仪协议命令和寄存器表10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20355" windowHeight="9525" activeTab="1"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="具体命令" sheetId="1" r:id="rId1"/>
@@ -2062,7 +2062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2080,9 +2080,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2836,243 +2833,243 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
       <c r="Y4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="3:26">
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="10" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="10"/>
+      <c r="Z5" s="9"/>
     </row>
     <row r="6" spans="3:26">
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="12"/>
+      <c r="H6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="16" t="s">
+      <c r="I6" s="14"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12" t="s">
+      <c r="S6" s="11"/>
+      <c r="T6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12" t="s">
+      <c r="U6" s="11"/>
+      <c r="V6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="W6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="X6" s="12" t="s">
+      <c r="X6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="3:26">
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="19" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="20" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="20" t="s">
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="19" t="s">
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="R7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="19" t="s">
+      <c r="S7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="T7" s="19" t="s">
+      <c r="T7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="U7" s="19" t="s">
+      <c r="U7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="19" t="s">
+      <c r="V7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="19" t="s">
+      <c r="W7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
+      <c r="X7" s="18"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="3:26">
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
     </row>
     <row r="9" spans="3:26">
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
     </row>
     <row r="10" spans="3:26">
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
     </row>
     <row r="12" spans="3:26">
       <c r="E12" s="3"/>
@@ -3197,7 +3194,7 @@
       <c r="H18" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="31" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="1"/>
@@ -3431,18 +3428,18 @@
       <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="31" t="s">
         <v>66</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="32" t="s">
         <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
@@ -3477,13 +3474,13 @@
       <c r="H25" t="s">
         <v>47</v>
       </c>
-      <c r="I25" s="34" t="s">
+      <c r="I25" s="33" t="s">
         <v>69</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
       </c>
-      <c r="M25" s="35" t="s">
+      <c r="M25" s="34" t="s">
         <v>70</v>
       </c>
       <c r="P25" s="1"/>
@@ -3508,13 +3505,13 @@
       <c r="H26" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="34" t="s">
+      <c r="I26" s="33" t="s">
         <v>72</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="36" t="s">
+      <c r="M26" s="35" t="s">
         <v>17</v>
       </c>
       <c r="P26" s="1"/>
@@ -3539,13 +3536,13 @@
       <c r="H27" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="33" t="s">
         <v>73</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="36" t="s">
+      <c r="M27" s="35" t="s">
         <v>17</v>
       </c>
       <c r="P27" s="1"/>
@@ -3570,13 +3567,13 @@
       <c r="H28" t="s">
         <v>47</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="33" t="s">
         <v>74</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
       </c>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>17</v>
       </c>
       <c r="N28" s="1"/>
@@ -3614,7 +3611,7 @@
       <c r="L29" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="35" t="s">
+      <c r="M29" s="34" t="s">
         <v>77</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -3660,13 +3657,13 @@
       <c r="F32" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" s="32" t="s">
         <v>46</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I32" s="37" t="s">
+      <c r="I32" s="36" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="1"/>
@@ -3688,59 +3685,59 @@
       </c>
     </row>
     <row r="36" spans="3:17">
-      <c r="E36" s="38"/>
-      <c r="F36" s="39" t="s">
+      <c r="E36" s="37"/>
+      <c r="F36" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="40" t="s">
+      <c r="H36" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40" t="s">
+      <c r="I36" s="39"/>
+      <c r="J36" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K36" s="40"/>
-      <c r="L36" s="39" t="s">
+      <c r="K36" s="39"/>
+      <c r="L36" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="39" t="s">
+      <c r="M36" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N36" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
+      <c r="N36" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
     </row>
     <row r="37" spans="3:17">
-      <c r="F37" s="41"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42" t="s">
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="42" t="s">
+      <c r="I37" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="42" t="s">
+      <c r="J37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="42" t="s">
+      <c r="K37" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42" t="s">
+      <c r="L37" s="41"/>
+      <c r="M37" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="43"/>
+      <c r="N37" s="42"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="1" t="s">
@@ -3749,46 +3746,46 @@
       <c r="D38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E38" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="45" t="s">
+      <c r="F38" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G38" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="I38" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J38" s="45" t="s">
+      <c r="I38" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K38" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L38" s="45" t="s">
+      <c r="K38" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M38" s="45" t="s">
+      <c r="M38" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" s="43"/>
-      <c r="Q38" s="43"/>
+      <c r="N38" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
     </row>
     <row r="39" spans="3:17">
       <c r="C39" s="1"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="46" t="s">
+      <c r="E39" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F39" t="s">
@@ -3819,7 +3816,7 @@
     <row r="40" spans="3:17">
       <c r="C40" s="1"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="46" t="s">
+      <c r="E40" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F40" t="s">
@@ -3850,187 +3847,187 @@
     <row r="41" spans="3:17">
       <c r="C41" s="1"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="39" t="s">
+      <c r="E41" s="46"/>
+      <c r="F41" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="40" t="s">
+      <c r="H41" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40" t="s">
+      <c r="I41" s="39"/>
+      <c r="J41" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K41" s="40"/>
-      <c r="L41" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="38"/>
+      <c r="Q41" s="38"/>
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="1"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="47" t="s">
+      <c r="E42" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="46" t="s">
+      <c r="G42" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="H42" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="I42" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42" s="45" t="s">
+      <c r="I42" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K42" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M42" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N42" s="46"/>
+      <c r="K42" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L42" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="45"/>
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="1"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48" t="s">
+      <c r="E43" s="46"/>
+      <c r="F43" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="48" t="s">
+      <c r="G43" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="48" t="s">
+      <c r="H43" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I43" s="48" t="s">
+      <c r="I43" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J43" s="48" t="s">
+      <c r="J43" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K43" s="49" t="s">
+      <c r="K43" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L43" s="49"/>
-      <c r="M43" s="48"/>
+      <c r="L43" s="48"/>
+      <c r="M43" s="47"/>
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="1"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="47" t="s">
+      <c r="E44" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H44" s="45" t="s">
+      <c r="H44" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I44" s="45" t="s">
+      <c r="I44" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="J44" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K44" s="50" t="s">
+      <c r="J44" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="L44" s="51"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O44" s="43" t="s">
+      <c r="L44" s="50"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="1"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="47" t="s">
+      <c r="E45" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
-      <c r="G45" s="46" t="s">
+      <c r="G45" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="H45" s="45" t="s">
+      <c r="H45" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="I45" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" s="46" t="s">
+      <c r="I45" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K45" s="46" t="s">
+      <c r="K45" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L45" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M45" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N45" s="46"/>
+      <c r="L45" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="45"/>
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="1"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="3:17">
-      <c r="F47" s="39" t="s">
+      <c r="F47" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="40" t="s">
+      <c r="H47" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40" t="s">
+      <c r="I47" s="39"/>
+      <c r="J47" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K47" s="40"/>
-      <c r="L47" s="39" t="s">
+      <c r="K47" s="39"/>
+      <c r="L47" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M47" s="39" t="s">
+      <c r="M47" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N47" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
+      <c r="N47" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" s="38"/>
+      <c r="Q47" s="38"/>
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="1" t="s">
@@ -4039,46 +4036,46 @@
       <c r="D48" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="44" t="s">
+      <c r="E48" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F48" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" s="45" t="s">
+      <c r="F48" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H48" s="45" t="s">
+      <c r="H48" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I48" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" s="45" t="s">
+      <c r="I48" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K48" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L48" s="45" t="s">
+      <c r="K48" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L48" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M48" s="45" t="s">
+      <c r="M48" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="N48" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="45"/>
-      <c r="Q48" s="45"/>
+      <c r="N48" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
     </row>
     <row r="49" spans="3:17">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="46" t="s">
+      <c r="E49" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F49" t="s">
@@ -4109,7 +4106,7 @@
     <row r="50" spans="3:17">
       <c r="C50" s="1"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="46" t="s">
+      <c r="E50" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F50" t="s">
@@ -4140,184 +4137,184 @@
     <row r="51" spans="3:17">
       <c r="C51" s="1"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="39" t="s">
+      <c r="E51" s="46"/>
+      <c r="F51" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="39" t="s">
+      <c r="G51" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H51" s="40" t="s">
+      <c r="H51" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40" t="s">
+      <c r="I51" s="39"/>
+      <c r="J51" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K51" s="40"/>
-      <c r="L51" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M51" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" s="39"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M51" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="38"/>
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="1"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="47" t="s">
+      <c r="E52" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="46" t="s">
+      <c r="G52" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="45" t="s">
+      <c r="H52" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I52" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J52" s="45" t="s">
+      <c r="I52" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K52" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L52" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M52" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" s="46"/>
+      <c r="K52" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L52" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="45"/>
     </row>
     <row r="53" spans="3:17">
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="48" t="s">
+      <c r="E53" s="46"/>
+      <c r="F53" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="48" t="s">
+      <c r="G53" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H53" s="48" t="s">
+      <c r="H53" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I53" s="48" t="s">
+      <c r="I53" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J53" s="48" t="s">
+      <c r="J53" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K53" s="49" t="s">
+      <c r="K53" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L53" s="49"/>
-      <c r="M53" s="48"/>
+      <c r="L53" s="48"/>
+      <c r="M53" s="47"/>
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="1"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="47" t="s">
+      <c r="E54" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="45" t="s">
+      <c r="G54" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H54" s="45" t="s">
+      <c r="H54" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I54" s="45" t="s">
+      <c r="I54" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="J54" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K54" s="50" t="s">
+      <c r="J54" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="L54" s="51"/>
-      <c r="M54" s="52"/>
-      <c r="N54" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" s="43" t="s">
+      <c r="L54" s="50"/>
+      <c r="M54" s="51"/>
+      <c r="N54" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="1"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="47" t="s">
+      <c r="E55" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="46" t="s">
+      <c r="G55" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H55" s="45" t="s">
+      <c r="H55" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I55" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J55" s="46" t="s">
+      <c r="I55" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K55" s="46" t="s">
+      <c r="K55" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L55" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M55" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N55" s="46"/>
+      <c r="L55" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="45"/>
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="1"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="3:17">
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="40" t="s">
+      <c r="H57" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40" t="s">
+      <c r="I57" s="39"/>
+      <c r="J57" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K57" s="40"/>
-      <c r="L57" s="39" t="s">
+      <c r="K57" s="39"/>
+      <c r="L57" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M57" s="39" t="s">
+      <c r="M57" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N57" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O57" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" s="39"/>
-      <c r="Q57" s="39"/>
+      <c r="N57" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="1" t="s">
@@ -4326,44 +4323,44 @@
       <c r="D58" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E58" s="44" t="s">
+      <c r="E58" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F58" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="45" t="s">
+      <c r="F58" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="45" t="s">
+      <c r="H58" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="I58" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J58" s="45" t="s">
+      <c r="I58" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K58" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="45" t="s">
+      <c r="K58" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L58" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M58" s="45" t="s">
+      <c r="M58" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="N58" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O58" s="43" t="s">
+      <c r="N58" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O58" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="1"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="46" t="s">
+      <c r="E59" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F59" t="s">
@@ -4394,7 +4391,7 @@
     <row r="60" spans="3:17">
       <c r="C60" s="1"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="46" t="s">
+      <c r="E60" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F60" t="s">
@@ -4425,184 +4422,184 @@
     <row r="61" spans="3:17">
       <c r="C61" s="1"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="39" t="s">
+      <c r="E61" s="46"/>
+      <c r="F61" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="39" t="s">
+      <c r="G61" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H61" s="40" t="s">
+      <c r="H61" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40" t="s">
+      <c r="I61" s="39"/>
+      <c r="J61" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K61" s="40"/>
-      <c r="L61" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M61" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="39"/>
+      <c r="K61" s="39"/>
+      <c r="L61" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M61" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="38"/>
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="1"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="47" t="s">
+      <c r="E62" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
       </c>
-      <c r="G62" s="46" t="s">
+      <c r="G62" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="45" t="s">
+      <c r="H62" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="I62" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J62" s="45" t="s">
+      <c r="I62" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K62" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L62" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M62" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="46"/>
+      <c r="K62" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L62" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M62" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="45"/>
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="1"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="48" t="s">
+      <c r="E63" s="46"/>
+      <c r="F63" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G63" s="48" t="s">
+      <c r="G63" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="48" t="s">
+      <c r="H63" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="48" t="s">
+      <c r="I63" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J63" s="48" t="s">
+      <c r="J63" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K63" s="49" t="s">
+      <c r="K63" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L63" s="49"/>
-      <c r="M63" s="48"/>
+      <c r="L63" s="48"/>
+      <c r="M63" s="47"/>
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="1"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="47" t="s">
+      <c r="E64" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
       </c>
-      <c r="G64" s="45" t="s">
+      <c r="G64" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H64" s="45" t="s">
+      <c r="H64" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I64" s="45" t="s">
+      <c r="I64" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="J64" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" s="50" t="s">
+      <c r="J64" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="L64" s="51"/>
-      <c r="M64" s="52"/>
-      <c r="N64" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="43" t="s">
+      <c r="L64" s="50"/>
+      <c r="M64" s="51"/>
+      <c r="N64" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O64" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="65" spans="3:17">
       <c r="C65" s="1"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="47" t="s">
+      <c r="E65" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F65" t="s">
         <v>39</v>
       </c>
-      <c r="G65" s="46" t="s">
+      <c r="G65" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H65" s="45" t="s">
+      <c r="H65" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="I65" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65" s="46" t="s">
+      <c r="I65" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K65" s="46" t="s">
+      <c r="K65" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L65" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M65" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N65" s="46"/>
+      <c r="L65" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M65" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="45"/>
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="1"/>
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="3:17">
-      <c r="F67" s="39" t="s">
+      <c r="F67" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G67" s="39" t="s">
+      <c r="G67" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H67" s="40" t="s">
+      <c r="H67" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I67" s="40"/>
-      <c r="J67" s="40" t="s">
+      <c r="I67" s="39"/>
+      <c r="J67" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K67" s="40"/>
-      <c r="L67" s="39" t="s">
+      <c r="K67" s="39"/>
+      <c r="L67" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M67" s="39" t="s">
+      <c r="M67" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N67" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O67" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P67" s="39"/>
-      <c r="Q67" s="39"/>
+      <c r="N67" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O67" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="38"/>
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="1" t="s">
@@ -4611,44 +4608,44 @@
       <c r="D68" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="44" t="s">
+      <c r="E68" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F68" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="45" t="s">
+      <c r="F68" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H68" s="45" t="s">
+      <c r="H68" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J68" s="45" t="s">
+      <c r="I68" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K68" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L68" s="45" t="s">
+      <c r="K68" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L68" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M68" s="45" t="s">
+      <c r="M68" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="N68" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O68" s="43" t="s">
+      <c r="N68" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="1"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="46" t="s">
+      <c r="E69" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F69" t="s">
@@ -4679,7 +4676,7 @@
     <row r="70" spans="3:17">
       <c r="C70" s="1"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="46" t="s">
+      <c r="E70" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F70" t="s">
@@ -4710,184 +4707,184 @@
     <row r="71" spans="3:17">
       <c r="C71" s="1"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="39" t="s">
+      <c r="E71" s="46"/>
+      <c r="F71" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G71" s="39" t="s">
+      <c r="G71" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H71" s="40" t="s">
+      <c r="H71" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40" t="s">
+      <c r="I71" s="39"/>
+      <c r="J71" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K71" s="40"/>
-      <c r="L71" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M71" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N71" s="39"/>
+      <c r="K71" s="39"/>
+      <c r="L71" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M71" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="38"/>
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="1"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="47" t="s">
+      <c r="E72" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F72" t="s">
         <v>39</v>
       </c>
-      <c r="G72" s="46" t="s">
+      <c r="G72" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="45" t="s">
+      <c r="H72" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I72" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J72" s="45" t="s">
+      <c r="I72" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K72" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L72" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M72" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N72" s="46"/>
+      <c r="K72" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="45"/>
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="48" t="s">
+      <c r="E73" s="46"/>
+      <c r="F73" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G73" s="48" t="s">
+      <c r="G73" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H73" s="48" t="s">
+      <c r="H73" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I73" s="48" t="s">
+      <c r="I73" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J73" s="48" t="s">
+      <c r="J73" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K73" s="49" t="s">
+      <c r="K73" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L73" s="49"/>
-      <c r="M73" s="48"/>
+      <c r="L73" s="48"/>
+      <c r="M73" s="47"/>
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="1"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="47" t="s">
+      <c r="E74" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="45" t="s">
+      <c r="G74" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H74" s="45" t="s">
+      <c r="H74" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I74" s="45" t="s">
+      <c r="I74" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="J74" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K74" s="50" t="s">
+      <c r="J74" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="L74" s="51"/>
-      <c r="M74" s="52"/>
-      <c r="N74" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O74" s="43" t="s">
+      <c r="L74" s="50"/>
+      <c r="M74" s="51"/>
+      <c r="N74" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O74" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="1"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="47" t="s">
+      <c r="E75" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F75" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="46" t="s">
+      <c r="G75" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H75" s="45" t="s">
+      <c r="H75" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I75" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J75" s="46" t="s">
+      <c r="I75" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J75" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K75" s="46" t="s">
+      <c r="K75" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L75" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M75" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N75" s="46"/>
+      <c r="L75" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M75" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75" s="45"/>
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="1"/>
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="3:17">
-      <c r="F77" s="39" t="s">
+      <c r="F77" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="39" t="s">
+      <c r="G77" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H77" s="40" t="s">
+      <c r="H77" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I77" s="40"/>
-      <c r="J77" s="40" t="s">
+      <c r="I77" s="39"/>
+      <c r="J77" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K77" s="40"/>
-      <c r="L77" s="39" t="s">
+      <c r="K77" s="39"/>
+      <c r="L77" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M77" s="39" t="s">
+      <c r="M77" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N77" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O77" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P77" s="39"/>
-      <c r="Q77" s="39"/>
+      <c r="N77" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P77" s="38"/>
+      <c r="Q77" s="38"/>
     </row>
     <row r="78" spans="3:17">
       <c r="C78" s="1" t="s">
@@ -4896,44 +4893,44 @@
       <c r="D78" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="44" t="s">
+      <c r="E78" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="45" t="s">
+      <c r="F78" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H78" s="45" t="s">
+      <c r="H78" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="I78" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="45" t="s">
+      <c r="I78" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K78" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L78" s="45" t="s">
+      <c r="K78" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L78" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M78" s="53" t="s">
+      <c r="M78" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="N78" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O78" s="43" t="s">
+      <c r="N78" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="1"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="46" t="s">
+      <c r="E79" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F79" t="s">
@@ -4964,7 +4961,7 @@
     <row r="80" spans="3:17">
       <c r="C80" s="1"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="46" t="s">
+      <c r="E80" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F80" t="s">
@@ -4995,184 +4992,184 @@
     <row r="81" spans="3:17">
       <c r="C81" s="1"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="39" t="s">
+      <c r="E81" s="46"/>
+      <c r="F81" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G81" s="39" t="s">
+      <c r="G81" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H81" s="40" t="s">
+      <c r="H81" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I81" s="40"/>
-      <c r="J81" s="40" t="s">
+      <c r="I81" s="39"/>
+      <c r="J81" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K81" s="40"/>
-      <c r="L81" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M81" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N81" s="39"/>
+      <c r="K81" s="39"/>
+      <c r="L81" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M81" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81" s="38"/>
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="1"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="47" t="s">
+      <c r="E82" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F82" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="46" t="s">
+      <c r="G82" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="45" t="s">
+      <c r="H82" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="I82" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J82" s="45" t="s">
+      <c r="I82" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K82" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L82" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M82" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N82" s="46"/>
+      <c r="K82" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L82" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M82" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N82" s="45"/>
     </row>
     <row r="83" spans="3:17">
       <c r="C83" s="1"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="48" t="s">
+      <c r="E83" s="46"/>
+      <c r="F83" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G83" s="48" t="s">
+      <c r="G83" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H83" s="48" t="s">
+      <c r="H83" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I83" s="48" t="s">
+      <c r="I83" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J83" s="48" t="s">
+      <c r="J83" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K83" s="49" t="s">
+      <c r="K83" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L83" s="49"/>
-      <c r="M83" s="48"/>
+      <c r="L83" s="48"/>
+      <c r="M83" s="47"/>
     </row>
     <row r="84" spans="3:17">
       <c r="C84" s="1"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="47" t="s">
+      <c r="E84" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F84" t="s">
         <v>39</v>
       </c>
-      <c r="G84" s="45" t="s">
+      <c r="G84" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H84" s="45" t="s">
+      <c r="H84" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I84" s="45" t="s">
+      <c r="I84" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="50" t="s">
+      <c r="J84" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="L84" s="51"/>
-      <c r="M84" s="52"/>
-      <c r="N84" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O84" s="43" t="s">
+      <c r="L84" s="50"/>
+      <c r="M84" s="51"/>
+      <c r="N84" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O84" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="1"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="47" t="s">
+      <c r="E85" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>39</v>
       </c>
-      <c r="G85" s="46" t="s">
+      <c r="G85" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H85" s="45" t="s">
+      <c r="H85" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="I85" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" s="46" t="s">
+      <c r="I85" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K85" s="46" t="s">
+      <c r="K85" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L85" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M85" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N85" s="46"/>
+      <c r="L85" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M85" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="45"/>
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
     </row>
     <row r="87" spans="3:17">
-      <c r="F87" s="39" t="s">
+      <c r="F87" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G87" s="39" t="s">
+      <c r="G87" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H87" s="40" t="s">
+      <c r="H87" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I87" s="40"/>
-      <c r="J87" s="40" t="s">
+      <c r="I87" s="39"/>
+      <c r="J87" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K87" s="40"/>
-      <c r="L87" s="39" t="s">
+      <c r="K87" s="39"/>
+      <c r="L87" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M87" s="39" t="s">
+      <c r="M87" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N87" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O87" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P87" s="39"/>
-      <c r="Q87" s="39"/>
+      <c r="N87" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O87" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P87" s="38"/>
+      <c r="Q87" s="38"/>
     </row>
     <row r="88" spans="3:17">
       <c r="C88" s="1" t="s">
@@ -5181,44 +5178,44 @@
       <c r="D88" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E88" s="44" t="s">
+      <c r="E88" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F88" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G88" s="45" t="s">
+      <c r="F88" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G88" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="45" t="s">
+      <c r="H88" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I88" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J88" s="45" t="s">
+      <c r="I88" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K88" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L88" s="45" t="s">
+      <c r="K88" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L88" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M88" s="53" t="s">
+      <c r="M88" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="N88" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O88" s="43" t="s">
+      <c r="N88" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="89" spans="3:17">
       <c r="C89" s="1"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="46" t="s">
+      <c r="E89" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F89" t="s">
@@ -5249,7 +5246,7 @@
     <row r="90" spans="3:17">
       <c r="C90" s="1"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="46" t="s">
+      <c r="E90" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F90" t="s">
@@ -5280,158 +5277,158 @@
     <row r="91" spans="3:17">
       <c r="C91" s="1"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="47" t="s">
+      <c r="E91" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F91" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="46" t="s">
+      <c r="G91" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="45" t="s">
+      <c r="H91" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I91" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J91" s="45" t="s">
+      <c r="I91" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J91" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K91" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L91" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M91" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N91" s="46"/>
+      <c r="K91" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L91" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M91" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N91" s="45"/>
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="48" t="s">
+      <c r="E92" s="46"/>
+      <c r="F92" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="48" t="s">
+      <c r="G92" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H92" s="48" t="s">
+      <c r="H92" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I92" s="48" t="s">
+      <c r="I92" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J92" s="48" t="s">
+      <c r="J92" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K92" s="49" t="s">
+      <c r="K92" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L92" s="49"/>
-      <c r="M92" s="48"/>
+      <c r="L92" s="48"/>
+      <c r="M92" s="47"/>
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="1"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="47" t="s">
+      <c r="E93" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F93" t="s">
         <v>39</v>
       </c>
-      <c r="G93" s="45" t="s">
+      <c r="G93" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H93" s="45" t="s">
+      <c r="H93" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I93" s="45" t="s">
+      <c r="I93" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="J93" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" s="50" t="s">
+      <c r="J93" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K93" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="L93" s="51"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O93" s="43" t="s">
+      <c r="L93" s="50"/>
+      <c r="M93" s="51"/>
+      <c r="N93" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O93" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="1"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="47" t="s">
+      <c r="E94" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F94" t="s">
         <v>39</v>
       </c>
-      <c r="G94" s="46" t="s">
+      <c r="G94" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H94" s="45" t="s">
+      <c r="H94" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I94" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J94" s="46" t="s">
+      <c r="I94" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K94" s="46" t="s">
+      <c r="K94" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L94" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M94" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N94" s="46"/>
+      <c r="L94" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M94" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94" s="45"/>
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="1"/>
       <c r="D95" s="2"/>
     </row>
     <row r="96" spans="3:17">
-      <c r="F96" s="39" t="s">
+      <c r="F96" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G96" s="39" t="s">
+      <c r="G96" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H96" s="40" t="s">
+      <c r="H96" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40" t="s">
+      <c r="I96" s="39"/>
+      <c r="J96" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K96" s="40"/>
-      <c r="L96" s="39" t="s">
+      <c r="K96" s="39"/>
+      <c r="L96" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M96" s="39" t="s">
+      <c r="M96" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N96" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O96" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P96" s="39"/>
-      <c r="Q96" s="39"/>
+      <c r="N96" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O96" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" s="38"/>
+      <c r="Q96" s="38"/>
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="1" t="s">
@@ -5440,44 +5437,44 @@
       <c r="D97" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E97" s="44" t="s">
+      <c r="E97" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F97" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="45" t="s">
+      <c r="F97" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H97" s="45" t="s">
+      <c r="H97" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I97" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J97" s="45" t="s">
+      <c r="I97" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K97" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L97" s="45" t="s">
+      <c r="K97" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L97" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M97" s="45" t="s">
+      <c r="M97" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="N97" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O97" s="43" t="s">
+      <c r="N97" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O97" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="98" spans="3:17">
       <c r="C98" s="1"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="46" t="s">
+      <c r="E98" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F98" t="s">
@@ -5508,7 +5505,7 @@
     <row r="99" spans="3:17">
       <c r="C99" s="1"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="46" t="s">
+      <c r="E99" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F99" t="s">
@@ -5539,158 +5536,158 @@
     <row r="100" spans="3:17">
       <c r="C100" s="1"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="47" t="s">
+      <c r="E100" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F100" t="s">
         <v>39</v>
       </c>
-      <c r="G100" s="46" t="s">
+      <c r="G100" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="45" t="s">
+      <c r="H100" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I100" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J100" s="45" t="s">
+      <c r="I100" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J100" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K100" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L100" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M100" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N100" s="46"/>
+      <c r="K100" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L100" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N100" s="45"/>
     </row>
     <row r="101" spans="3:17">
       <c r="C101" s="1"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="48" t="s">
+      <c r="E101" s="46"/>
+      <c r="F101" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="48" t="s">
+      <c r="G101" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H101" s="48" t="s">
+      <c r="H101" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I101" s="48" t="s">
+      <c r="I101" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J101" s="48" t="s">
+      <c r="J101" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K101" s="49" t="s">
+      <c r="K101" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L101" s="49"/>
-      <c r="M101" s="48"/>
+      <c r="L101" s="48"/>
+      <c r="M101" s="47"/>
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="1"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="47" t="s">
+      <c r="E102" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F102" t="s">
         <v>39</v>
       </c>
-      <c r="G102" s="45" t="s">
+      <c r="G102" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H102" s="45" t="s">
+      <c r="H102" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I102" s="45" t="s">
+      <c r="I102" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="J102" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="50" t="s">
+      <c r="J102" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="L102" s="51"/>
-      <c r="M102" s="52"/>
-      <c r="N102" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O102" s="43" t="s">
+      <c r="L102" s="50"/>
+      <c r="M102" s="51"/>
+      <c r="N102" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O102" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="1"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="47" t="s">
+      <c r="E103" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F103" t="s">
         <v>39</v>
       </c>
-      <c r="G103" s="46" t="s">
+      <c r="G103" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H103" s="45" t="s">
+      <c r="H103" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I103" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="46" t="s">
+      <c r="I103" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K103" s="46" t="s">
+      <c r="K103" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L103" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M103" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N103" s="46"/>
+      <c r="L103" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M103" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N103" s="45"/>
     </row>
     <row r="104" spans="3:17">
       <c r="C104" s="1"/>
       <c r="D104" s="2"/>
     </row>
     <row r="105" spans="3:17">
-      <c r="F105" s="39" t="s">
+      <c r="F105" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="39" t="s">
+      <c r="G105" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="40" t="s">
+      <c r="H105" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I105" s="40"/>
-      <c r="J105" s="40" t="s">
+      <c r="I105" s="39"/>
+      <c r="J105" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K105" s="40"/>
-      <c r="L105" s="39" t="s">
+      <c r="K105" s="39"/>
+      <c r="L105" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M105" s="39" t="s">
+      <c r="M105" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N105" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O105" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P105" s="39"/>
-      <c r="Q105" s="39"/>
+      <c r="N105" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O105" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P105" s="38"/>
+      <c r="Q105" s="38"/>
     </row>
     <row r="106" spans="3:17">
       <c r="C106" s="1" t="s">
@@ -5699,44 +5696,44 @@
       <c r="D106" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E106" s="44" t="s">
+      <c r="E106" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F106" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G106" s="45" t="s">
+      <c r="F106" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G106" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H106" s="45" t="s">
+      <c r="H106" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I106" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J106" s="45" t="s">
+      <c r="I106" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J106" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K106" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="45" t="s">
+      <c r="K106" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M106" s="45" t="s">
+      <c r="M106" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="N106" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O106" s="43" t="s">
+      <c r="N106" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O106" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="1"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="46" t="s">
+      <c r="E107" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F107" t="s">
@@ -5767,7 +5764,7 @@
     <row r="108" spans="3:17">
       <c r="C108" s="1"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="46" t="s">
+      <c r="E108" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F108" t="s">
@@ -5798,158 +5795,158 @@
     <row r="109" spans="3:17">
       <c r="C109" s="1"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="47" t="s">
+      <c r="E109" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F109" t="s">
         <v>39</v>
       </c>
-      <c r="G109" s="46" t="s">
+      <c r="G109" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H109" s="45" t="s">
+      <c r="H109" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I109" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="45" t="s">
+      <c r="I109" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K109" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L109" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M109" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N109" s="46"/>
+      <c r="K109" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L109" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M109" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N109" s="45"/>
     </row>
     <row r="110" spans="3:17">
       <c r="C110" s="1"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="48" t="s">
+      <c r="E110" s="46"/>
+      <c r="F110" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="48" t="s">
+      <c r="G110" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H110" s="48" t="s">
+      <c r="H110" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I110" s="48" t="s">
+      <c r="I110" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J110" s="48" t="s">
+      <c r="J110" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K110" s="49" t="s">
+      <c r="K110" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L110" s="49"/>
-      <c r="M110" s="48"/>
+      <c r="L110" s="48"/>
+      <c r="M110" s="47"/>
     </row>
     <row r="111" spans="3:17">
       <c r="C111" s="1"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="47" t="s">
+      <c r="E111" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F111" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="45" t="s">
+      <c r="G111" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H111" s="45" t="s">
+      <c r="H111" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I111" s="45" t="s">
+      <c r="I111" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="J111" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" s="50" t="s">
+      <c r="J111" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="L111" s="51"/>
-      <c r="M111" s="52"/>
-      <c r="N111" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O111" s="43" t="s">
+      <c r="L111" s="50"/>
+      <c r="M111" s="51"/>
+      <c r="N111" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O111" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="112" spans="3:17">
       <c r="C112" s="1"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="47" t="s">
+      <c r="E112" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F112" t="s">
         <v>39</v>
       </c>
-      <c r="G112" s="46" t="s">
+      <c r="G112" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H112" s="45" t="s">
+      <c r="H112" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I112" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J112" s="46" t="s">
+      <c r="I112" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J112" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K112" s="46" t="s">
+      <c r="K112" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L112" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M112" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N112" s="46"/>
+      <c r="L112" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M112" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N112" s="45"/>
     </row>
     <row r="113" spans="3:17">
       <c r="C113" s="1"/>
       <c r="D113" s="2"/>
     </row>
     <row r="114" spans="3:17">
-      <c r="F114" s="39" t="s">
+      <c r="F114" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G114" s="39" t="s">
+      <c r="G114" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H114" s="40" t="s">
+      <c r="H114" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I114" s="40"/>
-      <c r="J114" s="40" t="s">
+      <c r="I114" s="39"/>
+      <c r="J114" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="40"/>
-      <c r="L114" s="39" t="s">
+      <c r="K114" s="39"/>
+      <c r="L114" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M114" s="39" t="s">
+      <c r="M114" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N114" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O114" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P114" s="39"/>
-      <c r="Q114" s="39"/>
+      <c r="N114" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O114" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P114" s="38"/>
+      <c r="Q114" s="38"/>
     </row>
     <row r="115" spans="3:17">
       <c r="C115" s="1" t="s">
@@ -5958,44 +5955,44 @@
       <c r="D115" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E115" s="44" t="s">
+      <c r="E115" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F115" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G115" s="45" t="s">
+      <c r="F115" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G115" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H115" s="45" t="s">
+      <c r="H115" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="I115" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J115" s="45" t="s">
+      <c r="I115" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J115" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K115" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L115" s="45" t="s">
+      <c r="K115" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L115" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M115" s="53" t="s">
+      <c r="M115" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="N115" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O115" s="43" t="s">
+      <c r="N115" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O115" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="116" spans="3:17">
       <c r="C116" s="1"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="46" t="s">
+      <c r="E116" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F116" t="s">
@@ -6026,7 +6023,7 @@
     <row r="117" spans="3:17">
       <c r="C117" s="1"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="46" t="s">
+      <c r="E117" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F117" t="s">
@@ -6057,158 +6054,158 @@
     <row r="118" spans="3:17">
       <c r="C118" s="1"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="47" t="s">
+      <c r="E118" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F118" t="s">
         <v>39</v>
       </c>
-      <c r="G118" s="46" t="s">
+      <c r="G118" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H118" s="45" t="s">
+      <c r="H118" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="I118" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J118" s="45" t="s">
+      <c r="I118" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J118" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K118" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L118" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M118" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N118" s="46"/>
+      <c r="K118" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L118" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M118" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N118" s="45"/>
     </row>
     <row r="119" spans="3:17">
       <c r="C119" s="1"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="47"/>
-      <c r="F119" s="48" t="s">
+      <c r="E119" s="46"/>
+      <c r="F119" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="48" t="s">
+      <c r="G119" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H119" s="48" t="s">
+      <c r="H119" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I119" s="48" t="s">
+      <c r="I119" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J119" s="48" t="s">
+      <c r="J119" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K119" s="49" t="s">
+      <c r="K119" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L119" s="49"/>
-      <c r="M119" s="48"/>
+      <c r="L119" s="48"/>
+      <c r="M119" s="47"/>
     </row>
     <row r="120" spans="3:17">
       <c r="C120" s="1"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="47" t="s">
+      <c r="E120" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F120" t="s">
         <v>39</v>
       </c>
-      <c r="G120" s="45" t="s">
+      <c r="G120" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H120" s="45" t="s">
+      <c r="H120" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I120" s="45" t="s">
+      <c r="I120" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="J120" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" s="50" t="s">
+      <c r="J120" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="L120" s="51"/>
-      <c r="M120" s="52"/>
-      <c r="N120" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O120" s="43" t="s">
+      <c r="L120" s="50"/>
+      <c r="M120" s="51"/>
+      <c r="N120" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O120" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="121" spans="3:17">
       <c r="C121" s="1"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="47" t="s">
+      <c r="E121" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F121" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="46" t="s">
+      <c r="G121" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H121" s="45" t="s">
+      <c r="H121" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="I121" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="46" t="s">
+      <c r="I121" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K121" s="46" t="s">
+      <c r="K121" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L121" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M121" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N121" s="46"/>
+      <c r="L121" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M121" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N121" s="45"/>
     </row>
     <row r="122" spans="3:17">
       <c r="C122" s="1"/>
       <c r="D122" s="2"/>
     </row>
     <row r="123" spans="3:17">
-      <c r="F123" s="39" t="s">
+      <c r="F123" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G123" s="39" t="s">
+      <c r="G123" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H123" s="40" t="s">
+      <c r="H123" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I123" s="40"/>
-      <c r="J123" s="40" t="s">
+      <c r="I123" s="39"/>
+      <c r="J123" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K123" s="40"/>
-      <c r="L123" s="39" t="s">
+      <c r="K123" s="39"/>
+      <c r="L123" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M123" s="39" t="s">
+      <c r="M123" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N123" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O123" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P123" s="39"/>
-      <c r="Q123" s="39"/>
+      <c r="N123" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O123" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P123" s="38"/>
+      <c r="Q123" s="38"/>
     </row>
     <row r="124" spans="3:17">
       <c r="C124" s="1" t="s">
@@ -6217,44 +6214,44 @@
       <c r="D124" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E124" s="44" t="s">
+      <c r="E124" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F124" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G124" s="45" t="s">
+      <c r="F124" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G124" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H124" s="45" t="s">
+      <c r="H124" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I124" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J124" s="45" t="s">
+      <c r="I124" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K124" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L124" s="45" t="s">
+      <c r="K124" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L124" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M124" s="53" t="s">
+      <c r="M124" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="N124" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O124" s="43" t="s">
+      <c r="N124" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O124" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="125" spans="3:17">
       <c r="C125" s="1"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="46" t="s">
+      <c r="E125" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F125" t="s">
@@ -6285,7 +6282,7 @@
     <row r="126" spans="3:17">
       <c r="C126" s="1"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="46" t="s">
+      <c r="E126" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F126" t="s">
@@ -6316,158 +6313,158 @@
     <row r="127" spans="3:17">
       <c r="C127" s="1"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="47" t="s">
+      <c r="E127" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F127" t="s">
         <v>39</v>
       </c>
-      <c r="G127" s="46" t="s">
+      <c r="G127" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H127" s="45" t="s">
+      <c r="H127" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I127" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J127" s="45" t="s">
+      <c r="I127" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J127" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K127" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L127" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M127" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N127" s="46"/>
+      <c r="K127" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L127" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M127" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N127" s="45"/>
     </row>
     <row r="128" spans="3:17">
       <c r="C128" s="1"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="48" t="s">
+      <c r="E128" s="46"/>
+      <c r="F128" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="48" t="s">
+      <c r="G128" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H128" s="48" t="s">
+      <c r="H128" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I128" s="48" t="s">
+      <c r="I128" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J128" s="48" t="s">
+      <c r="J128" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K128" s="49" t="s">
+      <c r="K128" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L128" s="49"/>
-      <c r="M128" s="48"/>
+      <c r="L128" s="48"/>
+      <c r="M128" s="47"/>
     </row>
     <row r="129" spans="3:17">
       <c r="C129" s="1"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="47" t="s">
+      <c r="E129" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F129" t="s">
         <v>39</v>
       </c>
-      <c r="G129" s="45" t="s">
+      <c r="G129" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H129" s="45" t="s">
+      <c r="H129" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I129" s="45" t="s">
+      <c r="I129" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="J129" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="54" t="s">
+      <c r="J129" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K129" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="L129" s="51"/>
-      <c r="M129" s="52"/>
-      <c r="N129" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O129" s="43" t="s">
+      <c r="L129" s="50"/>
+      <c r="M129" s="51"/>
+      <c r="N129" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O129" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="130" spans="3:17">
       <c r="C130" s="1"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="47" t="s">
+      <c r="E130" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F130" t="s">
         <v>39</v>
       </c>
-      <c r="G130" s="46" t="s">
+      <c r="G130" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H130" s="45" t="s">
+      <c r="H130" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I130" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J130" s="46" t="s">
+      <c r="I130" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J130" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K130" s="46" t="s">
+      <c r="K130" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L130" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M130" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N130" s="46"/>
+      <c r="L130" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M130" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N130" s="45"/>
     </row>
     <row r="131" spans="3:17">
       <c r="C131" s="1"/>
       <c r="D131" s="2"/>
     </row>
     <row r="132" spans="3:17">
-      <c r="F132" s="39" t="s">
+      <c r="F132" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="39" t="s">
+      <c r="G132" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H132" s="40" t="s">
+      <c r="H132" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I132" s="40"/>
-      <c r="J132" s="40" t="s">
+      <c r="I132" s="39"/>
+      <c r="J132" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K132" s="40"/>
-      <c r="L132" s="39" t="s">
+      <c r="K132" s="39"/>
+      <c r="L132" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M132" s="39" t="s">
+      <c r="M132" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N132" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O132" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P132" s="39"/>
-      <c r="Q132" s="39"/>
+      <c r="N132" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O132" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P132" s="38"/>
+      <c r="Q132" s="38"/>
     </row>
     <row r="133" spans="3:17">
       <c r="C133" s="1" t="s">
@@ -6476,44 +6473,44 @@
       <c r="D133" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E133" s="44" t="s">
+      <c r="E133" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F133" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G133" s="45" t="s">
+      <c r="F133" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G133" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H133" s="45" t="s">
+      <c r="H133" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="I133" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="45" t="s">
+      <c r="I133" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K133" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L133" s="45" t="s">
+      <c r="K133" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L133" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M133" s="45" t="s">
+      <c r="M133" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="N133" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O133" s="43" t="s">
+      <c r="N133" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O133" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="134" spans="3:17">
       <c r="C134" s="1"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="46" t="s">
+      <c r="E134" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F134" t="s">
@@ -6544,7 +6541,7 @@
     <row r="135" spans="3:17">
       <c r="C135" s="1"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="46" t="s">
+      <c r="E135" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F135" t="s">
@@ -6575,158 +6572,158 @@
     <row r="136" spans="3:17">
       <c r="C136" s="1"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="47" t="s">
+      <c r="E136" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F136" t="s">
         <v>39</v>
       </c>
-      <c r="G136" s="46" t="s">
+      <c r="G136" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H136" s="45" t="s">
+      <c r="H136" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="I136" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J136" s="45" t="s">
+      <c r="I136" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K136" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L136" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M136" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N136" s="46"/>
+      <c r="K136" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L136" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M136" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N136" s="45"/>
     </row>
     <row r="137" spans="3:17">
       <c r="C137" s="1"/>
       <c r="D137" s="2"/>
-      <c r="E137" s="47"/>
-      <c r="F137" s="48" t="s">
+      <c r="E137" s="46"/>
+      <c r="F137" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G137" s="48" t="s">
+      <c r="G137" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H137" s="48" t="s">
+      <c r="H137" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I137" s="48" t="s">
+      <c r="I137" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J137" s="48" t="s">
+      <c r="J137" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K137" s="49" t="s">
+      <c r="K137" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L137" s="49"/>
-      <c r="M137" s="48"/>
+      <c r="L137" s="48"/>
+      <c r="M137" s="47"/>
     </row>
     <row r="138" spans="3:17">
       <c r="C138" s="1"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="47" t="s">
+      <c r="E138" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F138" t="s">
         <v>39</v>
       </c>
-      <c r="G138" s="45" t="s">
+      <c r="G138" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H138" s="45" t="s">
+      <c r="H138" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I138" s="45" t="s">
+      <c r="I138" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="J138" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K138" s="50" t="s">
+      <c r="J138" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K138" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="L138" s="51"/>
-      <c r="M138" s="52"/>
-      <c r="N138" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O138" s="43" t="s">
+      <c r="L138" s="50"/>
+      <c r="M138" s="51"/>
+      <c r="N138" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O138" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="139" spans="3:17">
       <c r="C139" s="1"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="47" t="s">
+      <c r="E139" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F139" t="s">
         <v>39</v>
       </c>
-      <c r="G139" s="46" t="s">
+      <c r="G139" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H139" s="45" t="s">
+      <c r="H139" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="I139" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" s="46" t="s">
+      <c r="I139" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J139" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K139" s="46" t="s">
+      <c r="K139" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L139" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M139" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N139" s="46"/>
+      <c r="L139" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M139" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N139" s="45"/>
     </row>
     <row r="140" spans="3:17">
       <c r="C140" s="1"/>
       <c r="D140" s="2"/>
     </row>
     <row r="141" spans="3:17">
-      <c r="F141" s="39" t="s">
+      <c r="F141" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G141" s="39" t="s">
+      <c r="G141" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H141" s="40" t="s">
+      <c r="H141" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I141" s="40"/>
-      <c r="J141" s="40" t="s">
+      <c r="I141" s="39"/>
+      <c r="J141" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K141" s="40"/>
-      <c r="L141" s="39" t="s">
+      <c r="K141" s="39"/>
+      <c r="L141" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M141" s="39" t="s">
+      <c r="M141" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N141" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O141" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P141" s="39"/>
-      <c r="Q141" s="39"/>
+      <c r="N141" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O141" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P141" s="38"/>
+      <c r="Q141" s="38"/>
     </row>
     <row r="142" spans="3:17">
       <c r="C142" s="1" t="s">
@@ -6735,44 +6732,44 @@
       <c r="D142" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E142" s="44" t="s">
+      <c r="E142" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F142" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G142" s="45" t="s">
+      <c r="F142" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H142" s="45" t="s">
+      <c r="H142" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="I142" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="45" t="s">
+      <c r="I142" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J142" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K142" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L142" s="45" t="s">
+      <c r="K142" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L142" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M142" s="45" t="s">
+      <c r="M142" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="N142" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O142" s="43" t="s">
+      <c r="N142" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O142" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="143" spans="3:17">
       <c r="C143" s="1"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="46" t="s">
+      <c r="E143" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F143" t="s">
@@ -6803,7 +6800,7 @@
     <row r="144" spans="3:17">
       <c r="C144" s="1"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="46" t="s">
+      <c r="E144" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F144" t="s">
@@ -6834,158 +6831,158 @@
     <row r="145" spans="3:17">
       <c r="C145" s="1"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="47" t="s">
+      <c r="E145" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F145" t="s">
         <v>39</v>
       </c>
-      <c r="G145" s="46" t="s">
+      <c r="G145" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H145" s="45" t="s">
+      <c r="H145" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="I145" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="45" t="s">
+      <c r="I145" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K145" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L145" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M145" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N145" s="46"/>
+      <c r="K145" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M145" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N145" s="45"/>
     </row>
     <row r="146" spans="3:17">
       <c r="C146" s="1"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="47"/>
-      <c r="F146" s="48" t="s">
+      <c r="E146" s="46"/>
+      <c r="F146" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G146" s="48" t="s">
+      <c r="G146" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H146" s="48" t="s">
+      <c r="H146" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I146" s="48" t="s">
+      <c r="I146" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J146" s="48" t="s">
+      <c r="J146" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K146" s="49" t="s">
+      <c r="K146" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L146" s="49"/>
-      <c r="M146" s="48"/>
+      <c r="L146" s="48"/>
+      <c r="M146" s="47"/>
     </row>
     <row r="147" spans="3:17">
       <c r="C147" s="1"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="47" t="s">
+      <c r="E147" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F147" t="s">
         <v>39</v>
       </c>
-      <c r="G147" s="45" t="s">
+      <c r="G147" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H147" s="45" t="s">
+      <c r="H147" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I147" s="45" t="s">
+      <c r="I147" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="J147" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="50" t="s">
+      <c r="J147" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="L147" s="51"/>
-      <c r="M147" s="52"/>
-      <c r="N147" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O147" s="43" t="s">
+      <c r="L147" s="50"/>
+      <c r="M147" s="51"/>
+      <c r="N147" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O147" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="148" spans="3:17">
       <c r="C148" s="1"/>
       <c r="D148" s="2"/>
-      <c r="E148" s="47" t="s">
+      <c r="E148" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F148" t="s">
         <v>39</v>
       </c>
-      <c r="G148" s="46" t="s">
+      <c r="G148" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H148" s="45" t="s">
+      <c r="H148" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="I148" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="46" t="s">
+      <c r="I148" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K148" s="46" t="s">
+      <c r="K148" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L148" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M148" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N148" s="46"/>
+      <c r="L148" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M148" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N148" s="45"/>
     </row>
     <row r="149" spans="3:17">
       <c r="C149" s="1"/>
       <c r="D149" s="2"/>
     </row>
     <row r="150" spans="3:17">
-      <c r="F150" s="39" t="s">
+      <c r="F150" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G150" s="39" t="s">
+      <c r="G150" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H150" s="40" t="s">
+      <c r="H150" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I150" s="40"/>
-      <c r="J150" s="40" t="s">
+      <c r="I150" s="39"/>
+      <c r="J150" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K150" s="40"/>
-      <c r="L150" s="39" t="s">
+      <c r="K150" s="39"/>
+      <c r="L150" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M150" s="39" t="s">
+      <c r="M150" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N150" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O150" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P150" s="39"/>
-      <c r="Q150" s="39"/>
+      <c r="N150" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O150" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P150" s="38"/>
+      <c r="Q150" s="38"/>
     </row>
     <row r="151" ht="81" spans="3:17">
       <c r="C151" s="1" t="s">
@@ -6994,44 +6991,44 @@
       <c r="D151" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E151" s="44" t="s">
+      <c r="E151" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F151" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G151" s="45" t="s">
+      <c r="F151" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G151" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H151" s="45" t="s">
+      <c r="H151" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="I151" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J151" s="45" t="s">
+      <c r="I151" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J151" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K151" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L151" s="45" t="s">
+      <c r="K151" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L151" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M151" s="55" t="s">
+      <c r="M151" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="N151" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O151" s="43" t="s">
+      <c r="N151" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O151" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="152" spans="3:17">
       <c r="C152" s="1"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="46" t="s">
+      <c r="E152" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F152" t="s">
@@ -7062,7 +7059,7 @@
     <row r="153" spans="3:17">
       <c r="C153" s="1"/>
       <c r="D153" s="2"/>
-      <c r="E153" s="46" t="s">
+      <c r="E153" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F153" t="s">
@@ -7093,160 +7090,160 @@
     <row r="154" spans="3:17">
       <c r="C154" s="1"/>
       <c r="D154" s="2"/>
-      <c r="E154" s="47" t="s">
+      <c r="E154" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F154" t="s">
         <v>39</v>
       </c>
-      <c r="G154" s="46" t="s">
+      <c r="G154" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H154" s="45" t="s">
+      <c r="H154" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="I154" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J154" s="45" t="s">
+      <c r="I154" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K154" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L154" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M154" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N154" s="46"/>
+      <c r="K154" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L154" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M154" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N154" s="45"/>
     </row>
     <row r="155" spans="3:17">
       <c r="C155" s="1"/>
       <c r="D155" s="2"/>
-      <c r="E155" s="47"/>
-      <c r="F155" s="48" t="s">
+      <c r="E155" s="46"/>
+      <c r="F155" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G155" s="48" t="s">
+      <c r="G155" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H155" s="48" t="s">
+      <c r="H155" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I155" s="48" t="s">
+      <c r="I155" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J155" s="48" t="s">
+      <c r="J155" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K155" s="49" t="s">
+      <c r="K155" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L155" s="49"/>
-      <c r="M155" s="48"/>
-      <c r="N155" s="45"/>
-      <c r="O155" s="43"/>
+      <c r="L155" s="48"/>
+      <c r="M155" s="47"/>
+      <c r="N155" s="44"/>
+      <c r="O155" s="42"/>
     </row>
     <row r="156" spans="3:17">
       <c r="C156" s="1"/>
       <c r="D156" s="2"/>
-      <c r="E156" s="47" t="s">
+      <c r="E156" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F156" t="s">
         <v>39</v>
       </c>
-      <c r="G156" s="45" t="s">
+      <c r="G156" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H156" s="45" t="s">
+      <c r="H156" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I156" s="45" t="s">
+      <c r="I156" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="J156" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K156" s="50" t="s">
+      <c r="J156" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="L156" s="51"/>
-      <c r="M156" s="52"/>
-      <c r="N156" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O156" s="43" t="s">
+      <c r="L156" s="50"/>
+      <c r="M156" s="51"/>
+      <c r="N156" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O156" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="157" spans="3:17">
       <c r="C157" s="1"/>
       <c r="D157" s="2"/>
-      <c r="E157" s="47" t="s">
+      <c r="E157" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F157" t="s">
         <v>39</v>
       </c>
-      <c r="G157" s="46" t="s">
+      <c r="G157" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H157" s="45" t="s">
+      <c r="H157" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="I157" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J157" s="46" t="s">
+      <c r="I157" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K157" s="46" t="s">
+      <c r="K157" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L157" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M157" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N157" s="46"/>
+      <c r="L157" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M157" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N157" s="45"/>
     </row>
     <row r="158" spans="3:17">
       <c r="C158" s="1"/>
       <c r="D158" s="2"/>
     </row>
     <row r="159" spans="3:17">
-      <c r="F159" s="39" t="s">
+      <c r="F159" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="39" t="s">
+      <c r="G159" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H159" s="40" t="s">
+      <c r="H159" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I159" s="40"/>
-      <c r="J159" s="40" t="s">
+      <c r="I159" s="39"/>
+      <c r="J159" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K159" s="40"/>
-      <c r="L159" s="39" t="s">
+      <c r="K159" s="39"/>
+      <c r="L159" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M159" s="39" t="s">
+      <c r="M159" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N159" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O159" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P159" s="39"/>
-      <c r="Q159" s="39"/>
+      <c r="N159" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O159" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P159" s="38"/>
+      <c r="Q159" s="38"/>
     </row>
     <row r="160" spans="3:17">
       <c r="C160" s="1" t="s">
@@ -7255,44 +7252,44 @@
       <c r="D160" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E160" s="44" t="s">
+      <c r="E160" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F160" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G160" s="45" t="s">
+      <c r="F160" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G160" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H160" s="45" t="s">
+      <c r="H160" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I160" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="45" t="s">
+      <c r="I160" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="K160" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L160" s="45" t="s">
+      <c r="K160" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L160" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="M160" s="45" t="s">
+      <c r="M160" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="N160" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O160" s="43" t="s">
+      <c r="N160" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O160" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="161" spans="3:17">
       <c r="C161" s="1"/>
       <c r="D161" s="2"/>
-      <c r="E161" s="46" t="s">
+      <c r="E161" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F161" t="s">
@@ -7323,7 +7320,7 @@
     <row r="162" spans="3:17">
       <c r="C162" s="1"/>
       <c r="D162" s="2"/>
-      <c r="E162" s="46" t="s">
+      <c r="E162" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F162" t="s">
@@ -7354,160 +7351,160 @@
     <row r="163" spans="3:17">
       <c r="C163" s="1"/>
       <c r="D163" s="2"/>
-      <c r="E163" s="47" t="s">
+      <c r="E163" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F163" t="s">
         <v>39</v>
       </c>
-      <c r="G163" s="46" t="s">
+      <c r="G163" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H163" s="45" t="s">
+      <c r="H163" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I163" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J163" s="45" t="s">
+      <c r="I163" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="K163" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L163" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M163" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N163" s="46"/>
+      <c r="K163" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L163" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M163" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N163" s="45"/>
     </row>
     <row r="164" spans="3:17">
       <c r="C164" s="1"/>
       <c r="D164" s="2"/>
-      <c r="E164" s="47"/>
-      <c r="F164" s="48" t="s">
+      <c r="E164" s="46"/>
+      <c r="F164" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G164" s="48" t="s">
+      <c r="G164" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H164" s="48" t="s">
+      <c r="H164" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I164" s="48" t="s">
+      <c r="I164" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J164" s="48" t="s">
+      <c r="J164" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K164" s="49" t="s">
+      <c r="K164" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L164" s="49"/>
-      <c r="M164" s="48"/>
-      <c r="N164" s="45"/>
-      <c r="O164" s="43"/>
+      <c r="L164" s="48"/>
+      <c r="M164" s="47"/>
+      <c r="N164" s="44"/>
+      <c r="O164" s="42"/>
     </row>
     <row r="165" spans="3:17">
       <c r="C165" s="1"/>
       <c r="D165" s="2"/>
-      <c r="E165" s="47" t="s">
+      <c r="E165" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F165" t="s">
         <v>39</v>
       </c>
-      <c r="G165" s="45" t="s">
+      <c r="G165" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H165" s="45" t="s">
+      <c r="H165" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="I165" s="45" t="s">
+      <c r="I165" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="J165" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K165" s="50" t="s">
+      <c r="J165" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K165" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L165" s="51"/>
-      <c r="M165" s="52"/>
-      <c r="N165" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O165" s="43" t="s">
+      <c r="L165" s="50"/>
+      <c r="M165" s="51"/>
+      <c r="N165" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O165" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="166" spans="3:17">
       <c r="C166" s="1"/>
       <c r="D166" s="2"/>
-      <c r="E166" s="47" t="s">
+      <c r="E166" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F166" t="s">
         <v>39</v>
       </c>
-      <c r="G166" s="46" t="s">
+      <c r="G166" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H166" s="45" t="s">
+      <c r="H166" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I166" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J166" s="46" t="s">
+      <c r="I166" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K166" s="46" t="s">
+      <c r="K166" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L166" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M166" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N166" s="46"/>
+      <c r="L166" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M166" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N166" s="45"/>
     </row>
     <row r="167" spans="3:17">
       <c r="C167" s="1"/>
       <c r="D167" s="2"/>
     </row>
     <row r="168" spans="3:17">
-      <c r="F168" s="39" t="s">
+      <c r="F168" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G168" s="39" t="s">
+      <c r="G168" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H168" s="40" t="s">
+      <c r="H168" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I168" s="40"/>
-      <c r="J168" s="40" t="s">
+      <c r="I168" s="39"/>
+      <c r="J168" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K168" s="40"/>
-      <c r="L168" s="39" t="s">
+      <c r="K168" s="39"/>
+      <c r="L168" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M168" s="39" t="s">
+      <c r="M168" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N168" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O168" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P168" s="39"/>
-      <c r="Q168" s="39"/>
+      <c r="N168" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O168" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P168" s="38"/>
+      <c r="Q168" s="38"/>
     </row>
     <row r="169" ht="81" spans="3:17">
       <c r="C169" s="1" t="s">
@@ -7516,44 +7513,44 @@
       <c r="D169" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E169" s="44" t="s">
+      <c r="E169" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F169" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G169" s="45" t="s">
+      <c r="F169" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G169" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H169" s="45" t="s">
+      <c r="H169" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I169" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J169" s="45" t="s">
+      <c r="I169" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K169" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L169" s="45" t="s">
+      <c r="K169" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L169" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="M169" s="55" t="s">
+      <c r="M169" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="N169" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O169" s="43" t="s">
+      <c r="N169" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O169" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="170" spans="3:17">
       <c r="C170" s="1"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="46" t="s">
+      <c r="E170" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F170" t="s">
@@ -7584,7 +7581,7 @@
     <row r="171" spans="3:17">
       <c r="C171" s="1"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="46" t="s">
+      <c r="E171" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F171" t="s">
@@ -7615,126 +7612,126 @@
     <row r="172" spans="3:17">
       <c r="C172" s="1"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="47" t="s">
+      <c r="E172" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F172" t="s">
         <v>39</v>
       </c>
-      <c r="G172" s="46" t="s">
+      <c r="G172" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H172" s="45" t="s">
+      <c r="H172" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I172" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J172" s="45" t="s">
+      <c r="I172" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K172" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L172" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M172" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N172" s="46"/>
+      <c r="K172" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L172" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M172" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N172" s="45"/>
     </row>
     <row r="173" spans="3:17">
       <c r="C173" s="1"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="47"/>
-      <c r="F173" s="48" t="s">
+      <c r="E173" s="46"/>
+      <c r="F173" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G173" s="48" t="s">
+      <c r="G173" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H173" s="48" t="s">
+      <c r="H173" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I173" s="48" t="s">
+      <c r="I173" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J173" s="48" t="s">
+      <c r="J173" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K173" s="49" t="s">
+      <c r="K173" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L173" s="49"/>
-      <c r="M173" s="48"/>
-      <c r="N173" s="45"/>
-      <c r="O173" s="43"/>
+      <c r="L173" s="48"/>
+      <c r="M173" s="47"/>
+      <c r="N173" s="44"/>
+      <c r="O173" s="42"/>
     </row>
     <row r="174" ht="70" customHeight="1" spans="3:17">
       <c r="C174" s="1"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="47" t="s">
+      <c r="E174" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F174" t="s">
         <v>39</v>
       </c>
-      <c r="G174" s="45" t="s">
+      <c r="G174" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H174" s="45" t="s">
+      <c r="H174" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="I174" s="45" t="s">
+      <c r="I174" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="J174" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K174" s="56" t="s">
+      <c r="J174" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K174" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="L174" s="51"/>
-      <c r="M174" s="52"/>
-      <c r="N174" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O174" s="43" t="s">
+      <c r="L174" s="50"/>
+      <c r="M174" s="51"/>
+      <c r="N174" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O174" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="175" spans="3:17">
       <c r="C175" s="1"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="47" t="s">
+      <c r="E175" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F175" t="s">
         <v>39</v>
       </c>
-      <c r="G175" s="46" t="s">
+      <c r="G175" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H175" s="45" t="s">
+      <c r="H175" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I175" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J175" s="46" t="s">
+      <c r="I175" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K175" s="46" t="s">
+      <c r="K175" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L175" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M175" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N175" s="46"/>
+      <c r="L175" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M175" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N175" s="45"/>
     </row>
     <row r="176" spans="3:17">
       <c r="C176" s="1"/>
@@ -7747,185 +7744,185 @@
       <c r="D178" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E178" s="44"/>
-      <c r="F178" s="45"/>
-      <c r="G178" s="45"/>
-      <c r="H178" s="45"/>
-      <c r="I178" s="45"/>
-      <c r="J178" s="45"/>
-      <c r="K178" s="45"/>
-      <c r="L178" s="45"/>
-      <c r="M178" s="45"/>
-      <c r="N178" s="45"/>
-      <c r="O178" s="43"/>
+      <c r="E178" s="43"/>
+      <c r="F178" s="44"/>
+      <c r="G178" s="44"/>
+      <c r="H178" s="44"/>
+      <c r="I178" s="44"/>
+      <c r="J178" s="44"/>
+      <c r="K178" s="44"/>
+      <c r="L178" s="44"/>
+      <c r="M178" s="44"/>
+      <c r="N178" s="44"/>
+      <c r="O178" s="42"/>
     </row>
     <row r="179" spans="3:17">
       <c r="C179" s="1"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="46"/>
+      <c r="E179" s="45"/>
     </row>
     <row r="180" spans="3:17">
       <c r="C180" s="1"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="46"/>
+      <c r="E180" s="45"/>
     </row>
     <row r="181" spans="3:17">
       <c r="C181" s="1"/>
       <c r="D181" s="2"/>
-      <c r="E181" s="47" t="s">
+      <c r="E181" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F181" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="46" t="s">
+      <c r="G181" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H181" s="45" t="s">
+      <c r="H181" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I181" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J181" s="45" t="s">
+      <c r="I181" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J181" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="K181" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L181" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M181" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N181" s="46"/>
+      <c r="K181" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L181" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M181" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N181" s="45"/>
     </row>
     <row r="182" ht="21" customHeight="1" spans="3:17">
       <c r="C182" s="1"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="47"/>
-      <c r="F182" s="48" t="s">
+      <c r="E182" s="46"/>
+      <c r="F182" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G182" s="48" t="s">
+      <c r="G182" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H182" s="48" t="s">
+      <c r="H182" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I182" s="48" t="s">
+      <c r="I182" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J182" s="48" t="s">
+      <c r="J182" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K182" s="49" t="s">
+      <c r="K182" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L182" s="49"/>
-      <c r="M182" s="48"/>
-      <c r="N182" s="45"/>
-      <c r="O182" s="43"/>
+      <c r="L182" s="48"/>
+      <c r="M182" s="47"/>
+      <c r="N182" s="44"/>
+      <c r="O182" s="42"/>
     </row>
     <row r="183" ht="45" customHeight="1" spans="3:17">
       <c r="C183" s="1"/>
       <c r="D183" s="2"/>
-      <c r="E183" s="47" t="s">
+      <c r="E183" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F183" t="s">
         <v>39</v>
       </c>
-      <c r="G183" s="45" t="s">
+      <c r="G183" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H183" s="45" t="s">
+      <c r="H183" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="I183" s="45" t="s">
+      <c r="I183" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="J183" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K183" s="56" t="s">
+      <c r="J183" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K183" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="L183" s="51"/>
-      <c r="M183" s="52"/>
-      <c r="N183" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O183" s="43" t="s">
+      <c r="L183" s="50"/>
+      <c r="M183" s="51"/>
+      <c r="N183" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O183" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="184" spans="3:17">
       <c r="C184" s="1"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="47" t="s">
+      <c r="E184" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F184" t="s">
         <v>39</v>
       </c>
-      <c r="G184" s="46" t="s">
+      <c r="G184" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H184" s="45" t="s">
+      <c r="H184" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I184" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J184" s="46" t="s">
+      <c r="I184" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J184" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K184" s="46" t="s">
+      <c r="K184" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L184" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M184" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N184" s="46"/>
+      <c r="L184" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M184" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N184" s="45"/>
     </row>
     <row r="185" spans="3:17">
       <c r="C185" s="1"/>
       <c r="D185" s="2"/>
     </row>
     <row r="186" spans="3:17">
-      <c r="F186" s="39" t="s">
+      <c r="F186" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G186" s="39" t="s">
+      <c r="G186" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H186" s="40" t="s">
+      <c r="H186" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I186" s="40"/>
-      <c r="J186" s="40" t="s">
+      <c r="I186" s="39"/>
+      <c r="J186" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K186" s="40"/>
-      <c r="L186" s="39" t="s">
+      <c r="K186" s="39"/>
+      <c r="L186" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M186" s="39" t="s">
+      <c r="M186" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N186" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O186" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P186" s="39"/>
-      <c r="Q186" s="39"/>
+      <c r="N186" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O186" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P186" s="38"/>
+      <c r="Q186" s="38"/>
     </row>
     <row r="187" spans="3:17">
       <c r="C187" s="1" t="s">
@@ -7934,44 +7931,44 @@
       <c r="D187" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E187" s="44" t="s">
+      <c r="E187" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F187" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G187" s="45" t="s">
+      <c r="F187" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G187" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H187" s="45" t="s">
+      <c r="H187" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="I187" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J187" s="45" t="s">
+      <c r="I187" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J187" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="K187" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L187" s="45" t="s">
+      <c r="K187" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L187" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="M187" s="45" t="s">
+      <c r="M187" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="N187" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O187" s="43" t="s">
+      <c r="N187" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O187" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="188" spans="3:17">
       <c r="C188" s="1"/>
       <c r="D188" s="2"/>
-      <c r="E188" s="46" t="s">
+      <c r="E188" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F188" t="s">
@@ -8002,7 +7999,7 @@
     <row r="189" spans="3:17">
       <c r="C189" s="1"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="46" t="s">
+      <c r="E189" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F189" t="s">
@@ -8033,56 +8030,56 @@
     <row r="190" spans="3:17">
       <c r="C190" s="1"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="47"/>
-      <c r="F190" s="57" t="s">
+      <c r="E190" s="46"/>
+      <c r="F190" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="G190" s="57" t="s">
+      <c r="G190" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="H190" s="57" t="s">
+      <c r="H190" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="I190" s="58" t="s">
+      <c r="I190" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="J190" s="58"/>
-      <c r="K190" s="58" t="s">
+      <c r="J190" s="57"/>
+      <c r="K190" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="L190" s="58"/>
-      <c r="M190" s="58"/>
-      <c r="N190" s="58"/>
-      <c r="O190" s="58"/>
+      <c r="L190" s="57"/>
+      <c r="M190" s="57"/>
+      <c r="N190" s="57"/>
+      <c r="O190" s="57"/>
     </row>
     <row r="191" spans="3:17">
       <c r="C191" s="1"/>
       <c r="D191" s="2"/>
-      <c r="E191" s="47" t="s">
+      <c r="E191" s="46" t="s">
         <v>156</v>
       </c>
       <c r="F191" t="s">
         <v>39</v>
       </c>
-      <c r="G191" s="59" t="s">
+      <c r="G191" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="H191" s="60" t="s">
+      <c r="H191" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="I191" s="60" t="s">
+      <c r="I191" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="J191" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="K191" s="61" t="s">
+      <c r="J191" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K191" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="L191" s="62"/>
-      <c r="M191" s="62"/>
-      <c r="N191" s="62"/>
-      <c r="O191" s="62"/>
+      <c r="L191" s="61"/>
+      <c r="M191" s="61"/>
+      <c r="N191" s="61"/>
+      <c r="O191" s="61"/>
       <c r="P191" t="s">
         <v>31</v>
       </c>
@@ -8093,179 +8090,179 @@
     <row r="192" spans="3:17">
       <c r="C192" s="1"/>
       <c r="D192" s="2"/>
-      <c r="E192" s="47"/>
-      <c r="G192" s="63"/>
-      <c r="H192" s="64"/>
-      <c r="I192" s="64"/>
-      <c r="J192" s="64"/>
-      <c r="K192" s="64"/>
-      <c r="L192" s="63"/>
-      <c r="M192" s="63"/>
-      <c r="N192" s="63"/>
+      <c r="E192" s="46"/>
+      <c r="G192" s="62"/>
+      <c r="H192" s="63"/>
+      <c r="I192" s="63"/>
+      <c r="J192" s="63"/>
+      <c r="K192" s="63"/>
+      <c r="L192" s="62"/>
+      <c r="M192" s="62"/>
+      <c r="N192" s="62"/>
     </row>
     <row r="193" spans="3:17">
       <c r="C193" s="1"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="47"/>
-      <c r="G193" s="45"/>
-      <c r="H193" s="45"/>
-      <c r="I193" s="45"/>
-      <c r="J193" s="45"/>
-      <c r="K193" s="45"/>
-      <c r="L193" s="45"/>
-      <c r="M193" s="45"/>
-      <c r="N193" s="45"/>
-      <c r="O193" s="43"/>
+      <c r="E193" s="46"/>
+      <c r="G193" s="44"/>
+      <c r="H193" s="44"/>
+      <c r="I193" s="44"/>
+      <c r="J193" s="44"/>
+      <c r="K193" s="44"/>
+      <c r="L193" s="44"/>
+      <c r="M193" s="44"/>
+      <c r="N193" s="44"/>
+      <c r="O193" s="42"/>
     </row>
     <row r="194" spans="3:17">
       <c r="C194" s="1"/>
       <c r="D194" s="2"/>
-      <c r="E194" s="47"/>
-      <c r="G194" s="46"/>
-      <c r="H194" s="45"/>
-      <c r="I194" s="45"/>
-      <c r="J194" s="46"/>
-      <c r="K194" s="46"/>
-      <c r="L194" s="46"/>
-      <c r="M194" s="46"/>
-      <c r="N194" s="46"/>
+      <c r="E194" s="46"/>
+      <c r="G194" s="45"/>
+      <c r="H194" s="44"/>
+      <c r="I194" s="44"/>
+      <c r="J194" s="45"/>
+      <c r="K194" s="45"/>
+      <c r="L194" s="45"/>
+      <c r="M194" s="45"/>
+      <c r="N194" s="45"/>
     </row>
     <row r="195" spans="3:17">
       <c r="D195" s="3"/>
-      <c r="E195" s="46"/>
-      <c r="F195" s="39"/>
-      <c r="G195" s="39"/>
-      <c r="H195" s="40"/>
-      <c r="I195" s="40"/>
-      <c r="J195" s="40"/>
-      <c r="K195" s="40"/>
-      <c r="L195" s="39"/>
-      <c r="M195" s="39"/>
-      <c r="N195" s="39"/>
-      <c r="O195" s="39"/>
-      <c r="P195" s="39"/>
-      <c r="Q195" s="39"/>
+      <c r="E195" s="45"/>
+      <c r="F195" s="38"/>
+      <c r="G195" s="38"/>
+      <c r="H195" s="39"/>
+      <c r="I195" s="39"/>
+      <c r="J195" s="39"/>
+      <c r="K195" s="39"/>
+      <c r="L195" s="38"/>
+      <c r="M195" s="38"/>
+      <c r="N195" s="38"/>
+      <c r="O195" s="38"/>
+      <c r="P195" s="38"/>
+      <c r="Q195" s="38"/>
     </row>
     <row r="196" spans="3:17">
       <c r="C196" s="1"/>
       <c r="D196" s="2"/>
-      <c r="E196" s="44"/>
-      <c r="F196" s="45"/>
-      <c r="G196" s="45"/>
-      <c r="H196" s="45"/>
-      <c r="I196" s="45"/>
-      <c r="J196" s="45"/>
-      <c r="K196" s="45"/>
-      <c r="L196" s="45"/>
-      <c r="M196" s="45"/>
-      <c r="N196" s="45"/>
-      <c r="O196" s="43"/>
+      <c r="E196" s="43"/>
+      <c r="F196" s="44"/>
+      <c r="G196" s="44"/>
+      <c r="H196" s="44"/>
+      <c r="I196" s="44"/>
+      <c r="J196" s="44"/>
+      <c r="K196" s="44"/>
+      <c r="L196" s="44"/>
+      <c r="M196" s="44"/>
+      <c r="N196" s="44"/>
+      <c r="O196" s="42"/>
     </row>
     <row r="197" spans="3:17">
       <c r="C197" s="1"/>
       <c r="D197" s="2"/>
-      <c r="E197" s="46"/>
+      <c r="E197" s="45"/>
     </row>
     <row r="198" spans="3:17">
       <c r="C198" s="1"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="65"/>
+      <c r="E198" s="64"/>
     </row>
     <row r="199" spans="3:17">
       <c r="C199" s="1"/>
       <c r="D199" s="2"/>
-      <c r="H199" s="60"/>
-      <c r="I199" s="60"/>
-      <c r="J199" s="60"/>
-      <c r="K199" s="66"/>
-      <c r="L199" s="67"/>
-      <c r="M199" s="67"/>
-      <c r="N199" s="67"/>
-      <c r="O199" s="67"/>
+      <c r="H199" s="59"/>
+      <c r="I199" s="59"/>
+      <c r="J199" s="59"/>
+      <c r="K199" s="65"/>
+      <c r="L199" s="66"/>
+      <c r="M199" s="66"/>
+      <c r="N199" s="66"/>
+      <c r="O199" s="66"/>
     </row>
     <row r="200" spans="3:17">
       <c r="C200" s="1"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="68"/>
-      <c r="G200" s="63"/>
-      <c r="H200" s="64"/>
-      <c r="I200" s="64"/>
-      <c r="J200" s="64"/>
-      <c r="K200" s="64"/>
-      <c r="L200" s="63"/>
-      <c r="M200" s="63"/>
-      <c r="N200" s="63"/>
+      <c r="E200" s="67"/>
+      <c r="G200" s="62"/>
+      <c r="H200" s="63"/>
+      <c r="I200" s="63"/>
+      <c r="J200" s="63"/>
+      <c r="K200" s="63"/>
+      <c r="L200" s="62"/>
+      <c r="M200" s="62"/>
+      <c r="N200" s="62"/>
     </row>
     <row r="201" spans="3:17">
       <c r="C201" s="1"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="47"/>
-      <c r="G201" s="45"/>
-      <c r="H201" s="45"/>
-      <c r="I201" s="45"/>
-      <c r="J201" s="45"/>
-      <c r="K201" s="45"/>
-      <c r="L201" s="45"/>
-      <c r="M201" s="45"/>
-      <c r="N201" s="45"/>
-      <c r="O201" s="43"/>
+      <c r="E201" s="46"/>
+      <c r="G201" s="44"/>
+      <c r="H201" s="44"/>
+      <c r="I201" s="44"/>
+      <c r="J201" s="44"/>
+      <c r="K201" s="44"/>
+      <c r="L201" s="44"/>
+      <c r="M201" s="44"/>
+      <c r="N201" s="44"/>
+      <c r="O201" s="42"/>
     </row>
     <row r="202" spans="3:17">
       <c r="C202" s="1"/>
       <c r="D202" s="2"/>
-      <c r="E202" s="47"/>
-      <c r="G202" s="46"/>
-      <c r="H202" s="45"/>
-      <c r="I202" s="45"/>
-      <c r="J202" s="46"/>
-      <c r="K202" s="46"/>
-      <c r="L202" s="46"/>
-      <c r="M202" s="46"/>
-      <c r="N202" s="46"/>
+      <c r="E202" s="46"/>
+      <c r="G202" s="45"/>
+      <c r="H202" s="44"/>
+      <c r="I202" s="44"/>
+      <c r="J202" s="45"/>
+      <c r="K202" s="45"/>
+      <c r="L202" s="45"/>
+      <c r="M202" s="45"/>
+      <c r="N202" s="45"/>
     </row>
     <row r="203" spans="3:17">
-      <c r="F203" s="69" t="s">
+      <c r="F203" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="G203" s="69" t="s">
+      <c r="G203" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="H203" s="70" t="s">
+      <c r="H203" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="I203" s="70"/>
-      <c r="J203" s="70" t="s">
+      <c r="I203" s="69"/>
+      <c r="J203" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="K203" s="70"/>
-      <c r="L203" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="M203" s="69" t="s">
+      <c r="K203" s="69"/>
+      <c r="L203" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="M203" s="68" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="204" spans="3:17">
-      <c r="F204" s="59"/>
-      <c r="G204" s="59" t="s">
+      <c r="F204" s="58"/>
+      <c r="G204" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="H204" s="60" t="s">
+      <c r="H204" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="I204" s="60" t="s">
+      <c r="I204" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="J204" s="60" t="s">
+      <c r="J204" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="K204" s="60" t="s">
+      <c r="K204" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="L204" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="M204" s="59" t="s">
+      <c r="L204" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="M204" s="58" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8276,7 +8273,7 @@
       <c r="D205" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E205" s="44" t="s">
+      <c r="E205" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F205" t="s">
@@ -8307,7 +8304,7 @@
     <row r="206" spans="3:17">
       <c r="C206" s="1"/>
       <c r="D206" s="2"/>
-      <c r="E206" s="46" t="s">
+      <c r="E206" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F206" t="s">
@@ -8338,7 +8335,7 @@
     <row r="207" spans="3:17">
       <c r="C207" s="1"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="65" t="s">
+      <c r="E207" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F207" t="s">
@@ -8373,17 +8370,17 @@
     <row r="209" spans="3:17">
       <c r="C209" s="1"/>
       <c r="D209" s="2"/>
-      <c r="E209" s="68"/>
+      <c r="E209" s="67"/>
     </row>
     <row r="210" spans="3:17">
       <c r="C210" s="1"/>
       <c r="D210" s="2"/>
-      <c r="E210" s="47"/>
+      <c r="E210" s="46"/>
     </row>
     <row r="211" spans="3:17">
       <c r="C211" s="1"/>
       <c r="D211" s="2"/>
-      <c r="E211" s="47"/>
+      <c r="E211" s="46"/>
     </row>
     <row r="213" spans="3:17">
       <c r="C213" s="1" t="s">
@@ -8392,7 +8389,7 @@
       <c r="D213" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E213" s="44" t="s">
+      <c r="E213" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F213" t="s">
@@ -8401,7 +8398,7 @@
       <c r="G213" t="s">
         <v>157</v>
       </c>
-      <c r="H213" s="33" t="s">
+      <c r="H213" s="32" t="s">
         <v>163</v>
       </c>
       <c r="I213" t="s">
@@ -8423,7 +8420,7 @@
     <row r="214" spans="3:17">
       <c r="C214" s="1"/>
       <c r="D214" s="2"/>
-      <c r="E214" s="46" t="s">
+      <c r="E214" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F214" t="s">
@@ -8454,7 +8451,7 @@
     <row r="215" spans="3:17">
       <c r="C215" s="1"/>
       <c r="D215" s="2"/>
-      <c r="E215" s="65" t="s">
+      <c r="E215" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F215" t="s">
@@ -8485,7 +8482,7 @@
     <row r="216" spans="3:17">
       <c r="C216" s="1"/>
       <c r="D216" s="2"/>
-      <c r="E216" s="44" t="s">
+      <c r="E216" s="43" t="s">
         <v>166</v>
       </c>
       <c r="F216" t="s">
@@ -8516,7 +8513,7 @@
     <row r="217" spans="3:17">
       <c r="C217" s="1"/>
       <c r="D217" s="2"/>
-      <c r="E217" s="46" t="s">
+      <c r="E217" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F217" t="s">
@@ -8547,7 +8544,7 @@
     <row r="218" spans="3:17">
       <c r="C218" s="1"/>
       <c r="D218" s="2"/>
-      <c r="E218" s="65" t="s">
+      <c r="E218" s="64" t="s">
         <v>103</v>
       </c>
       <c r="F218" t="s">
@@ -8578,16 +8575,16 @@
     <row r="219" spans="3:17">
       <c r="C219" s="1"/>
       <c r="D219" s="2"/>
-      <c r="E219" s="47"/>
+      <c r="E219" s="46"/>
     </row>
     <row r="221" spans="3:17">
       <c r="C221" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D221" s="35" t="s">
+      <c r="D221" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="E221" s="44" t="s">
+      <c r="E221" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F221" t="s">
@@ -8614,15 +8611,15 @@
       <c r="M221" t="s">
         <v>32</v>
       </c>
-      <c r="N221" s="71"/>
-      <c r="O221" s="71"/>
-      <c r="P221" s="71"/>
-      <c r="Q221" s="71"/>
+      <c r="N221" s="70"/>
+      <c r="O221" s="70"/>
+      <c r="P221" s="70"/>
+      <c r="Q221" s="70"/>
     </row>
     <row r="222" spans="3:17">
       <c r="C222" s="1"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="46" t="s">
+      <c r="E222" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F222" t="s">
@@ -8649,13 +8646,13 @@
       <c r="M222" t="s">
         <v>32</v>
       </c>
-      <c r="N222" s="72"/>
-      <c r="O222" s="73"/>
+      <c r="N222" s="71"/>
+      <c r="O222" s="72"/>
     </row>
     <row r="223" spans="3:17">
       <c r="C223" s="1"/>
       <c r="D223" s="2"/>
-      <c r="E223" s="65" t="s">
+      <c r="E223" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F223" t="s">
@@ -8686,7 +8683,7 @@
     <row r="224" spans="3:17">
       <c r="C224" s="1"/>
       <c r="D224" s="2"/>
-      <c r="E224" s="44" t="s">
+      <c r="E224" s="43" t="s">
         <v>166</v>
       </c>
       <c r="F224" t="s">
@@ -8717,7 +8714,7 @@
     <row r="225" spans="3:15">
       <c r="C225" s="1"/>
       <c r="D225" s="2"/>
-      <c r="E225" s="46" t="s">
+      <c r="E225" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F225" t="s">
@@ -8744,12 +8741,12 @@
       <c r="M225" t="s">
         <v>32</v>
       </c>
-      <c r="N225" s="46"/>
+      <c r="N225" s="45"/>
     </row>
     <row r="226" spans="3:15">
       <c r="C226" s="1"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="65" t="s">
+      <c r="E226" s="64" t="s">
         <v>103</v>
       </c>
       <c r="F226" t="s">
@@ -8776,50 +8773,50 @@
       <c r="M226" t="s">
         <v>32</v>
       </c>
-      <c r="N226" s="45"/>
-      <c r="O226" s="43"/>
+      <c r="N226" s="44"/>
+      <c r="O226" s="42"/>
     </row>
     <row r="227" spans="3:15">
       <c r="C227" s="1"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="47"/>
-      <c r="G227" s="45"/>
-      <c r="H227" s="45"/>
-      <c r="I227" s="45"/>
-      <c r="J227" s="45"/>
-      <c r="K227" s="50"/>
-      <c r="L227" s="51"/>
-      <c r="M227" s="52"/>
-      <c r="N227" s="45"/>
-      <c r="O227" s="43"/>
+      <c r="E227" s="46"/>
+      <c r="G227" s="44"/>
+      <c r="H227" s="44"/>
+      <c r="I227" s="44"/>
+      <c r="J227" s="44"/>
+      <c r="K227" s="49"/>
+      <c r="L227" s="50"/>
+      <c r="M227" s="51"/>
+      <c r="N227" s="44"/>
+      <c r="O227" s="42"/>
     </row>
     <row r="228" spans="3:15">
-      <c r="E228" s="47"/>
-      <c r="G228" s="46"/>
-      <c r="H228" s="45"/>
-      <c r="I228" s="45"/>
-      <c r="J228" s="46"/>
-      <c r="K228" s="46"/>
-      <c r="L228" s="46"/>
-      <c r="M228" s="46"/>
-      <c r="N228" s="46"/>
+      <c r="E228" s="46"/>
+      <c r="G228" s="45"/>
+      <c r="H228" s="44"/>
+      <c r="I228" s="44"/>
+      <c r="J228" s="45"/>
+      <c r="K228" s="45"/>
+      <c r="L228" s="45"/>
+      <c r="M228" s="45"/>
+      <c r="N228" s="45"/>
     </row>
     <row r="229" spans="3:15">
-      <c r="E229" s="47"/>
-      <c r="G229" s="46"/>
-      <c r="H229" s="72"/>
-      <c r="I229" s="72"/>
-      <c r="J229" s="46"/>
-      <c r="K229" s="46"/>
-      <c r="L229" s="46"/>
-      <c r="M229" s="46"/>
-      <c r="N229" s="46"/>
+      <c r="E229" s="46"/>
+      <c r="G229" s="45"/>
+      <c r="H229" s="71"/>
+      <c r="I229" s="71"/>
+      <c r="J229" s="45"/>
+      <c r="K229" s="45"/>
+      <c r="L229" s="45"/>
+      <c r="M229" s="45"/>
+      <c r="N229" s="45"/>
     </row>
     <row r="230" ht="44" customHeight="1" spans="3:15">
       <c r="D230" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E230" s="44" t="s">
+      <c r="E230" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F230" t="s">
@@ -8846,11 +8843,11 @@
       <c r="M230" t="s">
         <v>32</v>
       </c>
-      <c r="O230" s="73"/>
+      <c r="O230" s="72"/>
     </row>
     <row r="231" spans="3:15">
       <c r="D231" s="2"/>
-      <c r="E231" s="46" t="s">
+      <c r="E231" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F231" t="s">
@@ -8880,7 +8877,7 @@
     </row>
     <row r="232" spans="3:15">
       <c r="D232" s="2"/>
-      <c r="E232" s="65" t="s">
+      <c r="E232" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F232" t="s">
@@ -8910,7 +8907,7 @@
     </row>
     <row r="233" spans="3:15">
       <c r="D233" s="2"/>
-      <c r="E233" s="44" t="s">
+      <c r="E233" s="43" t="s">
         <v>166</v>
       </c>
       <c r="F233" t="s">
@@ -8940,7 +8937,7 @@
     </row>
     <row r="234" spans="3:15">
       <c r="D234" s="2"/>
-      <c r="E234" s="46" t="s">
+      <c r="E234" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F234" t="s">
@@ -8967,11 +8964,11 @@
       <c r="M234" t="s">
         <v>32</v>
       </c>
-      <c r="O234" s="43"/>
+      <c r="O234" s="42"/>
     </row>
     <row r="235" spans="3:15">
       <c r="D235" s="2"/>
-      <c r="E235" s="65" t="s">
+      <c r="E235" s="64" t="s">
         <v>103</v>
       </c>
       <c r="F235" t="s">
@@ -8998,42 +8995,42 @@
       <c r="M235" t="s">
         <v>32</v>
       </c>
-      <c r="N235" s="46"/>
+      <c r="N235" s="45"/>
     </row>
     <row r="236" spans="3:15">
       <c r="D236" s="2"/>
     </row>
     <row r="242" spans="3:17">
       <c r="D242" s="3"/>
-      <c r="E242" s="46"/>
-      <c r="F242" s="39" t="s">
+      <c r="E242" s="45"/>
+      <c r="F242" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G242" s="39" t="s">
+      <c r="G242" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H242" s="40" t="s">
+      <c r="H242" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I242" s="40"/>
-      <c r="J242" s="40" t="s">
+      <c r="I242" s="39"/>
+      <c r="J242" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K242" s="40"/>
-      <c r="L242" s="39" t="s">
+      <c r="K242" s="39"/>
+      <c r="L242" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M242" s="39" t="s">
+      <c r="M242" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N242" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O242" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P242" s="39"/>
-      <c r="Q242" s="39"/>
+      <c r="N242" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O242" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P242" s="38"/>
+      <c r="Q242" s="38"/>
     </row>
     <row r="243" spans="3:17">
       <c r="C243" s="1" t="s">
@@ -9042,44 +9039,44 @@
       <c r="D243" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E243" s="44" t="s">
+      <c r="E243" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="F243" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G243" s="45" t="s">
+      <c r="F243" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G243" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H243" s="45" t="s">
+      <c r="H243" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="I243" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J243" s="45" t="s">
+      <c r="I243" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J243" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K243" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L243" s="45" t="s">
+      <c r="K243" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L243" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M243" s="45" t="s">
+      <c r="M243" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="N243" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O243" s="43" t="s">
+      <c r="N243" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O243" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="244" spans="3:17">
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
-      <c r="E244" s="46" t="s">
+      <c r="E244" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F244" t="s">
@@ -9110,7 +9107,7 @@
     <row r="245" spans="3:17">
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="65" t="s">
+      <c r="E245" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F245" t="s">
@@ -9141,56 +9138,56 @@
     <row r="246" spans="3:17">
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
-      <c r="H246" s="60"/>
-      <c r="I246" s="60"/>
-      <c r="J246" s="60"/>
-      <c r="K246" s="66"/>
-      <c r="L246" s="67"/>
-      <c r="M246" s="67"/>
-      <c r="N246" s="67"/>
-      <c r="O246" s="67"/>
+      <c r="H246" s="59"/>
+      <c r="I246" s="59"/>
+      <c r="J246" s="59"/>
+      <c r="K246" s="65"/>
+      <c r="L246" s="66"/>
+      <c r="M246" s="66"/>
+      <c r="N246" s="66"/>
+      <c r="O246" s="66"/>
     </row>
     <row r="247" spans="3:17">
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
-      <c r="E247" s="44" t="s">
+      <c r="E247" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="F247" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G247" s="45" t="s">
+      <c r="F247" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G247" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H247" s="45" t="s">
+      <c r="H247" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="I247" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J247" s="45" t="s">
+      <c r="I247" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J247" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="K247" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L247" s="45" t="s">
+      <c r="K247" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L247" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="M247" s="45" t="s">
+      <c r="M247" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="N247" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O247" s="43" t="s">
+      <c r="N247" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O247" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="248" spans="3:17">
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
-      <c r="E248" s="46" t="s">
+      <c r="E248" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F248" t="s">
@@ -9221,7 +9218,7 @@
     <row r="249" spans="3:17">
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="65" t="s">
+      <c r="E249" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F249" t="s">
@@ -9250,42 +9247,42 @@
       </c>
     </row>
     <row r="251" spans="3:17">
-      <c r="E251" s="44" t="s">
+      <c r="E251" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="F251" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G251" s="45" t="s">
+      <c r="F251" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G251" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H251" s="45" t="s">
+      <c r="H251" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I251" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J251" s="45" t="s">
+      <c r="I251" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J251" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K251" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L251" s="45" t="s">
+      <c r="K251" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L251" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M251" s="45" t="s">
+      <c r="M251" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="N251" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O251" s="43" t="s">
+      <c r="N251" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O251" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="252" spans="3:17">
-      <c r="E252" s="46" t="s">
+      <c r="E252" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F252" t="s">
@@ -9314,7 +9311,7 @@
       </c>
     </row>
     <row r="253" spans="3:17">
-      <c r="E253" s="65" t="s">
+      <c r="E253" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F253" t="s">
@@ -9349,175 +9346,175 @@
       <c r="D255" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E255" s="44"/>
-      <c r="F255" s="45"/>
-      <c r="G255" s="45"/>
-      <c r="H255" s="45"/>
-      <c r="I255" s="45"/>
-      <c r="J255" s="45"/>
-      <c r="K255" s="45"/>
-      <c r="L255" s="45"/>
-      <c r="M255" s="45"/>
-      <c r="N255" s="45"/>
-      <c r="O255" s="43"/>
+      <c r="E255" s="43"/>
+      <c r="F255" s="44"/>
+      <c r="G255" s="44"/>
+      <c r="H255" s="44"/>
+      <c r="I255" s="44"/>
+      <c r="J255" s="44"/>
+      <c r="K255" s="44"/>
+      <c r="L255" s="44"/>
+      <c r="M255" s="44"/>
+      <c r="N255" s="44"/>
+      <c r="O255" s="42"/>
     </row>
     <row r="256" spans="3:17">
       <c r="C256" s="1"/>
       <c r="D256" s="2"/>
-      <c r="E256" s="46"/>
+      <c r="E256" s="45"/>
     </row>
     <row r="257" spans="3:17">
       <c r="C257" s="1"/>
       <c r="D257" s="2"/>
-      <c r="E257" s="46"/>
-      <c r="F257" s="39" t="s">
+      <c r="E257" s="45"/>
+      <c r="F257" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G257" s="39" t="s">
+      <c r="G257" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H257" s="40" t="s">
+      <c r="H257" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I257" s="40"/>
-      <c r="J257" s="40" t="s">
+      <c r="I257" s="39"/>
+      <c r="J257" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K257" s="40"/>
-      <c r="L257" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M257" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N257" s="39"/>
-      <c r="O257" s="39"/>
-      <c r="P257" s="39"/>
-      <c r="Q257" s="39"/>
+      <c r="K257" s="39"/>
+      <c r="L257" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M257" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N257" s="38"/>
+      <c r="O257" s="38"/>
+      <c r="P257" s="38"/>
+      <c r="Q257" s="38"/>
     </row>
     <row r="258" spans="3:17">
       <c r="C258" s="1"/>
       <c r="D258" s="2"/>
-      <c r="E258" s="47" t="s">
+      <c r="E258" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F258" t="s">
         <v>39</v>
       </c>
-      <c r="G258" s="46" t="s">
+      <c r="G258" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H258" s="45" t="s">
+      <c r="H258" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="I258" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J258" s="45" t="s">
+      <c r="I258" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J258" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K258" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L258" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M258" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N258" s="46"/>
+      <c r="K258" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L258" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M258" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N258" s="45"/>
     </row>
     <row r="259" spans="3:17">
       <c r="C259" s="1"/>
       <c r="D259" s="2"/>
-      <c r="E259" s="47"/>
-      <c r="F259" s="48" t="s">
+      <c r="E259" s="46"/>
+      <c r="F259" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G259" s="48" t="s">
+      <c r="G259" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H259" s="48" t="s">
+      <c r="H259" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I259" s="48" t="s">
+      <c r="I259" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J259" s="48" t="s">
+      <c r="J259" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K259" s="49" t="s">
+      <c r="K259" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L259" s="49"/>
-      <c r="M259" s="48"/>
-      <c r="N259" s="45"/>
-      <c r="O259" s="43"/>
+      <c r="L259" s="48"/>
+      <c r="M259" s="47"/>
+      <c r="N259" s="44"/>
+      <c r="O259" s="42"/>
     </row>
     <row r="260" spans="3:17">
       <c r="C260" s="1"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="47" t="s">
+      <c r="E260" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F260" t="s">
         <v>39</v>
       </c>
-      <c r="G260" s="45" t="s">
+      <c r="G260" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H260" s="45" t="s">
+      <c r="H260" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I260" s="45" t="s">
+      <c r="I260" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="J260" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K260" s="56" t="s">
+      <c r="J260" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K260" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="L260" s="51"/>
-      <c r="M260" s="52"/>
-      <c r="N260" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O260" s="43" t="s">
+      <c r="L260" s="50"/>
+      <c r="M260" s="51"/>
+      <c r="N260" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O260" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="261" spans="3:17">
       <c r="C261" s="1"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="47" t="s">
+      <c r="E261" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F261" t="s">
         <v>39</v>
       </c>
-      <c r="G261" s="46" t="s">
+      <c r="G261" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H261" s="45" t="s">
+      <c r="H261" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I261" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J261" s="46" t="s">
+      <c r="I261" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J261" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K261" s="46" t="s">
+      <c r="K261" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L261" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M261" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N261" s="46"/>
+      <c r="L261" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M261" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N261" s="45"/>
     </row>
     <row r="262" spans="3:17">
       <c r="D262" s="2"/>
@@ -10688,7 +10685,7 @@
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:8">
       <c r="A57">
-        <f>A56+B56</f>
+        <f t="shared" ref="A57:A62" si="2">A56+B56</f>
         <v>156</v>
       </c>
       <c r="B57">
@@ -10704,7 +10701,7 @@
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:8">
       <c r="A58">
-        <f>A57+B57</f>
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B58">
@@ -10720,7 +10717,7 @@
     </row>
     <row r="59" ht="18" customHeight="1" spans="1:8">
       <c r="A59">
-        <f>A58+B58</f>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B59">
@@ -10736,7 +10733,7 @@
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:8">
       <c r="A60">
-        <f>A59+B59</f>
+        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B60">
@@ -10752,7 +10749,7 @@
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:8">
       <c r="A61">
-        <f>A60+B60</f>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="B61">
@@ -10768,7 +10765,7 @@
     </row>
     <row r="62" ht="35" customHeight="1" spans="1:8">
       <c r="A62">
-        <f>A61+B61</f>
+        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B62">
@@ -10777,7 +10774,7 @@
       <c r="C62" t="s">
         <v>304</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="3" t="s">
         <v>305</v>
       </c>
       <c r="F62" s="3"/>

--- a/辐射报警仪协议命令和寄存器表10.xlsx
+++ b/辐射报警仪协议命令和寄存器表10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="1"/>
+    <workbookView windowWidth="26565" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="具体命令" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="330">
   <si>
     <t>数据</t>
   </si>
@@ -692,7 +692,7 @@
     <t>辐射量*100</t>
   </si>
   <si>
-    <t xml:space="preserve">uint32*100，单位uSv/h
+    <t xml:space="preserve">uint32*100，单位uSv/h 现在这一秒的剂量率（μSv/h）
 </t>
   </si>
   <si>
@@ -779,11 +779,34 @@
     <t>时间（五分钟值）</t>
   </si>
   <si>
-    <t>年月日时分秒 ，data_time[0]:年 data_time[1]:月  data_time[2]:日
-data_time[3]:时 data_time[4]:分  data_time[5]:秒data_time[6，7]预留</t>
+    <t>reg30  | 五分钟窗结束时间 byte0-1 | uint16×1      | 只读 | 见下方「时间编码」
+reg31  | 五分钟窗结束时间 byte2-3 | uint16×1      | 只读 |
+reg32  | 五分钟窗结束时间 byte4-5 | uint16×1      | 只读 |
+reg33  | 五分钟窗结束时间 byte6-7 | uint16×1      | 只读 |
+时间编码（reg30~33，与 reg94 相同格式）：
+  8 字节：[年%100, 月, 日, 时, 分, 秒, 0, 0]
+  例：2026-07-09 11:35:34 → 1A 07 09 0B 23 22 00 00</t>
   </si>
   <si>
     <t>辐射量*100（五分钟值）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reg34  | 五分钟累计剂量低字       | uint16×1      | 只读 | 与 reg35 组成 uint32
+reg35  | 五分钟累计剂量高字       | uint16×1      | 只读 |
+       | （合称 dose_5min / D5）  | uint32 小端   |      |
+       | 刚结束的 5min 窗累计剂量 D5，单位 μSv×100（裸 u32，无单位高位编码）。
+       | 例：0.01 μSv → 1；1.23 μSv → 123。
+       | 由 10 个 30 秒块 D30 相加；与 reg1 瞬时率分离。
+</t>
+  </si>
+  <si>
+    <t>报警阈值设置和其他控制</t>
+  </si>
+  <si>
+    <t>Alart_Threshold1</t>
+  </si>
+  <si>
+    <t>辐射量 报警上阈值*100</t>
   </si>
   <si>
     <t xml:space="preserve">uint16 高两位bit位是单位，00:uSv/h，01:mSv/h,10:Sv/h
@@ -792,15 +815,6 @@
 </t>
   </si>
   <si>
-    <t>报警阈值设置和其他控制</t>
-  </si>
-  <si>
-    <t>Alart_Threshold1</t>
-  </si>
-  <si>
-    <t>辐射量 报警上阈值*100</t>
-  </si>
-  <si>
     <t>读写</t>
   </si>
   <si>
@@ -892,6 +906,10 @@
   </si>
   <si>
     <t>时间</t>
+  </si>
+  <si>
+    <t>年月日时分秒 ，data_time[0]:年 data_time[1]:月  data_time[2]:日
+data_time[3]:时 data_time[4]:分  data_time[5]:秒data_time[6，7]预留</t>
   </si>
   <si>
     <t>char[20]</t>
@@ -960,10 +978,71 @@
 bit11：LORA模式M0                         0为低电平  1 高电平
 bit12: 是否启用声音报警                    0 不启用   1 为启用
 bit13: 是否启用光报警                      0 不启用   1 为启用
-bit14：是否启用屏幕                       0 不启用   1 启用</t>
-  </si>
-  <si>
-    <t>这里和转接板控制有些重合，从机不一定有蓝牙音箱这些</t>
+bit14：是否启用屏幕                       0 不启用   1 启用
+bit15：外置报警器是否在线                  0不在线   1 在线</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ── bit 定义（协议层统一语义）────────────────────────────────────────────
+  bit0  门状态
+        0=打开  1=关闭
+        【reg15 只读，zjb 采样门磁】
+        【reg123 不可写；NeiJi 忽略，恒 0】
+  bit1  PM2.5 电源引脚
+        0=低(断电)  1=高(上电)
+        【仅 zjb：reg123 可写，驱动 PM2_5_POWER_EN】
+        【NeiJi：忽略，恒 0】
+  bit2  PM2.5 复位引脚
+        0=低  1=高
+        【仅 zjb：reg123 可写，驱动 PM2_5_RESET】
+        【NeiJi：忽略，恒 0】
+  bit3  蓝牙音箱暂停键状态 (BT_PIO2)
+        0=低电平  1=高电平（低电平=按下）
+        【仅 zjb：reg15 只读采样；reg123 可写输出】
+        【NeiJi：忽略，恒 0】
+  bit4  蓝牙音箱音量-键 (BT_PIO3)
+        0=低电平  1=高电平（低电平=按下）
+        【仅 zjb】
+  bit5  蓝牙音箱音量+键 (BT_PIO4)
+        0=低电平  1=高电平（低电平=按下）
+        【仅 zjb】
+  bit6  蓝牙音箱静音键 (AUDIO_MUTE)
+        0=低电平  1=高电平（高电平=静音）
+        【仅 zjb】
+  bit7  风扇开关
+        0=关闭  1=开启
+        【仅 zjb：reg123 可写，Fan_Set 控制】
+  bit8  USB 路由选择 (USB_SEL)
+        0=USB2（识别/充电/默认口）
+        1=USB3（下程序口）
+        【仅 zjb：reg123 可写】
+        注：硬件命名以原理图为准；勿与旧文档 USB3/USB4 混用。
+  bit9  LoRa 使能
+        0=关  1=开
+        【zjb】LoRa 模块电源引脚 + 协议桥接总开关（断电且不走 LoRa）
+        【NeiJi】LoRa 协议输出软件开关（无 LoRa 电源脚，仅控制收发/上报）
+        语义统一为「LoRa 功能开关」，物理实现因设备而异。
+  bit10 LoRa 模式 M1
+        0=低  1=高
+        【仅 zjb：reg123 可写，驱动 LORA_M1】
+  bit11 LoRa 模式 M0
+        0=低  1=高
+        【仅 zjb：reg123 可写，驱动 LORA_M0】
+  bit12 声音报警使能（历史位）
+        0=不启用  1=启用
+        【NeiJi：不使用；声报警请写 reg122 音量】
+        【zjb：已废弃，Flash 升级时强制清 0；上位机写 reg123 时应保持 0】
+  bit13 光报警使能
+        0=不启用  1=启用
+        【NeiJi / zjb 共用】NeiJi 立即生效；zjb 存 Flash（本板不直接驱动光报警 GPIO）
+  bit14 屏幕/背光使能
+        0=不启用  1=启用
+        【NeiJi / zjb 共用】NeiJi 立即控制背光；zjb 存 Flash
+  bit15 外置报警器在线
+        0=不在线  1=在线
+        【只读，写入无效】
+        【NeiJi：当前未接 IO，恒 0（预留）】
+        【zjb：当前恒 0（预留）】
+  bit16~31  保留，读 0，写 0</t>
   </si>
   <si>
     <t>uchar[16]</t>
@@ -1002,49 +1081,58 @@
     <t>灵敏度</t>
   </si>
   <si>
-    <t>int33</t>
-  </si>
-  <si>
     <t>EWMA threshold_cps</t>
   </si>
   <si>
-    <t>int34</t>
-  </si>
-  <si>
     <t>EWMA threshold_delta</t>
   </si>
   <si>
-    <t>int35</t>
-  </si>
-  <si>
     <t>EWMA alpha_low</t>
   </si>
   <si>
-    <t>int36</t>
-  </si>
-  <si>
     <t>EWMA alpha_high</t>
   </si>
   <si>
-    <t>int37</t>
-  </si>
-  <si>
     <t>EWMA boost_duration</t>
   </si>
   <si>
-    <t>int38</t>
-  </si>
-  <si>
     <t>EWMA_limit</t>
   </si>
   <si>
+    <t>EWMA_cpm</t>
+  </si>
+  <si>
+    <t>盖革本底cpm</t>
+  </si>
+  <si>
     <t xml:space="preserve">dhcp 1 使能 </t>
   </si>
   <si>
+    <t>dead_time_us</t>
+  </si>
+  <si>
+    <t>死时间，协议值×100（μs）；0=不修正</t>
+  </si>
+  <si>
     <t>语言 0中文 1英文</t>
   </si>
   <si>
     <t>硬件版本</t>
+  </si>
+  <si>
+    <t>geiger_sec_cps</t>
+  </si>
+  <si>
+    <t>上一秒盖革 CPS，不落 Flash</t>
+  </si>
+  <si>
+    <t>4*uint8</t>
+  </si>
+  <si>
+    <t>current_ip</t>
+  </si>
+  <si>
+    <t>W5500 当前 SIPR，不落 Flash</t>
   </si>
   <si>
     <t>程序更新</t>
@@ -2062,7 +2150,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2080,6 +2168,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2833,243 +2924,243 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
       <c r="Y4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="3:26">
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="9" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="9"/>
+      <c r="Z5" s="10"/>
     </row>
     <row r="6" spans="3:26">
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13" t="s">
+      <c r="G6" s="13"/>
+      <c r="H6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="15" t="s">
+      <c r="I6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11" t="s">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11" t="s">
+      <c r="S6" s="12"/>
+      <c r="T6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11" t="s">
+      <c r="U6" s="12"/>
+      <c r="V6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="W6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="X6" s="11" t="s">
+      <c r="X6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
     </row>
     <row r="7" spans="3:26">
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="18" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="19" t="s">
+      <c r="I7" s="21"/>
+      <c r="J7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="19" t="s">
+      <c r="K7" s="21"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="18" t="s">
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="18" t="s">
+      <c r="S7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="T7" s="18" t="s">
+      <c r="T7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="U7" s="18" t="s">
+      <c r="U7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="18" t="s">
+      <c r="V7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="18" t="s">
+      <c r="W7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
     </row>
     <row r="8" spans="3:26">
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
     </row>
     <row r="9" spans="3:26">
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
     </row>
     <row r="10" spans="3:26">
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
     </row>
     <row r="12" spans="3:26">
       <c r="E12" s="3"/>
@@ -3194,7 +3285,7 @@
       <c r="H18" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="32" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="1"/>
@@ -3428,18 +3519,18 @@
       <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="32" t="s">
         <v>66</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="32" t="s">
+      <c r="L24" s="33" t="s">
         <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
@@ -3474,13 +3565,13 @@
       <c r="H25" t="s">
         <v>47</v>
       </c>
-      <c r="I25" s="33" t="s">
+      <c r="I25" s="34" t="s">
         <v>69</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
       </c>
-      <c r="M25" s="34" t="s">
+      <c r="M25" s="35" t="s">
         <v>70</v>
       </c>
       <c r="P25" s="1"/>
@@ -3505,13 +3596,13 @@
       <c r="H26" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="33" t="s">
+      <c r="I26" s="34" t="s">
         <v>72</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="35" t="s">
+      <c r="M26" s="36" t="s">
         <v>17</v>
       </c>
       <c r="P26" s="1"/>
@@ -3536,13 +3627,13 @@
       <c r="H27" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="33" t="s">
+      <c r="I27" s="34" t="s">
         <v>73</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="35" t="s">
+      <c r="M27" s="36" t="s">
         <v>17</v>
       </c>
       <c r="P27" s="1"/>
@@ -3567,13 +3658,13 @@
       <c r="H28" t="s">
         <v>47</v>
       </c>
-      <c r="I28" s="33" t="s">
+      <c r="I28" s="34" t="s">
         <v>74</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>17</v>
       </c>
       <c r="N28" s="1"/>
@@ -3611,7 +3702,7 @@
       <c r="L29" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="35" t="s">
         <v>77</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -3657,13 +3748,13 @@
       <c r="F32" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="33" t="s">
         <v>46</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="I32" s="37" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="1"/>
@@ -3685,59 +3776,59 @@
       </c>
     </row>
     <row r="36" spans="3:17">
-      <c r="E36" s="37"/>
-      <c r="F36" s="38" t="s">
+      <c r="E36" s="38"/>
+      <c r="F36" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="39" t="s">
+      <c r="H36" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39" t="s">
+      <c r="I36" s="40"/>
+      <c r="J36" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K36" s="39"/>
-      <c r="L36" s="38" t="s">
+      <c r="K36" s="40"/>
+      <c r="L36" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="38" t="s">
+      <c r="M36" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N36" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="38"/>
-      <c r="Q36" s="38"/>
+      <c r="N36" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
     </row>
     <row r="37" spans="3:17">
-      <c r="F37" s="40"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41" t="s">
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="41" t="s">
+      <c r="I37" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="41" t="s">
+      <c r="J37" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="41" t="s">
+      <c r="K37" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41" t="s">
+      <c r="L37" s="42"/>
+      <c r="M37" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="42"/>
-      <c r="Q37" s="42"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="1" t="s">
@@ -3746,46 +3837,46 @@
       <c r="D38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="44" t="s">
+      <c r="F38" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G38" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="I38" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J38" s="44" t="s">
+      <c r="I38" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K38" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L38" s="44" t="s">
+      <c r="K38" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M38" s="44" t="s">
+      <c r="M38" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" s="42"/>
-      <c r="Q38" s="42"/>
+      <c r="N38" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
     </row>
     <row r="39" spans="3:17">
       <c r="C39" s="1"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F39" t="s">
@@ -3816,7 +3907,7 @@
     <row r="40" spans="3:17">
       <c r="C40" s="1"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F40" t="s">
@@ -3847,187 +3938,187 @@
     <row r="41" spans="3:17">
       <c r="C41" s="1"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="38" t="s">
+      <c r="E41" s="47"/>
+      <c r="F41" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G41" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="39" t="s">
+      <c r="H41" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39" t="s">
+      <c r="I41" s="40"/>
+      <c r="J41" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K41" s="39"/>
-      <c r="L41" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N41" s="38"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="38"/>
-      <c r="Q41" s="38"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="1"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="46" t="s">
+      <c r="E42" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="H42" s="44" t="s">
+      <c r="H42" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="I42" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42" s="44" t="s">
+      <c r="I42" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K42" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M42" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N42" s="45"/>
+      <c r="K42" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L42" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="46"/>
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="1"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="47" t="s">
+      <c r="E43" s="47"/>
+      <c r="F43" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="47" t="s">
+      <c r="G43" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="47" t="s">
+      <c r="H43" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J43" s="47" t="s">
+      <c r="J43" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K43" s="48" t="s">
+      <c r="K43" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L43" s="48"/>
-      <c r="M43" s="47"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="48"/>
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="1"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="46" t="s">
+      <c r="E44" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="G44" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H44" s="44" t="s">
+      <c r="H44" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I44" s="44" t="s">
+      <c r="I44" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="J44" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K44" s="49" t="s">
+      <c r="J44" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O44" s="42" t="s">
+      <c r="L44" s="51"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="1"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="46" t="s">
+      <c r="E45" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="I45" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" s="45" t="s">
+      <c r="I45" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K45" s="45" t="s">
+      <c r="K45" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L45" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M45" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N45" s="45"/>
+      <c r="L45" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="46"/>
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="1"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="3:17">
-      <c r="F47" s="38" t="s">
+      <c r="F47" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="38" t="s">
+      <c r="G47" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="39" t="s">
+      <c r="H47" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39" t="s">
+      <c r="I47" s="40"/>
+      <c r="J47" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K47" s="39"/>
-      <c r="L47" s="38" t="s">
+      <c r="K47" s="40"/>
+      <c r="L47" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M47" s="38" t="s">
+      <c r="M47" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N47" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" s="38"/>
-      <c r="Q47" s="38"/>
+      <c r="N47" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" s="39"/>
+      <c r="Q47" s="39"/>
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="1" t="s">
@@ -4036,46 +4127,46 @@
       <c r="D48" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="43" t="s">
+      <c r="E48" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F48" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" s="44" t="s">
+      <c r="F48" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H48" s="44" t="s">
+      <c r="H48" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="I48" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" s="44" t="s">
+      <c r="I48" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K48" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L48" s="44" t="s">
+      <c r="K48" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L48" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M48" s="44" t="s">
+      <c r="M48" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="N48" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
+      <c r="N48" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="45"/>
+      <c r="Q48" s="45"/>
     </row>
     <row r="49" spans="3:17">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F49" t="s">
@@ -4106,7 +4197,7 @@
     <row r="50" spans="3:17">
       <c r="C50" s="1"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F50" t="s">
@@ -4137,184 +4228,184 @@
     <row r="51" spans="3:17">
       <c r="C51" s="1"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="38" t="s">
+      <c r="E51" s="47"/>
+      <c r="F51" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="38" t="s">
+      <c r="G51" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H51" s="39" t="s">
+      <c r="H51" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39" t="s">
+      <c r="I51" s="40"/>
+      <c r="J51" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K51" s="39"/>
-      <c r="L51" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M51" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" s="38"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M51" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="39"/>
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="1"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="46" t="s">
+      <c r="E52" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="45" t="s">
+      <c r="G52" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="44" t="s">
+      <c r="H52" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="I52" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J52" s="44" t="s">
+      <c r="I52" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K52" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L52" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M52" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" s="45"/>
+      <c r="K52" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L52" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="46"/>
     </row>
     <row r="53" spans="3:17">
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="47" t="s">
+      <c r="E53" s="47"/>
+      <c r="F53" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H53" s="47" t="s">
+      <c r="H53" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I53" s="47" t="s">
+      <c r="I53" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J53" s="47" t="s">
+      <c r="J53" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K53" s="48" t="s">
+      <c r="K53" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L53" s="48"/>
-      <c r="M53" s="47"/>
+      <c r="L53" s="49"/>
+      <c r="M53" s="48"/>
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="1"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="46" t="s">
+      <c r="E54" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="44" t="s">
+      <c r="G54" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H54" s="44" t="s">
+      <c r="H54" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I54" s="44" t="s">
+      <c r="I54" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="J54" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K54" s="49" t="s">
+      <c r="J54" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="L54" s="50"/>
-      <c r="M54" s="51"/>
-      <c r="N54" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" s="42" t="s">
+      <c r="L54" s="51"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="1"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="46" t="s">
+      <c r="E55" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H55" s="44" t="s">
+      <c r="H55" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="I55" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J55" s="45" t="s">
+      <c r="I55" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K55" s="45" t="s">
+      <c r="K55" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L55" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M55" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N55" s="45"/>
+      <c r="L55" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="46"/>
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="1"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="3:17">
-      <c r="F57" s="38" t="s">
+      <c r="F57" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G57" s="38" t="s">
+      <c r="G57" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="H57" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39" t="s">
+      <c r="I57" s="40"/>
+      <c r="J57" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K57" s="39"/>
-      <c r="L57" s="38" t="s">
+      <c r="K57" s="40"/>
+      <c r="L57" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M57" s="38" t="s">
+      <c r="M57" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N57" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O57" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
+      <c r="N57" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" s="39"/>
+      <c r="Q57" s="39"/>
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="1" t="s">
@@ -4323,44 +4414,44 @@
       <c r="D58" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E58" s="43" t="s">
+      <c r="E58" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F58" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="44" t="s">
+      <c r="F58" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="44" t="s">
+      <c r="H58" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I58" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J58" s="44" t="s">
+      <c r="I58" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K58" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="44" t="s">
+      <c r="K58" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L58" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M58" s="44" t="s">
+      <c r="M58" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="N58" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O58" s="42" t="s">
+      <c r="N58" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O58" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="1"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F59" t="s">
@@ -4391,7 +4482,7 @@
     <row r="60" spans="3:17">
       <c r="C60" s="1"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F60" t="s">
@@ -4422,184 +4513,184 @@
     <row r="61" spans="3:17">
       <c r="C61" s="1"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="38" t="s">
+      <c r="E61" s="47"/>
+      <c r="F61" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="38" t="s">
+      <c r="G61" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H61" s="39" t="s">
+      <c r="H61" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39" t="s">
+      <c r="I61" s="40"/>
+      <c r="J61" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K61" s="39"/>
-      <c r="L61" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M61" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="38"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M61" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="39"/>
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="1"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="46" t="s">
+      <c r="E62" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
       </c>
-      <c r="G62" s="45" t="s">
+      <c r="G62" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="44" t="s">
+      <c r="H62" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I62" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J62" s="44" t="s">
+      <c r="I62" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K62" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L62" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M62" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="45"/>
+      <c r="K62" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L62" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M62" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="46"/>
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="1"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="47" t="s">
+      <c r="E63" s="47"/>
+      <c r="F63" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G63" s="47" t="s">
+      <c r="G63" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="47" t="s">
+      <c r="H63" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="47" t="s">
+      <c r="I63" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J63" s="47" t="s">
+      <c r="J63" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K63" s="48" t="s">
+      <c r="K63" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L63" s="48"/>
-      <c r="M63" s="47"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="48"/>
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="1"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="46" t="s">
+      <c r="E64" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
       </c>
-      <c r="G64" s="44" t="s">
+      <c r="G64" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H64" s="44" t="s">
+      <c r="H64" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I64" s="44" t="s">
+      <c r="I64" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="J64" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" s="49" t="s">
+      <c r="J64" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="L64" s="50"/>
-      <c r="M64" s="51"/>
-      <c r="N64" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="42" t="s">
+      <c r="L64" s="51"/>
+      <c r="M64" s="52"/>
+      <c r="N64" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O64" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="65" spans="3:17">
       <c r="C65" s="1"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="46" t="s">
+      <c r="E65" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F65" t="s">
         <v>39</v>
       </c>
-      <c r="G65" s="45" t="s">
+      <c r="G65" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H65" s="44" t="s">
+      <c r="H65" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I65" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65" s="45" t="s">
+      <c r="I65" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K65" s="45" t="s">
+      <c r="K65" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L65" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M65" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N65" s="45"/>
+      <c r="L65" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M65" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="46"/>
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="1"/>
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="3:17">
-      <c r="F67" s="38" t="s">
+      <c r="F67" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G67" s="38" t="s">
+      <c r="G67" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H67" s="39" t="s">
+      <c r="H67" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39" t="s">
+      <c r="I67" s="40"/>
+      <c r="J67" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K67" s="39"/>
-      <c r="L67" s="38" t="s">
+      <c r="K67" s="40"/>
+      <c r="L67" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M67" s="38" t="s">
+      <c r="M67" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N67" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O67" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P67" s="38"/>
-      <c r="Q67" s="38"/>
+      <c r="N67" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O67" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="1" t="s">
@@ -4608,44 +4699,44 @@
       <c r="D68" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="43" t="s">
+      <c r="E68" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F68" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="44" t="s">
+      <c r="F68" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H68" s="44" t="s">
+      <c r="H68" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J68" s="44" t="s">
+      <c r="I68" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K68" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L68" s="44" t="s">
+      <c r="K68" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L68" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M68" s="44" t="s">
+      <c r="M68" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="N68" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O68" s="42" t="s">
+      <c r="N68" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="1"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="45" t="s">
+      <c r="E69" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F69" t="s">
@@ -4676,7 +4767,7 @@
     <row r="70" spans="3:17">
       <c r="C70" s="1"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="45" t="s">
+      <c r="E70" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F70" t="s">
@@ -4707,184 +4798,184 @@
     <row r="71" spans="3:17">
       <c r="C71" s="1"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="38" t="s">
+      <c r="E71" s="47"/>
+      <c r="F71" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G71" s="38" t="s">
+      <c r="G71" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H71" s="39" t="s">
+      <c r="H71" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39" t="s">
+      <c r="I71" s="40"/>
+      <c r="J71" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K71" s="39"/>
-      <c r="L71" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M71" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N71" s="38"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M71" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="39"/>
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="1"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="46" t="s">
+      <c r="E72" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F72" t="s">
         <v>39</v>
       </c>
-      <c r="G72" s="45" t="s">
+      <c r="G72" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="44" t="s">
+      <c r="H72" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I72" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J72" s="44" t="s">
+      <c r="I72" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K72" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L72" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M72" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N72" s="45"/>
+      <c r="K72" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="46"/>
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="47" t="s">
+      <c r="E73" s="47"/>
+      <c r="F73" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G73" s="47" t="s">
+      <c r="G73" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H73" s="47" t="s">
+      <c r="H73" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I73" s="47" t="s">
+      <c r="I73" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J73" s="47" t="s">
+      <c r="J73" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K73" s="48" t="s">
+      <c r="K73" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L73" s="48"/>
-      <c r="M73" s="47"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="48"/>
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="1"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="46" t="s">
+      <c r="E74" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="44" t="s">
+      <c r="G74" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H74" s="44" t="s">
+      <c r="H74" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I74" s="44" t="s">
+      <c r="I74" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="J74" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K74" s="49" t="s">
+      <c r="J74" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="L74" s="50"/>
-      <c r="M74" s="51"/>
-      <c r="N74" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O74" s="42" t="s">
+      <c r="L74" s="51"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O74" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="1"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="46" t="s">
+      <c r="E75" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F75" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="45" t="s">
+      <c r="G75" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H75" s="44" t="s">
+      <c r="H75" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I75" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J75" s="45" t="s">
+      <c r="I75" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J75" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K75" s="45" t="s">
+      <c r="K75" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L75" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M75" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N75" s="45"/>
+      <c r="L75" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M75" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75" s="46"/>
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="1"/>
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="3:17">
-      <c r="F77" s="38" t="s">
+      <c r="F77" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="38" t="s">
+      <c r="G77" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H77" s="39" t="s">
+      <c r="H77" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39" t="s">
+      <c r="I77" s="40"/>
+      <c r="J77" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K77" s="39"/>
-      <c r="L77" s="38" t="s">
+      <c r="K77" s="40"/>
+      <c r="L77" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M77" s="38" t="s">
+      <c r="M77" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N77" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O77" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P77" s="38"/>
-      <c r="Q77" s="38"/>
+      <c r="N77" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P77" s="39"/>
+      <c r="Q77" s="39"/>
     </row>
     <row r="78" spans="3:17">
       <c r="C78" s="1" t="s">
@@ -4893,44 +4984,44 @@
       <c r="D78" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="43" t="s">
+      <c r="E78" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="44" t="s">
+      <c r="F78" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H78" s="44" t="s">
+      <c r="H78" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I78" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="44" t="s">
+      <c r="I78" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K78" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L78" s="44" t="s">
+      <c r="K78" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L78" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M78" s="52" t="s">
+      <c r="M78" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="N78" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O78" s="42" t="s">
+      <c r="N78" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="1"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="45" t="s">
+      <c r="E79" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F79" t="s">
@@ -4961,7 +5052,7 @@
     <row r="80" spans="3:17">
       <c r="C80" s="1"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="45" t="s">
+      <c r="E80" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F80" t="s">
@@ -4992,184 +5083,184 @@
     <row r="81" spans="3:17">
       <c r="C81" s="1"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="46"/>
-      <c r="F81" s="38" t="s">
+      <c r="E81" s="47"/>
+      <c r="F81" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G81" s="38" t="s">
+      <c r="G81" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H81" s="39" t="s">
+      <c r="H81" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39" t="s">
+      <c r="I81" s="40"/>
+      <c r="J81" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K81" s="39"/>
-      <c r="L81" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M81" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N81" s="38"/>
+      <c r="K81" s="40"/>
+      <c r="L81" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M81" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81" s="39"/>
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="1"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="46" t="s">
+      <c r="E82" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F82" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="45" t="s">
+      <c r="G82" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="44" t="s">
+      <c r="H82" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I82" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J82" s="44" t="s">
+      <c r="I82" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K82" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L82" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M82" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N82" s="45"/>
+      <c r="K82" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L82" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M82" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N82" s="46"/>
     </row>
     <row r="83" spans="3:17">
       <c r="C83" s="1"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="47" t="s">
+      <c r="E83" s="47"/>
+      <c r="F83" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G83" s="47" t="s">
+      <c r="G83" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H83" s="47" t="s">
+      <c r="H83" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I83" s="47" t="s">
+      <c r="I83" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J83" s="47" t="s">
+      <c r="J83" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K83" s="48" t="s">
+      <c r="K83" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L83" s="48"/>
-      <c r="M83" s="47"/>
+      <c r="L83" s="49"/>
+      <c r="M83" s="48"/>
     </row>
     <row r="84" spans="3:17">
       <c r="C84" s="1"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="46" t="s">
+      <c r="E84" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F84" t="s">
         <v>39</v>
       </c>
-      <c r="G84" s="44" t="s">
+      <c r="G84" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H84" s="44" t="s">
+      <c r="H84" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I84" s="44" t="s">
+      <c r="I84" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="49" t="s">
+      <c r="J84" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="L84" s="50"/>
-      <c r="M84" s="51"/>
-      <c r="N84" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O84" s="42" t="s">
+      <c r="L84" s="51"/>
+      <c r="M84" s="52"/>
+      <c r="N84" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O84" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="1"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="46" t="s">
+      <c r="E85" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>39</v>
       </c>
-      <c r="G85" s="45" t="s">
+      <c r="G85" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H85" s="44" t="s">
+      <c r="H85" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I85" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" s="45" t="s">
+      <c r="I85" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K85" s="45" t="s">
+      <c r="K85" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L85" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M85" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N85" s="45"/>
+      <c r="L85" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M85" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="46"/>
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
     </row>
     <row r="87" spans="3:17">
-      <c r="F87" s="38" t="s">
+      <c r="F87" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H87" s="39" t="s">
+      <c r="H87" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I87" s="39"/>
-      <c r="J87" s="39" t="s">
+      <c r="I87" s="40"/>
+      <c r="J87" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K87" s="39"/>
-      <c r="L87" s="38" t="s">
+      <c r="K87" s="40"/>
+      <c r="L87" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M87" s="38" t="s">
+      <c r="M87" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N87" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O87" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P87" s="38"/>
-      <c r="Q87" s="38"/>
+      <c r="N87" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O87" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P87" s="39"/>
+      <c r="Q87" s="39"/>
     </row>
     <row r="88" spans="3:17">
       <c r="C88" s="1" t="s">
@@ -5178,44 +5269,44 @@
       <c r="D88" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E88" s="43" t="s">
+      <c r="E88" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F88" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G88" s="44" t="s">
+      <c r="F88" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G88" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="44" t="s">
+      <c r="H88" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="I88" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J88" s="44" t="s">
+      <c r="I88" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K88" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L88" s="44" t="s">
+      <c r="K88" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L88" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M88" s="52" t="s">
+      <c r="M88" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="N88" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O88" s="42" t="s">
+      <c r="N88" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="89" spans="3:17">
       <c r="C89" s="1"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="45" t="s">
+      <c r="E89" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F89" t="s">
@@ -5246,7 +5337,7 @@
     <row r="90" spans="3:17">
       <c r="C90" s="1"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="45" t="s">
+      <c r="E90" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F90" t="s">
@@ -5277,158 +5368,158 @@
     <row r="91" spans="3:17">
       <c r="C91" s="1"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="46" t="s">
+      <c r="E91" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F91" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="45" t="s">
+      <c r="G91" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="44" t="s">
+      <c r="H91" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="I91" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J91" s="44" t="s">
+      <c r="I91" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J91" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K91" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L91" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M91" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N91" s="45"/>
+      <c r="K91" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L91" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M91" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N91" s="46"/>
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="46"/>
-      <c r="F92" s="47" t="s">
+      <c r="E92" s="47"/>
+      <c r="F92" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="47" t="s">
+      <c r="G92" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H92" s="47" t="s">
+      <c r="H92" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I92" s="47" t="s">
+      <c r="I92" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J92" s="47" t="s">
+      <c r="J92" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K92" s="48" t="s">
+      <c r="K92" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L92" s="48"/>
-      <c r="M92" s="47"/>
+      <c r="L92" s="49"/>
+      <c r="M92" s="48"/>
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="1"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="46" t="s">
+      <c r="E93" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F93" t="s">
         <v>39</v>
       </c>
-      <c r="G93" s="44" t="s">
+      <c r="G93" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H93" s="44" t="s">
+      <c r="H93" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I93" s="44" t="s">
+      <c r="I93" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="J93" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" s="49" t="s">
+      <c r="J93" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K93" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="L93" s="50"/>
-      <c r="M93" s="51"/>
-      <c r="N93" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O93" s="42" t="s">
+      <c r="L93" s="51"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O93" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="1"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="46" t="s">
+      <c r="E94" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F94" t="s">
         <v>39</v>
       </c>
-      <c r="G94" s="45" t="s">
+      <c r="G94" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H94" s="44" t="s">
+      <c r="H94" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="I94" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J94" s="45" t="s">
+      <c r="I94" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K94" s="45" t="s">
+      <c r="K94" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L94" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M94" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N94" s="45"/>
+      <c r="L94" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M94" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94" s="46"/>
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="1"/>
       <c r="D95" s="2"/>
     </row>
     <row r="96" spans="3:17">
-      <c r="F96" s="38" t="s">
+      <c r="F96" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G96" s="38" t="s">
+      <c r="G96" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H96" s="39" t="s">
+      <c r="H96" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I96" s="39"/>
-      <c r="J96" s="39" t="s">
+      <c r="I96" s="40"/>
+      <c r="J96" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K96" s="39"/>
-      <c r="L96" s="38" t="s">
+      <c r="K96" s="40"/>
+      <c r="L96" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M96" s="38" t="s">
+      <c r="M96" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N96" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O96" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P96" s="38"/>
-      <c r="Q96" s="38"/>
+      <c r="N96" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O96" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" s="39"/>
+      <c r="Q96" s="39"/>
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="1" t="s">
@@ -5437,44 +5528,44 @@
       <c r="D97" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E97" s="43" t="s">
+      <c r="E97" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F97" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="44" t="s">
+      <c r="F97" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H97" s="44" t="s">
+      <c r="H97" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="I97" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J97" s="44" t="s">
+      <c r="I97" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K97" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L97" s="44" t="s">
+      <c r="K97" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L97" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M97" s="44" t="s">
+      <c r="M97" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="N97" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O97" s="42" t="s">
+      <c r="N97" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O97" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="98" spans="3:17">
       <c r="C98" s="1"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="45" t="s">
+      <c r="E98" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F98" t="s">
@@ -5505,7 +5596,7 @@
     <row r="99" spans="3:17">
       <c r="C99" s="1"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="45" t="s">
+      <c r="E99" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F99" t="s">
@@ -5536,158 +5627,158 @@
     <row r="100" spans="3:17">
       <c r="C100" s="1"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="46" t="s">
+      <c r="E100" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F100" t="s">
         <v>39</v>
       </c>
-      <c r="G100" s="45" t="s">
+      <c r="G100" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="44" t="s">
+      <c r="H100" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="I100" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J100" s="44" t="s">
+      <c r="I100" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J100" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K100" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L100" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M100" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N100" s="45"/>
+      <c r="K100" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L100" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N100" s="46"/>
     </row>
     <row r="101" spans="3:17">
       <c r="C101" s="1"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="47" t="s">
+      <c r="E101" s="47"/>
+      <c r="F101" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="47" t="s">
+      <c r="G101" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H101" s="47" t="s">
+      <c r="H101" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I101" s="47" t="s">
+      <c r="I101" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J101" s="47" t="s">
+      <c r="J101" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K101" s="48" t="s">
+      <c r="K101" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L101" s="48"/>
-      <c r="M101" s="47"/>
+      <c r="L101" s="49"/>
+      <c r="M101" s="48"/>
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="1"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="46" t="s">
+      <c r="E102" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F102" t="s">
         <v>39</v>
       </c>
-      <c r="G102" s="44" t="s">
+      <c r="G102" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H102" s="44" t="s">
+      <c r="H102" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I102" s="44" t="s">
+      <c r="I102" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="J102" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="49" t="s">
+      <c r="J102" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="L102" s="50"/>
-      <c r="M102" s="51"/>
-      <c r="N102" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O102" s="42" t="s">
+      <c r="L102" s="51"/>
+      <c r="M102" s="52"/>
+      <c r="N102" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O102" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="1"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="46" t="s">
+      <c r="E103" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F103" t="s">
         <v>39</v>
       </c>
-      <c r="G103" s="45" t="s">
+      <c r="G103" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H103" s="44" t="s">
+      <c r="H103" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="I103" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="45" t="s">
+      <c r="I103" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K103" s="45" t="s">
+      <c r="K103" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L103" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M103" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N103" s="45"/>
+      <c r="L103" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M103" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N103" s="46"/>
     </row>
     <row r="104" spans="3:17">
       <c r="C104" s="1"/>
       <c r="D104" s="2"/>
     </row>
     <row r="105" spans="3:17">
-      <c r="F105" s="38" t="s">
+      <c r="F105" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="38" t="s">
+      <c r="G105" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="39" t="s">
+      <c r="H105" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I105" s="39"/>
-      <c r="J105" s="39" t="s">
+      <c r="I105" s="40"/>
+      <c r="J105" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K105" s="39"/>
-      <c r="L105" s="38" t="s">
+      <c r="K105" s="40"/>
+      <c r="L105" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M105" s="38" t="s">
+      <c r="M105" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N105" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O105" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P105" s="38"/>
-      <c r="Q105" s="38"/>
+      <c r="N105" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O105" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P105" s="39"/>
+      <c r="Q105" s="39"/>
     </row>
     <row r="106" spans="3:17">
       <c r="C106" s="1" t="s">
@@ -5696,44 +5787,44 @@
       <c r="D106" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E106" s="43" t="s">
+      <c r="E106" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F106" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G106" s="44" t="s">
+      <c r="F106" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G106" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H106" s="44" t="s">
+      <c r="H106" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="I106" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J106" s="44" t="s">
+      <c r="I106" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J106" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K106" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="44" t="s">
+      <c r="K106" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M106" s="44" t="s">
+      <c r="M106" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="N106" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O106" s="42" t="s">
+      <c r="N106" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O106" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="1"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="45" t="s">
+      <c r="E107" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F107" t="s">
@@ -5764,7 +5855,7 @@
     <row r="108" spans="3:17">
       <c r="C108" s="1"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="45" t="s">
+      <c r="E108" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F108" t="s">
@@ -5795,158 +5886,158 @@
     <row r="109" spans="3:17">
       <c r="C109" s="1"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="46" t="s">
+      <c r="E109" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F109" t="s">
         <v>39</v>
       </c>
-      <c r="G109" s="45" t="s">
+      <c r="G109" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H109" s="44" t="s">
+      <c r="H109" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="I109" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="44" t="s">
+      <c r="I109" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K109" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L109" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M109" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N109" s="45"/>
+      <c r="K109" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L109" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M109" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N109" s="46"/>
     </row>
     <row r="110" spans="3:17">
       <c r="C110" s="1"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="46"/>
-      <c r="F110" s="47" t="s">
+      <c r="E110" s="47"/>
+      <c r="F110" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="47" t="s">
+      <c r="G110" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H110" s="47" t="s">
+      <c r="H110" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I110" s="47" t="s">
+      <c r="I110" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J110" s="47" t="s">
+      <c r="J110" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K110" s="48" t="s">
+      <c r="K110" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L110" s="48"/>
-      <c r="M110" s="47"/>
+      <c r="L110" s="49"/>
+      <c r="M110" s="48"/>
     </row>
     <row r="111" spans="3:17">
       <c r="C111" s="1"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="46" t="s">
+      <c r="E111" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F111" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="44" t="s">
+      <c r="G111" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H111" s="44" t="s">
+      <c r="H111" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I111" s="44" t="s">
+      <c r="I111" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="J111" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" s="49" t="s">
+      <c r="J111" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="L111" s="50"/>
-      <c r="M111" s="51"/>
-      <c r="N111" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O111" s="42" t="s">
+      <c r="L111" s="51"/>
+      <c r="M111" s="52"/>
+      <c r="N111" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O111" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="112" spans="3:17">
       <c r="C112" s="1"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="46" t="s">
+      <c r="E112" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F112" t="s">
         <v>39</v>
       </c>
-      <c r="G112" s="45" t="s">
+      <c r="G112" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H112" s="44" t="s">
+      <c r="H112" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="I112" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J112" s="45" t="s">
+      <c r="I112" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J112" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K112" s="45" t="s">
+      <c r="K112" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L112" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M112" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N112" s="45"/>
+      <c r="L112" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M112" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N112" s="46"/>
     </row>
     <row r="113" spans="3:17">
       <c r="C113" s="1"/>
       <c r="D113" s="2"/>
     </row>
     <row r="114" spans="3:17">
-      <c r="F114" s="38" t="s">
+      <c r="F114" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G114" s="38" t="s">
+      <c r="G114" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H114" s="39" t="s">
+      <c r="H114" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I114" s="39"/>
-      <c r="J114" s="39" t="s">
+      <c r="I114" s="40"/>
+      <c r="J114" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="39"/>
-      <c r="L114" s="38" t="s">
+      <c r="K114" s="40"/>
+      <c r="L114" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M114" s="38" t="s">
+      <c r="M114" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N114" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O114" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P114" s="38"/>
-      <c r="Q114" s="38"/>
+      <c r="N114" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O114" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P114" s="39"/>
+      <c r="Q114" s="39"/>
     </row>
     <row r="115" spans="3:17">
       <c r="C115" s="1" t="s">
@@ -5955,44 +6046,44 @@
       <c r="D115" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E115" s="43" t="s">
+      <c r="E115" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F115" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G115" s="44" t="s">
+      <c r="F115" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G115" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H115" s="44" t="s">
+      <c r="H115" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="I115" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J115" s="44" t="s">
+      <c r="I115" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J115" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K115" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L115" s="44" t="s">
+      <c r="K115" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L115" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M115" s="52" t="s">
+      <c r="M115" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="N115" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O115" s="42" t="s">
+      <c r="N115" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O115" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="116" spans="3:17">
       <c r="C116" s="1"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="45" t="s">
+      <c r="E116" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F116" t="s">
@@ -6023,7 +6114,7 @@
     <row r="117" spans="3:17">
       <c r="C117" s="1"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="45" t="s">
+      <c r="E117" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F117" t="s">
@@ -6054,158 +6145,158 @@
     <row r="118" spans="3:17">
       <c r="C118" s="1"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="46" t="s">
+      <c r="E118" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F118" t="s">
         <v>39</v>
       </c>
-      <c r="G118" s="45" t="s">
+      <c r="G118" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H118" s="44" t="s">
+      <c r="H118" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="I118" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J118" s="44" t="s">
+      <c r="I118" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J118" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K118" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L118" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M118" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N118" s="45"/>
+      <c r="K118" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L118" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M118" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N118" s="46"/>
     </row>
     <row r="119" spans="3:17">
       <c r="C119" s="1"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="46"/>
-      <c r="F119" s="47" t="s">
+      <c r="E119" s="47"/>
+      <c r="F119" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="47" t="s">
+      <c r="G119" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H119" s="47" t="s">
+      <c r="H119" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I119" s="47" t="s">
+      <c r="I119" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J119" s="47" t="s">
+      <c r="J119" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K119" s="48" t="s">
+      <c r="K119" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L119" s="48"/>
-      <c r="M119" s="47"/>
+      <c r="L119" s="49"/>
+      <c r="M119" s="48"/>
     </row>
     <row r="120" spans="3:17">
       <c r="C120" s="1"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="46" t="s">
+      <c r="E120" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F120" t="s">
         <v>39</v>
       </c>
-      <c r="G120" s="44" t="s">
+      <c r="G120" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H120" s="44" t="s">
+      <c r="H120" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I120" s="44" t="s">
+      <c r="I120" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="J120" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" s="49" t="s">
+      <c r="J120" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="L120" s="50"/>
-      <c r="M120" s="51"/>
-      <c r="N120" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O120" s="42" t="s">
+      <c r="L120" s="51"/>
+      <c r="M120" s="52"/>
+      <c r="N120" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O120" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="121" spans="3:17">
       <c r="C121" s="1"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="46" t="s">
+      <c r="E121" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F121" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="45" t="s">
+      <c r="G121" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H121" s="44" t="s">
+      <c r="H121" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="I121" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="45" t="s">
+      <c r="I121" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K121" s="45" t="s">
+      <c r="K121" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L121" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M121" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N121" s="45"/>
+      <c r="L121" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M121" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N121" s="46"/>
     </row>
     <row r="122" spans="3:17">
       <c r="C122" s="1"/>
       <c r="D122" s="2"/>
     </row>
     <row r="123" spans="3:17">
-      <c r="F123" s="38" t="s">
+      <c r="F123" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G123" s="38" t="s">
+      <c r="G123" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H123" s="39" t="s">
+      <c r="H123" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I123" s="39"/>
-      <c r="J123" s="39" t="s">
+      <c r="I123" s="40"/>
+      <c r="J123" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K123" s="39"/>
-      <c r="L123" s="38" t="s">
+      <c r="K123" s="40"/>
+      <c r="L123" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M123" s="38" t="s">
+      <c r="M123" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N123" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O123" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P123" s="38"/>
-      <c r="Q123" s="38"/>
+      <c r="N123" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O123" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P123" s="39"/>
+      <c r="Q123" s="39"/>
     </row>
     <row r="124" spans="3:17">
       <c r="C124" s="1" t="s">
@@ -6214,44 +6305,44 @@
       <c r="D124" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E124" s="43" t="s">
+      <c r="E124" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F124" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G124" s="44" t="s">
+      <c r="F124" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G124" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H124" s="44" t="s">
+      <c r="H124" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="I124" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J124" s="44" t="s">
+      <c r="I124" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K124" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L124" s="44" t="s">
+      <c r="K124" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L124" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M124" s="52" t="s">
+      <c r="M124" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="N124" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O124" s="42" t="s">
+      <c r="N124" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O124" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="125" spans="3:17">
       <c r="C125" s="1"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="45" t="s">
+      <c r="E125" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F125" t="s">
@@ -6282,7 +6373,7 @@
     <row r="126" spans="3:17">
       <c r="C126" s="1"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="45" t="s">
+      <c r="E126" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F126" t="s">
@@ -6313,158 +6404,158 @@
     <row r="127" spans="3:17">
       <c r="C127" s="1"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="46" t="s">
+      <c r="E127" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F127" t="s">
         <v>39</v>
       </c>
-      <c r="G127" s="45" t="s">
+      <c r="G127" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H127" s="44" t="s">
+      <c r="H127" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="I127" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J127" s="44" t="s">
+      <c r="I127" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J127" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K127" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L127" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M127" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N127" s="45"/>
+      <c r="K127" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L127" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M127" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N127" s="46"/>
     </row>
     <row r="128" spans="3:17">
       <c r="C128" s="1"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="46"/>
-      <c r="F128" s="47" t="s">
+      <c r="E128" s="47"/>
+      <c r="F128" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="47" t="s">
+      <c r="G128" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H128" s="47" t="s">
+      <c r="H128" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I128" s="47" t="s">
+      <c r="I128" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J128" s="47" t="s">
+      <c r="J128" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K128" s="48" t="s">
+      <c r="K128" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L128" s="48"/>
-      <c r="M128" s="47"/>
+      <c r="L128" s="49"/>
+      <c r="M128" s="48"/>
     </row>
     <row r="129" spans="3:17">
       <c r="C129" s="1"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="46" t="s">
+      <c r="E129" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F129" t="s">
         <v>39</v>
       </c>
-      <c r="G129" s="44" t="s">
+      <c r="G129" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H129" s="44" t="s">
+      <c r="H129" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I129" s="44" t="s">
+      <c r="I129" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="J129" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="53" t="s">
+      <c r="J129" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K129" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="L129" s="50"/>
-      <c r="M129" s="51"/>
-      <c r="N129" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O129" s="42" t="s">
+      <c r="L129" s="51"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O129" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="130" spans="3:17">
       <c r="C130" s="1"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="46" t="s">
+      <c r="E130" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F130" t="s">
         <v>39</v>
       </c>
-      <c r="G130" s="45" t="s">
+      <c r="G130" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H130" s="44" t="s">
+      <c r="H130" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="I130" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J130" s="45" t="s">
+      <c r="I130" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J130" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K130" s="45" t="s">
+      <c r="K130" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L130" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M130" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N130" s="45"/>
+      <c r="L130" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M130" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N130" s="46"/>
     </row>
     <row r="131" spans="3:17">
       <c r="C131" s="1"/>
       <c r="D131" s="2"/>
     </row>
     <row r="132" spans="3:17">
-      <c r="F132" s="38" t="s">
+      <c r="F132" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="38" t="s">
+      <c r="G132" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H132" s="39" t="s">
+      <c r="H132" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I132" s="39"/>
-      <c r="J132" s="39" t="s">
+      <c r="I132" s="40"/>
+      <c r="J132" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K132" s="39"/>
-      <c r="L132" s="38" t="s">
+      <c r="K132" s="40"/>
+      <c r="L132" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M132" s="38" t="s">
+      <c r="M132" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N132" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O132" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P132" s="38"/>
-      <c r="Q132" s="38"/>
+      <c r="N132" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O132" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P132" s="39"/>
+      <c r="Q132" s="39"/>
     </row>
     <row r="133" spans="3:17">
       <c r="C133" s="1" t="s">
@@ -6473,44 +6564,44 @@
       <c r="D133" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E133" s="43" t="s">
+      <c r="E133" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F133" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G133" s="44" t="s">
+      <c r="F133" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G133" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H133" s="44" t="s">
+      <c r="H133" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="I133" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="44" t="s">
+      <c r="I133" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K133" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L133" s="44" t="s">
+      <c r="K133" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L133" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M133" s="44" t="s">
+      <c r="M133" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="N133" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O133" s="42" t="s">
+      <c r="N133" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O133" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="134" spans="3:17">
       <c r="C134" s="1"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="45" t="s">
+      <c r="E134" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F134" t="s">
@@ -6541,7 +6632,7 @@
     <row r="135" spans="3:17">
       <c r="C135" s="1"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="45" t="s">
+      <c r="E135" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F135" t="s">
@@ -6572,158 +6663,158 @@
     <row r="136" spans="3:17">
       <c r="C136" s="1"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="46" t="s">
+      <c r="E136" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F136" t="s">
         <v>39</v>
       </c>
-      <c r="G136" s="45" t="s">
+      <c r="G136" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H136" s="44" t="s">
+      <c r="H136" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="I136" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J136" s="44" t="s">
+      <c r="I136" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K136" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L136" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M136" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N136" s="45"/>
+      <c r="K136" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L136" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M136" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N136" s="46"/>
     </row>
     <row r="137" spans="3:17">
       <c r="C137" s="1"/>
       <c r="D137" s="2"/>
-      <c r="E137" s="46"/>
-      <c r="F137" s="47" t="s">
+      <c r="E137" s="47"/>
+      <c r="F137" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G137" s="47" t="s">
+      <c r="G137" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H137" s="47" t="s">
+      <c r="H137" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I137" s="47" t="s">
+      <c r="I137" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J137" s="47" t="s">
+      <c r="J137" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K137" s="48" t="s">
+      <c r="K137" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L137" s="48"/>
-      <c r="M137" s="47"/>
+      <c r="L137" s="49"/>
+      <c r="M137" s="48"/>
     </row>
     <row r="138" spans="3:17">
       <c r="C138" s="1"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="46" t="s">
+      <c r="E138" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F138" t="s">
         <v>39</v>
       </c>
-      <c r="G138" s="44" t="s">
+      <c r="G138" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H138" s="44" t="s">
+      <c r="H138" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I138" s="44" t="s">
+      <c r="I138" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="J138" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K138" s="49" t="s">
+      <c r="J138" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K138" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="L138" s="50"/>
-      <c r="M138" s="51"/>
-      <c r="N138" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O138" s="42" t="s">
+      <c r="L138" s="51"/>
+      <c r="M138" s="52"/>
+      <c r="N138" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O138" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="139" spans="3:17">
       <c r="C139" s="1"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="46" t="s">
+      <c r="E139" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F139" t="s">
         <v>39</v>
       </c>
-      <c r="G139" s="45" t="s">
+      <c r="G139" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H139" s="44" t="s">
+      <c r="H139" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="I139" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" s="45" t="s">
+      <c r="I139" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J139" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K139" s="45" t="s">
+      <c r="K139" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L139" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M139" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N139" s="45"/>
+      <c r="L139" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M139" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N139" s="46"/>
     </row>
     <row r="140" spans="3:17">
       <c r="C140" s="1"/>
       <c r="D140" s="2"/>
     </row>
     <row r="141" spans="3:17">
-      <c r="F141" s="38" t="s">
+      <c r="F141" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G141" s="38" t="s">
+      <c r="G141" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H141" s="39" t="s">
+      <c r="H141" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I141" s="39"/>
-      <c r="J141" s="39" t="s">
+      <c r="I141" s="40"/>
+      <c r="J141" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K141" s="39"/>
-      <c r="L141" s="38" t="s">
+      <c r="K141" s="40"/>
+      <c r="L141" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M141" s="38" t="s">
+      <c r="M141" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N141" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O141" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P141" s="38"/>
-      <c r="Q141" s="38"/>
+      <c r="N141" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O141" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P141" s="39"/>
+      <c r="Q141" s="39"/>
     </row>
     <row r="142" spans="3:17">
       <c r="C142" s="1" t="s">
@@ -6732,44 +6823,44 @@
       <c r="D142" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E142" s="43" t="s">
+      <c r="E142" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F142" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G142" s="44" t="s">
+      <c r="F142" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H142" s="44" t="s">
+      <c r="H142" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I142" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="44" t="s">
+      <c r="I142" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J142" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K142" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L142" s="44" t="s">
+      <c r="K142" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L142" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M142" s="44" t="s">
+      <c r="M142" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="N142" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O142" s="42" t="s">
+      <c r="N142" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O142" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="143" spans="3:17">
       <c r="C143" s="1"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="45" t="s">
+      <c r="E143" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F143" t="s">
@@ -6800,7 +6891,7 @@
     <row r="144" spans="3:17">
       <c r="C144" s="1"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="45" t="s">
+      <c r="E144" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F144" t="s">
@@ -6831,158 +6922,158 @@
     <row r="145" spans="3:17">
       <c r="C145" s="1"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="46" t="s">
+      <c r="E145" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F145" t="s">
         <v>39</v>
       </c>
-      <c r="G145" s="45" t="s">
+      <c r="G145" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H145" s="44" t="s">
+      <c r="H145" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I145" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="44" t="s">
+      <c r="I145" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K145" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L145" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M145" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N145" s="45"/>
+      <c r="K145" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M145" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N145" s="46"/>
     </row>
     <row r="146" spans="3:17">
       <c r="C146" s="1"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="46"/>
-      <c r="F146" s="47" t="s">
+      <c r="E146" s="47"/>
+      <c r="F146" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G146" s="47" t="s">
+      <c r="G146" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H146" s="47" t="s">
+      <c r="H146" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I146" s="47" t="s">
+      <c r="I146" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J146" s="47" t="s">
+      <c r="J146" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K146" s="48" t="s">
+      <c r="K146" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L146" s="48"/>
-      <c r="M146" s="47"/>
+      <c r="L146" s="49"/>
+      <c r="M146" s="48"/>
     </row>
     <row r="147" spans="3:17">
       <c r="C147" s="1"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="46" t="s">
+      <c r="E147" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F147" t="s">
         <v>39</v>
       </c>
-      <c r="G147" s="44" t="s">
+      <c r="G147" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H147" s="44" t="s">
+      <c r="H147" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I147" s="44" t="s">
+      <c r="I147" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="J147" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="49" t="s">
+      <c r="J147" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="L147" s="50"/>
-      <c r="M147" s="51"/>
-      <c r="N147" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O147" s="42" t="s">
+      <c r="L147" s="51"/>
+      <c r="M147" s="52"/>
+      <c r="N147" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O147" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="148" spans="3:17">
       <c r="C148" s="1"/>
       <c r="D148" s="2"/>
-      <c r="E148" s="46" t="s">
+      <c r="E148" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F148" t="s">
         <v>39</v>
       </c>
-      <c r="G148" s="45" t="s">
+      <c r="G148" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H148" s="44" t="s">
+      <c r="H148" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I148" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="45" t="s">
+      <c r="I148" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K148" s="45" t="s">
+      <c r="K148" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L148" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M148" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N148" s="45"/>
+      <c r="L148" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M148" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N148" s="46"/>
     </row>
     <row r="149" spans="3:17">
       <c r="C149" s="1"/>
       <c r="D149" s="2"/>
     </row>
     <row r="150" spans="3:17">
-      <c r="F150" s="38" t="s">
+      <c r="F150" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G150" s="38" t="s">
+      <c r="G150" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H150" s="39" t="s">
+      <c r="H150" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I150" s="39"/>
-      <c r="J150" s="39" t="s">
+      <c r="I150" s="40"/>
+      <c r="J150" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K150" s="39"/>
-      <c r="L150" s="38" t="s">
+      <c r="K150" s="40"/>
+      <c r="L150" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M150" s="38" t="s">
+      <c r="M150" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N150" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O150" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P150" s="38"/>
-      <c r="Q150" s="38"/>
+      <c r="N150" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O150" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P150" s="39"/>
+      <c r="Q150" s="39"/>
     </row>
     <row r="151" ht="81" spans="3:17">
       <c r="C151" s="1" t="s">
@@ -6991,44 +7082,44 @@
       <c r="D151" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E151" s="43" t="s">
+      <c r="E151" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F151" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G151" s="44" t="s">
+      <c r="F151" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G151" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H151" s="44" t="s">
+      <c r="H151" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I151" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J151" s="44" t="s">
+      <c r="I151" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J151" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K151" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L151" s="44" t="s">
+      <c r="K151" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L151" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M151" s="54" t="s">
+      <c r="M151" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="N151" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O151" s="42" t="s">
+      <c r="N151" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O151" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="152" spans="3:17">
       <c r="C152" s="1"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="45" t="s">
+      <c r="E152" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F152" t="s">
@@ -7059,7 +7150,7 @@
     <row r="153" spans="3:17">
       <c r="C153" s="1"/>
       <c r="D153" s="2"/>
-      <c r="E153" s="45" t="s">
+      <c r="E153" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F153" t="s">
@@ -7090,160 +7181,160 @@
     <row r="154" spans="3:17">
       <c r="C154" s="1"/>
       <c r="D154" s="2"/>
-      <c r="E154" s="46" t="s">
+      <c r="E154" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F154" t="s">
         <v>39</v>
       </c>
-      <c r="G154" s="45" t="s">
+      <c r="G154" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H154" s="44" t="s">
+      <c r="H154" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I154" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J154" s="44" t="s">
+      <c r="I154" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K154" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L154" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M154" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N154" s="45"/>
+      <c r="K154" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L154" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M154" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N154" s="46"/>
     </row>
     <row r="155" spans="3:17">
       <c r="C155" s="1"/>
       <c r="D155" s="2"/>
-      <c r="E155" s="46"/>
-      <c r="F155" s="47" t="s">
+      <c r="E155" s="47"/>
+      <c r="F155" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G155" s="47" t="s">
+      <c r="G155" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H155" s="47" t="s">
+      <c r="H155" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I155" s="47" t="s">
+      <c r="I155" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J155" s="47" t="s">
+      <c r="J155" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K155" s="48" t="s">
+      <c r="K155" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L155" s="48"/>
-      <c r="M155" s="47"/>
-      <c r="N155" s="44"/>
-      <c r="O155" s="42"/>
+      <c r="L155" s="49"/>
+      <c r="M155" s="48"/>
+      <c r="N155" s="45"/>
+      <c r="O155" s="43"/>
     </row>
     <row r="156" spans="3:17">
       <c r="C156" s="1"/>
       <c r="D156" s="2"/>
-      <c r="E156" s="46" t="s">
+      <c r="E156" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F156" t="s">
         <v>39</v>
       </c>
-      <c r="G156" s="44" t="s">
+      <c r="G156" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H156" s="44" t="s">
+      <c r="H156" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I156" s="44" t="s">
+      <c r="I156" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="J156" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K156" s="49" t="s">
+      <c r="J156" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="L156" s="50"/>
-      <c r="M156" s="51"/>
-      <c r="N156" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O156" s="42" t="s">
+      <c r="L156" s="51"/>
+      <c r="M156" s="52"/>
+      <c r="N156" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O156" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="157" spans="3:17">
       <c r="C157" s="1"/>
       <c r="D157" s="2"/>
-      <c r="E157" s="46" t="s">
+      <c r="E157" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F157" t="s">
         <v>39</v>
       </c>
-      <c r="G157" s="45" t="s">
+      <c r="G157" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H157" s="44" t="s">
+      <c r="H157" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I157" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J157" s="45" t="s">
+      <c r="I157" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K157" s="45" t="s">
+      <c r="K157" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L157" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M157" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N157" s="45"/>
+      <c r="L157" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M157" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N157" s="46"/>
     </row>
     <row r="158" spans="3:17">
       <c r="C158" s="1"/>
       <c r="D158" s="2"/>
     </row>
     <row r="159" spans="3:17">
-      <c r="F159" s="38" t="s">
+      <c r="F159" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="38" t="s">
+      <c r="G159" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H159" s="39" t="s">
+      <c r="H159" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I159" s="39"/>
-      <c r="J159" s="39" t="s">
+      <c r="I159" s="40"/>
+      <c r="J159" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K159" s="39"/>
-      <c r="L159" s="38" t="s">
+      <c r="K159" s="40"/>
+      <c r="L159" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M159" s="38" t="s">
+      <c r="M159" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N159" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O159" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P159" s="38"/>
-      <c r="Q159" s="38"/>
+      <c r="N159" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O159" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P159" s="39"/>
+      <c r="Q159" s="39"/>
     </row>
     <row r="160" spans="3:17">
       <c r="C160" s="1" t="s">
@@ -7252,44 +7343,44 @@
       <c r="D160" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E160" s="43" t="s">
+      <c r="E160" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F160" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G160" s="44" t="s">
+      <c r="F160" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G160" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H160" s="44" t="s">
+      <c r="H160" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I160" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="44" t="s">
+      <c r="I160" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K160" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L160" s="44" t="s">
+      <c r="K160" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L160" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="M160" s="44" t="s">
+      <c r="M160" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="N160" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O160" s="42" t="s">
+      <c r="N160" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O160" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="161" spans="3:17">
       <c r="C161" s="1"/>
       <c r="D161" s="2"/>
-      <c r="E161" s="45" t="s">
+      <c r="E161" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F161" t="s">
@@ -7320,7 +7411,7 @@
     <row r="162" spans="3:17">
       <c r="C162" s="1"/>
       <c r="D162" s="2"/>
-      <c r="E162" s="45" t="s">
+      <c r="E162" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F162" t="s">
@@ -7351,160 +7442,160 @@
     <row r="163" spans="3:17">
       <c r="C163" s="1"/>
       <c r="D163" s="2"/>
-      <c r="E163" s="46" t="s">
+      <c r="E163" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F163" t="s">
         <v>39</v>
       </c>
-      <c r="G163" s="45" t="s">
+      <c r="G163" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H163" s="44" t="s">
+      <c r="H163" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I163" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J163" s="44" t="s">
+      <c r="I163" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K163" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L163" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M163" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N163" s="45"/>
+      <c r="K163" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L163" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M163" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N163" s="46"/>
     </row>
     <row r="164" spans="3:17">
       <c r="C164" s="1"/>
       <c r="D164" s="2"/>
-      <c r="E164" s="46"/>
-      <c r="F164" s="47" t="s">
+      <c r="E164" s="47"/>
+      <c r="F164" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G164" s="47" t="s">
+      <c r="G164" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H164" s="47" t="s">
+      <c r="H164" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I164" s="47" t="s">
+      <c r="I164" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J164" s="47" t="s">
+      <c r="J164" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K164" s="48" t="s">
+      <c r="K164" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L164" s="48"/>
-      <c r="M164" s="47"/>
-      <c r="N164" s="44"/>
-      <c r="O164" s="42"/>
+      <c r="L164" s="49"/>
+      <c r="M164" s="48"/>
+      <c r="N164" s="45"/>
+      <c r="O164" s="43"/>
     </row>
     <row r="165" spans="3:17">
       <c r="C165" s="1"/>
       <c r="D165" s="2"/>
-      <c r="E165" s="46" t="s">
+      <c r="E165" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F165" t="s">
         <v>39</v>
       </c>
-      <c r="G165" s="44" t="s">
+      <c r="G165" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H165" s="44" t="s">
+      <c r="H165" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="I165" s="44" t="s">
+      <c r="I165" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="J165" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K165" s="49" t="s">
+      <c r="J165" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K165" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="L165" s="50"/>
-      <c r="M165" s="51"/>
-      <c r="N165" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O165" s="42" t="s">
+      <c r="L165" s="51"/>
+      <c r="M165" s="52"/>
+      <c r="N165" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O165" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="166" spans="3:17">
       <c r="C166" s="1"/>
       <c r="D166" s="2"/>
-      <c r="E166" s="46" t="s">
+      <c r="E166" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F166" t="s">
         <v>39</v>
       </c>
-      <c r="G166" s="45" t="s">
+      <c r="G166" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H166" s="44" t="s">
+      <c r="H166" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I166" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J166" s="45" t="s">
+      <c r="I166" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K166" s="45" t="s">
+      <c r="K166" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L166" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M166" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N166" s="45"/>
+      <c r="L166" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M166" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N166" s="46"/>
     </row>
     <row r="167" spans="3:17">
       <c r="C167" s="1"/>
       <c r="D167" s="2"/>
     </row>
     <row r="168" spans="3:17">
-      <c r="F168" s="38" t="s">
+      <c r="F168" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G168" s="38" t="s">
+      <c r="G168" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H168" s="39" t="s">
+      <c r="H168" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I168" s="39"/>
-      <c r="J168" s="39" t="s">
+      <c r="I168" s="40"/>
+      <c r="J168" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K168" s="39"/>
-      <c r="L168" s="38" t="s">
+      <c r="K168" s="40"/>
+      <c r="L168" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M168" s="38" t="s">
+      <c r="M168" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N168" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O168" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P168" s="38"/>
-      <c r="Q168" s="38"/>
+      <c r="N168" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O168" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P168" s="39"/>
+      <c r="Q168" s="39"/>
     </row>
     <row r="169" ht="81" spans="3:17">
       <c r="C169" s="1" t="s">
@@ -7513,44 +7604,44 @@
       <c r="D169" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E169" s="43" t="s">
+      <c r="E169" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F169" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G169" s="44" t="s">
+      <c r="F169" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G169" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H169" s="44" t="s">
+      <c r="H169" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="I169" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J169" s="44" t="s">
+      <c r="I169" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="K169" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L169" s="44" t="s">
+      <c r="K169" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L169" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="M169" s="54" t="s">
+      <c r="M169" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="N169" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O169" s="42" t="s">
+      <c r="N169" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O169" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="170" spans="3:17">
       <c r="C170" s="1"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="45" t="s">
+      <c r="E170" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F170" t="s">
@@ -7581,7 +7672,7 @@
     <row r="171" spans="3:17">
       <c r="C171" s="1"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="45" t="s">
+      <c r="E171" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F171" t="s">
@@ -7612,126 +7703,126 @@
     <row r="172" spans="3:17">
       <c r="C172" s="1"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="46" t="s">
+      <c r="E172" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F172" t="s">
         <v>39</v>
       </c>
-      <c r="G172" s="45" t="s">
+      <c r="G172" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H172" s="44" t="s">
+      <c r="H172" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="I172" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J172" s="44" t="s">
+      <c r="I172" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="K172" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L172" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M172" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N172" s="45"/>
+      <c r="K172" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L172" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M172" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N172" s="46"/>
     </row>
     <row r="173" spans="3:17">
       <c r="C173" s="1"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="46"/>
-      <c r="F173" s="47" t="s">
+      <c r="E173" s="47"/>
+      <c r="F173" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G173" s="47" t="s">
+      <c r="G173" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H173" s="47" t="s">
+      <c r="H173" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I173" s="47" t="s">
+      <c r="I173" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J173" s="47" t="s">
+      <c r="J173" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K173" s="48" t="s">
+      <c r="K173" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L173" s="48"/>
-      <c r="M173" s="47"/>
-      <c r="N173" s="44"/>
-      <c r="O173" s="42"/>
+      <c r="L173" s="49"/>
+      <c r="M173" s="48"/>
+      <c r="N173" s="45"/>
+      <c r="O173" s="43"/>
     </row>
     <row r="174" ht="70" customHeight="1" spans="3:17">
       <c r="C174" s="1"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="46" t="s">
+      <c r="E174" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F174" t="s">
         <v>39</v>
       </c>
-      <c r="G174" s="44" t="s">
+      <c r="G174" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H174" s="44" t="s">
+      <c r="H174" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="I174" s="44" t="s">
+      <c r="I174" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="J174" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K174" s="55" t="s">
+      <c r="J174" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K174" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="L174" s="50"/>
-      <c r="M174" s="51"/>
-      <c r="N174" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O174" s="42" t="s">
+      <c r="L174" s="51"/>
+      <c r="M174" s="52"/>
+      <c r="N174" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O174" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="175" spans="3:17">
       <c r="C175" s="1"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="46" t="s">
+      <c r="E175" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F175" t="s">
         <v>39</v>
       </c>
-      <c r="G175" s="45" t="s">
+      <c r="G175" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H175" s="44" t="s">
+      <c r="H175" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="I175" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J175" s="45" t="s">
+      <c r="I175" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K175" s="45" t="s">
+      <c r="K175" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L175" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M175" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N175" s="45"/>
+      <c r="L175" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M175" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N175" s="46"/>
     </row>
     <row r="176" spans="3:17">
       <c r="C176" s="1"/>
@@ -7744,185 +7835,185 @@
       <c r="D178" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E178" s="43"/>
-      <c r="F178" s="44"/>
-      <c r="G178" s="44"/>
-      <c r="H178" s="44"/>
-      <c r="I178" s="44"/>
-      <c r="J178" s="44"/>
-      <c r="K178" s="44"/>
-      <c r="L178" s="44"/>
-      <c r="M178" s="44"/>
-      <c r="N178" s="44"/>
-      <c r="O178" s="42"/>
+      <c r="E178" s="44"/>
+      <c r="F178" s="45"/>
+      <c r="G178" s="45"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="45"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="45"/>
+      <c r="L178" s="45"/>
+      <c r="M178" s="45"/>
+      <c r="N178" s="45"/>
+      <c r="O178" s="43"/>
     </row>
     <row r="179" spans="3:17">
       <c r="C179" s="1"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="45"/>
+      <c r="E179" s="46"/>
     </row>
     <row r="180" spans="3:17">
       <c r="C180" s="1"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="45"/>
+      <c r="E180" s="46"/>
     </row>
     <row r="181" spans="3:17">
       <c r="C181" s="1"/>
       <c r="D181" s="2"/>
-      <c r="E181" s="46" t="s">
+      <c r="E181" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F181" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="45" t="s">
+      <c r="G181" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H181" s="44" t="s">
+      <c r="H181" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="I181" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J181" s="44" t="s">
+      <c r="I181" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J181" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="K181" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L181" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M181" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N181" s="45"/>
+      <c r="K181" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L181" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M181" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N181" s="46"/>
     </row>
     <row r="182" ht="21" customHeight="1" spans="3:17">
       <c r="C182" s="1"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="46"/>
-      <c r="F182" s="47" t="s">
+      <c r="E182" s="47"/>
+      <c r="F182" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G182" s="47" t="s">
+      <c r="G182" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H182" s="47" t="s">
+      <c r="H182" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I182" s="47" t="s">
+      <c r="I182" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J182" s="47" t="s">
+      <c r="J182" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K182" s="48" t="s">
+      <c r="K182" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L182" s="48"/>
-      <c r="M182" s="47"/>
-      <c r="N182" s="44"/>
-      <c r="O182" s="42"/>
+      <c r="L182" s="49"/>
+      <c r="M182" s="48"/>
+      <c r="N182" s="45"/>
+      <c r="O182" s="43"/>
     </row>
     <row r="183" ht="45" customHeight="1" spans="3:17">
       <c r="C183" s="1"/>
       <c r="D183" s="2"/>
-      <c r="E183" s="46" t="s">
+      <c r="E183" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F183" t="s">
         <v>39</v>
       </c>
-      <c r="G183" s="44" t="s">
+      <c r="G183" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H183" s="44" t="s">
+      <c r="H183" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="I183" s="44" t="s">
+      <c r="I183" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="J183" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K183" s="55" t="s">
+      <c r="J183" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K183" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="L183" s="50"/>
-      <c r="M183" s="51"/>
-      <c r="N183" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O183" s="42" t="s">
+      <c r="L183" s="51"/>
+      <c r="M183" s="52"/>
+      <c r="N183" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O183" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="184" spans="3:17">
       <c r="C184" s="1"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="46" t="s">
+      <c r="E184" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F184" t="s">
         <v>39</v>
       </c>
-      <c r="G184" s="45" t="s">
+      <c r="G184" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H184" s="44" t="s">
+      <c r="H184" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="I184" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J184" s="45" t="s">
+      <c r="I184" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J184" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K184" s="45" t="s">
+      <c r="K184" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L184" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M184" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N184" s="45"/>
+      <c r="L184" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M184" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N184" s="46"/>
     </row>
     <row r="185" spans="3:17">
       <c r="C185" s="1"/>
       <c r="D185" s="2"/>
     </row>
     <row r="186" spans="3:17">
-      <c r="F186" s="38" t="s">
+      <c r="F186" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G186" s="38" t="s">
+      <c r="G186" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H186" s="39" t="s">
+      <c r="H186" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I186" s="39"/>
-      <c r="J186" s="39" t="s">
+      <c r="I186" s="40"/>
+      <c r="J186" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K186" s="39"/>
-      <c r="L186" s="38" t="s">
+      <c r="K186" s="40"/>
+      <c r="L186" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M186" s="38" t="s">
+      <c r="M186" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N186" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O186" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P186" s="38"/>
-      <c r="Q186" s="38"/>
+      <c r="N186" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O186" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P186" s="39"/>
+      <c r="Q186" s="39"/>
     </row>
     <row r="187" spans="3:17">
       <c r="C187" s="1" t="s">
@@ -7931,44 +8022,44 @@
       <c r="D187" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E187" s="43" t="s">
+      <c r="E187" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F187" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G187" s="44" t="s">
+      <c r="F187" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G187" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H187" s="44" t="s">
+      <c r="H187" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="I187" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J187" s="44" t="s">
+      <c r="I187" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J187" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="K187" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L187" s="44" t="s">
+      <c r="K187" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L187" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="M187" s="44" t="s">
+      <c r="M187" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="N187" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O187" s="42" t="s">
+      <c r="N187" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O187" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="188" spans="3:17">
       <c r="C188" s="1"/>
       <c r="D188" s="2"/>
-      <c r="E188" s="45" t="s">
+      <c r="E188" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F188" t="s">
@@ -7999,7 +8090,7 @@
     <row r="189" spans="3:17">
       <c r="C189" s="1"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="45" t="s">
+      <c r="E189" s="46" t="s">
         <v>92</v>
       </c>
       <c r="F189" t="s">
@@ -8030,56 +8121,56 @@
     <row r="190" spans="3:17">
       <c r="C190" s="1"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="46"/>
-      <c r="F190" s="56" t="s">
+      <c r="E190" s="47"/>
+      <c r="F190" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="G190" s="56" t="s">
+      <c r="G190" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="H190" s="56" t="s">
+      <c r="H190" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="I190" s="57" t="s">
+      <c r="I190" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="J190" s="57"/>
-      <c r="K190" s="57" t="s">
+      <c r="J190" s="58"/>
+      <c r="K190" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="L190" s="57"/>
-      <c r="M190" s="57"/>
-      <c r="N190" s="57"/>
-      <c r="O190" s="57"/>
+      <c r="L190" s="58"/>
+      <c r="M190" s="58"/>
+      <c r="N190" s="58"/>
+      <c r="O190" s="58"/>
     </row>
     <row r="191" spans="3:17">
       <c r="C191" s="1"/>
       <c r="D191" s="2"/>
-      <c r="E191" s="46" t="s">
+      <c r="E191" s="47" t="s">
         <v>156</v>
       </c>
       <c r="F191" t="s">
         <v>39</v>
       </c>
-      <c r="G191" s="58" t="s">
+      <c r="G191" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="H191" s="59" t="s">
+      <c r="H191" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="I191" s="59" t="s">
+      <c r="I191" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="J191" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="K191" s="60" t="s">
+      <c r="J191" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="K191" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="L191" s="61"/>
-      <c r="M191" s="61"/>
-      <c r="N191" s="61"/>
-      <c r="O191" s="61"/>
+      <c r="L191" s="62"/>
+      <c r="M191" s="62"/>
+      <c r="N191" s="62"/>
+      <c r="O191" s="62"/>
       <c r="P191" t="s">
         <v>31</v>
       </c>
@@ -8090,179 +8181,179 @@
     <row r="192" spans="3:17">
       <c r="C192" s="1"/>
       <c r="D192" s="2"/>
-      <c r="E192" s="46"/>
-      <c r="G192" s="62"/>
-      <c r="H192" s="63"/>
-      <c r="I192" s="63"/>
-      <c r="J192" s="63"/>
-      <c r="K192" s="63"/>
-      <c r="L192" s="62"/>
-      <c r="M192" s="62"/>
-      <c r="N192" s="62"/>
+      <c r="E192" s="47"/>
+      <c r="G192" s="63"/>
+      <c r="H192" s="64"/>
+      <c r="I192" s="64"/>
+      <c r="J192" s="64"/>
+      <c r="K192" s="64"/>
+      <c r="L192" s="63"/>
+      <c r="M192" s="63"/>
+      <c r="N192" s="63"/>
     </row>
     <row r="193" spans="3:17">
       <c r="C193" s="1"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="46"/>
-      <c r="G193" s="44"/>
-      <c r="H193" s="44"/>
-      <c r="I193" s="44"/>
-      <c r="J193" s="44"/>
-      <c r="K193" s="44"/>
-      <c r="L193" s="44"/>
-      <c r="M193" s="44"/>
-      <c r="N193" s="44"/>
-      <c r="O193" s="42"/>
+      <c r="E193" s="47"/>
+      <c r="G193" s="45"/>
+      <c r="H193" s="45"/>
+      <c r="I193" s="45"/>
+      <c r="J193" s="45"/>
+      <c r="K193" s="45"/>
+      <c r="L193" s="45"/>
+      <c r="M193" s="45"/>
+      <c r="N193" s="45"/>
+      <c r="O193" s="43"/>
     </row>
     <row r="194" spans="3:17">
       <c r="C194" s="1"/>
       <c r="D194" s="2"/>
-      <c r="E194" s="46"/>
-      <c r="G194" s="45"/>
-      <c r="H194" s="44"/>
-      <c r="I194" s="44"/>
-      <c r="J194" s="45"/>
-      <c r="K194" s="45"/>
-      <c r="L194" s="45"/>
-      <c r="M194" s="45"/>
-      <c r="N194" s="45"/>
+      <c r="E194" s="47"/>
+      <c r="G194" s="46"/>
+      <c r="H194" s="45"/>
+      <c r="I194" s="45"/>
+      <c r="J194" s="46"/>
+      <c r="K194" s="46"/>
+      <c r="L194" s="46"/>
+      <c r="M194" s="46"/>
+      <c r="N194" s="46"/>
     </row>
     <row r="195" spans="3:17">
       <c r="D195" s="3"/>
-      <c r="E195" s="45"/>
-      <c r="F195" s="38"/>
-      <c r="G195" s="38"/>
-      <c r="H195" s="39"/>
-      <c r="I195" s="39"/>
-      <c r="J195" s="39"/>
-      <c r="K195" s="39"/>
-      <c r="L195" s="38"/>
-      <c r="M195" s="38"/>
-      <c r="N195" s="38"/>
-      <c r="O195" s="38"/>
-      <c r="P195" s="38"/>
-      <c r="Q195" s="38"/>
+      <c r="E195" s="46"/>
+      <c r="F195" s="39"/>
+      <c r="G195" s="39"/>
+      <c r="H195" s="40"/>
+      <c r="I195" s="40"/>
+      <c r="J195" s="40"/>
+      <c r="K195" s="40"/>
+      <c r="L195" s="39"/>
+      <c r="M195" s="39"/>
+      <c r="N195" s="39"/>
+      <c r="O195" s="39"/>
+      <c r="P195" s="39"/>
+      <c r="Q195" s="39"/>
     </row>
     <row r="196" spans="3:17">
       <c r="C196" s="1"/>
       <c r="D196" s="2"/>
-      <c r="E196" s="43"/>
-      <c r="F196" s="44"/>
-      <c r="G196" s="44"/>
-      <c r="H196" s="44"/>
-      <c r="I196" s="44"/>
-      <c r="J196" s="44"/>
-      <c r="K196" s="44"/>
-      <c r="L196" s="44"/>
-      <c r="M196" s="44"/>
-      <c r="N196" s="44"/>
-      <c r="O196" s="42"/>
+      <c r="E196" s="44"/>
+      <c r="F196" s="45"/>
+      <c r="G196" s="45"/>
+      <c r="H196" s="45"/>
+      <c r="I196" s="45"/>
+      <c r="J196" s="45"/>
+      <c r="K196" s="45"/>
+      <c r="L196" s="45"/>
+      <c r="M196" s="45"/>
+      <c r="N196" s="45"/>
+      <c r="O196" s="43"/>
     </row>
     <row r="197" spans="3:17">
       <c r="C197" s="1"/>
       <c r="D197" s="2"/>
-      <c r="E197" s="45"/>
+      <c r="E197" s="46"/>
     </row>
     <row r="198" spans="3:17">
       <c r="C198" s="1"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="64"/>
+      <c r="E198" s="65"/>
     </row>
     <row r="199" spans="3:17">
       <c r="C199" s="1"/>
       <c r="D199" s="2"/>
-      <c r="H199" s="59"/>
-      <c r="I199" s="59"/>
-      <c r="J199" s="59"/>
-      <c r="K199" s="65"/>
-      <c r="L199" s="66"/>
-      <c r="M199" s="66"/>
-      <c r="N199" s="66"/>
-      <c r="O199" s="66"/>
+      <c r="H199" s="60"/>
+      <c r="I199" s="60"/>
+      <c r="J199" s="60"/>
+      <c r="K199" s="66"/>
+      <c r="L199" s="67"/>
+      <c r="M199" s="67"/>
+      <c r="N199" s="67"/>
+      <c r="O199" s="67"/>
     </row>
     <row r="200" spans="3:17">
       <c r="C200" s="1"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="67"/>
-      <c r="G200" s="62"/>
-      <c r="H200" s="63"/>
-      <c r="I200" s="63"/>
-      <c r="J200" s="63"/>
-      <c r="K200" s="63"/>
-      <c r="L200" s="62"/>
-      <c r="M200" s="62"/>
-      <c r="N200" s="62"/>
+      <c r="E200" s="68"/>
+      <c r="G200" s="63"/>
+      <c r="H200" s="64"/>
+      <c r="I200" s="64"/>
+      <c r="J200" s="64"/>
+      <c r="K200" s="64"/>
+      <c r="L200" s="63"/>
+      <c r="M200" s="63"/>
+      <c r="N200" s="63"/>
     </row>
     <row r="201" spans="3:17">
       <c r="C201" s="1"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="46"/>
-      <c r="G201" s="44"/>
-      <c r="H201" s="44"/>
-      <c r="I201" s="44"/>
-      <c r="J201" s="44"/>
-      <c r="K201" s="44"/>
-      <c r="L201" s="44"/>
-      <c r="M201" s="44"/>
-      <c r="N201" s="44"/>
-      <c r="O201" s="42"/>
+      <c r="E201" s="47"/>
+      <c r="G201" s="45"/>
+      <c r="H201" s="45"/>
+      <c r="I201" s="45"/>
+      <c r="J201" s="45"/>
+      <c r="K201" s="45"/>
+      <c r="L201" s="45"/>
+      <c r="M201" s="45"/>
+      <c r="N201" s="45"/>
+      <c r="O201" s="43"/>
     </row>
     <row r="202" spans="3:17">
       <c r="C202" s="1"/>
       <c r="D202" s="2"/>
-      <c r="E202" s="46"/>
-      <c r="G202" s="45"/>
-      <c r="H202" s="44"/>
-      <c r="I202" s="44"/>
-      <c r="J202" s="45"/>
-      <c r="K202" s="45"/>
-      <c r="L202" s="45"/>
-      <c r="M202" s="45"/>
-      <c r="N202" s="45"/>
+      <c r="E202" s="47"/>
+      <c r="G202" s="46"/>
+      <c r="H202" s="45"/>
+      <c r="I202" s="45"/>
+      <c r="J202" s="46"/>
+      <c r="K202" s="46"/>
+      <c r="L202" s="46"/>
+      <c r="M202" s="46"/>
+      <c r="N202" s="46"/>
     </row>
     <row r="203" spans="3:17">
-      <c r="F203" s="68" t="s">
+      <c r="F203" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="G203" s="68" t="s">
+      <c r="G203" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="H203" s="69" t="s">
+      <c r="H203" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="I203" s="69"/>
-      <c r="J203" s="69" t="s">
+      <c r="I203" s="70"/>
+      <c r="J203" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="K203" s="69"/>
-      <c r="L203" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="M203" s="68" t="s">
+      <c r="K203" s="70"/>
+      <c r="L203" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="M203" s="69" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="204" spans="3:17">
-      <c r="F204" s="58"/>
-      <c r="G204" s="58" t="s">
+      <c r="F204" s="59"/>
+      <c r="G204" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="H204" s="59" t="s">
+      <c r="H204" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="I204" s="59" t="s">
+      <c r="I204" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="J204" s="59" t="s">
+      <c r="J204" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="K204" s="59" t="s">
+      <c r="K204" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="L204" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="M204" s="58" t="s">
+      <c r="L204" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="M204" s="59" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8273,7 +8364,7 @@
       <c r="D205" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E205" s="43" t="s">
+      <c r="E205" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F205" t="s">
@@ -8304,7 +8395,7 @@
     <row r="206" spans="3:17">
       <c r="C206" s="1"/>
       <c r="D206" s="2"/>
-      <c r="E206" s="45" t="s">
+      <c r="E206" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F206" t="s">
@@ -8335,7 +8426,7 @@
     <row r="207" spans="3:17">
       <c r="C207" s="1"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="64" t="s">
+      <c r="E207" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F207" t="s">
@@ -8370,17 +8461,17 @@
     <row r="209" spans="3:17">
       <c r="C209" s="1"/>
       <c r="D209" s="2"/>
-      <c r="E209" s="67"/>
+      <c r="E209" s="68"/>
     </row>
     <row r="210" spans="3:17">
       <c r="C210" s="1"/>
       <c r="D210" s="2"/>
-      <c r="E210" s="46"/>
+      <c r="E210" s="47"/>
     </row>
     <row r="211" spans="3:17">
       <c r="C211" s="1"/>
       <c r="D211" s="2"/>
-      <c r="E211" s="46"/>
+      <c r="E211" s="47"/>
     </row>
     <row r="213" spans="3:17">
       <c r="C213" s="1" t="s">
@@ -8389,7 +8480,7 @@
       <c r="D213" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E213" s="43" t="s">
+      <c r="E213" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F213" t="s">
@@ -8398,7 +8489,7 @@
       <c r="G213" t="s">
         <v>157</v>
       </c>
-      <c r="H213" s="32" t="s">
+      <c r="H213" s="33" t="s">
         <v>163</v>
       </c>
       <c r="I213" t="s">
@@ -8420,7 +8511,7 @@
     <row r="214" spans="3:17">
       <c r="C214" s="1"/>
       <c r="D214" s="2"/>
-      <c r="E214" s="45" t="s">
+      <c r="E214" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F214" t="s">
@@ -8451,7 +8542,7 @@
     <row r="215" spans="3:17">
       <c r="C215" s="1"/>
       <c r="D215" s="2"/>
-      <c r="E215" s="64" t="s">
+      <c r="E215" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F215" t="s">
@@ -8482,7 +8573,7 @@
     <row r="216" spans="3:17">
       <c r="C216" s="1"/>
       <c r="D216" s="2"/>
-      <c r="E216" s="43" t="s">
+      <c r="E216" s="44" t="s">
         <v>166</v>
       </c>
       <c r="F216" t="s">
@@ -8513,7 +8604,7 @@
     <row r="217" spans="3:17">
       <c r="C217" s="1"/>
       <c r="D217" s="2"/>
-      <c r="E217" s="45" t="s">
+      <c r="E217" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F217" t="s">
@@ -8544,7 +8635,7 @@
     <row r="218" spans="3:17">
       <c r="C218" s="1"/>
       <c r="D218" s="2"/>
-      <c r="E218" s="64" t="s">
+      <c r="E218" s="65" t="s">
         <v>103</v>
       </c>
       <c r="F218" t="s">
@@ -8575,16 +8666,16 @@
     <row r="219" spans="3:17">
       <c r="C219" s="1"/>
       <c r="D219" s="2"/>
-      <c r="E219" s="46"/>
+      <c r="E219" s="47"/>
     </row>
     <row r="221" spans="3:17">
       <c r="C221" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D221" s="34" t="s">
+      <c r="D221" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="E221" s="43" t="s">
+      <c r="E221" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F221" t="s">
@@ -8611,15 +8702,15 @@
       <c r="M221" t="s">
         <v>32</v>
       </c>
-      <c r="N221" s="70"/>
-      <c r="O221" s="70"/>
-      <c r="P221" s="70"/>
-      <c r="Q221" s="70"/>
+      <c r="N221" s="71"/>
+      <c r="O221" s="71"/>
+      <c r="P221" s="71"/>
+      <c r="Q221" s="71"/>
     </row>
     <row r="222" spans="3:17">
       <c r="C222" s="1"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="45" t="s">
+      <c r="E222" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F222" t="s">
@@ -8646,13 +8737,13 @@
       <c r="M222" t="s">
         <v>32</v>
       </c>
-      <c r="N222" s="71"/>
-      <c r="O222" s="72"/>
+      <c r="N222" s="72"/>
+      <c r="O222" s="73"/>
     </row>
     <row r="223" spans="3:17">
       <c r="C223" s="1"/>
       <c r="D223" s="2"/>
-      <c r="E223" s="64" t="s">
+      <c r="E223" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F223" t="s">
@@ -8683,7 +8774,7 @@
     <row r="224" spans="3:17">
       <c r="C224" s="1"/>
       <c r="D224" s="2"/>
-      <c r="E224" s="43" t="s">
+      <c r="E224" s="44" t="s">
         <v>166</v>
       </c>
       <c r="F224" t="s">
@@ -8714,7 +8805,7 @@
     <row r="225" spans="3:15">
       <c r="C225" s="1"/>
       <c r="D225" s="2"/>
-      <c r="E225" s="45" t="s">
+      <c r="E225" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F225" t="s">
@@ -8741,12 +8832,12 @@
       <c r="M225" t="s">
         <v>32</v>
       </c>
-      <c r="N225" s="45"/>
+      <c r="N225" s="46"/>
     </row>
     <row r="226" spans="3:15">
       <c r="C226" s="1"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="64" t="s">
+      <c r="E226" s="65" t="s">
         <v>103</v>
       </c>
       <c r="F226" t="s">
@@ -8773,50 +8864,50 @@
       <c r="M226" t="s">
         <v>32</v>
       </c>
-      <c r="N226" s="44"/>
-      <c r="O226" s="42"/>
+      <c r="N226" s="45"/>
+      <c r="O226" s="43"/>
     </row>
     <row r="227" spans="3:15">
       <c r="C227" s="1"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="46"/>
-      <c r="G227" s="44"/>
-      <c r="H227" s="44"/>
-      <c r="I227" s="44"/>
-      <c r="J227" s="44"/>
-      <c r="K227" s="49"/>
-      <c r="L227" s="50"/>
-      <c r="M227" s="51"/>
-      <c r="N227" s="44"/>
-      <c r="O227" s="42"/>
+      <c r="E227" s="47"/>
+      <c r="G227" s="45"/>
+      <c r="H227" s="45"/>
+      <c r="I227" s="45"/>
+      <c r="J227" s="45"/>
+      <c r="K227" s="50"/>
+      <c r="L227" s="51"/>
+      <c r="M227" s="52"/>
+      <c r="N227" s="45"/>
+      <c r="O227" s="43"/>
     </row>
     <row r="228" spans="3:15">
-      <c r="E228" s="46"/>
-      <c r="G228" s="45"/>
-      <c r="H228" s="44"/>
-      <c r="I228" s="44"/>
-      <c r="J228" s="45"/>
-      <c r="K228" s="45"/>
-      <c r="L228" s="45"/>
-      <c r="M228" s="45"/>
-      <c r="N228" s="45"/>
+      <c r="E228" s="47"/>
+      <c r="G228" s="46"/>
+      <c r="H228" s="45"/>
+      <c r="I228" s="45"/>
+      <c r="J228" s="46"/>
+      <c r="K228" s="46"/>
+      <c r="L228" s="46"/>
+      <c r="M228" s="46"/>
+      <c r="N228" s="46"/>
     </row>
     <row r="229" spans="3:15">
-      <c r="E229" s="46"/>
-      <c r="G229" s="45"/>
-      <c r="H229" s="71"/>
-      <c r="I229" s="71"/>
-      <c r="J229" s="45"/>
-      <c r="K229" s="45"/>
-      <c r="L229" s="45"/>
-      <c r="M229" s="45"/>
-      <c r="N229" s="45"/>
+      <c r="E229" s="47"/>
+      <c r="G229" s="46"/>
+      <c r="H229" s="72"/>
+      <c r="I229" s="72"/>
+      <c r="J229" s="46"/>
+      <c r="K229" s="46"/>
+      <c r="L229" s="46"/>
+      <c r="M229" s="46"/>
+      <c r="N229" s="46"/>
     </row>
     <row r="230" ht="44" customHeight="1" spans="3:15">
       <c r="D230" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E230" s="43" t="s">
+      <c r="E230" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F230" t="s">
@@ -8843,11 +8934,11 @@
       <c r="M230" t="s">
         <v>32</v>
       </c>
-      <c r="O230" s="72"/>
+      <c r="O230" s="73"/>
     </row>
     <row r="231" spans="3:15">
       <c r="D231" s="2"/>
-      <c r="E231" s="45" t="s">
+      <c r="E231" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F231" t="s">
@@ -8877,7 +8968,7 @@
     </row>
     <row r="232" spans="3:15">
       <c r="D232" s="2"/>
-      <c r="E232" s="64" t="s">
+      <c r="E232" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F232" t="s">
@@ -8907,7 +8998,7 @@
     </row>
     <row r="233" spans="3:15">
       <c r="D233" s="2"/>
-      <c r="E233" s="43" t="s">
+      <c r="E233" s="44" t="s">
         <v>166</v>
       </c>
       <c r="F233" t="s">
@@ -8937,7 +9028,7 @@
     </row>
     <row r="234" spans="3:15">
       <c r="D234" s="2"/>
-      <c r="E234" s="45" t="s">
+      <c r="E234" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F234" t="s">
@@ -8964,11 +9055,11 @@
       <c r="M234" t="s">
         <v>32</v>
       </c>
-      <c r="O234" s="42"/>
+      <c r="O234" s="43"/>
     </row>
     <row r="235" spans="3:15">
       <c r="D235" s="2"/>
-      <c r="E235" s="64" t="s">
+      <c r="E235" s="65" t="s">
         <v>103</v>
       </c>
       <c r="F235" t="s">
@@ -8995,42 +9086,42 @@
       <c r="M235" t="s">
         <v>32</v>
       </c>
-      <c r="N235" s="45"/>
+      <c r="N235" s="46"/>
     </row>
     <row r="236" spans="3:15">
       <c r="D236" s="2"/>
     </row>
     <row r="242" spans="3:17">
       <c r="D242" s="3"/>
-      <c r="E242" s="45"/>
-      <c r="F242" s="38" t="s">
+      <c r="E242" s="46"/>
+      <c r="F242" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G242" s="38" t="s">
+      <c r="G242" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H242" s="39" t="s">
+      <c r="H242" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I242" s="39"/>
-      <c r="J242" s="39" t="s">
+      <c r="I242" s="40"/>
+      <c r="J242" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K242" s="39"/>
-      <c r="L242" s="38" t="s">
+      <c r="K242" s="40"/>
+      <c r="L242" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="M242" s="38" t="s">
+      <c r="M242" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N242" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O242" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P242" s="38"/>
-      <c r="Q242" s="38"/>
+      <c r="N242" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O242" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P242" s="39"/>
+      <c r="Q242" s="39"/>
     </row>
     <row r="243" spans="3:17">
       <c r="C243" s="1" t="s">
@@ -9039,44 +9130,44 @@
       <c r="D243" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E243" s="43" t="s">
+      <c r="E243" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="F243" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G243" s="44" t="s">
+      <c r="F243" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G243" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H243" s="44" t="s">
+      <c r="H243" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="I243" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J243" s="44" t="s">
+      <c r="I243" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J243" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K243" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L243" s="44" t="s">
+      <c r="K243" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L243" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M243" s="44" t="s">
+      <c r="M243" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="N243" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O243" s="42" t="s">
+      <c r="N243" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O243" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="244" spans="3:17">
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
-      <c r="E244" s="45" t="s">
+      <c r="E244" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F244" t="s">
@@ -9107,7 +9198,7 @@
     <row r="245" spans="3:17">
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="64" t="s">
+      <c r="E245" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F245" t="s">
@@ -9138,56 +9229,56 @@
     <row r="246" spans="3:17">
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
-      <c r="H246" s="59"/>
-      <c r="I246" s="59"/>
-      <c r="J246" s="59"/>
-      <c r="K246" s="65"/>
-      <c r="L246" s="66"/>
-      <c r="M246" s="66"/>
-      <c r="N246" s="66"/>
-      <c r="O246" s="66"/>
+      <c r="H246" s="60"/>
+      <c r="I246" s="60"/>
+      <c r="J246" s="60"/>
+      <c r="K246" s="66"/>
+      <c r="L246" s="67"/>
+      <c r="M246" s="67"/>
+      <c r="N246" s="67"/>
+      <c r="O246" s="67"/>
     </row>
     <row r="247" spans="3:17">
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
-      <c r="E247" s="43" t="s">
+      <c r="E247" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="F247" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G247" s="44" t="s">
+      <c r="F247" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G247" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H247" s="44" t="s">
+      <c r="H247" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="I247" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J247" s="44" t="s">
+      <c r="I247" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J247" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="K247" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L247" s="44" t="s">
+      <c r="K247" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L247" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="M247" s="44" t="s">
+      <c r="M247" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="N247" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O247" s="42" t="s">
+      <c r="N247" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O247" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="248" spans="3:17">
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
-      <c r="E248" s="45" t="s">
+      <c r="E248" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F248" t="s">
@@ -9218,7 +9309,7 @@
     <row r="249" spans="3:17">
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="64" t="s">
+      <c r="E249" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F249" t="s">
@@ -9247,42 +9338,42 @@
       </c>
     </row>
     <row r="251" spans="3:17">
-      <c r="E251" s="43" t="s">
+      <c r="E251" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="F251" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G251" s="44" t="s">
+      <c r="F251" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G251" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H251" s="44" t="s">
+      <c r="H251" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="I251" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J251" s="44" t="s">
+      <c r="I251" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J251" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K251" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L251" s="44" t="s">
+      <c r="K251" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L251" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="M251" s="44" t="s">
+      <c r="M251" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="N251" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O251" s="42" t="s">
+      <c r="N251" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O251" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="252" spans="3:17">
-      <c r="E252" s="45" t="s">
+      <c r="E252" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F252" t="s">
@@ -9311,7 +9402,7 @@
       </c>
     </row>
     <row r="253" spans="3:17">
-      <c r="E253" s="64" t="s">
+      <c r="E253" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F253" t="s">
@@ -9346,175 +9437,175 @@
       <c r="D255" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E255" s="43"/>
-      <c r="F255" s="44"/>
-      <c r="G255" s="44"/>
-      <c r="H255" s="44"/>
-      <c r="I255" s="44"/>
-      <c r="J255" s="44"/>
-      <c r="K255" s="44"/>
-      <c r="L255" s="44"/>
-      <c r="M255" s="44"/>
-      <c r="N255" s="44"/>
-      <c r="O255" s="42"/>
+      <c r="E255" s="44"/>
+      <c r="F255" s="45"/>
+      <c r="G255" s="45"/>
+      <c r="H255" s="45"/>
+      <c r="I255" s="45"/>
+      <c r="J255" s="45"/>
+      <c r="K255" s="45"/>
+      <c r="L255" s="45"/>
+      <c r="M255" s="45"/>
+      <c r="N255" s="45"/>
+      <c r="O255" s="43"/>
     </row>
     <row r="256" spans="3:17">
       <c r="C256" s="1"/>
       <c r="D256" s="2"/>
-      <c r="E256" s="45"/>
+      <c r="E256" s="46"/>
     </row>
     <row r="257" spans="3:17">
       <c r="C257" s="1"/>
       <c r="D257" s="2"/>
-      <c r="E257" s="45"/>
-      <c r="F257" s="38" t="s">
+      <c r="E257" s="46"/>
+      <c r="F257" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G257" s="38" t="s">
+      <c r="G257" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H257" s="39" t="s">
+      <c r="H257" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I257" s="39"/>
-      <c r="J257" s="39" t="s">
+      <c r="I257" s="40"/>
+      <c r="J257" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K257" s="39"/>
-      <c r="L257" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M257" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N257" s="38"/>
-      <c r="O257" s="38"/>
-      <c r="P257" s="38"/>
-      <c r="Q257" s="38"/>
+      <c r="K257" s="40"/>
+      <c r="L257" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M257" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N257" s="39"/>
+      <c r="O257" s="39"/>
+      <c r="P257" s="39"/>
+      <c r="Q257" s="39"/>
     </row>
     <row r="258" spans="3:17">
       <c r="C258" s="1"/>
       <c r="D258" s="2"/>
-      <c r="E258" s="46" t="s">
+      <c r="E258" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F258" t="s">
         <v>39</v>
       </c>
-      <c r="G258" s="45" t="s">
+      <c r="G258" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H258" s="44" t="s">
+      <c r="H258" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="I258" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J258" s="44" t="s">
+      <c r="I258" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J258" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="K258" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L258" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M258" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N258" s="45"/>
+      <c r="K258" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="L258" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M258" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N258" s="46"/>
     </row>
     <row r="259" spans="3:17">
       <c r="C259" s="1"/>
       <c r="D259" s="2"/>
-      <c r="E259" s="46"/>
-      <c r="F259" s="47" t="s">
+      <c r="E259" s="47"/>
+      <c r="F259" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G259" s="47" t="s">
+      <c r="G259" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="H259" s="47" t="s">
+      <c r="H259" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I259" s="47" t="s">
+      <c r="I259" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="J259" s="47" t="s">
+      <c r="J259" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="K259" s="48" t="s">
+      <c r="K259" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L259" s="48"/>
-      <c r="M259" s="47"/>
-      <c r="N259" s="44"/>
-      <c r="O259" s="42"/>
+      <c r="L259" s="49"/>
+      <c r="M259" s="48"/>
+      <c r="N259" s="45"/>
+      <c r="O259" s="43"/>
     </row>
     <row r="260" spans="3:17">
       <c r="C260" s="1"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="46" t="s">
+      <c r="E260" s="47" t="s">
         <v>90</v>
       </c>
       <c r="F260" t="s">
         <v>39</v>
       </c>
-      <c r="G260" s="44" t="s">
+      <c r="G260" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="H260" s="44" t="s">
+      <c r="H260" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="I260" s="44" t="s">
+      <c r="I260" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="J260" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="K260" s="55" t="s">
+      <c r="J260" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K260" s="56" t="s">
         <v>190</v>
       </c>
-      <c r="L260" s="50"/>
-      <c r="M260" s="51"/>
-      <c r="N260" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O260" s="42" t="s">
+      <c r="L260" s="51"/>
+      <c r="M260" s="52"/>
+      <c r="N260" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O260" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="261" spans="3:17">
       <c r="C261" s="1"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="46" t="s">
+      <c r="E261" s="47" t="s">
         <v>103</v>
       </c>
       <c r="F261" t="s">
         <v>39</v>
       </c>
-      <c r="G261" s="45" t="s">
+      <c r="G261" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="H261" s="44" t="s">
+      <c r="H261" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="I261" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J261" s="45" t="s">
+      <c r="I261" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J261" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K261" s="45" t="s">
+      <c r="K261" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="L261" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M261" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N261" s="45"/>
+      <c r="L261" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M261" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N261" s="46"/>
     </row>
     <row r="262" spans="3:17">
       <c r="D262" s="2"/>
@@ -10002,7 +10093,7 @@
     <row r="13" ht="33" customHeight="1" spans="1:7">
       <c r="F13" s="3"/>
     </row>
-    <row r="14" ht="33" customHeight="1" spans="1:7">
+    <row r="14" ht="100" customHeight="1" spans="1:7">
       <c r="A14">
         <v>30</v>
       </c>
@@ -10025,7 +10116,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="15" ht="51" customHeight="1" spans="1:7">
+    <row r="15" ht="118" customHeight="1" spans="1:7">
       <c r="A15">
         <v>34</v>
       </c>
@@ -10070,10 +10161,10 @@
         <v>231</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1" spans="1:7">
@@ -10088,16 +10179,16 @@
         <v>197</v>
       </c>
       <c r="D22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" t="s">
         <v>233</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G22" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -10112,16 +10203,16 @@
         <v>197</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F23" t="s">
         <v>205</v>
       </c>
       <c r="G23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -10136,16 +10227,16 @@
         <v>197</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F24" t="s">
         <v>205</v>
       </c>
       <c r="G24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -10160,16 +10251,16 @@
         <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -10184,16 +10275,16 @@
         <v>197</v>
       </c>
       <c r="D26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F26" t="s">
         <v>242</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="F26" t="s">
-        <v>241</v>
-      </c>
       <c r="G26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -10208,16 +10299,16 @@
         <v>197</v>
       </c>
       <c r="D27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F27" t="s">
         <v>211</v>
       </c>
       <c r="G27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -10232,16 +10323,16 @@
         <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F28" t="s">
         <v>211</v>
       </c>
       <c r="G28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -10256,16 +10347,16 @@
         <v>197</v>
       </c>
       <c r="D29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F29" t="s">
         <v>211</v>
       </c>
       <c r="G29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -10280,13 +10371,13 @@
         <v>197</v>
       </c>
       <c r="D30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -10301,10 +10392,10 @@
         <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F31" t="s">
         <v>211</v>
@@ -10322,10 +10413,10 @@
         <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -10376,10 +10467,10 @@
         <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>139</v>
@@ -10406,19 +10497,19 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G39" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" ht="43" customHeight="1" spans="1:7">
@@ -10436,13 +10527,13 @@
         <v>224</v>
       </c>
       <c r="E40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="G40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -10454,10 +10545,10 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E41" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>151</v>
@@ -10478,16 +10569,16 @@
         <v>223</v>
       </c>
       <c r="D42" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E42" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="G42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" ht="27" spans="1:7">
@@ -10502,16 +10593,16 @@
         <v>223</v>
       </c>
       <c r="D43" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="G43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -10522,16 +10613,16 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D48" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E48" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F48" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -10543,13 +10634,13 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D49" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E49" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -10560,19 +10651,19 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" ht="264.75" customHeight="1" spans="1:8">
@@ -10583,22 +10674,22 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E51" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G51" t="s">
-        <v>232</v>
-      </c>
-      <c r="H51" t="s">
-        <v>281</v>
+        <v>233</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:8">
@@ -10609,16 +10700,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:8">
@@ -10630,16 +10721,16 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D53" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E53" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:8">
@@ -10653,16 +10744,16 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D55" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E55" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:8">
@@ -10673,13 +10764,13 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D56" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E56" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F56" s="3"/>
     </row>
@@ -10692,10 +10783,10 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="D57" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F57" s="3"/>
     </row>
@@ -10708,7 +10799,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>296</v>
+        <v>197</v>
       </c>
       <c r="D58" t="s">
         <v>297</v>
@@ -10724,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" t="s">
         <v>298</v>
-      </c>
-      <c r="D59" t="s">
-        <v>299</v>
       </c>
       <c r="F59" s="3"/>
     </row>
@@ -10740,10 +10831,10 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>300</v>
+        <v>197</v>
       </c>
       <c r="D60" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F60" s="3"/>
     </row>
@@ -10756,10 +10847,10 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>302</v>
+        <v>197</v>
       </c>
       <c r="D61" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3"/>
     </row>
@@ -10772,14 +10863,30 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>304</v>
+        <v>197</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F62" s="3"/>
     </row>
     <row r="63" ht="18" customHeight="1" spans="1:8">
+      <c r="A63">
+        <f>A62+B62</f>
+        <v>168</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63" t="s">
+        <v>302</v>
+      </c>
+      <c r="E63" t="s">
+        <v>303</v>
+      </c>
       <c r="F63" s="3"/>
     </row>
     <row r="64" ht="18" customHeight="1" spans="1:8">
@@ -10793,14 +10900,29 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E65" t="s">
+        <v>304</v>
+      </c>
+      <c r="F65" s="3"/>
+    </row>
+    <row r="66" ht="33" customHeight="1" spans="1:8">
+      <c r="A66">
+        <v>171</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E66" t="s">
         <v>306</v>
       </c>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" ht="18" customHeight="1" spans="1:8">
       <c r="F66" s="3"/>
     </row>
     <row r="67" ht="18" customHeight="1" spans="1:8">
@@ -10811,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E67" t="s">
         <v>307</v>
@@ -10829,7 +10951,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E69" t="s">
         <v>308</v>
@@ -10840,14 +10962,50 @@
       <c r="F70" s="3"/>
     </row>
     <row r="71" ht="18" customHeight="1" spans="1:8">
+      <c r="A71">
+        <v>190</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" t="s">
+        <v>309</v>
+      </c>
+      <c r="E71" t="s">
+        <v>310</v>
+      </c>
       <c r="F71" s="3"/>
+      <c r="G71" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1" spans="1:8">
+      <c r="A72">
+        <v>192</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>311</v>
+      </c>
+      <c r="D72" t="s">
+        <v>312</v>
+      </c>
+      <c r="E72" t="s">
+        <v>313</v>
+      </c>
       <c r="F72" s="3"/>
+      <c r="G72" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1" spans="1:8">
@@ -10867,13 +11025,13 @@
         <v>179</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G75" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -10887,16 +11045,16 @@
         <v>197</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E76" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G76" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H76" s="1"/>
     </row>
@@ -10909,19 +11067,19 @@
         <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D77" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E77" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G77" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H77" s="1"/>
     </row>
@@ -10931,22 +11089,22 @@
         <v>208</v>
       </c>
       <c r="B78" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C78" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D78" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E78" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="G78" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H78" s="1"/>
     </row>
@@ -10977,7 +11135,7 @@
   <sheetData>
     <row r="1" spans="2:17">
       <c r="B1" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>

--- a/辐射报警仪协议命令和寄存器表10.xlsx
+++ b/辐射报警仪协议命令和寄存器表10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26565" windowHeight="12315" activeTab="1"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="具体命令" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="334">
   <si>
     <t>数据</t>
   </si>
@@ -776,7 +776,7 @@
     <t>data_time</t>
   </si>
   <si>
-    <t>时间（五分钟值）</t>
+    <t>时间（五分钟值）实时</t>
   </si>
   <si>
     <t>reg30  | 五分钟窗结束时间 byte0-1 | uint16×1      | 只读 | 见下方「时间编码」
@@ -798,6 +798,18 @@
        | 例：0.01 μSv → 1；1.23 μSv → 123。
        | 由 10 个 30 秒块 D30 相加；与 reg1 瞬时率分离。
 </t>
+  </si>
+  <si>
+    <t>hdata_time</t>
+  </si>
+  <si>
+    <t>时间（五分钟值）历史</t>
+  </si>
+  <si>
+    <t>hdose_rate</t>
+  </si>
+  <si>
+    <t>辐射量*100（五分钟值）历史</t>
   </si>
   <si>
     <t>报警阈值设置和其他控制</t>
@@ -2150,7 +2162,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2168,9 +2180,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2924,243 +2933,243 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
       <c r="Y4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="3:26">
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="10" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="10"/>
+      <c r="Z5" s="9"/>
     </row>
     <row r="6" spans="3:26">
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="12"/>
+      <c r="H6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="16" t="s">
+      <c r="I6" s="14"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12" t="s">
+      <c r="S6" s="11"/>
+      <c r="T6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12" t="s">
+      <c r="U6" s="11"/>
+      <c r="V6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="W6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="X6" s="12" t="s">
+      <c r="X6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="3:26">
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="19" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="20" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="20" t="s">
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="19" t="s">
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="R7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="19" t="s">
+      <c r="S7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="T7" s="19" t="s">
+      <c r="T7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="U7" s="19" t="s">
+      <c r="U7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="19" t="s">
+      <c r="V7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="19" t="s">
+      <c r="W7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
+      <c r="X7" s="18"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="3:26">
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
     </row>
     <row r="9" spans="3:26">
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
     </row>
     <row r="10" spans="3:26">
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
     </row>
     <row r="12" spans="3:26">
       <c r="E12" s="3"/>
@@ -3285,7 +3294,7 @@
       <c r="H18" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="31" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="1"/>
@@ -3519,18 +3528,18 @@
       <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="31" t="s">
         <v>66</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="32" t="s">
         <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
@@ -3565,13 +3574,13 @@
       <c r="H25" t="s">
         <v>47</v>
       </c>
-      <c r="I25" s="34" t="s">
+      <c r="I25" s="33" t="s">
         <v>69</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
       </c>
-      <c r="M25" s="35" t="s">
+      <c r="M25" s="34" t="s">
         <v>70</v>
       </c>
       <c r="P25" s="1"/>
@@ -3596,13 +3605,13 @@
       <c r="H26" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="34" t="s">
+      <c r="I26" s="33" t="s">
         <v>72</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="36" t="s">
+      <c r="M26" s="35" t="s">
         <v>17</v>
       </c>
       <c r="P26" s="1"/>
@@ -3627,13 +3636,13 @@
       <c r="H27" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="33" t="s">
         <v>73</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="36" t="s">
+      <c r="M27" s="35" t="s">
         <v>17</v>
       </c>
       <c r="P27" s="1"/>
@@ -3658,13 +3667,13 @@
       <c r="H28" t="s">
         <v>47</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="33" t="s">
         <v>74</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
       </c>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>17</v>
       </c>
       <c r="N28" s="1"/>
@@ -3702,7 +3711,7 @@
       <c r="L29" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="35" t="s">
+      <c r="M29" s="34" t="s">
         <v>77</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -3748,13 +3757,13 @@
       <c r="F32" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" s="32" t="s">
         <v>46</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I32" s="37" t="s">
+      <c r="I32" s="36" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="1"/>
@@ -3776,59 +3785,59 @@
       </c>
     </row>
     <row r="36" spans="3:17">
-      <c r="E36" s="38"/>
-      <c r="F36" s="39" t="s">
+      <c r="E36" s="37"/>
+      <c r="F36" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="40" t="s">
+      <c r="H36" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40" t="s">
+      <c r="I36" s="39"/>
+      <c r="J36" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K36" s="40"/>
-      <c r="L36" s="39" t="s">
+      <c r="K36" s="39"/>
+      <c r="L36" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="39" t="s">
+      <c r="M36" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N36" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
+      <c r="N36" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
     </row>
     <row r="37" spans="3:17">
-      <c r="F37" s="41"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42" t="s">
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="42" t="s">
+      <c r="I37" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="42" t="s">
+      <c r="J37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="42" t="s">
+      <c r="K37" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42" t="s">
+      <c r="L37" s="41"/>
+      <c r="M37" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="43"/>
+      <c r="N37" s="42"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="1" t="s">
@@ -3837,46 +3846,46 @@
       <c r="D38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E38" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="45" t="s">
+      <c r="F38" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G38" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="I38" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J38" s="45" t="s">
+      <c r="I38" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K38" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L38" s="45" t="s">
+      <c r="K38" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M38" s="45" t="s">
+      <c r="M38" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" s="43"/>
-      <c r="Q38" s="43"/>
+      <c r="N38" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
     </row>
     <row r="39" spans="3:17">
       <c r="C39" s="1"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="46" t="s">
+      <c r="E39" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F39" t="s">
@@ -3907,7 +3916,7 @@
     <row r="40" spans="3:17">
       <c r="C40" s="1"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="46" t="s">
+      <c r="E40" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F40" t="s">
@@ -3938,187 +3947,187 @@
     <row r="41" spans="3:17">
       <c r="C41" s="1"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="39" t="s">
+      <c r="E41" s="46"/>
+      <c r="F41" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="40" t="s">
+      <c r="H41" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40" t="s">
+      <c r="I41" s="39"/>
+      <c r="J41" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K41" s="40"/>
-      <c r="L41" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="38"/>
+      <c r="Q41" s="38"/>
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="1"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="47" t="s">
+      <c r="E42" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="46" t="s">
+      <c r="G42" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="H42" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="I42" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42" s="45" t="s">
+      <c r="I42" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K42" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M42" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N42" s="46"/>
+      <c r="K42" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L42" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="45"/>
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="1"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48" t="s">
+      <c r="E43" s="46"/>
+      <c r="F43" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="48" t="s">
+      <c r="G43" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="48" t="s">
+      <c r="H43" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I43" s="48" t="s">
+      <c r="I43" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J43" s="48" t="s">
+      <c r="J43" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K43" s="49" t="s">
+      <c r="K43" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L43" s="49"/>
-      <c r="M43" s="48"/>
+      <c r="L43" s="48"/>
+      <c r="M43" s="47"/>
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="1"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="47" t="s">
+      <c r="E44" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H44" s="45" t="s">
+      <c r="H44" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I44" s="45" t="s">
+      <c r="I44" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="J44" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K44" s="50" t="s">
+      <c r="J44" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="L44" s="51"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O44" s="43" t="s">
+      <c r="L44" s="50"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="1"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="47" t="s">
+      <c r="E45" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
-      <c r="G45" s="46" t="s">
+      <c r="G45" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="H45" s="45" t="s">
+      <c r="H45" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="I45" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" s="46" t="s">
+      <c r="I45" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K45" s="46" t="s">
+      <c r="K45" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L45" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M45" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N45" s="46"/>
+      <c r="L45" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="45"/>
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="1"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="3:17">
-      <c r="F47" s="39" t="s">
+      <c r="F47" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="40" t="s">
+      <c r="H47" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40" t="s">
+      <c r="I47" s="39"/>
+      <c r="J47" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K47" s="40"/>
-      <c r="L47" s="39" t="s">
+      <c r="K47" s="39"/>
+      <c r="L47" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M47" s="39" t="s">
+      <c r="M47" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N47" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
+      <c r="N47" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" s="38"/>
+      <c r="Q47" s="38"/>
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="1" t="s">
@@ -4127,46 +4136,46 @@
       <c r="D48" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="44" t="s">
+      <c r="E48" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F48" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" s="45" t="s">
+      <c r="F48" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H48" s="45" t="s">
+      <c r="H48" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I48" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" s="45" t="s">
+      <c r="I48" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K48" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L48" s="45" t="s">
+      <c r="K48" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L48" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M48" s="45" t="s">
+      <c r="M48" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="N48" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="45"/>
-      <c r="Q48" s="45"/>
+      <c r="N48" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
     </row>
     <row r="49" spans="3:17">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="46" t="s">
+      <c r="E49" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F49" t="s">
@@ -4197,7 +4206,7 @@
     <row r="50" spans="3:17">
       <c r="C50" s="1"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="46" t="s">
+      <c r="E50" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F50" t="s">
@@ -4228,184 +4237,184 @@
     <row r="51" spans="3:17">
       <c r="C51" s="1"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="39" t="s">
+      <c r="E51" s="46"/>
+      <c r="F51" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="39" t="s">
+      <c r="G51" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H51" s="40" t="s">
+      <c r="H51" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40" t="s">
+      <c r="I51" s="39"/>
+      <c r="J51" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K51" s="40"/>
-      <c r="L51" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M51" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" s="39"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M51" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="38"/>
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="1"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="47" t="s">
+      <c r="E52" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="46" t="s">
+      <c r="G52" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="45" t="s">
+      <c r="H52" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I52" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J52" s="45" t="s">
+      <c r="I52" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K52" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L52" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M52" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" s="46"/>
+      <c r="K52" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L52" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="45"/>
     </row>
     <row r="53" spans="3:17">
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="48" t="s">
+      <c r="E53" s="46"/>
+      <c r="F53" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="48" t="s">
+      <c r="G53" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H53" s="48" t="s">
+      <c r="H53" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I53" s="48" t="s">
+      <c r="I53" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J53" s="48" t="s">
+      <c r="J53" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K53" s="49" t="s">
+      <c r="K53" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L53" s="49"/>
-      <c r="M53" s="48"/>
+      <c r="L53" s="48"/>
+      <c r="M53" s="47"/>
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="1"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="47" t="s">
+      <c r="E54" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="45" t="s">
+      <c r="G54" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H54" s="45" t="s">
+      <c r="H54" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I54" s="45" t="s">
+      <c r="I54" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="J54" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K54" s="50" t="s">
+      <c r="J54" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="L54" s="51"/>
-      <c r="M54" s="52"/>
-      <c r="N54" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" s="43" t="s">
+      <c r="L54" s="50"/>
+      <c r="M54" s="51"/>
+      <c r="N54" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="1"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="47" t="s">
+      <c r="E55" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="46" t="s">
+      <c r="G55" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H55" s="45" t="s">
+      <c r="H55" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I55" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J55" s="46" t="s">
+      <c r="I55" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K55" s="46" t="s">
+      <c r="K55" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L55" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M55" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N55" s="46"/>
+      <c r="L55" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="45"/>
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="1"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="3:17">
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="40" t="s">
+      <c r="H57" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40" t="s">
+      <c r="I57" s="39"/>
+      <c r="J57" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K57" s="40"/>
-      <c r="L57" s="39" t="s">
+      <c r="K57" s="39"/>
+      <c r="L57" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M57" s="39" t="s">
+      <c r="M57" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N57" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O57" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" s="39"/>
-      <c r="Q57" s="39"/>
+      <c r="N57" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="1" t="s">
@@ -4414,44 +4423,44 @@
       <c r="D58" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E58" s="44" t="s">
+      <c r="E58" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F58" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="45" t="s">
+      <c r="F58" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="45" t="s">
+      <c r="H58" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="I58" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J58" s="45" t="s">
+      <c r="I58" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K58" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="45" t="s">
+      <c r="K58" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L58" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M58" s="45" t="s">
+      <c r="M58" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="N58" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O58" s="43" t="s">
+      <c r="N58" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O58" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="1"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="46" t="s">
+      <c r="E59" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F59" t="s">
@@ -4482,7 +4491,7 @@
     <row r="60" spans="3:17">
       <c r="C60" s="1"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="46" t="s">
+      <c r="E60" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F60" t="s">
@@ -4513,184 +4522,184 @@
     <row r="61" spans="3:17">
       <c r="C61" s="1"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="39" t="s">
+      <c r="E61" s="46"/>
+      <c r="F61" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="39" t="s">
+      <c r="G61" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H61" s="40" t="s">
+      <c r="H61" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40" t="s">
+      <c r="I61" s="39"/>
+      <c r="J61" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K61" s="40"/>
-      <c r="L61" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M61" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="39"/>
+      <c r="K61" s="39"/>
+      <c r="L61" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M61" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="38"/>
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="1"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="47" t="s">
+      <c r="E62" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
       </c>
-      <c r="G62" s="46" t="s">
+      <c r="G62" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="45" t="s">
+      <c r="H62" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="I62" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J62" s="45" t="s">
+      <c r="I62" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K62" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L62" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M62" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="46"/>
+      <c r="K62" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L62" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M62" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="45"/>
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="1"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="48" t="s">
+      <c r="E63" s="46"/>
+      <c r="F63" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G63" s="48" t="s">
+      <c r="G63" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="48" t="s">
+      <c r="H63" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="48" t="s">
+      <c r="I63" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J63" s="48" t="s">
+      <c r="J63" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K63" s="49" t="s">
+      <c r="K63" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L63" s="49"/>
-      <c r="M63" s="48"/>
+      <c r="L63" s="48"/>
+      <c r="M63" s="47"/>
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="1"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="47" t="s">
+      <c r="E64" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
       </c>
-      <c r="G64" s="45" t="s">
+      <c r="G64" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H64" s="45" t="s">
+      <c r="H64" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I64" s="45" t="s">
+      <c r="I64" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="J64" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" s="50" t="s">
+      <c r="J64" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="L64" s="51"/>
-      <c r="M64" s="52"/>
-      <c r="N64" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="43" t="s">
+      <c r="L64" s="50"/>
+      <c r="M64" s="51"/>
+      <c r="N64" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O64" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="65" spans="3:17">
       <c r="C65" s="1"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="47" t="s">
+      <c r="E65" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F65" t="s">
         <v>39</v>
       </c>
-      <c r="G65" s="46" t="s">
+      <c r="G65" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H65" s="45" t="s">
+      <c r="H65" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="I65" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65" s="46" t="s">
+      <c r="I65" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K65" s="46" t="s">
+      <c r="K65" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L65" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M65" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N65" s="46"/>
+      <c r="L65" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M65" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="45"/>
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="1"/>
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="3:17">
-      <c r="F67" s="39" t="s">
+      <c r="F67" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G67" s="39" t="s">
+      <c r="G67" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H67" s="40" t="s">
+      <c r="H67" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I67" s="40"/>
-      <c r="J67" s="40" t="s">
+      <c r="I67" s="39"/>
+      <c r="J67" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K67" s="40"/>
-      <c r="L67" s="39" t="s">
+      <c r="K67" s="39"/>
+      <c r="L67" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M67" s="39" t="s">
+      <c r="M67" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N67" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O67" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P67" s="39"/>
-      <c r="Q67" s="39"/>
+      <c r="N67" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O67" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="38"/>
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="1" t="s">
@@ -4699,44 +4708,44 @@
       <c r="D68" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="44" t="s">
+      <c r="E68" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F68" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="45" t="s">
+      <c r="F68" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H68" s="45" t="s">
+      <c r="H68" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J68" s="45" t="s">
+      <c r="I68" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K68" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L68" s="45" t="s">
+      <c r="K68" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L68" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M68" s="45" t="s">
+      <c r="M68" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="N68" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O68" s="43" t="s">
+      <c r="N68" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="1"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="46" t="s">
+      <c r="E69" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F69" t="s">
@@ -4767,7 +4776,7 @@
     <row r="70" spans="3:17">
       <c r="C70" s="1"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="46" t="s">
+      <c r="E70" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F70" t="s">
@@ -4798,184 +4807,184 @@
     <row r="71" spans="3:17">
       <c r="C71" s="1"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="39" t="s">
+      <c r="E71" s="46"/>
+      <c r="F71" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G71" s="39" t="s">
+      <c r="G71" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H71" s="40" t="s">
+      <c r="H71" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40" t="s">
+      <c r="I71" s="39"/>
+      <c r="J71" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K71" s="40"/>
-      <c r="L71" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M71" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N71" s="39"/>
+      <c r="K71" s="39"/>
+      <c r="L71" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M71" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="38"/>
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="1"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="47" t="s">
+      <c r="E72" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F72" t="s">
         <v>39</v>
       </c>
-      <c r="G72" s="46" t="s">
+      <c r="G72" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="45" t="s">
+      <c r="H72" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I72" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J72" s="45" t="s">
+      <c r="I72" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K72" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L72" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M72" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N72" s="46"/>
+      <c r="K72" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="45"/>
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="48" t="s">
+      <c r="E73" s="46"/>
+      <c r="F73" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G73" s="48" t="s">
+      <c r="G73" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H73" s="48" t="s">
+      <c r="H73" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I73" s="48" t="s">
+      <c r="I73" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J73" s="48" t="s">
+      <c r="J73" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K73" s="49" t="s">
+      <c r="K73" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L73" s="49"/>
-      <c r="M73" s="48"/>
+      <c r="L73" s="48"/>
+      <c r="M73" s="47"/>
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="1"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="47" t="s">
+      <c r="E74" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>39</v>
       </c>
-      <c r="G74" s="45" t="s">
+      <c r="G74" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H74" s="45" t="s">
+      <c r="H74" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I74" s="45" t="s">
+      <c r="I74" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="J74" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K74" s="50" t="s">
+      <c r="J74" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="L74" s="51"/>
-      <c r="M74" s="52"/>
-      <c r="N74" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O74" s="43" t="s">
+      <c r="L74" s="50"/>
+      <c r="M74" s="51"/>
+      <c r="N74" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O74" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="1"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="47" t="s">
+      <c r="E75" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F75" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="46" t="s">
+      <c r="G75" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H75" s="45" t="s">
+      <c r="H75" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I75" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J75" s="46" t="s">
+      <c r="I75" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J75" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K75" s="46" t="s">
+      <c r="K75" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L75" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M75" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N75" s="46"/>
+      <c r="L75" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M75" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75" s="45"/>
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="1"/>
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="3:17">
-      <c r="F77" s="39" t="s">
+      <c r="F77" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="39" t="s">
+      <c r="G77" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H77" s="40" t="s">
+      <c r="H77" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I77" s="40"/>
-      <c r="J77" s="40" t="s">
+      <c r="I77" s="39"/>
+      <c r="J77" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K77" s="40"/>
-      <c r="L77" s="39" t="s">
+      <c r="K77" s="39"/>
+      <c r="L77" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M77" s="39" t="s">
+      <c r="M77" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N77" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O77" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P77" s="39"/>
-      <c r="Q77" s="39"/>
+      <c r="N77" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P77" s="38"/>
+      <c r="Q77" s="38"/>
     </row>
     <row r="78" spans="3:17">
       <c r="C78" s="1" t="s">
@@ -4984,44 +4993,44 @@
       <c r="D78" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="44" t="s">
+      <c r="E78" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="45" t="s">
+      <c r="F78" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H78" s="45" t="s">
+      <c r="H78" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="I78" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="45" t="s">
+      <c r="I78" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K78" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L78" s="45" t="s">
+      <c r="K78" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L78" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M78" s="53" t="s">
+      <c r="M78" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="N78" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O78" s="43" t="s">
+      <c r="N78" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="1"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="46" t="s">
+      <c r="E79" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F79" t="s">
@@ -5052,7 +5061,7 @@
     <row r="80" spans="3:17">
       <c r="C80" s="1"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="46" t="s">
+      <c r="E80" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F80" t="s">
@@ -5083,184 +5092,184 @@
     <row r="81" spans="3:17">
       <c r="C81" s="1"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="39" t="s">
+      <c r="E81" s="46"/>
+      <c r="F81" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G81" s="39" t="s">
+      <c r="G81" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H81" s="40" t="s">
+      <c r="H81" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I81" s="40"/>
-      <c r="J81" s="40" t="s">
+      <c r="I81" s="39"/>
+      <c r="J81" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K81" s="40"/>
-      <c r="L81" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M81" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N81" s="39"/>
+      <c r="K81" s="39"/>
+      <c r="L81" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M81" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81" s="38"/>
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="1"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="47" t="s">
+      <c r="E82" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F82" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="46" t="s">
+      <c r="G82" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="45" t="s">
+      <c r="H82" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="I82" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J82" s="45" t="s">
+      <c r="I82" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K82" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L82" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M82" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N82" s="46"/>
+      <c r="K82" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L82" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M82" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N82" s="45"/>
     </row>
     <row r="83" spans="3:17">
       <c r="C83" s="1"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="48" t="s">
+      <c r="E83" s="46"/>
+      <c r="F83" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G83" s="48" t="s">
+      <c r="G83" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H83" s="48" t="s">
+      <c r="H83" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I83" s="48" t="s">
+      <c r="I83" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J83" s="48" t="s">
+      <c r="J83" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K83" s="49" t="s">
+      <c r="K83" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L83" s="49"/>
-      <c r="M83" s="48"/>
+      <c r="L83" s="48"/>
+      <c r="M83" s="47"/>
     </row>
     <row r="84" spans="3:17">
       <c r="C84" s="1"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="47" t="s">
+      <c r="E84" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F84" t="s">
         <v>39</v>
       </c>
-      <c r="G84" s="45" t="s">
+      <c r="G84" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H84" s="45" t="s">
+      <c r="H84" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I84" s="45" t="s">
+      <c r="I84" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="50" t="s">
+      <c r="J84" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="L84" s="51"/>
-      <c r="M84" s="52"/>
-      <c r="N84" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O84" s="43" t="s">
+      <c r="L84" s="50"/>
+      <c r="M84" s="51"/>
+      <c r="N84" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O84" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="1"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="47" t="s">
+      <c r="E85" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>39</v>
       </c>
-      <c r="G85" s="46" t="s">
+      <c r="G85" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H85" s="45" t="s">
+      <c r="H85" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="I85" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" s="46" t="s">
+      <c r="I85" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K85" s="46" t="s">
+      <c r="K85" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L85" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M85" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N85" s="46"/>
+      <c r="L85" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M85" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="45"/>
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
     </row>
     <row r="87" spans="3:17">
-      <c r="F87" s="39" t="s">
+      <c r="F87" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G87" s="39" t="s">
+      <c r="G87" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H87" s="40" t="s">
+      <c r="H87" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I87" s="40"/>
-      <c r="J87" s="40" t="s">
+      <c r="I87" s="39"/>
+      <c r="J87" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K87" s="40"/>
-      <c r="L87" s="39" t="s">
+      <c r="K87" s="39"/>
+      <c r="L87" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M87" s="39" t="s">
+      <c r="M87" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N87" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O87" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P87" s="39"/>
-      <c r="Q87" s="39"/>
+      <c r="N87" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O87" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P87" s="38"/>
+      <c r="Q87" s="38"/>
     </row>
     <row r="88" spans="3:17">
       <c r="C88" s="1" t="s">
@@ -5269,44 +5278,44 @@
       <c r="D88" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E88" s="44" t="s">
+      <c r="E88" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F88" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G88" s="45" t="s">
+      <c r="F88" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G88" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="45" t="s">
+      <c r="H88" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I88" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J88" s="45" t="s">
+      <c r="I88" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K88" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L88" s="45" t="s">
+      <c r="K88" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L88" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M88" s="53" t="s">
+      <c r="M88" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="N88" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O88" s="43" t="s">
+      <c r="N88" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="89" spans="3:17">
       <c r="C89" s="1"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="46" t="s">
+      <c r="E89" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F89" t="s">
@@ -5337,7 +5346,7 @@
     <row r="90" spans="3:17">
       <c r="C90" s="1"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="46" t="s">
+      <c r="E90" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F90" t="s">
@@ -5368,158 +5377,158 @@
     <row r="91" spans="3:17">
       <c r="C91" s="1"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="47" t="s">
+      <c r="E91" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F91" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="46" t="s">
+      <c r="G91" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="45" t="s">
+      <c r="H91" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I91" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J91" s="45" t="s">
+      <c r="I91" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J91" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K91" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L91" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M91" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N91" s="46"/>
+      <c r="K91" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L91" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M91" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N91" s="45"/>
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="48" t="s">
+      <c r="E92" s="46"/>
+      <c r="F92" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="48" t="s">
+      <c r="G92" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H92" s="48" t="s">
+      <c r="H92" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I92" s="48" t="s">
+      <c r="I92" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J92" s="48" t="s">
+      <c r="J92" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K92" s="49" t="s">
+      <c r="K92" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L92" s="49"/>
-      <c r="M92" s="48"/>
+      <c r="L92" s="48"/>
+      <c r="M92" s="47"/>
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="1"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="47" t="s">
+      <c r="E93" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F93" t="s">
         <v>39</v>
       </c>
-      <c r="G93" s="45" t="s">
+      <c r="G93" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H93" s="45" t="s">
+      <c r="H93" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I93" s="45" t="s">
+      <c r="I93" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="J93" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" s="50" t="s">
+      <c r="J93" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K93" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="L93" s="51"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O93" s="43" t="s">
+      <c r="L93" s="50"/>
+      <c r="M93" s="51"/>
+      <c r="N93" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O93" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="1"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="47" t="s">
+      <c r="E94" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F94" t="s">
         <v>39</v>
       </c>
-      <c r="G94" s="46" t="s">
+      <c r="G94" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H94" s="45" t="s">
+      <c r="H94" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I94" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J94" s="46" t="s">
+      <c r="I94" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K94" s="46" t="s">
+      <c r="K94" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L94" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M94" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N94" s="46"/>
+      <c r="L94" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M94" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94" s="45"/>
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="1"/>
       <c r="D95" s="2"/>
     </row>
     <row r="96" spans="3:17">
-      <c r="F96" s="39" t="s">
+      <c r="F96" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G96" s="39" t="s">
+      <c r="G96" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H96" s="40" t="s">
+      <c r="H96" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40" t="s">
+      <c r="I96" s="39"/>
+      <c r="J96" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K96" s="40"/>
-      <c r="L96" s="39" t="s">
+      <c r="K96" s="39"/>
+      <c r="L96" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M96" s="39" t="s">
+      <c r="M96" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N96" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O96" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P96" s="39"/>
-      <c r="Q96" s="39"/>
+      <c r="N96" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O96" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" s="38"/>
+      <c r="Q96" s="38"/>
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="1" t="s">
@@ -5528,44 +5537,44 @@
       <c r="D97" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E97" s="44" t="s">
+      <c r="E97" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F97" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="45" t="s">
+      <c r="F97" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H97" s="45" t="s">
+      <c r="H97" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I97" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J97" s="45" t="s">
+      <c r="I97" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K97" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L97" s="45" t="s">
+      <c r="K97" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L97" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M97" s="45" t="s">
+      <c r="M97" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="N97" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O97" s="43" t="s">
+      <c r="N97" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O97" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="98" spans="3:17">
       <c r="C98" s="1"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="46" t="s">
+      <c r="E98" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F98" t="s">
@@ -5596,7 +5605,7 @@
     <row r="99" spans="3:17">
       <c r="C99" s="1"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="46" t="s">
+      <c r="E99" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F99" t="s">
@@ -5627,158 +5636,158 @@
     <row r="100" spans="3:17">
       <c r="C100" s="1"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="47" t="s">
+      <c r="E100" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F100" t="s">
         <v>39</v>
       </c>
-      <c r="G100" s="46" t="s">
+      <c r="G100" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="45" t="s">
+      <c r="H100" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I100" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J100" s="45" t="s">
+      <c r="I100" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J100" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K100" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L100" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M100" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N100" s="46"/>
+      <c r="K100" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L100" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N100" s="45"/>
     </row>
     <row r="101" spans="3:17">
       <c r="C101" s="1"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="48" t="s">
+      <c r="E101" s="46"/>
+      <c r="F101" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="48" t="s">
+      <c r="G101" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H101" s="48" t="s">
+      <c r="H101" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I101" s="48" t="s">
+      <c r="I101" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J101" s="48" t="s">
+      <c r="J101" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K101" s="49" t="s">
+      <c r="K101" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L101" s="49"/>
-      <c r="M101" s="48"/>
+      <c r="L101" s="48"/>
+      <c r="M101" s="47"/>
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="1"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="47" t="s">
+      <c r="E102" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F102" t="s">
         <v>39</v>
       </c>
-      <c r="G102" s="45" t="s">
+      <c r="G102" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H102" s="45" t="s">
+      <c r="H102" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I102" s="45" t="s">
+      <c r="I102" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="J102" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="50" t="s">
+      <c r="J102" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="L102" s="51"/>
-      <c r="M102" s="52"/>
-      <c r="N102" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O102" s="43" t="s">
+      <c r="L102" s="50"/>
+      <c r="M102" s="51"/>
+      <c r="N102" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O102" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="1"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="47" t="s">
+      <c r="E103" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F103" t="s">
         <v>39</v>
       </c>
-      <c r="G103" s="46" t="s">
+      <c r="G103" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H103" s="45" t="s">
+      <c r="H103" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I103" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="46" t="s">
+      <c r="I103" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K103" s="46" t="s">
+      <c r="K103" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L103" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M103" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N103" s="46"/>
+      <c r="L103" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M103" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N103" s="45"/>
     </row>
     <row r="104" spans="3:17">
       <c r="C104" s="1"/>
       <c r="D104" s="2"/>
     </row>
     <row r="105" spans="3:17">
-      <c r="F105" s="39" t="s">
+      <c r="F105" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="39" t="s">
+      <c r="G105" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="40" t="s">
+      <c r="H105" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I105" s="40"/>
-      <c r="J105" s="40" t="s">
+      <c r="I105" s="39"/>
+      <c r="J105" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K105" s="40"/>
-      <c r="L105" s="39" t="s">
+      <c r="K105" s="39"/>
+      <c r="L105" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M105" s="39" t="s">
+      <c r="M105" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N105" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O105" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P105" s="39"/>
-      <c r="Q105" s="39"/>
+      <c r="N105" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O105" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P105" s="38"/>
+      <c r="Q105" s="38"/>
     </row>
     <row r="106" spans="3:17">
       <c r="C106" s="1" t="s">
@@ -5787,44 +5796,44 @@
       <c r="D106" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E106" s="44" t="s">
+      <c r="E106" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F106" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G106" s="45" t="s">
+      <c r="F106" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G106" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H106" s="45" t="s">
+      <c r="H106" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I106" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J106" s="45" t="s">
+      <c r="I106" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J106" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K106" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="45" t="s">
+      <c r="K106" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M106" s="45" t="s">
+      <c r="M106" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="N106" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O106" s="43" t="s">
+      <c r="N106" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O106" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="1"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="46" t="s">
+      <c r="E107" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F107" t="s">
@@ -5855,7 +5864,7 @@
     <row r="108" spans="3:17">
       <c r="C108" s="1"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="46" t="s">
+      <c r="E108" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F108" t="s">
@@ -5886,158 +5895,158 @@
     <row r="109" spans="3:17">
       <c r="C109" s="1"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="47" t="s">
+      <c r="E109" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F109" t="s">
         <v>39</v>
       </c>
-      <c r="G109" s="46" t="s">
+      <c r="G109" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H109" s="45" t="s">
+      <c r="H109" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I109" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="45" t="s">
+      <c r="I109" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K109" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L109" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M109" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N109" s="46"/>
+      <c r="K109" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L109" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M109" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N109" s="45"/>
     </row>
     <row r="110" spans="3:17">
       <c r="C110" s="1"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="48" t="s">
+      <c r="E110" s="46"/>
+      <c r="F110" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="48" t="s">
+      <c r="G110" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H110" s="48" t="s">
+      <c r="H110" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I110" s="48" t="s">
+      <c r="I110" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J110" s="48" t="s">
+      <c r="J110" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K110" s="49" t="s">
+      <c r="K110" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L110" s="49"/>
-      <c r="M110" s="48"/>
+      <c r="L110" s="48"/>
+      <c r="M110" s="47"/>
     </row>
     <row r="111" spans="3:17">
       <c r="C111" s="1"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="47" t="s">
+      <c r="E111" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F111" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="45" t="s">
+      <c r="G111" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H111" s="45" t="s">
+      <c r="H111" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I111" s="45" t="s">
+      <c r="I111" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="J111" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" s="50" t="s">
+      <c r="J111" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="L111" s="51"/>
-      <c r="M111" s="52"/>
-      <c r="N111" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O111" s="43" t="s">
+      <c r="L111" s="50"/>
+      <c r="M111" s="51"/>
+      <c r="N111" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O111" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="112" spans="3:17">
       <c r="C112" s="1"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="47" t="s">
+      <c r="E112" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F112" t="s">
         <v>39</v>
       </c>
-      <c r="G112" s="46" t="s">
+      <c r="G112" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H112" s="45" t="s">
+      <c r="H112" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I112" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J112" s="46" t="s">
+      <c r="I112" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J112" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K112" s="46" t="s">
+      <c r="K112" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L112" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M112" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N112" s="46"/>
+      <c r="L112" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M112" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N112" s="45"/>
     </row>
     <row r="113" spans="3:17">
       <c r="C113" s="1"/>
       <c r="D113" s="2"/>
     </row>
     <row r="114" spans="3:17">
-      <c r="F114" s="39" t="s">
+      <c r="F114" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G114" s="39" t="s">
+      <c r="G114" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H114" s="40" t="s">
+      <c r="H114" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I114" s="40"/>
-      <c r="J114" s="40" t="s">
+      <c r="I114" s="39"/>
+      <c r="J114" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="40"/>
-      <c r="L114" s="39" t="s">
+      <c r="K114" s="39"/>
+      <c r="L114" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M114" s="39" t="s">
+      <c r="M114" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N114" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O114" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P114" s="39"/>
-      <c r="Q114" s="39"/>
+      <c r="N114" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O114" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P114" s="38"/>
+      <c r="Q114" s="38"/>
     </row>
     <row r="115" spans="3:17">
       <c r="C115" s="1" t="s">
@@ -6046,44 +6055,44 @@
       <c r="D115" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E115" s="44" t="s">
+      <c r="E115" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F115" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G115" s="45" t="s">
+      <c r="F115" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G115" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H115" s="45" t="s">
+      <c r="H115" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="I115" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J115" s="45" t="s">
+      <c r="I115" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J115" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K115" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L115" s="45" t="s">
+      <c r="K115" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L115" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M115" s="53" t="s">
+      <c r="M115" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="N115" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O115" s="43" t="s">
+      <c r="N115" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O115" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="116" spans="3:17">
       <c r="C116" s="1"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="46" t="s">
+      <c r="E116" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F116" t="s">
@@ -6114,7 +6123,7 @@
     <row r="117" spans="3:17">
       <c r="C117" s="1"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="46" t="s">
+      <c r="E117" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F117" t="s">
@@ -6145,158 +6154,158 @@
     <row r="118" spans="3:17">
       <c r="C118" s="1"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="47" t="s">
+      <c r="E118" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F118" t="s">
         <v>39</v>
       </c>
-      <c r="G118" s="46" t="s">
+      <c r="G118" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H118" s="45" t="s">
+      <c r="H118" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="I118" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J118" s="45" t="s">
+      <c r="I118" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J118" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K118" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L118" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M118" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N118" s="46"/>
+      <c r="K118" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L118" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M118" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N118" s="45"/>
     </row>
     <row r="119" spans="3:17">
       <c r="C119" s="1"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="47"/>
-      <c r="F119" s="48" t="s">
+      <c r="E119" s="46"/>
+      <c r="F119" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="48" t="s">
+      <c r="G119" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H119" s="48" t="s">
+      <c r="H119" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I119" s="48" t="s">
+      <c r="I119" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J119" s="48" t="s">
+      <c r="J119" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K119" s="49" t="s">
+      <c r="K119" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L119" s="49"/>
-      <c r="M119" s="48"/>
+      <c r="L119" s="48"/>
+      <c r="M119" s="47"/>
     </row>
     <row r="120" spans="3:17">
       <c r="C120" s="1"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="47" t="s">
+      <c r="E120" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F120" t="s">
         <v>39</v>
       </c>
-      <c r="G120" s="45" t="s">
+      <c r="G120" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H120" s="45" t="s">
+      <c r="H120" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I120" s="45" t="s">
+      <c r="I120" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="J120" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" s="50" t="s">
+      <c r="J120" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="L120" s="51"/>
-      <c r="M120" s="52"/>
-      <c r="N120" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O120" s="43" t="s">
+      <c r="L120" s="50"/>
+      <c r="M120" s="51"/>
+      <c r="N120" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O120" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="121" spans="3:17">
       <c r="C121" s="1"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="47" t="s">
+      <c r="E121" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F121" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="46" t="s">
+      <c r="G121" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H121" s="45" t="s">
+      <c r="H121" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="I121" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="46" t="s">
+      <c r="I121" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K121" s="46" t="s">
+      <c r="K121" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L121" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M121" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N121" s="46"/>
+      <c r="L121" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M121" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N121" s="45"/>
     </row>
     <row r="122" spans="3:17">
       <c r="C122" s="1"/>
       <c r="D122" s="2"/>
     </row>
     <row r="123" spans="3:17">
-      <c r="F123" s="39" t="s">
+      <c r="F123" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G123" s="39" t="s">
+      <c r="G123" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H123" s="40" t="s">
+      <c r="H123" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I123" s="40"/>
-      <c r="J123" s="40" t="s">
+      <c r="I123" s="39"/>
+      <c r="J123" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K123" s="40"/>
-      <c r="L123" s="39" t="s">
+      <c r="K123" s="39"/>
+      <c r="L123" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M123" s="39" t="s">
+      <c r="M123" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N123" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O123" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P123" s="39"/>
-      <c r="Q123" s="39"/>
+      <c r="N123" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O123" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P123" s="38"/>
+      <c r="Q123" s="38"/>
     </row>
     <row r="124" spans="3:17">
       <c r="C124" s="1" t="s">
@@ -6305,44 +6314,44 @@
       <c r="D124" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E124" s="44" t="s">
+      <c r="E124" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F124" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G124" s="45" t="s">
+      <c r="F124" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G124" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H124" s="45" t="s">
+      <c r="H124" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I124" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J124" s="45" t="s">
+      <c r="I124" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K124" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L124" s="45" t="s">
+      <c r="K124" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L124" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M124" s="53" t="s">
+      <c r="M124" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="N124" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O124" s="43" t="s">
+      <c r="N124" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O124" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="125" spans="3:17">
       <c r="C125" s="1"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="46" t="s">
+      <c r="E125" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F125" t="s">
@@ -6373,7 +6382,7 @@
     <row r="126" spans="3:17">
       <c r="C126" s="1"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="46" t="s">
+      <c r="E126" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F126" t="s">
@@ -6404,158 +6413,158 @@
     <row r="127" spans="3:17">
       <c r="C127" s="1"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="47" t="s">
+      <c r="E127" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F127" t="s">
         <v>39</v>
       </c>
-      <c r="G127" s="46" t="s">
+      <c r="G127" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H127" s="45" t="s">
+      <c r="H127" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I127" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J127" s="45" t="s">
+      <c r="I127" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J127" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K127" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L127" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M127" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N127" s="46"/>
+      <c r="K127" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L127" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M127" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N127" s="45"/>
     </row>
     <row r="128" spans="3:17">
       <c r="C128" s="1"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="48" t="s">
+      <c r="E128" s="46"/>
+      <c r="F128" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="48" t="s">
+      <c r="G128" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H128" s="48" t="s">
+      <c r="H128" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I128" s="48" t="s">
+      <c r="I128" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J128" s="48" t="s">
+      <c r="J128" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K128" s="49" t="s">
+      <c r="K128" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L128" s="49"/>
-      <c r="M128" s="48"/>
+      <c r="L128" s="48"/>
+      <c r="M128" s="47"/>
     </row>
     <row r="129" spans="3:17">
       <c r="C129" s="1"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="47" t="s">
+      <c r="E129" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F129" t="s">
         <v>39</v>
       </c>
-      <c r="G129" s="45" t="s">
+      <c r="G129" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H129" s="45" t="s">
+      <c r="H129" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I129" s="45" t="s">
+      <c r="I129" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="J129" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="54" t="s">
+      <c r="J129" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K129" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="L129" s="51"/>
-      <c r="M129" s="52"/>
-      <c r="N129" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O129" s="43" t="s">
+      <c r="L129" s="50"/>
+      <c r="M129" s="51"/>
+      <c r="N129" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O129" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="130" spans="3:17">
       <c r="C130" s="1"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="47" t="s">
+      <c r="E130" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F130" t="s">
         <v>39</v>
       </c>
-      <c r="G130" s="46" t="s">
+      <c r="G130" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H130" s="45" t="s">
+      <c r="H130" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I130" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J130" s="46" t="s">
+      <c r="I130" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J130" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K130" s="46" t="s">
+      <c r="K130" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L130" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M130" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N130" s="46"/>
+      <c r="L130" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M130" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N130" s="45"/>
     </row>
     <row r="131" spans="3:17">
       <c r="C131" s="1"/>
       <c r="D131" s="2"/>
     </row>
     <row r="132" spans="3:17">
-      <c r="F132" s="39" t="s">
+      <c r="F132" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="39" t="s">
+      <c r="G132" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H132" s="40" t="s">
+      <c r="H132" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I132" s="40"/>
-      <c r="J132" s="40" t="s">
+      <c r="I132" s="39"/>
+      <c r="J132" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K132" s="40"/>
-      <c r="L132" s="39" t="s">
+      <c r="K132" s="39"/>
+      <c r="L132" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M132" s="39" t="s">
+      <c r="M132" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N132" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O132" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P132" s="39"/>
-      <c r="Q132" s="39"/>
+      <c r="N132" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O132" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P132" s="38"/>
+      <c r="Q132" s="38"/>
     </row>
     <row r="133" spans="3:17">
       <c r="C133" s="1" t="s">
@@ -6564,44 +6573,44 @@
       <c r="D133" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E133" s="44" t="s">
+      <c r="E133" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F133" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G133" s="45" t="s">
+      <c r="F133" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G133" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H133" s="45" t="s">
+      <c r="H133" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="I133" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="45" t="s">
+      <c r="I133" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K133" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L133" s="45" t="s">
+      <c r="K133" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L133" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M133" s="45" t="s">
+      <c r="M133" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="N133" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O133" s="43" t="s">
+      <c r="N133" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O133" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="134" spans="3:17">
       <c r="C134" s="1"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="46" t="s">
+      <c r="E134" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F134" t="s">
@@ -6632,7 +6641,7 @@
     <row r="135" spans="3:17">
       <c r="C135" s="1"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="46" t="s">
+      <c r="E135" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F135" t="s">
@@ -6663,158 +6672,158 @@
     <row r="136" spans="3:17">
       <c r="C136" s="1"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="47" t="s">
+      <c r="E136" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F136" t="s">
         <v>39</v>
       </c>
-      <c r="G136" s="46" t="s">
+      <c r="G136" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H136" s="45" t="s">
+      <c r="H136" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="I136" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J136" s="45" t="s">
+      <c r="I136" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K136" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L136" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M136" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N136" s="46"/>
+      <c r="K136" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L136" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M136" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N136" s="45"/>
     </row>
     <row r="137" spans="3:17">
       <c r="C137" s="1"/>
       <c r="D137" s="2"/>
-      <c r="E137" s="47"/>
-      <c r="F137" s="48" t="s">
+      <c r="E137" s="46"/>
+      <c r="F137" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G137" s="48" t="s">
+      <c r="G137" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H137" s="48" t="s">
+      <c r="H137" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I137" s="48" t="s">
+      <c r="I137" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J137" s="48" t="s">
+      <c r="J137" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K137" s="49" t="s">
+      <c r="K137" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L137" s="49"/>
-      <c r="M137" s="48"/>
+      <c r="L137" s="48"/>
+      <c r="M137" s="47"/>
     </row>
     <row r="138" spans="3:17">
       <c r="C138" s="1"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="47" t="s">
+      <c r="E138" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F138" t="s">
         <v>39</v>
       </c>
-      <c r="G138" s="45" t="s">
+      <c r="G138" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H138" s="45" t="s">
+      <c r="H138" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I138" s="45" t="s">
+      <c r="I138" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="J138" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K138" s="50" t="s">
+      <c r="J138" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K138" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="L138" s="51"/>
-      <c r="M138" s="52"/>
-      <c r="N138" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O138" s="43" t="s">
+      <c r="L138" s="50"/>
+      <c r="M138" s="51"/>
+      <c r="N138" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O138" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="139" spans="3:17">
       <c r="C139" s="1"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="47" t="s">
+      <c r="E139" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F139" t="s">
         <v>39</v>
       </c>
-      <c r="G139" s="46" t="s">
+      <c r="G139" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H139" s="45" t="s">
+      <c r="H139" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="I139" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" s="46" t="s">
+      <c r="I139" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J139" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K139" s="46" t="s">
+      <c r="K139" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L139" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M139" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N139" s="46"/>
+      <c r="L139" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M139" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N139" s="45"/>
     </row>
     <row r="140" spans="3:17">
       <c r="C140" s="1"/>
       <c r="D140" s="2"/>
     </row>
     <row r="141" spans="3:17">
-      <c r="F141" s="39" t="s">
+      <c r="F141" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G141" s="39" t="s">
+      <c r="G141" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H141" s="40" t="s">
+      <c r="H141" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I141" s="40"/>
-      <c r="J141" s="40" t="s">
+      <c r="I141" s="39"/>
+      <c r="J141" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K141" s="40"/>
-      <c r="L141" s="39" t="s">
+      <c r="K141" s="39"/>
+      <c r="L141" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M141" s="39" t="s">
+      <c r="M141" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N141" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O141" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P141" s="39"/>
-      <c r="Q141" s="39"/>
+      <c r="N141" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O141" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P141" s="38"/>
+      <c r="Q141" s="38"/>
     </row>
     <row r="142" spans="3:17">
       <c r="C142" s="1" t="s">
@@ -6823,44 +6832,44 @@
       <c r="D142" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E142" s="44" t="s">
+      <c r="E142" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F142" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G142" s="45" t="s">
+      <c r="F142" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H142" s="45" t="s">
+      <c r="H142" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="I142" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="45" t="s">
+      <c r="I142" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J142" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K142" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L142" s="45" t="s">
+      <c r="K142" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L142" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M142" s="45" t="s">
+      <c r="M142" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="N142" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O142" s="43" t="s">
+      <c r="N142" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O142" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="143" spans="3:17">
       <c r="C143" s="1"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="46" t="s">
+      <c r="E143" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F143" t="s">
@@ -6891,7 +6900,7 @@
     <row r="144" spans="3:17">
       <c r="C144" s="1"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="46" t="s">
+      <c r="E144" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F144" t="s">
@@ -6922,158 +6931,158 @@
     <row r="145" spans="3:17">
       <c r="C145" s="1"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="47" t="s">
+      <c r="E145" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F145" t="s">
         <v>39</v>
       </c>
-      <c r="G145" s="46" t="s">
+      <c r="G145" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H145" s="45" t="s">
+      <c r="H145" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="I145" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="45" t="s">
+      <c r="I145" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K145" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L145" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M145" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N145" s="46"/>
+      <c r="K145" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M145" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N145" s="45"/>
     </row>
     <row r="146" spans="3:17">
       <c r="C146" s="1"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="47"/>
-      <c r="F146" s="48" t="s">
+      <c r="E146" s="46"/>
+      <c r="F146" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G146" s="48" t="s">
+      <c r="G146" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H146" s="48" t="s">
+      <c r="H146" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I146" s="48" t="s">
+      <c r="I146" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J146" s="48" t="s">
+      <c r="J146" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K146" s="49" t="s">
+      <c r="K146" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L146" s="49"/>
-      <c r="M146" s="48"/>
+      <c r="L146" s="48"/>
+      <c r="M146" s="47"/>
     </row>
     <row r="147" spans="3:17">
       <c r="C147" s="1"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="47" t="s">
+      <c r="E147" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F147" t="s">
         <v>39</v>
       </c>
-      <c r="G147" s="45" t="s">
+      <c r="G147" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H147" s="45" t="s">
+      <c r="H147" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I147" s="45" t="s">
+      <c r="I147" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="J147" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="50" t="s">
+      <c r="J147" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="L147" s="51"/>
-      <c r="M147" s="52"/>
-      <c r="N147" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O147" s="43" t="s">
+      <c r="L147" s="50"/>
+      <c r="M147" s="51"/>
+      <c r="N147" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O147" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="148" spans="3:17">
       <c r="C148" s="1"/>
       <c r="D148" s="2"/>
-      <c r="E148" s="47" t="s">
+      <c r="E148" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F148" t="s">
         <v>39</v>
       </c>
-      <c r="G148" s="46" t="s">
+      <c r="G148" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H148" s="45" t="s">
+      <c r="H148" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="I148" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="46" t="s">
+      <c r="I148" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K148" s="46" t="s">
+      <c r="K148" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L148" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M148" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N148" s="46"/>
+      <c r="L148" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M148" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N148" s="45"/>
     </row>
     <row r="149" spans="3:17">
       <c r="C149" s="1"/>
       <c r="D149" s="2"/>
     </row>
     <row r="150" spans="3:17">
-      <c r="F150" s="39" t="s">
+      <c r="F150" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G150" s="39" t="s">
+      <c r="G150" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H150" s="40" t="s">
+      <c r="H150" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I150" s="40"/>
-      <c r="J150" s="40" t="s">
+      <c r="I150" s="39"/>
+      <c r="J150" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K150" s="40"/>
-      <c r="L150" s="39" t="s">
+      <c r="K150" s="39"/>
+      <c r="L150" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M150" s="39" t="s">
+      <c r="M150" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N150" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O150" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P150" s="39"/>
-      <c r="Q150" s="39"/>
+      <c r="N150" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O150" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P150" s="38"/>
+      <c r="Q150" s="38"/>
     </row>
     <row r="151" ht="81" spans="3:17">
       <c r="C151" s="1" t="s">
@@ -7082,44 +7091,44 @@
       <c r="D151" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E151" s="44" t="s">
+      <c r="E151" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F151" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G151" s="45" t="s">
+      <c r="F151" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G151" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H151" s="45" t="s">
+      <c r="H151" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="I151" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J151" s="45" t="s">
+      <c r="I151" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J151" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K151" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L151" s="45" t="s">
+      <c r="K151" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L151" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M151" s="55" t="s">
+      <c r="M151" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="N151" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O151" s="43" t="s">
+      <c r="N151" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O151" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="152" spans="3:17">
       <c r="C152" s="1"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="46" t="s">
+      <c r="E152" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F152" t="s">
@@ -7150,7 +7159,7 @@
     <row r="153" spans="3:17">
       <c r="C153" s="1"/>
       <c r="D153" s="2"/>
-      <c r="E153" s="46" t="s">
+      <c r="E153" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F153" t="s">
@@ -7181,160 +7190,160 @@
     <row r="154" spans="3:17">
       <c r="C154" s="1"/>
       <c r="D154" s="2"/>
-      <c r="E154" s="47" t="s">
+      <c r="E154" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F154" t="s">
         <v>39</v>
       </c>
-      <c r="G154" s="46" t="s">
+      <c r="G154" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H154" s="45" t="s">
+      <c r="H154" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="I154" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J154" s="45" t="s">
+      <c r="I154" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K154" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L154" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M154" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N154" s="46"/>
+      <c r="K154" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L154" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M154" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N154" s="45"/>
     </row>
     <row r="155" spans="3:17">
       <c r="C155" s="1"/>
       <c r="D155" s="2"/>
-      <c r="E155" s="47"/>
-      <c r="F155" s="48" t="s">
+      <c r="E155" s="46"/>
+      <c r="F155" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G155" s="48" t="s">
+      <c r="G155" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H155" s="48" t="s">
+      <c r="H155" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I155" s="48" t="s">
+      <c r="I155" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J155" s="48" t="s">
+      <c r="J155" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K155" s="49" t="s">
+      <c r="K155" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L155" s="49"/>
-      <c r="M155" s="48"/>
-      <c r="N155" s="45"/>
-      <c r="O155" s="43"/>
+      <c r="L155" s="48"/>
+      <c r="M155" s="47"/>
+      <c r="N155" s="44"/>
+      <c r="O155" s="42"/>
     </row>
     <row r="156" spans="3:17">
       <c r="C156" s="1"/>
       <c r="D156" s="2"/>
-      <c r="E156" s="47" t="s">
+      <c r="E156" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F156" t="s">
         <v>39</v>
       </c>
-      <c r="G156" s="45" t="s">
+      <c r="G156" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H156" s="45" t="s">
+      <c r="H156" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I156" s="45" t="s">
+      <c r="I156" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="J156" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K156" s="50" t="s">
+      <c r="J156" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="L156" s="51"/>
-      <c r="M156" s="52"/>
-      <c r="N156" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O156" s="43" t="s">
+      <c r="L156" s="50"/>
+      <c r="M156" s="51"/>
+      <c r="N156" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O156" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="157" spans="3:17">
       <c r="C157" s="1"/>
       <c r="D157" s="2"/>
-      <c r="E157" s="47" t="s">
+      <c r="E157" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F157" t="s">
         <v>39</v>
       </c>
-      <c r="G157" s="46" t="s">
+      <c r="G157" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H157" s="45" t="s">
+      <c r="H157" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="I157" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J157" s="46" t="s">
+      <c r="I157" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K157" s="46" t="s">
+      <c r="K157" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L157" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M157" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N157" s="46"/>
+      <c r="L157" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M157" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N157" s="45"/>
     </row>
     <row r="158" spans="3:17">
       <c r="C158" s="1"/>
       <c r="D158" s="2"/>
     </row>
     <row r="159" spans="3:17">
-      <c r="F159" s="39" t="s">
+      <c r="F159" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="39" t="s">
+      <c r="G159" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H159" s="40" t="s">
+      <c r="H159" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I159" s="40"/>
-      <c r="J159" s="40" t="s">
+      <c r="I159" s="39"/>
+      <c r="J159" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K159" s="40"/>
-      <c r="L159" s="39" t="s">
+      <c r="K159" s="39"/>
+      <c r="L159" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M159" s="39" t="s">
+      <c r="M159" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N159" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O159" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P159" s="39"/>
-      <c r="Q159" s="39"/>
+      <c r="N159" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O159" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P159" s="38"/>
+      <c r="Q159" s="38"/>
     </row>
     <row r="160" spans="3:17">
       <c r="C160" s="1" t="s">
@@ -7343,44 +7352,44 @@
       <c r="D160" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E160" s="44" t="s">
+      <c r="E160" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F160" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G160" s="45" t="s">
+      <c r="F160" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G160" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H160" s="45" t="s">
+      <c r="H160" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I160" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="45" t="s">
+      <c r="I160" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="K160" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L160" s="45" t="s">
+      <c r="K160" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L160" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="M160" s="45" t="s">
+      <c r="M160" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="N160" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O160" s="43" t="s">
+      <c r="N160" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O160" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="161" spans="3:17">
       <c r="C161" s="1"/>
       <c r="D161" s="2"/>
-      <c r="E161" s="46" t="s">
+      <c r="E161" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F161" t="s">
@@ -7411,7 +7420,7 @@
     <row r="162" spans="3:17">
       <c r="C162" s="1"/>
       <c r="D162" s="2"/>
-      <c r="E162" s="46" t="s">
+      <c r="E162" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F162" t="s">
@@ -7442,160 +7451,160 @@
     <row r="163" spans="3:17">
       <c r="C163" s="1"/>
       <c r="D163" s="2"/>
-      <c r="E163" s="47" t="s">
+      <c r="E163" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F163" t="s">
         <v>39</v>
       </c>
-      <c r="G163" s="46" t="s">
+      <c r="G163" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H163" s="45" t="s">
+      <c r="H163" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I163" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J163" s="45" t="s">
+      <c r="I163" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="K163" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L163" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M163" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N163" s="46"/>
+      <c r="K163" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L163" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M163" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N163" s="45"/>
     </row>
     <row r="164" spans="3:17">
       <c r="C164" s="1"/>
       <c r="D164" s="2"/>
-      <c r="E164" s="47"/>
-      <c r="F164" s="48" t="s">
+      <c r="E164" s="46"/>
+      <c r="F164" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G164" s="48" t="s">
+      <c r="G164" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H164" s="48" t="s">
+      <c r="H164" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I164" s="48" t="s">
+      <c r="I164" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J164" s="48" t="s">
+      <c r="J164" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K164" s="49" t="s">
+      <c r="K164" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L164" s="49"/>
-      <c r="M164" s="48"/>
-      <c r="N164" s="45"/>
-      <c r="O164" s="43"/>
+      <c r="L164" s="48"/>
+      <c r="M164" s="47"/>
+      <c r="N164" s="44"/>
+      <c r="O164" s="42"/>
     </row>
     <row r="165" spans="3:17">
       <c r="C165" s="1"/>
       <c r="D165" s="2"/>
-      <c r="E165" s="47" t="s">
+      <c r="E165" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F165" t="s">
         <v>39</v>
       </c>
-      <c r="G165" s="45" t="s">
+      <c r="G165" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H165" s="45" t="s">
+      <c r="H165" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="I165" s="45" t="s">
+      <c r="I165" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="J165" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K165" s="50" t="s">
+      <c r="J165" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K165" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L165" s="51"/>
-      <c r="M165" s="52"/>
-      <c r="N165" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O165" s="43" t="s">
+      <c r="L165" s="50"/>
+      <c r="M165" s="51"/>
+      <c r="N165" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O165" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="166" spans="3:17">
       <c r="C166" s="1"/>
       <c r="D166" s="2"/>
-      <c r="E166" s="47" t="s">
+      <c r="E166" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F166" t="s">
         <v>39</v>
       </c>
-      <c r="G166" s="46" t="s">
+      <c r="G166" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H166" s="45" t="s">
+      <c r="H166" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I166" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J166" s="46" t="s">
+      <c r="I166" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K166" s="46" t="s">
+      <c r="K166" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L166" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M166" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N166" s="46"/>
+      <c r="L166" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M166" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N166" s="45"/>
     </row>
     <row r="167" spans="3:17">
       <c r="C167" s="1"/>
       <c r="D167" s="2"/>
     </row>
     <row r="168" spans="3:17">
-      <c r="F168" s="39" t="s">
+      <c r="F168" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G168" s="39" t="s">
+      <c r="G168" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H168" s="40" t="s">
+      <c r="H168" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I168" s="40"/>
-      <c r="J168" s="40" t="s">
+      <c r="I168" s="39"/>
+      <c r="J168" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K168" s="40"/>
-      <c r="L168" s="39" t="s">
+      <c r="K168" s="39"/>
+      <c r="L168" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M168" s="39" t="s">
+      <c r="M168" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N168" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O168" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P168" s="39"/>
-      <c r="Q168" s="39"/>
+      <c r="N168" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O168" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P168" s="38"/>
+      <c r="Q168" s="38"/>
     </row>
     <row r="169" ht="81" spans="3:17">
       <c r="C169" s="1" t="s">
@@ -7604,44 +7613,44 @@
       <c r="D169" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E169" s="44" t="s">
+      <c r="E169" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F169" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G169" s="45" t="s">
+      <c r="F169" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G169" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H169" s="45" t="s">
+      <c r="H169" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I169" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J169" s="45" t="s">
+      <c r="I169" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K169" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L169" s="45" t="s">
+      <c r="K169" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L169" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="M169" s="55" t="s">
+      <c r="M169" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="N169" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O169" s="43" t="s">
+      <c r="N169" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O169" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="170" spans="3:17">
       <c r="C170" s="1"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="46" t="s">
+      <c r="E170" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F170" t="s">
@@ -7672,7 +7681,7 @@
     <row r="171" spans="3:17">
       <c r="C171" s="1"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="46" t="s">
+      <c r="E171" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F171" t="s">
@@ -7703,126 +7712,126 @@
     <row r="172" spans="3:17">
       <c r="C172" s="1"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="47" t="s">
+      <c r="E172" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F172" t="s">
         <v>39</v>
       </c>
-      <c r="G172" s="46" t="s">
+      <c r="G172" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H172" s="45" t="s">
+      <c r="H172" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I172" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J172" s="45" t="s">
+      <c r="I172" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K172" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L172" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M172" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N172" s="46"/>
+      <c r="K172" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L172" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M172" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N172" s="45"/>
     </row>
     <row r="173" spans="3:17">
       <c r="C173" s="1"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="47"/>
-      <c r="F173" s="48" t="s">
+      <c r="E173" s="46"/>
+      <c r="F173" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G173" s="48" t="s">
+      <c r="G173" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H173" s="48" t="s">
+      <c r="H173" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I173" s="48" t="s">
+      <c r="I173" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J173" s="48" t="s">
+      <c r="J173" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K173" s="49" t="s">
+      <c r="K173" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L173" s="49"/>
-      <c r="M173" s="48"/>
-      <c r="N173" s="45"/>
-      <c r="O173" s="43"/>
+      <c r="L173" s="48"/>
+      <c r="M173" s="47"/>
+      <c r="N173" s="44"/>
+      <c r="O173" s="42"/>
     </row>
     <row r="174" ht="70" customHeight="1" spans="3:17">
       <c r="C174" s="1"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="47" t="s">
+      <c r="E174" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F174" t="s">
         <v>39</v>
       </c>
-      <c r="G174" s="45" t="s">
+      <c r="G174" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H174" s="45" t="s">
+      <c r="H174" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="I174" s="45" t="s">
+      <c r="I174" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="J174" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K174" s="56" t="s">
+      <c r="J174" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K174" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="L174" s="51"/>
-      <c r="M174" s="52"/>
-      <c r="N174" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O174" s="43" t="s">
+      <c r="L174" s="50"/>
+      <c r="M174" s="51"/>
+      <c r="N174" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O174" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="175" spans="3:17">
       <c r="C175" s="1"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="47" t="s">
+      <c r="E175" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F175" t="s">
         <v>39</v>
       </c>
-      <c r="G175" s="46" t="s">
+      <c r="G175" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H175" s="45" t="s">
+      <c r="H175" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I175" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J175" s="46" t="s">
+      <c r="I175" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K175" s="46" t="s">
+      <c r="K175" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L175" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M175" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N175" s="46"/>
+      <c r="L175" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M175" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N175" s="45"/>
     </row>
     <row r="176" spans="3:17">
       <c r="C176" s="1"/>
@@ -7835,185 +7844,185 @@
       <c r="D178" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E178" s="44"/>
-      <c r="F178" s="45"/>
-      <c r="G178" s="45"/>
-      <c r="H178" s="45"/>
-      <c r="I178" s="45"/>
-      <c r="J178" s="45"/>
-      <c r="K178" s="45"/>
-      <c r="L178" s="45"/>
-      <c r="M178" s="45"/>
-      <c r="N178" s="45"/>
-      <c r="O178" s="43"/>
+      <c r="E178" s="43"/>
+      <c r="F178" s="44"/>
+      <c r="G178" s="44"/>
+      <c r="H178" s="44"/>
+      <c r="I178" s="44"/>
+      <c r="J178" s="44"/>
+      <c r="K178" s="44"/>
+      <c r="L178" s="44"/>
+      <c r="M178" s="44"/>
+      <c r="N178" s="44"/>
+      <c r="O178" s="42"/>
     </row>
     <row r="179" spans="3:17">
       <c r="C179" s="1"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="46"/>
+      <c r="E179" s="45"/>
     </row>
     <row r="180" spans="3:17">
       <c r="C180" s="1"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="46"/>
+      <c r="E180" s="45"/>
     </row>
     <row r="181" spans="3:17">
       <c r="C181" s="1"/>
       <c r="D181" s="2"/>
-      <c r="E181" s="47" t="s">
+      <c r="E181" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F181" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="46" t="s">
+      <c r="G181" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H181" s="45" t="s">
+      <c r="H181" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I181" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J181" s="45" t="s">
+      <c r="I181" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J181" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="K181" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L181" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M181" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N181" s="46"/>
+      <c r="K181" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L181" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M181" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N181" s="45"/>
     </row>
     <row r="182" ht="21" customHeight="1" spans="3:17">
       <c r="C182" s="1"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="47"/>
-      <c r="F182" s="48" t="s">
+      <c r="E182" s="46"/>
+      <c r="F182" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G182" s="48" t="s">
+      <c r="G182" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H182" s="48" t="s">
+      <c r="H182" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I182" s="48" t="s">
+      <c r="I182" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J182" s="48" t="s">
+      <c r="J182" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K182" s="49" t="s">
+      <c r="K182" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L182" s="49"/>
-      <c r="M182" s="48"/>
-      <c r="N182" s="45"/>
-      <c r="O182" s="43"/>
+      <c r="L182" s="48"/>
+      <c r="M182" s="47"/>
+      <c r="N182" s="44"/>
+      <c r="O182" s="42"/>
     </row>
     <row r="183" ht="45" customHeight="1" spans="3:17">
       <c r="C183" s="1"/>
       <c r="D183" s="2"/>
-      <c r="E183" s="47" t="s">
+      <c r="E183" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F183" t="s">
         <v>39</v>
       </c>
-      <c r="G183" s="45" t="s">
+      <c r="G183" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H183" s="45" t="s">
+      <c r="H183" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="I183" s="45" t="s">
+      <c r="I183" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="J183" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K183" s="56" t="s">
+      <c r="J183" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K183" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="L183" s="51"/>
-      <c r="M183" s="52"/>
-      <c r="N183" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O183" s="43" t="s">
+      <c r="L183" s="50"/>
+      <c r="M183" s="51"/>
+      <c r="N183" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O183" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="184" spans="3:17">
       <c r="C184" s="1"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="47" t="s">
+      <c r="E184" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F184" t="s">
         <v>39</v>
       </c>
-      <c r="G184" s="46" t="s">
+      <c r="G184" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H184" s="45" t="s">
+      <c r="H184" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I184" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J184" s="46" t="s">
+      <c r="I184" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J184" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K184" s="46" t="s">
+      <c r="K184" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L184" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M184" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N184" s="46"/>
+      <c r="L184" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M184" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N184" s="45"/>
     </row>
     <row r="185" spans="3:17">
       <c r="C185" s="1"/>
       <c r="D185" s="2"/>
     </row>
     <row r="186" spans="3:17">
-      <c r="F186" s="39" t="s">
+      <c r="F186" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G186" s="39" t="s">
+      <c r="G186" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H186" s="40" t="s">
+      <c r="H186" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I186" s="40"/>
-      <c r="J186" s="40" t="s">
+      <c r="I186" s="39"/>
+      <c r="J186" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K186" s="40"/>
-      <c r="L186" s="39" t="s">
+      <c r="K186" s="39"/>
+      <c r="L186" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M186" s="39" t="s">
+      <c r="M186" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N186" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O186" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P186" s="39"/>
-      <c r="Q186" s="39"/>
+      <c r="N186" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O186" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P186" s="38"/>
+      <c r="Q186" s="38"/>
     </row>
     <row r="187" spans="3:17">
       <c r="C187" s="1" t="s">
@@ -8022,44 +8031,44 @@
       <c r="D187" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E187" s="44" t="s">
+      <c r="E187" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F187" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G187" s="45" t="s">
+      <c r="F187" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G187" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H187" s="45" t="s">
+      <c r="H187" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="I187" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J187" s="45" t="s">
+      <c r="I187" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J187" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="K187" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L187" s="45" t="s">
+      <c r="K187" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L187" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="M187" s="45" t="s">
+      <c r="M187" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="N187" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O187" s="43" t="s">
+      <c r="N187" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O187" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="188" spans="3:17">
       <c r="C188" s="1"/>
       <c r="D188" s="2"/>
-      <c r="E188" s="46" t="s">
+      <c r="E188" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F188" t="s">
@@ -8090,7 +8099,7 @@
     <row r="189" spans="3:17">
       <c r="C189" s="1"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="46" t="s">
+      <c r="E189" s="45" t="s">
         <v>92</v>
       </c>
       <c r="F189" t="s">
@@ -8121,56 +8130,56 @@
     <row r="190" spans="3:17">
       <c r="C190" s="1"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="47"/>
-      <c r="F190" s="57" t="s">
+      <c r="E190" s="46"/>
+      <c r="F190" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="G190" s="57" t="s">
+      <c r="G190" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="H190" s="57" t="s">
+      <c r="H190" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="I190" s="58" t="s">
+      <c r="I190" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="J190" s="58"/>
-      <c r="K190" s="58" t="s">
+      <c r="J190" s="57"/>
+      <c r="K190" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="L190" s="58"/>
-      <c r="M190" s="58"/>
-      <c r="N190" s="58"/>
-      <c r="O190" s="58"/>
+      <c r="L190" s="57"/>
+      <c r="M190" s="57"/>
+      <c r="N190" s="57"/>
+      <c r="O190" s="57"/>
     </row>
     <row r="191" spans="3:17">
       <c r="C191" s="1"/>
       <c r="D191" s="2"/>
-      <c r="E191" s="47" t="s">
+      <c r="E191" s="46" t="s">
         <v>156</v>
       </c>
       <c r="F191" t="s">
         <v>39</v>
       </c>
-      <c r="G191" s="59" t="s">
+      <c r="G191" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="H191" s="60" t="s">
+      <c r="H191" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="I191" s="60" t="s">
+      <c r="I191" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="J191" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="K191" s="61" t="s">
+      <c r="J191" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K191" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="L191" s="62"/>
-      <c r="M191" s="62"/>
-      <c r="N191" s="62"/>
-      <c r="O191" s="62"/>
+      <c r="L191" s="61"/>
+      <c r="M191" s="61"/>
+      <c r="N191" s="61"/>
+      <c r="O191" s="61"/>
       <c r="P191" t="s">
         <v>31</v>
       </c>
@@ -8181,179 +8190,179 @@
     <row r="192" spans="3:17">
       <c r="C192" s="1"/>
       <c r="D192" s="2"/>
-      <c r="E192" s="47"/>
-      <c r="G192" s="63"/>
-      <c r="H192" s="64"/>
-      <c r="I192" s="64"/>
-      <c r="J192" s="64"/>
-      <c r="K192" s="64"/>
-      <c r="L192" s="63"/>
-      <c r="M192" s="63"/>
-      <c r="N192" s="63"/>
+      <c r="E192" s="46"/>
+      <c r="G192" s="62"/>
+      <c r="H192" s="63"/>
+      <c r="I192" s="63"/>
+      <c r="J192" s="63"/>
+      <c r="K192" s="63"/>
+      <c r="L192" s="62"/>
+      <c r="M192" s="62"/>
+      <c r="N192" s="62"/>
     </row>
     <row r="193" spans="3:17">
       <c r="C193" s="1"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="47"/>
-      <c r="G193" s="45"/>
-      <c r="H193" s="45"/>
-      <c r="I193" s="45"/>
-      <c r="J193" s="45"/>
-      <c r="K193" s="45"/>
-      <c r="L193" s="45"/>
-      <c r="M193" s="45"/>
-      <c r="N193" s="45"/>
-      <c r="O193" s="43"/>
+      <c r="E193" s="46"/>
+      <c r="G193" s="44"/>
+      <c r="H193" s="44"/>
+      <c r="I193" s="44"/>
+      <c r="J193" s="44"/>
+      <c r="K193" s="44"/>
+      <c r="L193" s="44"/>
+      <c r="M193" s="44"/>
+      <c r="N193" s="44"/>
+      <c r="O193" s="42"/>
     </row>
     <row r="194" spans="3:17">
       <c r="C194" s="1"/>
       <c r="D194" s="2"/>
-      <c r="E194" s="47"/>
-      <c r="G194" s="46"/>
-      <c r="H194" s="45"/>
-      <c r="I194" s="45"/>
-      <c r="J194" s="46"/>
-      <c r="K194" s="46"/>
-      <c r="L194" s="46"/>
-      <c r="M194" s="46"/>
-      <c r="N194" s="46"/>
+      <c r="E194" s="46"/>
+      <c r="G194" s="45"/>
+      <c r="H194" s="44"/>
+      <c r="I194" s="44"/>
+      <c r="J194" s="45"/>
+      <c r="K194" s="45"/>
+      <c r="L194" s="45"/>
+      <c r="M194" s="45"/>
+      <c r="N194" s="45"/>
     </row>
     <row r="195" spans="3:17">
       <c r="D195" s="3"/>
-      <c r="E195" s="46"/>
-      <c r="F195" s="39"/>
-      <c r="G195" s="39"/>
-      <c r="H195" s="40"/>
-      <c r="I195" s="40"/>
-      <c r="J195" s="40"/>
-      <c r="K195" s="40"/>
-      <c r="L195" s="39"/>
-      <c r="M195" s="39"/>
-      <c r="N195" s="39"/>
-      <c r="O195" s="39"/>
-      <c r="P195" s="39"/>
-      <c r="Q195" s="39"/>
+      <c r="E195" s="45"/>
+      <c r="F195" s="38"/>
+      <c r="G195" s="38"/>
+      <c r="H195" s="39"/>
+      <c r="I195" s="39"/>
+      <c r="J195" s="39"/>
+      <c r="K195" s="39"/>
+      <c r="L195" s="38"/>
+      <c r="M195" s="38"/>
+      <c r="N195" s="38"/>
+      <c r="O195" s="38"/>
+      <c r="P195" s="38"/>
+      <c r="Q195" s="38"/>
     </row>
     <row r="196" spans="3:17">
       <c r="C196" s="1"/>
       <c r="D196" s="2"/>
-      <c r="E196" s="44"/>
-      <c r="F196" s="45"/>
-      <c r="G196" s="45"/>
-      <c r="H196" s="45"/>
-      <c r="I196" s="45"/>
-      <c r="J196" s="45"/>
-      <c r="K196" s="45"/>
-      <c r="L196" s="45"/>
-      <c r="M196" s="45"/>
-      <c r="N196" s="45"/>
-      <c r="O196" s="43"/>
+      <c r="E196" s="43"/>
+      <c r="F196" s="44"/>
+      <c r="G196" s="44"/>
+      <c r="H196" s="44"/>
+      <c r="I196" s="44"/>
+      <c r="J196" s="44"/>
+      <c r="K196" s="44"/>
+      <c r="L196" s="44"/>
+      <c r="M196" s="44"/>
+      <c r="N196" s="44"/>
+      <c r="O196" s="42"/>
     </row>
     <row r="197" spans="3:17">
       <c r="C197" s="1"/>
       <c r="D197" s="2"/>
-      <c r="E197" s="46"/>
+      <c r="E197" s="45"/>
     </row>
     <row r="198" spans="3:17">
       <c r="C198" s="1"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="65"/>
+      <c r="E198" s="64"/>
     </row>
     <row r="199" spans="3:17">
       <c r="C199" s="1"/>
       <c r="D199" s="2"/>
-      <c r="H199" s="60"/>
-      <c r="I199" s="60"/>
-      <c r="J199" s="60"/>
-      <c r="K199" s="66"/>
-      <c r="L199" s="67"/>
-      <c r="M199" s="67"/>
-      <c r="N199" s="67"/>
-      <c r="O199" s="67"/>
+      <c r="H199" s="59"/>
+      <c r="I199" s="59"/>
+      <c r="J199" s="59"/>
+      <c r="K199" s="65"/>
+      <c r="L199" s="66"/>
+      <c r="M199" s="66"/>
+      <c r="N199" s="66"/>
+      <c r="O199" s="66"/>
     </row>
     <row r="200" spans="3:17">
       <c r="C200" s="1"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="68"/>
-      <c r="G200" s="63"/>
-      <c r="H200" s="64"/>
-      <c r="I200" s="64"/>
-      <c r="J200" s="64"/>
-      <c r="K200" s="64"/>
-      <c r="L200" s="63"/>
-      <c r="M200" s="63"/>
-      <c r="N200" s="63"/>
+      <c r="E200" s="67"/>
+      <c r="G200" s="62"/>
+      <c r="H200" s="63"/>
+      <c r="I200" s="63"/>
+      <c r="J200" s="63"/>
+      <c r="K200" s="63"/>
+      <c r="L200" s="62"/>
+      <c r="M200" s="62"/>
+      <c r="N200" s="62"/>
     </row>
     <row r="201" spans="3:17">
       <c r="C201" s="1"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="47"/>
-      <c r="G201" s="45"/>
-      <c r="H201" s="45"/>
-      <c r="I201" s="45"/>
-      <c r="J201" s="45"/>
-      <c r="K201" s="45"/>
-      <c r="L201" s="45"/>
-      <c r="M201" s="45"/>
-      <c r="N201" s="45"/>
-      <c r="O201" s="43"/>
+      <c r="E201" s="46"/>
+      <c r="G201" s="44"/>
+      <c r="H201" s="44"/>
+      <c r="I201" s="44"/>
+      <c r="J201" s="44"/>
+      <c r="K201" s="44"/>
+      <c r="L201" s="44"/>
+      <c r="M201" s="44"/>
+      <c r="N201" s="44"/>
+      <c r="O201" s="42"/>
     </row>
     <row r="202" spans="3:17">
       <c r="C202" s="1"/>
       <c r="D202" s="2"/>
-      <c r="E202" s="47"/>
-      <c r="G202" s="46"/>
-      <c r="H202" s="45"/>
-      <c r="I202" s="45"/>
-      <c r="J202" s="46"/>
-      <c r="K202" s="46"/>
-      <c r="L202" s="46"/>
-      <c r="M202" s="46"/>
-      <c r="N202" s="46"/>
+      <c r="E202" s="46"/>
+      <c r="G202" s="45"/>
+      <c r="H202" s="44"/>
+      <c r="I202" s="44"/>
+      <c r="J202" s="45"/>
+      <c r="K202" s="45"/>
+      <c r="L202" s="45"/>
+      <c r="M202" s="45"/>
+      <c r="N202" s="45"/>
     </row>
     <row r="203" spans="3:17">
-      <c r="F203" s="69" t="s">
+      <c r="F203" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="G203" s="69" t="s">
+      <c r="G203" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="H203" s="70" t="s">
+      <c r="H203" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="I203" s="70"/>
-      <c r="J203" s="70" t="s">
+      <c r="I203" s="69"/>
+      <c r="J203" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="K203" s="70"/>
-      <c r="L203" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="M203" s="69" t="s">
+      <c r="K203" s="69"/>
+      <c r="L203" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="M203" s="68" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="204" spans="3:17">
-      <c r="F204" s="59"/>
-      <c r="G204" s="59" t="s">
+      <c r="F204" s="58"/>
+      <c r="G204" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="H204" s="60" t="s">
+      <c r="H204" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="I204" s="60" t="s">
+      <c r="I204" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="J204" s="60" t="s">
+      <c r="J204" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="K204" s="60" t="s">
+      <c r="K204" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="L204" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="M204" s="59" t="s">
+      <c r="L204" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="M204" s="58" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8364,7 +8373,7 @@
       <c r="D205" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E205" s="44" t="s">
+      <c r="E205" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F205" t="s">
@@ -8395,7 +8404,7 @@
     <row r="206" spans="3:17">
       <c r="C206" s="1"/>
       <c r="D206" s="2"/>
-      <c r="E206" s="46" t="s">
+      <c r="E206" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F206" t="s">
@@ -8426,7 +8435,7 @@
     <row r="207" spans="3:17">
       <c r="C207" s="1"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="65" t="s">
+      <c r="E207" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F207" t="s">
@@ -8461,17 +8470,17 @@
     <row r="209" spans="3:17">
       <c r="C209" s="1"/>
       <c r="D209" s="2"/>
-      <c r="E209" s="68"/>
+      <c r="E209" s="67"/>
     </row>
     <row r="210" spans="3:17">
       <c r="C210" s="1"/>
       <c r="D210" s="2"/>
-      <c r="E210" s="47"/>
+      <c r="E210" s="46"/>
     </row>
     <row r="211" spans="3:17">
       <c r="C211" s="1"/>
       <c r="D211" s="2"/>
-      <c r="E211" s="47"/>
+      <c r="E211" s="46"/>
     </row>
     <row r="213" spans="3:17">
       <c r="C213" s="1" t="s">
@@ -8480,7 +8489,7 @@
       <c r="D213" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E213" s="44" t="s">
+      <c r="E213" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F213" t="s">
@@ -8489,7 +8498,7 @@
       <c r="G213" t="s">
         <v>157</v>
       </c>
-      <c r="H213" s="33" t="s">
+      <c r="H213" s="32" t="s">
         <v>163</v>
       </c>
       <c r="I213" t="s">
@@ -8511,7 +8520,7 @@
     <row r="214" spans="3:17">
       <c r="C214" s="1"/>
       <c r="D214" s="2"/>
-      <c r="E214" s="46" t="s">
+      <c r="E214" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F214" t="s">
@@ -8542,7 +8551,7 @@
     <row r="215" spans="3:17">
       <c r="C215" s="1"/>
       <c r="D215" s="2"/>
-      <c r="E215" s="65" t="s">
+      <c r="E215" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F215" t="s">
@@ -8573,7 +8582,7 @@
     <row r="216" spans="3:17">
       <c r="C216" s="1"/>
       <c r="D216" s="2"/>
-      <c r="E216" s="44" t="s">
+      <c r="E216" s="43" t="s">
         <v>166</v>
       </c>
       <c r="F216" t="s">
@@ -8604,7 +8613,7 @@
     <row r="217" spans="3:17">
       <c r="C217" s="1"/>
       <c r="D217" s="2"/>
-      <c r="E217" s="46" t="s">
+      <c r="E217" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F217" t="s">
@@ -8635,7 +8644,7 @@
     <row r="218" spans="3:17">
       <c r="C218" s="1"/>
       <c r="D218" s="2"/>
-      <c r="E218" s="65" t="s">
+      <c r="E218" s="64" t="s">
         <v>103</v>
       </c>
       <c r="F218" t="s">
@@ -8666,16 +8675,16 @@
     <row r="219" spans="3:17">
       <c r="C219" s="1"/>
       <c r="D219" s="2"/>
-      <c r="E219" s="47"/>
+      <c r="E219" s="46"/>
     </row>
     <row r="221" spans="3:17">
       <c r="C221" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D221" s="35" t="s">
+      <c r="D221" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="E221" s="44" t="s">
+      <c r="E221" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F221" t="s">
@@ -8702,15 +8711,15 @@
       <c r="M221" t="s">
         <v>32</v>
       </c>
-      <c r="N221" s="71"/>
-      <c r="O221" s="71"/>
-      <c r="P221" s="71"/>
-      <c r="Q221" s="71"/>
+      <c r="N221" s="70"/>
+      <c r="O221" s="70"/>
+      <c r="P221" s="70"/>
+      <c r="Q221" s="70"/>
     </row>
     <row r="222" spans="3:17">
       <c r="C222" s="1"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="46" t="s">
+      <c r="E222" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F222" t="s">
@@ -8737,13 +8746,13 @@
       <c r="M222" t="s">
         <v>32</v>
       </c>
-      <c r="N222" s="72"/>
-      <c r="O222" s="73"/>
+      <c r="N222" s="71"/>
+      <c r="O222" s="72"/>
     </row>
     <row r="223" spans="3:17">
       <c r="C223" s="1"/>
       <c r="D223" s="2"/>
-      <c r="E223" s="65" t="s">
+      <c r="E223" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F223" t="s">
@@ -8774,7 +8783,7 @@
     <row r="224" spans="3:17">
       <c r="C224" s="1"/>
       <c r="D224" s="2"/>
-      <c r="E224" s="44" t="s">
+      <c r="E224" s="43" t="s">
         <v>166</v>
       </c>
       <c r="F224" t="s">
@@ -8805,7 +8814,7 @@
     <row r="225" spans="3:15">
       <c r="C225" s="1"/>
       <c r="D225" s="2"/>
-      <c r="E225" s="46" t="s">
+      <c r="E225" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F225" t="s">
@@ -8832,12 +8841,12 @@
       <c r="M225" t="s">
         <v>32</v>
       </c>
-      <c r="N225" s="46"/>
+      <c r="N225" s="45"/>
     </row>
     <row r="226" spans="3:15">
       <c r="C226" s="1"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="65" t="s">
+      <c r="E226" s="64" t="s">
         <v>103</v>
       </c>
       <c r="F226" t="s">
@@ -8864,50 +8873,50 @@
       <c r="M226" t="s">
         <v>32</v>
       </c>
-      <c r="N226" s="45"/>
-      <c r="O226" s="43"/>
+      <c r="N226" s="44"/>
+      <c r="O226" s="42"/>
     </row>
     <row r="227" spans="3:15">
       <c r="C227" s="1"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="47"/>
-      <c r="G227" s="45"/>
-      <c r="H227" s="45"/>
-      <c r="I227" s="45"/>
-      <c r="J227" s="45"/>
-      <c r="K227" s="50"/>
-      <c r="L227" s="51"/>
-      <c r="M227" s="52"/>
-      <c r="N227" s="45"/>
-      <c r="O227" s="43"/>
+      <c r="E227" s="46"/>
+      <c r="G227" s="44"/>
+      <c r="H227" s="44"/>
+      <c r="I227" s="44"/>
+      <c r="J227" s="44"/>
+      <c r="K227" s="49"/>
+      <c r="L227" s="50"/>
+      <c r="M227" s="51"/>
+      <c r="N227" s="44"/>
+      <c r="O227" s="42"/>
     </row>
     <row r="228" spans="3:15">
-      <c r="E228" s="47"/>
-      <c r="G228" s="46"/>
-      <c r="H228" s="45"/>
-      <c r="I228" s="45"/>
-      <c r="J228" s="46"/>
-      <c r="K228" s="46"/>
-      <c r="L228" s="46"/>
-      <c r="M228" s="46"/>
-      <c r="N228" s="46"/>
+      <c r="E228" s="46"/>
+      <c r="G228" s="45"/>
+      <c r="H228" s="44"/>
+      <c r="I228" s="44"/>
+      <c r="J228" s="45"/>
+      <c r="K228" s="45"/>
+      <c r="L228" s="45"/>
+      <c r="M228" s="45"/>
+      <c r="N228" s="45"/>
     </row>
     <row r="229" spans="3:15">
-      <c r="E229" s="47"/>
-      <c r="G229" s="46"/>
-      <c r="H229" s="72"/>
-      <c r="I229" s="72"/>
-      <c r="J229" s="46"/>
-      <c r="K229" s="46"/>
-      <c r="L229" s="46"/>
-      <c r="M229" s="46"/>
-      <c r="N229" s="46"/>
+      <c r="E229" s="46"/>
+      <c r="G229" s="45"/>
+      <c r="H229" s="71"/>
+      <c r="I229" s="71"/>
+      <c r="J229" s="45"/>
+      <c r="K229" s="45"/>
+      <c r="L229" s="45"/>
+      <c r="M229" s="45"/>
+      <c r="N229" s="45"/>
     </row>
     <row r="230" ht="44" customHeight="1" spans="3:15">
       <c r="D230" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E230" s="44" t="s">
+      <c r="E230" s="43" t="s">
         <v>85</v>
       </c>
       <c r="F230" t="s">
@@ -8934,11 +8943,11 @@
       <c r="M230" t="s">
         <v>32</v>
       </c>
-      <c r="O230" s="73"/>
+      <c r="O230" s="72"/>
     </row>
     <row r="231" spans="3:15">
       <c r="D231" s="2"/>
-      <c r="E231" s="46" t="s">
+      <c r="E231" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F231" t="s">
@@ -8968,7 +8977,7 @@
     </row>
     <row r="232" spans="3:15">
       <c r="D232" s="2"/>
-      <c r="E232" s="65" t="s">
+      <c r="E232" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F232" t="s">
@@ -8998,7 +9007,7 @@
     </row>
     <row r="233" spans="3:15">
       <c r="D233" s="2"/>
-      <c r="E233" s="44" t="s">
+      <c r="E233" s="43" t="s">
         <v>166</v>
       </c>
       <c r="F233" t="s">
@@ -9028,7 +9037,7 @@
     </row>
     <row r="234" spans="3:15">
       <c r="D234" s="2"/>
-      <c r="E234" s="46" t="s">
+      <c r="E234" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F234" t="s">
@@ -9055,11 +9064,11 @@
       <c r="M234" t="s">
         <v>32</v>
       </c>
-      <c r="O234" s="43"/>
+      <c r="O234" s="42"/>
     </row>
     <row r="235" spans="3:15">
       <c r="D235" s="2"/>
-      <c r="E235" s="65" t="s">
+      <c r="E235" s="64" t="s">
         <v>103</v>
       </c>
       <c r="F235" t="s">
@@ -9086,42 +9095,42 @@
       <c r="M235" t="s">
         <v>32</v>
       </c>
-      <c r="N235" s="46"/>
+      <c r="N235" s="45"/>
     </row>
     <row r="236" spans="3:15">
       <c r="D236" s="2"/>
     </row>
     <row r="242" spans="3:17">
       <c r="D242" s="3"/>
-      <c r="E242" s="46"/>
-      <c r="F242" s="39" t="s">
+      <c r="E242" s="45"/>
+      <c r="F242" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G242" s="39" t="s">
+      <c r="G242" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H242" s="40" t="s">
+      <c r="H242" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I242" s="40"/>
-      <c r="J242" s="40" t="s">
+      <c r="I242" s="39"/>
+      <c r="J242" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K242" s="40"/>
-      <c r="L242" s="39" t="s">
+      <c r="K242" s="39"/>
+      <c r="L242" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M242" s="39" t="s">
+      <c r="M242" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N242" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O242" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P242" s="39"/>
-      <c r="Q242" s="39"/>
+      <c r="N242" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O242" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P242" s="38"/>
+      <c r="Q242" s="38"/>
     </row>
     <row r="243" spans="3:17">
       <c r="C243" s="1" t="s">
@@ -9130,44 +9139,44 @@
       <c r="D243" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E243" s="44" t="s">
+      <c r="E243" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="F243" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G243" s="45" t="s">
+      <c r="F243" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G243" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H243" s="45" t="s">
+      <c r="H243" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="I243" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J243" s="45" t="s">
+      <c r="I243" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J243" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K243" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L243" s="45" t="s">
+      <c r="K243" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L243" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M243" s="45" t="s">
+      <c r="M243" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="N243" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O243" s="43" t="s">
+      <c r="N243" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O243" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="244" spans="3:17">
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
-      <c r="E244" s="46" t="s">
+      <c r="E244" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F244" t="s">
@@ -9198,7 +9207,7 @@
     <row r="245" spans="3:17">
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="65" t="s">
+      <c r="E245" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F245" t="s">
@@ -9229,56 +9238,56 @@
     <row r="246" spans="3:17">
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
-      <c r="H246" s="60"/>
-      <c r="I246" s="60"/>
-      <c r="J246" s="60"/>
-      <c r="K246" s="66"/>
-      <c r="L246" s="67"/>
-      <c r="M246" s="67"/>
-      <c r="N246" s="67"/>
-      <c r="O246" s="67"/>
+      <c r="H246" s="59"/>
+      <c r="I246" s="59"/>
+      <c r="J246" s="59"/>
+      <c r="K246" s="65"/>
+      <c r="L246" s="66"/>
+      <c r="M246" s="66"/>
+      <c r="N246" s="66"/>
+      <c r="O246" s="66"/>
     </row>
     <row r="247" spans="3:17">
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
-      <c r="E247" s="44" t="s">
+      <c r="E247" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="F247" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G247" s="45" t="s">
+      <c r="F247" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G247" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H247" s="45" t="s">
+      <c r="H247" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="I247" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J247" s="45" t="s">
+      <c r="I247" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J247" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="K247" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L247" s="45" t="s">
+      <c r="K247" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L247" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="M247" s="45" t="s">
+      <c r="M247" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="N247" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O247" s="43" t="s">
+      <c r="N247" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O247" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="248" spans="3:17">
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
-      <c r="E248" s="46" t="s">
+      <c r="E248" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F248" t="s">
@@ -9309,7 +9318,7 @@
     <row r="249" spans="3:17">
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="65" t="s">
+      <c r="E249" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F249" t="s">
@@ -9338,42 +9347,42 @@
       </c>
     </row>
     <row r="251" spans="3:17">
-      <c r="E251" s="44" t="s">
+      <c r="E251" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="F251" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G251" s="45" t="s">
+      <c r="F251" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G251" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H251" s="45" t="s">
+      <c r="H251" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I251" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J251" s="45" t="s">
+      <c r="I251" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J251" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K251" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L251" s="45" t="s">
+      <c r="K251" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L251" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="M251" s="45" t="s">
+      <c r="M251" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="N251" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O251" s="43" t="s">
+      <c r="N251" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O251" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="252" spans="3:17">
-      <c r="E252" s="46" t="s">
+      <c r="E252" s="45" t="s">
         <v>90</v>
       </c>
       <c r="F252" t="s">
@@ -9402,7 +9411,7 @@
       </c>
     </row>
     <row r="253" spans="3:17">
-      <c r="E253" s="65" t="s">
+      <c r="E253" s="64" t="s">
         <v>92</v>
       </c>
       <c r="F253" t="s">
@@ -9437,175 +9446,175 @@
       <c r="D255" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E255" s="44"/>
-      <c r="F255" s="45"/>
-      <c r="G255" s="45"/>
-      <c r="H255" s="45"/>
-      <c r="I255" s="45"/>
-      <c r="J255" s="45"/>
-      <c r="K255" s="45"/>
-      <c r="L255" s="45"/>
-      <c r="M255" s="45"/>
-      <c r="N255" s="45"/>
-      <c r="O255" s="43"/>
+      <c r="E255" s="43"/>
+      <c r="F255" s="44"/>
+      <c r="G255" s="44"/>
+      <c r="H255" s="44"/>
+      <c r="I255" s="44"/>
+      <c r="J255" s="44"/>
+      <c r="K255" s="44"/>
+      <c r="L255" s="44"/>
+      <c r="M255" s="44"/>
+      <c r="N255" s="44"/>
+      <c r="O255" s="42"/>
     </row>
     <row r="256" spans="3:17">
       <c r="C256" s="1"/>
       <c r="D256" s="2"/>
-      <c r="E256" s="46"/>
+      <c r="E256" s="45"/>
     </row>
     <row r="257" spans="3:17">
       <c r="C257" s="1"/>
       <c r="D257" s="2"/>
-      <c r="E257" s="46"/>
-      <c r="F257" s="39" t="s">
+      <c r="E257" s="45"/>
+      <c r="F257" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G257" s="39" t="s">
+      <c r="G257" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H257" s="40" t="s">
+      <c r="H257" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I257" s="40"/>
-      <c r="J257" s="40" t="s">
+      <c r="I257" s="39"/>
+      <c r="J257" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K257" s="40"/>
-      <c r="L257" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="M257" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N257" s="39"/>
-      <c r="O257" s="39"/>
-      <c r="P257" s="39"/>
-      <c r="Q257" s="39"/>
+      <c r="K257" s="39"/>
+      <c r="L257" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M257" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N257" s="38"/>
+      <c r="O257" s="38"/>
+      <c r="P257" s="38"/>
+      <c r="Q257" s="38"/>
     </row>
     <row r="258" spans="3:17">
       <c r="C258" s="1"/>
       <c r="D258" s="2"/>
-      <c r="E258" s="47" t="s">
+      <c r="E258" s="46" t="s">
         <v>96</v>
       </c>
       <c r="F258" t="s">
         <v>39</v>
       </c>
-      <c r="G258" s="46" t="s">
+      <c r="G258" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H258" s="45" t="s">
+      <c r="H258" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="I258" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J258" s="45" t="s">
+      <c r="I258" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J258" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K258" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L258" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M258" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N258" s="46"/>
+      <c r="K258" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="L258" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M258" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N258" s="45"/>
     </row>
     <row r="259" spans="3:17">
       <c r="C259" s="1"/>
       <c r="D259" s="2"/>
-      <c r="E259" s="47"/>
-      <c r="F259" s="48" t="s">
+      <c r="E259" s="46"/>
+      <c r="F259" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G259" s="48" t="s">
+      <c r="G259" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H259" s="48" t="s">
+      <c r="H259" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I259" s="48" t="s">
+      <c r="I259" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="J259" s="48" t="s">
+      <c r="J259" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="K259" s="49" t="s">
+      <c r="K259" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L259" s="49"/>
-      <c r="M259" s="48"/>
-      <c r="N259" s="45"/>
-      <c r="O259" s="43"/>
+      <c r="L259" s="48"/>
+      <c r="M259" s="47"/>
+      <c r="N259" s="44"/>
+      <c r="O259" s="42"/>
     </row>
     <row r="260" spans="3:17">
       <c r="C260" s="1"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="47" t="s">
+      <c r="E260" s="46" t="s">
         <v>90</v>
       </c>
       <c r="F260" t="s">
         <v>39</v>
       </c>
-      <c r="G260" s="45" t="s">
+      <c r="G260" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="H260" s="45" t="s">
+      <c r="H260" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I260" s="45" t="s">
+      <c r="I260" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="J260" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K260" s="56" t="s">
+      <c r="J260" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="K260" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="L260" s="51"/>
-      <c r="M260" s="52"/>
-      <c r="N260" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O260" s="43" t="s">
+      <c r="L260" s="50"/>
+      <c r="M260" s="51"/>
+      <c r="N260" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O260" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="261" spans="3:17">
       <c r="C261" s="1"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="47" t="s">
+      <c r="E261" s="46" t="s">
         <v>103</v>
       </c>
       <c r="F261" t="s">
         <v>39</v>
       </c>
-      <c r="G261" s="46" t="s">
+      <c r="G261" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H261" s="45" t="s">
+      <c r="H261" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I261" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J261" s="46" t="s">
+      <c r="I261" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J261" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="K261" s="46" t="s">
+      <c r="K261" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="L261" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M261" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N261" s="46"/>
+      <c r="L261" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M261" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N261" s="45"/>
     </row>
     <row r="262" spans="3:17">
       <c r="D262" s="2"/>
@@ -10139,9 +10148,37 @@
         <v>201</v>
       </c>
     </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>36</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" t="s">
+        <v>232</v>
+      </c>
+    </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" ht="51" customHeight="1" spans="1:7">
@@ -10155,16 +10192,16 @@
         <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E21" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G21" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1" spans="1:7">
@@ -10179,16 +10216,16 @@
         <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G22" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -10203,16 +10240,16 @@
         <v>197</v>
       </c>
       <c r="D23" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E23" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F23" t="s">
         <v>205</v>
       </c>
       <c r="G23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -10227,16 +10264,16 @@
         <v>197</v>
       </c>
       <c r="D24" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F24" t="s">
         <v>205</v>
       </c>
       <c r="G24" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -10251,16 +10288,16 @@
         <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G25" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -10275,16 +10312,16 @@
         <v>197</v>
       </c>
       <c r="D26" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -10299,16 +10336,16 @@
         <v>197</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E27" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F27" t="s">
         <v>211</v>
       </c>
       <c r="G27" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -10323,16 +10360,16 @@
         <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F28" t="s">
         <v>211</v>
       </c>
       <c r="G28" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -10347,16 +10384,16 @@
         <v>197</v>
       </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F29" t="s">
         <v>211</v>
       </c>
       <c r="G29" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -10371,13 +10408,13 @@
         <v>197</v>
       </c>
       <c r="D30" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G30" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -10392,10 +10429,10 @@
         <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F31" t="s">
         <v>211</v>
@@ -10413,10 +10450,10 @@
         <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -10467,10 +10504,10 @@
         <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E37" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>139</v>
@@ -10497,19 +10534,19 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E39" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F39" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G39" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" ht="43" customHeight="1" spans="1:7">
@@ -10527,13 +10564,13 @@
         <v>224</v>
       </c>
       <c r="E40" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G40" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -10545,10 +10582,10 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E41" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>151</v>
@@ -10569,16 +10606,16 @@
         <v>223</v>
       </c>
       <c r="D42" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>264</v>
-      </c>
       <c r="G42" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" ht="27" spans="1:7">
@@ -10593,16 +10630,16 @@
         <v>223</v>
       </c>
       <c r="D43" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E43" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G43" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -10613,16 +10650,16 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D48" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E48" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F48" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -10634,13 +10671,13 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E49" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -10651,19 +10688,19 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D50" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E50" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G50" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" ht="264.75" customHeight="1" spans="1:8">
@@ -10674,22 +10711,22 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D51" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E51" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G51" t="s">
-        <v>233</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>283</v>
+        <v>237</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:8">
@@ -10700,16 +10737,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D52" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:8">
@@ -10721,16 +10758,16 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D53" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E53" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:8">
@@ -10744,16 +10781,16 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D55" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E55" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:8">
@@ -10767,16 +10804,16 @@
         <v>197</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E56" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:8">
       <c r="A57">
-        <f t="shared" ref="A57:A62" si="2">A56+B56</f>
+        <f t="shared" ref="A57:A63" si="2">A56+B56</f>
         <v>156</v>
       </c>
       <c r="B57">
@@ -10786,7 +10823,7 @@
         <v>197</v>
       </c>
       <c r="D57" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F57" s="3"/>
     </row>
@@ -10802,7 +10839,7 @@
         <v>197</v>
       </c>
       <c r="D58" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F58" s="3"/>
     </row>
@@ -10818,7 +10855,7 @@
         <v>197</v>
       </c>
       <c r="D59" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F59" s="3"/>
     </row>
@@ -10834,7 +10871,7 @@
         <v>197</v>
       </c>
       <c r="D60" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F60" s="3"/>
     </row>
@@ -10850,7 +10887,7 @@
         <v>197</v>
       </c>
       <c r="D61" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F61" s="3"/>
     </row>
@@ -10866,13 +10903,13 @@
         <v>197</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F62" s="3"/>
     </row>
     <row r="63" ht="18" customHeight="1" spans="1:8">
       <c r="A63">
-        <f>A62+B62</f>
+        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="B63">
@@ -10882,10 +10919,10 @@
         <v>197</v>
       </c>
       <c r="D63" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E63" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F63" s="3"/>
     </row>
@@ -10900,10 +10937,10 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E65" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F65" s="3"/>
     </row>
@@ -10917,11 +10954,11 @@
       <c r="C66" t="s">
         <v>197</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>305</v>
+      <c r="D66" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="E66" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F66" s="3"/>
     </row>
@@ -10933,10 +10970,10 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E67" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F67" s="3"/>
     </row>
@@ -10951,10 +10988,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E69" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F69" s="3"/>
     </row>
@@ -10972,10 +11009,10 @@
         <v>197</v>
       </c>
       <c r="D71" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E71" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" t="s">
@@ -10990,13 +11027,13 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D72" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E72" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" t="s">
@@ -11005,7 +11042,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1" spans="1:8">
@@ -11025,13 +11062,13 @@
         <v>179</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G75" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -11045,16 +11082,16 @@
         <v>197</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E76" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G76" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H76" s="1"/>
     </row>
@@ -11067,19 +11104,19 @@
         <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D77" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E77" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G77" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H77" s="1"/>
     </row>
@@ -11089,22 +11126,22 @@
         <v>208</v>
       </c>
       <c r="B78" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C78" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D78" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E78" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G78" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H78" s="1"/>
     </row>
@@ -11135,7 +11172,7 @@
   <sheetData>
     <row r="1" spans="2:17">
       <c r="B1" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
